--- a/results/job_matches_2026-03-05.xlsx
+++ b/results/job_matches_2026-03-05.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G114"/>
+  <dimension ref="A1:G125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,17 +468,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Engineer/Python Developer</t>
+          <t>Junior Oracle Apps Developer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Zifo</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -486,7 +486,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Scala, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, ECS, RDS, Azure, Blob Storage</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3419a1d7b4acb559</t>
+          <t>https://www.indeed.com/viewjob?jk=0adde35786282b2b</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Junior Oracle Apps Developer</t>
+          <t>Software Engineer III: DevOps</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20.1</v>
+        <v>18.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, ECS, RDS, Azure, Blob Storage</t>
+          <t>AWS, S3, SQS, SNS, API Gateway, ECS, RDS, Azure, GCP, Scala</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,24 +531,24 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0adde35786282b2b</t>
+          <t>https://www.indeed.com/viewjob?jk=bc952e4224a3aa24</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software Engineer III: DevOps</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Jersey Mikes Corporate</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Tinton Falls, NJ, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, API Gateway, ECS, RDS, Azure, GCP, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc952e4224a3aa24</t>
+          <t>https://www.indeed.com/viewjob?jk=31cf41e0387f0b72</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer, Client Authentication</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Jersey Mikes Corporate</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Tinton Falls, NJ, US USA</t>
+          <t>Southlake, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling</t>
+          <t>IAM, RDS, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31cf41e0387f0b72</t>
+          <t>https://www.indeed.com/viewjob?jk=a908b362cb914674</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Client Authentication</t>
+          <t>Senior Data Engineer, ACVMax</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>ACV Auctions</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Southlake, TX, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>IAM, RDS, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,42 +636,42 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a908b362cb914674</t>
+          <t>https://www.indeed.com/viewjob?jk=6c28dd5d00192a5b</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, ACVMax</t>
+          <t>Databricks Data Engineer - Consultant</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ACV Auctions</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c28dd5d00192a5b</t>
+          <t>https://www.indeed.com/viewjob?jk=7167050c109be2d4</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7167050c109be2d4</t>
+          <t>https://www.indeed.com/viewjob?jk=862a4a8989448fa0</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=862a4a8989448fa0</t>
+          <t>https://www.indeed.com/viewjob?jk=07e542bb4713fad0</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07e542bb4713fad0</t>
+          <t>https://www.indeed.com/viewjob?jk=2c88dff775194e30</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c88dff775194e30</t>
+          <t>https://www.indeed.com/viewjob?jk=c8ced45fe117deb8</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8ced45fe117deb8</t>
+          <t>https://www.indeed.com/viewjob?jk=2dc8e0c810b3e7cd</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dc8e0c810b3e7cd</t>
+          <t>https://www.indeed.com/viewjob?jk=7791942c877daada</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7791942c877daada</t>
+          <t>https://www.indeed.com/viewjob?jk=b6b39b9b56abc0bd</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6b39b9b56abc0bd</t>
+          <t>https://www.indeed.com/viewjob?jk=648774ee33ca3b76</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=648774ee33ca3b76</t>
+          <t>https://www.indeed.com/viewjob?jk=a93ca1ad887e17f0</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a93ca1ad887e17f0</t>
+          <t>https://www.indeed.com/viewjob?jk=d963e90dfb3fa4d6</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d963e90dfb3fa4d6</t>
+          <t>https://www.indeed.com/viewjob?jk=783ac47e6d62e414</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=783ac47e6d62e414</t>
+          <t>https://www.indeed.com/viewjob?jk=e511c7108cd6e82d</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e511c7108cd6e82d</t>
+          <t>https://www.indeed.com/viewjob?jk=2a6a2ad30fc1236d</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a6a2ad30fc1236d</t>
+          <t>https://www.indeed.com/viewjob?jk=e2d42f6d55a07b48</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2d42f6d55a07b48</t>
+          <t>https://www.indeed.com/viewjob?jk=c423f392a018bf22</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c423f392a018bf22</t>
+          <t>https://www.indeed.com/viewjob?jk=cb49af32ea451f63</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb49af32ea451f63</t>
+          <t>https://www.indeed.com/viewjob?jk=1e7468c4fe6bdb23</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e7468c4fe6bdb23</t>
+          <t>https://www.indeed.com/viewjob?jk=3a3485c3c6153843</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a3485c3c6153843</t>
+          <t>https://www.indeed.com/viewjob?jk=ef4166ba4aa9b5a3</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef4166ba4aa9b5a3</t>
+          <t>https://www.indeed.com/viewjob?jk=91d6e4beb774dd25</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91d6e4beb774dd25</t>
+          <t>https://www.indeed.com/viewjob?jk=adcf2824745a050e</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adcf2824745a050e</t>
+          <t>https://www.indeed.com/viewjob?jk=64b296145590b995</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64b296145590b995</t>
+          <t>https://www.indeed.com/viewjob?jk=8c4169879098b22b</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c4169879098b22b</t>
+          <t>https://www.indeed.com/viewjob?jk=44e1222f0eb14744</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44e1222f0eb14744</t>
+          <t>https://www.indeed.com/viewjob?jk=37bd1a8719f0aafc</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37bd1a8719f0aafc</t>
+          <t>https://www.indeed.com/viewjob?jk=e151b2c0a32e2723</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e151b2c0a32e2723</t>
+          <t>https://www.indeed.com/viewjob?jk=c07dcca1b609463e</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c07dcca1b609463e</t>
+          <t>https://www.indeed.com/viewjob?jk=c721bd4ca7bdffe1</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c721bd4ca7bdffe1</t>
+          <t>https://www.indeed.com/viewjob?jk=e8e182c6058fd2a4</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8e182c6058fd2a4</t>
+          <t>https://www.indeed.com/viewjob?jk=4997f8f92f05b9d2</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4997f8f92f05b9d2</t>
+          <t>https://www.indeed.com/viewjob?jk=2a56481df82d7aa6</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a56481df82d7aa6</t>
+          <t>https://www.indeed.com/viewjob?jk=fb00c80fb9cb9b65</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb00c80fb9cb9b65</t>
+          <t>https://www.indeed.com/viewjob?jk=3fd1863254c88e5d</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer - Consultant</t>
+          <t>Sr. Data Platform Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Real Time Medical Systems</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,17 +1851,17 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, IAM, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fd1863254c88e5d</t>
+          <t>https://www.indeed.com/viewjob?jk=415686b53cfda723</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Columbia, MD, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=415686b53cfda723</t>
+          <t>https://www.indeed.com/viewjob?jk=41a92f9802d4f918</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Sr. Data Platform Engineer</t>
+          <t>Senior Software Engineer, Cloud Infrastructure</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Real Time Medical Systems</t>
+          <t>ALTRUIST</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Columbia, MD, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, IAM, RDS, Spark, PySpark</t>
+          <t>AWS, S3, API Gateway, IAM, RDS, Scala, Kafka, PostgreSQL, DynamoDB, MLOps</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41a92f9802d4f918</t>
+          <t>https://www.indeed.com/viewjob?jk=b2b2e3b90367f3b4</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2b2e3b90367f3b4</t>
+          <t>https://www.indeed.com/viewjob?jk=15721c69bc524693</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Cloud Infrastructure</t>
+          <t>Sr. Database Administrator - Computing Services</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>ALTRUIST</t>
+          <t>Carnegie Mellon University</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, IAM, RDS, Scala, Kafka, PostgreSQL, DynamoDB, MLOps</t>
+          <t>AWS, Redshift, S3, IAM, RDS, Azure, GCP, BigQuery, Cloud Storage, Scala</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,67 +2001,67 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15721c69bc524693</t>
+          <t>https://www.indeed.com/viewjob?jk=506f6b3eeea1e8bf</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Enterprise Data Platform Engineer – Washington, DC</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Surgery Partners</t>
+          <t>Creative Information Technology India</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Falls Church, VA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>17.4</v>
+        <v>16</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Delta Live Tables</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Delta Live Tables, Photon, Scala, ETL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6c4839e7fe64d8e</t>
+          <t>https://www.indeed.com/viewjob?jk=0a74e373b48da5fc</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Enterprise Data Platform Engineer – Washington, DC</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Creative Information Technology India</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Falls Church, VA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Delta Live Tables, Photon, Scala, ETL</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,42 +2071,42 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a74e373b48da5fc</t>
+          <t>https://www.indeed.com/viewjob?jk=9e8500146d476812</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Blockchain Java Backend Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e49019e3e57d794c</t>
+          <t>https://www.indeed.com/viewjob?jk=2ad2838bd8f61427</t>
         </is>
       </c>
     </row>
@@ -2183,17 +2183,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Software Engineer, AI Analytics</t>
+          <t>Google Cloud Data Architect</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Residex, LLC</t>
+          <t>Cloudious</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Greenwood Village, CO, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, GCP, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, HDFS, Hive</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b994e1736909aed</t>
+          <t>https://www.indeed.com/viewjob?jk=73dc517b82db140b</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Google Cloud Data Architect</t>
+          <t>Senior Specialist - System Management</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Cloudious</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Glen Allen, VA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, HDFS, Hive</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Unity Catalog, Delta Live Tables, Spark, Databricks Lakehouse, SQL Server</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73dc517b82db140b</t>
+          <t>https://www.indeed.com/viewjob?jk=293f842904007fda</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Specialist - System Management</t>
+          <t>Senior Engineer - DevOps/ DataOps</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>FICO</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Glen Allen, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Unity Catalog, Delta Live Tables, Spark, Databricks Lakehouse, SQL Server</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, DataOps, MLOps, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=293f842904007fda</t>
+          <t>https://www.indeed.com/viewjob?jk=e1ed15cfc823b0b7</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Engineer - DevOps/ DataOps</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>FICO</t>
+          <t>Alight Solutions</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, DataOps, MLOps, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, GCP, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1ed15cfc823b0b7</t>
+          <t>https://www.indeed.com/viewjob?jk=398f35933211332f</t>
         </is>
       </c>
     </row>
@@ -2568,17 +2568,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Sr. Java Developer</t>
+          <t>Specialist Programmer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Infosys</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>IAM, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, Kafka, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Azure, GCP, Hadoop, Hive, Spark, PySpark, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29bb162ca9316c93</t>
+          <t>https://www.indeed.com/viewjob?jk=9772b3b8d4167ecc</t>
         </is>
       </c>
     </row>
@@ -2708,17 +2708,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer + Snowflake (On-Site)</t>
+          <t>SSO Administrator</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Regions Financial</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,42 +2726,42 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, RDS, BigQuery, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, PostgreSQL, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58e9f31119d31013</t>
+          <t>https://www.indeed.com/viewjob?jk=a9064a81c91aa262</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>SSO Administrator</t>
+          <t>Senior Software Engineer - Commercial Software</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, PostgreSQL, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, Oracle, MySQL</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9064a81c91aa262</t>
+          <t>https://www.indeed.com/viewjob?jk=5f3de39cf73c3663</t>
         </is>
       </c>
     </row>
@@ -2883,17 +2883,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Risk Data AI/ML Engineer</t>
+          <t>Senior Software Engineer II - AI/ML</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>SoFi</t>
+          <t>Seismic</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,42 +2901,42 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Scala, Snowflake, Data Modeling, dbt, CI/CD</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=979402388d34b409</t>
+          <t>https://www.indeed.com/viewjob?jk=5d0bc9a390582054</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II - AI/ML</t>
+          <t>Senior Software Engineer, Back End (Java, Go, AWS)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Seismic</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d0bc9a390582054</t>
+          <t>https://www.indeed.com/viewjob?jk=e716b4195b2da30b</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Databricks AI Engineer</t>
+          <t>Senior Software Engineer, Back End (Java, Go, AWS)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Powerplan</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, Scala, Snowflake</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b5753d39b44c782</t>
+          <t>https://www.indeed.com/viewjob?jk=e1b9bbef981d9232</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End (Java, Go, AWS)</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Daniels Health</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Docker</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1b9bbef981d9232</t>
+          <t>https://www.indeed.com/viewjob?jk=1df7caac86af2291</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Data Product</t>
+          <t>ATC - AI &amp; Data Analyst - NAELFY26</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>TRM Labs</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Saint Petersburg, FL, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Dataflow, Spark, Scala, Kafka, dbt, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=351b720407fa6f6d</t>
+          <t>https://www.indeed.com/viewjob?jk=1ce7a50a4bbe9ef2</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Analytics, Full-Stack Engineer</t>
+          <t>Senior Data Engineer, Data Product</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>SCAN Health Plan</t>
+          <t>TRM Labs</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Snowflake, ETL, ELT, dbt</t>
+          <t>RDS, BigQuery, Dataflow, Spark, Scala, Kafka, dbt, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c24274a4aa989f95</t>
+          <t>https://www.indeed.com/viewjob?jk=351b720407fa6f6d</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Analytics, Full-Stack Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Waters</t>
+          <t>SCAN Health Plan</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Milford, MA, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1975adb5bfc7de33</t>
+          <t>https://www.indeed.com/viewjob?jk=c24274a4aa989f95</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Software Engineer (Hybrid)</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Nightwing</t>
+          <t>Waters</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Clarksville, TN, US USA</t>
+          <t>Milford, MA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=887221a715d1ff03</t>
+          <t>https://www.indeed.com/viewjob?jk=1975adb5bfc7de33</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Software Engineer (Hybrid)</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Nightwing</t>
+          <t>Weyerhaeuser</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Sterling, VA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, MLOps, MLflow, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3322d87953168bdc</t>
+          <t>https://www.indeed.com/viewjob?jk=7d9f82346c5ff2d3</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Advanced Metering Infrastructure (AMI) Engineer</t>
+          <t>Senior Software Engineer - MDM / RDM &amp; API Development</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>WSSC Water</t>
+          <t>Prudential</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Laurel, MD, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Oracle, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps</t>
+          <t>AWS, Kinesis, SQS, RDS, Spark, Scala, MySQL, NoSQL, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5b2aa36ee050b9b</t>
+          <t>https://www.indeed.com/viewjob?jk=d75a6cef6409e12b</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Software Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Amplify</t>
+          <t>Nightwing</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Clarksville, TN, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Snowflake, DynamoDB, Data Modeling, Kimball, ETL, ELT, dbt</t>
+          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4d16d721d2057f3</t>
+          <t>https://www.indeed.com/viewjob?jk=887221a715d1ff03</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Software Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Nightwing</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8b55e090bbab627</t>
+          <t>https://www.indeed.com/viewjob?jk=3322d87953168bdc</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Software Engineer III - Java/Spark/AWS</t>
+          <t>Advanced Metering Infrastructure (AMI) Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>WSSC Water</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Laurel, MD, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, ECS, RDS, Databricks, Spark, Scala, Snowflake</t>
+          <t>RDS, Azure, Scala, Kafka, Oracle, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c95674c932d41fb6</t>
+          <t>https://www.indeed.com/viewjob?jk=c5b2aa36ee050b9b</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Tableau Developer</t>
+          <t>Software Systems Engineer, Release Reliability &amp; Automation (Autonomous Vehicles)</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Michael Kors</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>East Rutherford, NJ, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, Power BI, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=904e084e965a45c4</t>
+          <t>https://www.indeed.com/viewjob?jk=864266ab5f8e3aac</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Database Administrator</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Rogue Community College</t>
+          <t>Amplify</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,42 +3391,42 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, Power BI</t>
+          <t>AWS, S3, RDS, Snowflake, DynamoDB, Data Modeling, Kimball, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f9335cc41b5edf2</t>
+          <t>https://www.indeed.com/viewjob?jk=b4d16d721d2057f3</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Platform</t>
+          <t>Software Engineer III - Java/Spark/AWS</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>TRM Labs</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Spark, Scala, Kafka, ETL, dbt, Terraform, Docker, Kubernetes</t>
+          <t>AWS, EMR, Lambda, S3, ECS, RDS, Databricks, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,32 +3436,32 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a517be0e10b2a44</t>
+          <t>https://www.indeed.com/viewjob?jk=c95674c932d41fb6</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Data Platform</t>
+          <t>Tableau Developer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>TRM Labs</t>
+          <t>Michael Kors</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>East Rutherford, NJ, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Spark, Scala, Kafka, ETL, dbt, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Glue, Redshift, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,129 +3471,129 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60f6c2aecd2d1bdf</t>
+          <t>https://www.indeed.com/viewjob?jk=904e084e965a45c4</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Software Engineer (Backend) - Global Dining</t>
+          <t>Software Engineer (Junior)</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>TORCH.AI</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Leawood, KS, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Kafka, MySQL, MongoDB, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, IAM, Azure, GCP, Kafka, PostgreSQL, MongoDB, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8f71d52efce43e2</t>
+          <t>https://www.indeed.com/viewjob?jk=28e432d03da8db08</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>AWS Data Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Appex Innovation</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f3534222ab81e17</t>
+          <t>https://www.indeed.com/viewjob?jk=a8b55e090bbab627</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
+          <t>Database Administrator</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Rogue Community College</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, Power BI</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9637232a826c3ad</t>
+          <t>https://www.indeed.com/viewjob?jk=7f9335cc41b5edf2</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Software Engineer, Back End (Python)</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>CNH Industrial</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5b3837921976566</t>
+          <t>https://www.indeed.com/viewjob?jk=3864c05dc9b353f8</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Microsoft Fabric</t>
+          <t>Data Engineer 2</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>EoS Fitness</t>
+          <t>BLOC Resources, LLC</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bd7f3590528db3c</t>
+          <t>https://www.indeed.com/viewjob?jk=c51290628ce41b82</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Software Engineer I, Applied AI</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>PGA TOUR Superstore</t>
+          <t>Axon</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Roswell, GA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73bdb2d180484ce2</t>
+          <t>https://www.indeed.com/viewjob?jk=e858c83fc09cd77d</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Senior Software Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>TRM Labs</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Gilbert, AZ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,34 +3706,34 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>RDS, BigQuery, Spark, Scala, Kafka, ETL, dbt, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=110f275787ec7bdb</t>
+          <t>https://www.indeed.com/viewjob?jk=8a517be0e10b2a44</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Data, Autonomy</t>
+          <t>Senior Data Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Rivian</t>
+          <t>TRM Labs</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,34 +3741,34 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, Databricks, Unity Catalog, Spark, Scala, DynamoDB, CI/CD</t>
+          <t>RDS, BigQuery, Spark, Scala, Kafka, ETL, dbt, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-01-31</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a3560765ed8e488</t>
+          <t>https://www.indeed.com/viewjob?jk=60f6c2aecd2d1bdf</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>AI Data Engineer-LLMs / Agentic Systems</t>
+          <t>Software Engineer (Backend) - Global Dining</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,34 +3776,34 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, PostgreSQL, MongoDB, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Kafka, MySQL, MongoDB, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92b5658394aee4e3</t>
+          <t>https://www.indeed.com/viewjob?jk=e8f71d52efce43e2</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Customer Reliability Engineer, Airflow</t>
+          <t>AWS Data Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Astronomer</t>
+          <t>Appex Innovation</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,34 +3811,34 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, Snowflake, PostgreSQL, dbt, DataOps, Docker</t>
+          <t>AWS, Glue, Lambda, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ac244565083c1d9</t>
+          <t>https://www.indeed.com/viewjob?jk=7f3534222ab81e17</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Reporting Engineer</t>
+          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Surgery Partners</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,34 +3846,34 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Dataflow, Snowflake, Dimensional Modeling, Star Schema, ELT, dbt</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57ca41478bb936cd</t>
+          <t>https://www.indeed.com/viewjob?jk=f9637232a826c3ad</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Salesforce Architect - Senior</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>CommunityForce Inc.</t>
+          <t>CNH Industrial</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>ECS, RDS, Azure, Scala, Kafka, Data Modeling, ETL, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d236cba8a6e8ae3</t>
+          <t>https://www.indeed.com/viewjob?jk=e5b3837921976566</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Data Engineer - Microsoft Fabric</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Skechers</t>
+          <t>EoS Fitness</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Hermosa Beach, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,42 +3916,42 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Spark, Scala, Snowflake, Data Modeling, MLOps, Git, Python</t>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ELT, Power BI</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bf4b62fe049b84e</t>
+          <t>https://www.indeed.com/viewjob?jk=7bd7f3590528db3c</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Software Engineer - Master</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>PGA TOUR Superstore</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Roswell, GA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,102 +3961,102 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fb1207979169793</t>
+          <t>https://www.indeed.com/viewjob?jk=73bdb2d180484ce2</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Data Engineer - GRC Technology</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Gilbert, AZ, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, ETL, ELT</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8842e67bf37c518a</t>
+          <t>https://www.indeed.com/viewjob?jk=110f275787ec7bdb</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Sr. Software Engineer, Data, Autonomy</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Callaway Golf</t>
+          <t>Rivian</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Spark, Snowflake, ETL, ELT, Terraform, Kubernetes, Git</t>
+          <t>AWS, Lambda, S3, IAM, Databricks, Unity Catalog, Spark, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab2d181891cc2eee</t>
+          <t>https://www.indeed.com/viewjob?jk=6a3560765ed8e488</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AI Applications Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Emed</t>
+          <t>Stanford University</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Vertex AI, Scala, Oracle, NoSQL, Data Modeling, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,32 +4066,32 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e29e1c3d36f0e7c</t>
+          <t>https://www.indeed.com/viewjob?jk=d0dc1867fdcc5324</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer, Engineering &amp; Ops</t>
+          <t>Customer Reliability Engineer, Airflow</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>NBCUniversal</t>
+          <t>Astronomer</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Snowflake, ELT, dbt, MLOps, Airflow</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, Snowflake, PostgreSQL, dbt, DataOps, Docker</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,67 +4101,67 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df536a2594fa5881</t>
+          <t>https://www.indeed.com/viewjob?jk=6ac244565083c1d9</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>TRM Labs</t>
+          <t>Skechers</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Hermosa Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, ETL, dbt, Power BI, Tableau, CI/CD</t>
+          <t>AWS, RDS, BigQuery, Spark, Scala, Snowflake, Data Modeling, MLOps, Git, Python</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dcb7ea8003fbc5dc</t>
+          <t>https://www.indeed.com/viewjob?jk=4bf4b62fe049b84e</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Microsoft Entra</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>RapidFire Safety &amp; Security</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Oracle, Data Modeling, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
+          <t>RDS, Azure, Scala, SQL Server, Data Modeling, Star Schema, Fact Tables, Dimension Tables, ETL, Power BI</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,94 +4171,94 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f61688604ed96074</t>
+          <t>https://www.indeed.com/viewjob?jk=8afc73df8ef8f40e</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Entry-Level Data Engineer</t>
+          <t>Salesforce Architect - Senior</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>CommunityForce Inc.</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>ECS, RDS, Azure, Scala, Kafka, Data Modeling, ETL, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd80dc2e6636141e</t>
+          <t>https://www.indeed.com/viewjob?jk=7d236cba8a6e8ae3</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Data Engineer-LLMs / Agentic Systems</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Lyric</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Spark, Scala, Kafka, Snowflake, ETL, ELT, dbt, CI/CD</t>
+          <t>AWS, S3, RDS, Scala, PostgreSQL, MongoDB, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b5cdc524b199967</t>
+          <t>https://www.indeed.com/viewjob?jk=92b5658394aee4e3</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Software Engineer - Master</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Westchester Medical Center Health Network</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Valhalla, NY, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,34 +4266,34 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Snowflake, SQL Server, Data Modeling, ELT, Power BI, Tableau, CI/CD</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d807a7856ebe08db</t>
+          <t>https://www.indeed.com/viewjob?jk=3fb1207979169793</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer, Enterprise Data &amp; Analytics</t>
+          <t>Data Engineer - GRC Technology</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Rivian</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,34 +4301,34 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, ECS, Databricks, Data Modeling, ELT, dbt</t>
+          <t>AWS, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b74ac1e46b3dfa89</t>
+          <t>https://www.indeed.com/viewjob?jk=8842e67bf37c518a</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Callaway Golf</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
+          <t>AWS, Azure, Databricks, Spark, Snowflake, ETL, ELT, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,24 +4346,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af8d363b230dfbc2</t>
+          <t>https://www.indeed.com/viewjob?jk=ab2d181891cc2eee</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Attribution Expansion</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>TRM Labs</t>
+          <t>Emed</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Spark, Snowflake, Data Modeling, dbt, MLflow, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=539a18aebac4ef5f</t>
+          <t>https://www.indeed.com/viewjob?jk=1e29e1c3d36f0e7c</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Attribution Expansion</t>
+          <t>Sr. Data Engineer, Engineering &amp; Ops</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>TRM Labs</t>
+          <t>NBCUniversal</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,15 +4406,400 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Snowflake, ELT, dbt, MLOps, Airflow</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=df536a2594fa5881</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Senior Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>TRM Labs</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, ETL, dbt, Power BI, Tableau, CI/CD</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dcb7ea8003fbc5dc</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Microsoft Entra</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Oracle, Data Modeling, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f61688604ed96074</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Westchester Medical Center Health Network</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Valhalla, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Snowflake, SQL Server, Data Modeling, ELT, Power BI, Tableau, CI/CD</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d807a7856ebe08db</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Sr. Data Engineer, Enterprise Data &amp; Analytics</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Rivian</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>AWS, Glue, EMR, Lambda, S3, ECS, Databricks, Data Modeling, ELT, dbt</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>2025-11-21</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b74ac1e46b3dfa89</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>.NET Developer</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Caterpillar</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Cary, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>S3, RDS, Azure, Scala, Snowflake, SQL Server, Power BI, CI/CD, Azure DevOps, Git</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4afc3e61f8ae8b7b</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1315e6e62a7714e8</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Sr. Informatica IDMC MDM Software Engineer</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>RBC</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Minneapolis, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, ETL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5346f4c5e2b5352a</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>LTIMindtree</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Oracle, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=af8d363b230dfbc2</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Data Platform Engineer - Alteryx Platform Management</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Truist</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, MongoDB, Jenkins, Maven, Jenkins</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bde05d459024e776</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer, Attribution Expansion</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>TRM Labs</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
           <t>RDS, BigQuery, Spark, Snowflake, Data Modeling, dbt, MLflow, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=539a18aebac4ef5f</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer, Attribution Expansion</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>TRM Labs</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>RDS, BigQuery, Spark, Snowflake, Data Modeling, dbt, MLflow, CI/CD, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=26436308d22e947d</t>
         </is>

--- a/results/job_matches_2026-03-05.xlsx
+++ b/results/job_matches_2026-03-05.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G125"/>
+  <dimension ref="A1:G127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,17 +503,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Engineer III: DevOps</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Jersey Mikes Corporate</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Tinton Falls, NJ, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, API Gateway, ECS, RDS, Azure, GCP, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,24 +531,24 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc952e4224a3aa24</t>
+          <t>https://www.indeed.com/viewjob?jk=31cf41e0387f0b72</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer III: DevOps</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Jersey Mikes Corporate</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Tinton Falls, NJ, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, S3, SQS, SNS, API Gateway, ECS, RDS, Azure, GCP, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31cf41e0387f0b72</t>
+          <t>https://www.indeed.com/viewjob?jk=bc952e4224a3aa24</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Client Authentication</t>
+          <t>Senior Data Engineer, ACVMax</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>ACV Auctions</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Southlake, TX, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>IAM, RDS, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a908b362cb914674</t>
+          <t>https://www.indeed.com/viewjob?jk=6c28dd5d00192a5b</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, ACVMax</t>
+          <t>Senior Data Engineer, Client Authentication</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ACV Auctions</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>Southlake, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS</t>
+          <t>IAM, RDS, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c28dd5d00192a5b</t>
+          <t>https://www.indeed.com/viewjob?jk=a908b362cb914674</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer - Consultant</t>
+          <t>Sr. Data Platform Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Real Time Medical Systems</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,34 +661,34 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, IAM, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7167050c109be2d4</t>
+          <t>https://www.indeed.com/viewjob?jk=415686b53cfda723</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer - Consultant</t>
+          <t>Sr. Data Platform Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Real Time Medical Systems</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Columbia, MD, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,34 +696,34 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, IAM, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=862a4a8989448fa0</t>
+          <t>https://www.indeed.com/viewjob?jk=41a92f9802d4f918</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer - Consultant</t>
+          <t>Senior Software Engineer, Cloud Infrastructure</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>ALTRUIST</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,34 +731,34 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark</t>
+          <t>AWS, S3, API Gateway, IAM, RDS, Scala, Kafka, PostgreSQL, DynamoDB, MLOps</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07e542bb4713fad0</t>
+          <t>https://www.indeed.com/viewjob?jk=b2b2e3b90367f3b4</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer - Consultant</t>
+          <t>Senior Software Engineer, Cloud Infrastructure</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>ALTRUIST</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,17 +766,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark</t>
+          <t>AWS, S3, API Gateway, IAM, RDS, Scala, Kafka, PostgreSQL, DynamoDB, MLOps</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c88dff775194e30</t>
+          <t>https://www.indeed.com/viewjob?jk=15721c69bc524693</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8ced45fe117deb8</t>
+          <t>https://www.indeed.com/viewjob?jk=7167050c109be2d4</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dc8e0c810b3e7cd</t>
+          <t>https://www.indeed.com/viewjob?jk=862a4a8989448fa0</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7791942c877daada</t>
+          <t>https://www.indeed.com/viewjob?jk=07e542bb4713fad0</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6b39b9b56abc0bd</t>
+          <t>https://www.indeed.com/viewjob?jk=2c88dff775194e30</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=648774ee33ca3b76</t>
+          <t>https://www.indeed.com/viewjob?jk=c8ced45fe117deb8</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a93ca1ad887e17f0</t>
+          <t>https://www.indeed.com/viewjob?jk=2dc8e0c810b3e7cd</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d963e90dfb3fa4d6</t>
+          <t>https://www.indeed.com/viewjob?jk=7791942c877daada</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=783ac47e6d62e414</t>
+          <t>https://www.indeed.com/viewjob?jk=b6b39b9b56abc0bd</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e511c7108cd6e82d</t>
+          <t>https://www.indeed.com/viewjob?jk=648774ee33ca3b76</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a6a2ad30fc1236d</t>
+          <t>https://www.indeed.com/viewjob?jk=a93ca1ad887e17f0</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2d42f6d55a07b48</t>
+          <t>https://www.indeed.com/viewjob?jk=d963e90dfb3fa4d6</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c423f392a018bf22</t>
+          <t>https://www.indeed.com/viewjob?jk=783ac47e6d62e414</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb49af32ea451f63</t>
+          <t>https://www.indeed.com/viewjob?jk=e511c7108cd6e82d</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e7468c4fe6bdb23</t>
+          <t>https://www.indeed.com/viewjob?jk=2a6a2ad30fc1236d</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a3485c3c6153843</t>
+          <t>https://www.indeed.com/viewjob?jk=e2d42f6d55a07b48</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef4166ba4aa9b5a3</t>
+          <t>https://www.indeed.com/viewjob?jk=c423f392a018bf22</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91d6e4beb774dd25</t>
+          <t>https://www.indeed.com/viewjob?jk=cb49af32ea451f63</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adcf2824745a050e</t>
+          <t>https://www.indeed.com/viewjob?jk=1e7468c4fe6bdb23</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64b296145590b995</t>
+          <t>https://www.indeed.com/viewjob?jk=3a3485c3c6153843</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c4169879098b22b</t>
+          <t>https://www.indeed.com/viewjob?jk=ef4166ba4aa9b5a3</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44e1222f0eb14744</t>
+          <t>https://www.indeed.com/viewjob?jk=91d6e4beb774dd25</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37bd1a8719f0aafc</t>
+          <t>https://www.indeed.com/viewjob?jk=adcf2824745a050e</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e151b2c0a32e2723</t>
+          <t>https://www.indeed.com/viewjob?jk=64b296145590b995</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c07dcca1b609463e</t>
+          <t>https://www.indeed.com/viewjob?jk=8c4169879098b22b</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c721bd4ca7bdffe1</t>
+          <t>https://www.indeed.com/viewjob?jk=44e1222f0eb14744</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8e182c6058fd2a4</t>
+          <t>https://www.indeed.com/viewjob?jk=37bd1a8719f0aafc</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4997f8f92f05b9d2</t>
+          <t>https://www.indeed.com/viewjob?jk=e151b2c0a32e2723</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a56481df82d7aa6</t>
+          <t>https://www.indeed.com/viewjob?jk=c07dcca1b609463e</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb00c80fb9cb9b65</t>
+          <t>https://www.indeed.com/viewjob?jk=c721bd4ca7bdffe1</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fd1863254c88e5d</t>
+          <t>https://www.indeed.com/viewjob?jk=e8e182c6058fd2a4</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Sr. Data Platform Engineer</t>
+          <t>Databricks Data Engineer - Consultant</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Real Time Medical Systems</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, IAM, RDS, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=415686b53cfda723</t>
+          <t>https://www.indeed.com/viewjob?jk=4997f8f92f05b9d2</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Sr. Data Platform Engineer</t>
+          <t>Databricks Data Engineer - Consultant</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Real Time Medical Systems</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Columbia, MD, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, IAM, RDS, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41a92f9802d4f918</t>
+          <t>https://www.indeed.com/viewjob?jk=2a56481df82d7aa6</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Cloud Infrastructure</t>
+          <t>Databricks Data Engineer - Consultant</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>ALTRUIST</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, IAM, RDS, Scala, Kafka, PostgreSQL, DynamoDB, MLOps</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2b2e3b90367f3b4</t>
+          <t>https://www.indeed.com/viewjob?jk=fb00c80fb9cb9b65</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Cloud Infrastructure</t>
+          <t>Databricks Data Engineer - Consultant</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>ALTRUIST</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,17 +1956,17 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, IAM, RDS, Scala, Kafka, PostgreSQL, DynamoDB, MLOps</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15721c69bc524693</t>
+          <t>https://www.indeed.com/viewjob?jk=3fd1863254c88e5d</t>
         </is>
       </c>
     </row>
@@ -2113,17 +2113,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Google Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>NMI</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Schaumburg, IL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Kafka, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9188fd233f524c42</t>
+          <t>https://www.indeed.com/viewjob?jk=e7cac4b03aa7cfe7</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Google Cloud Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>NMI</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Schaumburg, IL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,17 +2166,17 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Kafka, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7cac4b03aa7cfe7</t>
+          <t>https://www.indeed.com/viewjob?jk=9188fd233f524c42</t>
         </is>
       </c>
     </row>
@@ -2253,17 +2253,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Engineer - DevOps/ DataOps</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>FICO</t>
+          <t>Alight Solutions</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, DataOps, MLOps, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, GCP, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1ed15cfc823b0b7</t>
+          <t>https://www.indeed.com/viewjob?jk=398f35933211332f</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>Senior Engineer - DevOps/ DataOps</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Alight Solutions</t>
+          <t>FICO</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, GCP, Scala, CI/CD</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, DataOps, MLOps, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=398f35933211332f</t>
+          <t>https://www.indeed.com/viewjob?jk=e1ed15cfc823b0b7</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>SQL Developer - Enterprise Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>SRS Distribution</t>
+          <t>Pantherx Specialty Llc</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>McKinney, TX, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Hadoop, Hive, Spark, Scala, Snowflake</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cde050af8749e53</t>
+          <t>https://www.indeed.com/viewjob?jk=41d495363374161e</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>SQL Developer - Enterprise Data &amp; Analytics</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Pantherx Specialty Llc</t>
+          <t>SRS Distribution</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>McKinney, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Hadoop, Hive, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41d495363374161e</t>
+          <t>https://www.indeed.com/viewjob?jk=4cde050af8749e53</t>
         </is>
       </c>
     </row>
@@ -2743,17 +2743,17 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Commercial Software</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>SRR Consultants</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Piscataway, NJ, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, Oracle, MySQL</t>
+          <t>AWS, Glue, S3, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f3de39cf73c3663</t>
+          <t>https://www.indeed.com/viewjob?jk=88619a1e983eef30</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer, Data Lakehouse Infrastructure</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>SRR Consultants</t>
+          <t>TRM Labs</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Piscataway, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88619a1e983eef30</t>
+          <t>https://www.indeed.com/viewjob?jk=e899ea40640da235</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Data Lakehouse Infrastructure</t>
+          <t>AWS DevOps Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>TRM Labs</t>
+          <t>Seqster PDM, Inc</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, IAM, RDS, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e899ea40640da235</t>
+          <t>https://www.indeed.com/viewjob?jk=191c0857581cffe3</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>AWS DevOps Engineer</t>
+          <t>Senior Software Engineer - Commercial Software</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Seqster PDM, Inc</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, Oracle, MySQL</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=191c0857581cffe3</t>
+          <t>https://www.indeed.com/viewjob?jk=5f3de39cf73c3663</t>
         </is>
       </c>
     </row>
@@ -2918,17 +2918,17 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End (Java, Go, AWS)</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Daniels Health</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Docker</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e716b4195b2da30b</t>
+          <t>https://www.indeed.com/viewjob?jk=1df7caac86af2291</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End (Java, Go, AWS)</t>
+          <t>ATC - AI &amp; Data Analyst - NAELFY26</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Saint Petersburg, FL, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1b9bbef981d9232</t>
+          <t>https://www.indeed.com/viewjob?jk=1ce7a50a4bbe9ef2</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Data Engineer, Data Product</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Daniels Health</t>
+          <t>TRM Labs</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
+          <t>RDS, BigQuery, Dataflow, Spark, Scala, Kafka, dbt, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1df7caac86af2291</t>
+          <t>https://www.indeed.com/viewjob?jk=351b720407fa6f6d</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>ATC - AI &amp; Data Analyst - NAELFY26</t>
+          <t>Analytics, Full-Stack Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>SCAN Health Plan</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Saint Petersburg, FL, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ce7a50a4bbe9ef2</t>
+          <t>https://www.indeed.com/viewjob?jk=c24274a4aa989f95</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Data Product</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>TRM Labs</t>
+          <t>Waters</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Milford, MA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Dataflow, Spark, Scala, Kafka, dbt, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=351b720407fa6f6d</t>
+          <t>https://www.indeed.com/viewjob?jk=1975adb5bfc7de33</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Analytics, Full-Stack Engineer</t>
+          <t>Senior Software Engineer, Back End (Java, Go, AWS)</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>SCAN Health Plan</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Snowflake, ETL, ELT, dbt</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c24274a4aa989f95</t>
+          <t>https://www.indeed.com/viewjob?jk=e716b4195b2da30b</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Software Engineer, Back End (Java, Go, AWS)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Waters</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Milford, MA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1975adb5bfc7de33</t>
+          <t>https://www.indeed.com/viewjob?jk=e1b9bbef981d9232</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Application Developer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Weyerhaeuser</t>
+          <t>Munich Re</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Amelia, OH, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, MLOps, MLflow, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d9f82346c5ff2d3</t>
+          <t>https://www.indeed.com/viewjob?jk=1c8f07e938168692</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - MDM / RDM &amp; API Development</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Prudential</t>
+          <t>Weyerhaeuser</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Spark, Scala, MySQL, NoSQL, Jenkins, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, MLOps, MLflow, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d75a6cef6409e12b</t>
+          <t>https://www.indeed.com/viewjob?jk=7d9f82346c5ff2d3</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Software Engineer (Hybrid)</t>
+          <t>Senior Software Engineer - MDM / RDM &amp; API Development</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Nightwing</t>
+          <t>Prudential</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Clarksville, TN, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, Kinesis, SQS, RDS, Spark, Scala, MySQL, NoSQL, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=887221a715d1ff03</t>
+          <t>https://www.indeed.com/viewjob?jk=d75a6cef6409e12b</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Sterling, VA, US USA</t>
+          <t>Clarksville, TN, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3322d87953168bdc</t>
+          <t>https://www.indeed.com/viewjob?jk=887221a715d1ff03</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Advanced Metering Infrastructure (AMI) Engineer</t>
+          <t>Software Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>WSSC Water</t>
+          <t>Nightwing</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Laurel, MD, US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Oracle, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps</t>
+          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5b2aa36ee050b9b</t>
+          <t>https://www.indeed.com/viewjob?jk=3322d87953168bdc</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Software Systems Engineer, Release Reliability &amp; Automation (Autonomous Vehicles)</t>
+          <t>Advanced Metering Infrastructure (AMI) Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>WSSC Water</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Laurel, MD, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, Power BI, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Scala, Kafka, Oracle, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=864266ab5f8e3aac</t>
+          <t>https://www.indeed.com/viewjob?jk=c5b2aa36ee050b9b</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Software Systems Engineer, Release Reliability &amp; Automation (Autonomous Vehicles)</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Amplify</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Snowflake, DynamoDB, Data Modeling, Kimball, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, Power BI, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4d16d721d2057f3</t>
+          <t>https://www.indeed.com/viewjob?jk=864266ab5f8e3aac</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Software Engineer III - Java/Spark/AWS</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Amplify</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, ECS, RDS, Databricks, Spark, Scala, Snowflake</t>
+          <t>AWS, S3, RDS, Snowflake, DynamoDB, Data Modeling, Kimball, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c95674c932d41fb6</t>
+          <t>https://www.indeed.com/viewjob?jk=b4d16d721d2057f3</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Tableau Developer</t>
+          <t>Software Engineer III - Java/Spark/AWS</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Michael Kors</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>East Rutherford, NJ, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Star Schema</t>
+          <t>AWS, EMR, Lambda, S3, ECS, RDS, Databricks, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=904e084e965a45c4</t>
+          <t>https://www.indeed.com/viewjob?jk=c95674c932d41fb6</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Software Engineer (Junior)</t>
+          <t>Tableau Developer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>TORCH.AI</t>
+          <t>Michael Kors</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Leawood, KS, US USA</t>
+          <t>East Rutherford, NJ, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Kafka, PostgreSQL, MongoDB, NoSQL, ETL, CI/CD</t>
+          <t>AWS, Glue, Redshift, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28e432d03da8db08</t>
+          <t>https://www.indeed.com/viewjob?jk=904e084e965a45c4</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Software Engineer (Junior)</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>TORCH.AI</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Leawood, KS, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, IAM, Azure, GCP, Kafka, PostgreSQL, MongoDB, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8b55e090bbab627</t>
+          <t>https://www.indeed.com/viewjob?jk=28e432d03da8db08</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Database Administrator</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Rogue Community College</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,69 +3566,69 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f9335cc41b5edf2</t>
+          <t>https://www.indeed.com/viewjob?jk=a8b55e090bbab627</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End (Python)</t>
+          <t>Database Administrator</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Rogue Community College</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, Power BI</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3864c05dc9b353f8</t>
+          <t>https://www.indeed.com/viewjob?jk=7f9335cc41b5edf2</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Data Engineer 2</t>
+          <t>AWS Data Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>BLOC Resources, LLC</t>
+          <t>Appex Innovation</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Data Modeling, CI/CD</t>
+          <t>AWS, Glue, Lambda, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c51290628ce41b82</t>
+          <t>https://www.indeed.com/viewjob?jk=7f3534222ab81e17</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer I, Applied AI</t>
+          <t>AWS Data Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Axon</t>
+          <t>Appex Innovation</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Glue, Lambda, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e858c83fc09cd77d</t>
+          <t>https://www.indeed.com/viewjob?jk=3886cb86a753634c</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Platform</t>
+          <t>Data Engineer 2</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>TRM Labs</t>
+          <t>BLOC Resources, LLC</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Spark, Scala, Kafka, ETL, dbt, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a517be0e10b2a44</t>
+          <t>https://www.indeed.com/viewjob?jk=c51290628ce41b82</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Data Platform</t>
+          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>TRM Labs</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Spark, Scala, Kafka, ETL, dbt, Terraform, Docker, Kubernetes</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60f6c2aecd2d1bdf</t>
+          <t>https://www.indeed.com/viewjob?jk=f9637232a826c3ad</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Software Engineer (Backend) - Global Dining</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>CNH Industrial</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,34 +3776,34 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Kafka, MySQL, MongoDB, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8f71d52efce43e2</t>
+          <t>https://www.indeed.com/viewjob?jk=e5b3837921976566</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>AWS Data Engineer</t>
+          <t>Senior Software Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Appex Innovation</t>
+          <t>TRM Labs</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,34 +3811,34 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD</t>
+          <t>RDS, BigQuery, Spark, Scala, Kafka, ETL, dbt, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f3534222ab81e17</t>
+          <t>https://www.indeed.com/viewjob?jk=8a517be0e10b2a44</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
+          <t>Senior Data Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>TRM Labs</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>RDS, BigQuery, Spark, Scala, Kafka, ETL, dbt, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9637232a826c3ad</t>
+          <t>https://www.indeed.com/viewjob?jk=60f6c2aecd2d1bdf</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer - Microsoft Fabric</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>CNH Industrial</t>
+          <t>EoS Fitness</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ELT, Power BI</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5b3837921976566</t>
+          <t>https://www.indeed.com/viewjob?jk=7bd7f3590528db3c</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Microsoft Fabric</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>EoS Fitness</t>
+          <t>PGA TOUR Superstore</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Roswell, GA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ELT, Power BI</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bd7f3590528db3c</t>
+          <t>https://www.indeed.com/viewjob?jk=73bdb2d180484ce2</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>PGA TOUR Superstore</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Roswell, GA, US USA</t>
+          <t>Gilbert, AZ, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,34 +3951,34 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73bdb2d180484ce2</t>
+          <t>https://www.indeed.com/viewjob?jk=110f275787ec7bdb</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Sr. Software Engineer, Data, Autonomy</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Rivian</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Gilbert, AZ, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,34 +3986,34 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, S3, IAM, Databricks, Unity Catalog, Spark, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=110f275787ec7bdb</t>
+          <t>https://www.indeed.com/viewjob?jk=6a3560765ed8e488</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Data, Autonomy</t>
+          <t>Senior Software Engineer, Back End (Python)</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Rivian</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,34 +4021,34 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, Databricks, Unity Catalog, Spark, Scala, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-01-31</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a3560765ed8e488</t>
+          <t>https://www.indeed.com/viewjob?jk=3864c05dc9b353f8</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>AI Applications Engineer</t>
+          <t>Sr. Software Engineer I, Applied AI</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Stanford University</t>
+          <t>Axon</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Vertex AI, Scala, Oracle, NoSQL, Data Modeling, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0dc1867fdcc5324</t>
+          <t>https://www.indeed.com/viewjob?jk=e858c83fc09cd77d</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Customer Reliability Engineer, Airflow</t>
+          <t>AI Applications Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Astronomer</t>
+          <t>Stanford University</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, Snowflake, PostgreSQL, dbt, DataOps, Docker</t>
+          <t>AWS, RDS, Azure, Vertex AI, Scala, Oracle, NoSQL, Data Modeling, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ac244565083c1d9</t>
+          <t>https://www.indeed.com/viewjob?jk=d0dc1867fdcc5324</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Customer Reliability Engineer, Airflow</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Skechers</t>
+          <t>Astronomer</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Hermosa Beach, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,17 +4126,17 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Spark, Scala, Snowflake, Data Modeling, MLOps, Git, Python</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, Snowflake, PostgreSQL, dbt, DataOps, Docker</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bf4b62fe049b84e</t>
+          <t>https://www.indeed.com/viewjob?jk=6ac244565083c1d9</t>
         </is>
       </c>
     </row>
@@ -4248,17 +4248,17 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Software Engineer - Master</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Callaway Golf</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, Azure, Databricks, Spark, Snowflake, ETL, ELT, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fb1207979169793</t>
+          <t>https://www.indeed.com/viewjob?jk=ab2d181891cc2eee</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Data Engineer - GRC Technology</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Emed</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,34 +4301,34 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8842e67bf37c518a</t>
+          <t>https://www.indeed.com/viewjob?jk=1e29e1c3d36f0e7c</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Sr. Data Engineer, Engineering &amp; Ops</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Callaway Golf</t>
+          <t>NBCUniversal</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Spark, Snowflake, ETL, ELT, Terraform, Kubernetes, Git</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Snowflake, ELT, dbt, MLOps, Airflow</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,24 +4346,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab2d181891cc2eee</t>
+          <t>https://www.indeed.com/viewjob?jk=df536a2594fa5881</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Emed</t>
+          <t>TRM Labs</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, ETL, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e29e1c3d36f0e7c</t>
+          <t>https://www.indeed.com/viewjob?jk=dcb7ea8003fbc5dc</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer, Engineering &amp; Ops</t>
+          <t>Microsoft Entra</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>NBCUniversal</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Snowflake, ELT, dbt, MLOps, Airflow</t>
+          <t>RDS, Azure, Data Factory, Oracle, Data Modeling, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df536a2594fa5881</t>
+          <t>https://www.indeed.com/viewjob?jk=f61688604ed96074</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>TRM Labs</t>
+          <t>Westchester Medical Center Health Network</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Valhalla, NY, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,34 +4441,34 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, ETL, dbt, Power BI, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, Snowflake, SQL Server, Data Modeling, ELT, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dcb7ea8003fbc5dc</t>
+          <t>https://www.indeed.com/viewjob?jk=d807a7856ebe08db</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Microsoft Entra</t>
+          <t>Data Engineer - GRC Technology</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,34 +4476,34 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Oracle, Data Modeling, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f61688604ed96074</t>
+          <t>https://www.indeed.com/viewjob?jk=8842e67bf37c518a</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Sr. Data Engineer, Enterprise Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Westchester Medical Center Health Network</t>
+          <t>Rivian</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Valhalla, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,34 +4511,34 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Snowflake, SQL Server, Data Modeling, ELT, Power BI, Tableau, CI/CD</t>
+          <t>AWS, Glue, EMR, Lambda, S3, ECS, Databricks, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d807a7856ebe08db</t>
+          <t>https://www.indeed.com/viewjob?jk=b74ac1e46b3dfa89</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer, Enterprise Data &amp; Analytics</t>
+          <t>Software Engineer - Master</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Rivian</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,17 +4546,17 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, ECS, Databricks, Data Modeling, ELT, dbt</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b74ac1e46b3dfa89</t>
+          <t>https://www.indeed.com/viewjob?jk=3fb1207979169793</t>
         </is>
       </c>
     </row>
@@ -4633,17 +4633,17 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Sr. Informatica IDMC MDM Software Engineer</t>
+          <t>Data Platform Engineer - Alteryx Platform Management</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>RBC</t>
+          <t>Truist</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, MongoDB, Jenkins, Maven, Jenkins</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,24 +4661,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5346f4c5e2b5352a</t>
+          <t>https://www.indeed.com/viewjob?jk=a738d45466c580a9</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Guidewire Software, Inc.</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af8d363b230dfbc2</t>
+          <t>https://www.indeed.com/viewjob?jk=3b5e082bd1857b0f</t>
         </is>
       </c>
     </row>
@@ -4738,17 +4738,17 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Attribution Expansion</t>
+          <t>Sr. Informatica IDMC MDM Software Engineer</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>TRM Labs</t>
+          <t>RBC</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Spark, Snowflake, Data Modeling, dbt, MLflow, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,24 +4766,24 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=539a18aebac4ef5f</t>
+          <t>https://www.indeed.com/viewjob?jk=5346f4c5e2b5352a</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Attribution Expansion</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>TRM Labs</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,15 +4791,85 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
+          <t>AWS, RDS, Scala, Oracle, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=af8d363b230dfbc2</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer, Attribution Expansion</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>TRM Labs</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
           <t>RDS, BigQuery, Spark, Snowflake, Data Modeling, dbt, MLflow, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr">
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=539a18aebac4ef5f</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer, Attribution Expansion</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>TRM Labs</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>RDS, BigQuery, Spark, Snowflake, Data Modeling, dbt, MLflow, CI/CD, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=26436308d22e947d</t>
         </is>

--- a/results/job_matches_2026-03-05.xlsx
+++ b/results/job_matches_2026-03-05.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G127"/>
+  <dimension ref="A1:G129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,17 +503,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer III: DevOps</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Jersey Mikes Corporate</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Tinton Falls, NJ, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, S3, SQS, SNS, API Gateway, ECS, RDS, Azure, GCP, Scala</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,24 +531,24 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31cf41e0387f0b72</t>
+          <t>https://www.indeed.com/viewjob?jk=bc952e4224a3aa24</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software Engineer III: DevOps</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Jersey Mikes Corporate</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Tinton Falls, NJ, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, API Gateway, ECS, RDS, Azure, GCP, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc952e4224a3aa24</t>
+          <t>https://www.indeed.com/viewjob?jk=31cf41e0387f0b72</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, ACVMax</t>
+          <t>Senior Data Engineer, Client Authentication</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ACV Auctions</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>Southlake, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS</t>
+          <t>IAM, RDS, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c28dd5d00192a5b</t>
+          <t>https://www.indeed.com/viewjob?jk=a908b362cb914674</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Client Authentication</t>
+          <t>Senior Data Engineer, ACVMax</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>ACV Auctions</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Southlake, TX, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>IAM, RDS, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a908b362cb914674</t>
+          <t>https://www.indeed.com/viewjob?jk=6c28dd5d00192a5b</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sr. Data Platform Engineer</t>
+          <t>Databricks Data Engineer - Consultant</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Real Time Medical Systems</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,34 +661,34 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, IAM, RDS, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=415686b53cfda723</t>
+          <t>https://www.indeed.com/viewjob?jk=7167050c109be2d4</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sr. Data Platform Engineer</t>
+          <t>Databricks Data Engineer - Consultant</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Real Time Medical Systems</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Columbia, MD, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,34 +696,34 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, IAM, RDS, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41a92f9802d4f918</t>
+          <t>https://www.indeed.com/viewjob?jk=862a4a8989448fa0</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Cloud Infrastructure</t>
+          <t>Databricks Data Engineer - Consultant</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ALTRUIST</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,34 +731,34 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, IAM, RDS, Scala, Kafka, PostgreSQL, DynamoDB, MLOps</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2b2e3b90367f3b4</t>
+          <t>https://www.indeed.com/viewjob?jk=07e542bb4713fad0</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Cloud Infrastructure</t>
+          <t>Databricks Data Engineer - Consultant</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ALTRUIST</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,17 +766,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, IAM, RDS, Scala, Kafka, PostgreSQL, DynamoDB, MLOps</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15721c69bc524693</t>
+          <t>https://www.indeed.com/viewjob?jk=2c88dff775194e30</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7167050c109be2d4</t>
+          <t>https://www.indeed.com/viewjob?jk=c8ced45fe117deb8</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=862a4a8989448fa0</t>
+          <t>https://www.indeed.com/viewjob?jk=2dc8e0c810b3e7cd</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07e542bb4713fad0</t>
+          <t>https://www.indeed.com/viewjob?jk=7791942c877daada</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c88dff775194e30</t>
+          <t>https://www.indeed.com/viewjob?jk=b6b39b9b56abc0bd</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8ced45fe117deb8</t>
+          <t>https://www.indeed.com/viewjob?jk=648774ee33ca3b76</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dc8e0c810b3e7cd</t>
+          <t>https://www.indeed.com/viewjob?jk=a93ca1ad887e17f0</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7791942c877daada</t>
+          <t>https://www.indeed.com/viewjob?jk=d963e90dfb3fa4d6</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6b39b9b56abc0bd</t>
+          <t>https://www.indeed.com/viewjob?jk=783ac47e6d62e414</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=648774ee33ca3b76</t>
+          <t>https://www.indeed.com/viewjob?jk=e511c7108cd6e82d</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a93ca1ad887e17f0</t>
+          <t>https://www.indeed.com/viewjob?jk=2a6a2ad30fc1236d</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d963e90dfb3fa4d6</t>
+          <t>https://www.indeed.com/viewjob?jk=e2d42f6d55a07b48</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=783ac47e6d62e414</t>
+          <t>https://www.indeed.com/viewjob?jk=c423f392a018bf22</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e511c7108cd6e82d</t>
+          <t>https://www.indeed.com/viewjob?jk=cb49af32ea451f63</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a6a2ad30fc1236d</t>
+          <t>https://www.indeed.com/viewjob?jk=1e7468c4fe6bdb23</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2d42f6d55a07b48</t>
+          <t>https://www.indeed.com/viewjob?jk=3a3485c3c6153843</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c423f392a018bf22</t>
+          <t>https://www.indeed.com/viewjob?jk=ef4166ba4aa9b5a3</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb49af32ea451f63</t>
+          <t>https://www.indeed.com/viewjob?jk=91d6e4beb774dd25</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e7468c4fe6bdb23</t>
+          <t>https://www.indeed.com/viewjob?jk=adcf2824745a050e</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a3485c3c6153843</t>
+          <t>https://www.indeed.com/viewjob?jk=64b296145590b995</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef4166ba4aa9b5a3</t>
+          <t>https://www.indeed.com/viewjob?jk=8c4169879098b22b</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91d6e4beb774dd25</t>
+          <t>https://www.indeed.com/viewjob?jk=44e1222f0eb14744</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adcf2824745a050e</t>
+          <t>https://www.indeed.com/viewjob?jk=37bd1a8719f0aafc</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64b296145590b995</t>
+          <t>https://www.indeed.com/viewjob?jk=e151b2c0a32e2723</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c4169879098b22b</t>
+          <t>https://www.indeed.com/viewjob?jk=c07dcca1b609463e</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44e1222f0eb14744</t>
+          <t>https://www.indeed.com/viewjob?jk=c721bd4ca7bdffe1</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37bd1a8719f0aafc</t>
+          <t>https://www.indeed.com/viewjob?jk=e8e182c6058fd2a4</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e151b2c0a32e2723</t>
+          <t>https://www.indeed.com/viewjob?jk=4997f8f92f05b9d2</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c07dcca1b609463e</t>
+          <t>https://www.indeed.com/viewjob?jk=2a56481df82d7aa6</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c721bd4ca7bdffe1</t>
+          <t>https://www.indeed.com/viewjob?jk=fb00c80fb9cb9b65</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8e182c6058fd2a4</t>
+          <t>https://www.indeed.com/viewjob?jk=3fd1863254c88e5d</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer - Consultant</t>
+          <t>Sr. Data Platform Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Real Time Medical Systems</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, IAM, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4997f8f92f05b9d2</t>
+          <t>https://www.indeed.com/viewjob?jk=415686b53cfda723</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer - Consultant</t>
+          <t>Sr. Data Platform Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Real Time Medical Systems</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Columbia, MD, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, IAM, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a56481df82d7aa6</t>
+          <t>https://www.indeed.com/viewjob?jk=41a92f9802d4f918</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer - Consultant</t>
+          <t>Senior Software Engineer, Cloud Infrastructure</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>ALTRUIST</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark</t>
+          <t>AWS, S3, API Gateway, IAM, RDS, Scala, Kafka, PostgreSQL, DynamoDB, MLOps</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb00c80fb9cb9b65</t>
+          <t>https://www.indeed.com/viewjob?jk=b2b2e3b90367f3b4</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer - Consultant</t>
+          <t>Senior Software Engineer, Cloud Infrastructure</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>ALTRUIST</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,17 +1956,17 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark</t>
+          <t>AWS, S3, API Gateway, IAM, RDS, Scala, Kafka, PostgreSQL, DynamoDB, MLOps</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fd1863254c88e5d</t>
+          <t>https://www.indeed.com/viewjob?jk=15721c69bc524693</t>
         </is>
       </c>
     </row>
@@ -2008,17 +2008,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Enterprise Data Platform Engineer – Washington, DC</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Creative Information Technology India</t>
+          <t>Valvoline Global Operations</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Falls Church, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,42 +2026,42 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Delta Live Tables, Photon, Scala, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP, Cloud Storage, Spark, PySpark</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a74e373b48da5fc</t>
+          <t>https://www.indeed.com/viewjob?jk=ab16510fd1c2841d</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Enterprise Data Platform Engineer – Washington, DC</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Creative Information Technology India</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Falls Church, VA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Delta Live Tables, Photon, Scala, ETL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e8500146d476812</t>
+          <t>https://www.indeed.com/viewjob?jk=0a74e373b48da5fc</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ad2838bd8f61427</t>
+          <t>https://www.indeed.com/viewjob?jk=9e8500146d476812</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Google Cloud Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>NMI</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Schaumburg, IL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Kafka, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7cac4b03aa7cfe7</t>
+          <t>https://www.indeed.com/viewjob?jk=2ad2838bd8f61427</t>
         </is>
       </c>
     </row>
@@ -2183,17 +2183,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Google Cloud Data Architect</t>
+          <t>Google Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Cloudious</t>
+          <t>NMI</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Schaumburg, IL, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, HDFS, Hive</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Kafka, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73dc517b82db140b</t>
+          <t>https://www.indeed.com/viewjob?jk=e7cac4b03aa7cfe7</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Specialist - System Management</t>
+          <t>Google Cloud Data Architect</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Cloudious</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Glen Allen, VA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Unity Catalog, Delta Live Tables, Spark, Databricks Lakehouse, SQL Server</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, HDFS, Hive</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=293f842904007fda</t>
+          <t>https://www.indeed.com/viewjob?jk=73dc517b82db140b</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>Senior Specialist - System Management</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Alight Solutions</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Glen Allen, VA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, GCP, Scala, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Unity Catalog, Delta Live Tables, Spark, Databricks Lakehouse, SQL Server</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=398f35933211332f</t>
+          <t>https://www.indeed.com/viewjob?jk=293f842904007fda</t>
         </is>
       </c>
     </row>
@@ -2323,25 +2323,25 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>SQL Developer - Enterprise Data &amp; Analytics</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Pantherx Specialty Llc</t>
+          <t>Alight Solutions</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, GCP, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41d495363374161e</t>
+          <t>https://www.indeed.com/viewjob?jk=398f35933211332f</t>
         </is>
       </c>
     </row>
@@ -2393,17 +2393,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>SQL Developer - Enterprise Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>The Cheesecake Factory</t>
+          <t>Pantherx Specialty Llc</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Calabasas Hills, CA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, BigQuery, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf6f08ab2860bc5c</t>
+          <t>https://www.indeed.com/viewjob?jk=41d495363374161e</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Cloud Data Platform Administrator - 26-02191</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>The Cheesecake Factory</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Calabasas Hills, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, BigQuery, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3695a4ce423ac8e5</t>
+          <t>https://www.indeed.com/viewjob?jk=bf6f08ab2860bc5c</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Alexandria, VA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67be12c15c92c4c5</t>
+          <t>https://www.indeed.com/viewjob?jk=3695a4ce423ac8e5</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Alexandria, VA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=861fabb5acea2ca4</t>
+          <t>https://www.indeed.com/viewjob?jk=67be12c15c92c4c5</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6235a9d4364b9757</t>
+          <t>https://www.indeed.com/viewjob?jk=861fabb5acea2ca4</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Specialist Programmer</t>
+          <t>Cloud Data Platform Administrator - 26-02191</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Infosys</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, Hive, Spark, PySpark, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9772b3b8d4167ecc</t>
+          <t>https://www.indeed.com/viewjob?jk=6235a9d4364b9757</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Incremental CRM - Data Developer 1</t>
+          <t>Specialist Programmer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Barclays</t>
+          <t>Infosys</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Whippany, NJ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,69 +2621,69 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, RDS, Databricks, Scala, SQL Server, ETL</t>
+          <t>AWS, Azure, GCP, Hadoop, Hive, Spark, PySpark, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c7931e975a12585</t>
+          <t>https://www.indeed.com/viewjob?jk=9772b3b8d4167ecc</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Incremental CRM - Data Developer 1</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Barclays</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Whippany, NJ, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, IAM, Databricks, Spark, Scala, Kafka, Snowflake, NoSQL, CI/CD</t>
+          <t>AWS, Glue, Redshift, Athena, S3, RDS, Databricks, Scala, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a021dbda97cc3405</t>
+          <t>https://www.indeed.com/viewjob?jk=3c7931e975a12585</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Disney Experiences</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Scala, DynamoDB, NoSQL, ETL</t>
+          <t>AWS, Kinesis, IAM, Databricks, Spark, Scala, Kafka, Snowflake, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a7ddc3760328a54</t>
+          <t>https://www.indeed.com/viewjob?jk=a021dbda97cc3405</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>SSO Administrator</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Disney Experiences</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, PostgreSQL, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Scala, DynamoDB, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9064a81c91aa262</t>
+          <t>https://www.indeed.com/viewjob?jk=0a7ddc3760328a54</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>SSO Administrator</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>SRR Consultants</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Piscataway, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, PostgreSQL, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88619a1e983eef30</t>
+          <t>https://www.indeed.com/viewjob?jk=a9064a81c91aa262</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Data Lakehouse Infrastructure</t>
+          <t>Senior Software Engineer - Commercial Software</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>TRM Labs</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, Oracle, MySQL</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e899ea40640da235</t>
+          <t>https://www.indeed.com/viewjob?jk=5f3de39cf73c3663</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>AWS DevOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Seqster PDM, Inc</t>
+          <t>SRR Consultants</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Piscataway, NJ, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Glue, S3, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=191c0857581cffe3</t>
+          <t>https://www.indeed.com/viewjob?jk=88619a1e983eef30</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Commercial Software</t>
+          <t>Senior Data Engineer, Data Lakehouse Infrastructure</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>TRM Labs</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, Oracle, MySQL</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f3de39cf73c3663</t>
+          <t>https://www.indeed.com/viewjob?jk=e899ea40640da235</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II - AI/ML</t>
+          <t>AWS DevOps Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Seismic</t>
+          <t>Seqster PDM, Inc</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,42 +2901,42 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, IAM, RDS, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d0bc9a390582054</t>
+          <t>https://www.indeed.com/viewjob?jk=191c0857581cffe3</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Java Software Engineer II (US)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Daniels Health</t>
+          <t>TD Bank</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Mount Laurel, NJ, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
+          <t>RDS, Azure, Scala, NoSQL, Splunk, Jenkins, Maven, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,59 +2946,59 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1df7caac86af2291</t>
+          <t>https://www.indeed.com/viewjob?jk=8ee89e940b02cc06</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>ATC - AI &amp; Data Analyst - NAELFY26</t>
+          <t>Senior Software Engineer II - AI/ML</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>Seismic</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Saint Petersburg, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ce7a50a4bbe9ef2</t>
+          <t>https://www.indeed.com/viewjob?jk=5d0bc9a390582054</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Data Product</t>
+          <t>Senior Software Engineer, Back End (Java, Go, AWS)</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>TRM Labs</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Dataflow, Spark, Scala, Kafka, dbt, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=351b720407fa6f6d</t>
+          <t>https://www.indeed.com/viewjob?jk=e716b4195b2da30b</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Analytics, Full-Stack Engineer</t>
+          <t>Senior Software Engineer, Back End (Java, Go, AWS)</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>SCAN Health Plan</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Snowflake, ETL, ELT, dbt</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c24274a4aa989f95</t>
+          <t>https://www.indeed.com/viewjob?jk=e1b9bbef981d9232</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Waters</t>
+          <t>Daniels Health</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Milford, MA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1975adb5bfc7de33</t>
+          <t>https://www.indeed.com/viewjob?jk=1df7caac86af2291</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End (Java, Go, AWS)</t>
+          <t>ATC - AI &amp; Data Analyst - NAELFY26</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Saint Petersburg, FL, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e716b4195b2da30b</t>
+          <t>https://www.indeed.com/viewjob?jk=1ce7a50a4bbe9ef2</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End (Java, Go, AWS)</t>
+          <t>Senior Data Engineer, Data Product</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>TRM Labs</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Docker</t>
+          <t>RDS, BigQuery, Dataflow, Spark, Scala, Kafka, dbt, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1b9bbef981d9232</t>
+          <t>https://www.indeed.com/viewjob?jk=351b720407fa6f6d</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Application Developer</t>
+          <t>Analytics, Full-Stack Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Munich Re</t>
+          <t>SCAN Health Plan</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Amelia, OH, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c8f07e938168692</t>
+          <t>https://www.indeed.com/viewjob?jk=c24274a4aa989f95</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Weyerhaeuser</t>
+          <t>Waters</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Milford, MA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, MLOps, MLflow, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d9f82346c5ff2d3</t>
+          <t>https://www.indeed.com/viewjob?jk=1975adb5bfc7de33</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - MDM / RDM &amp; API Development</t>
+          <t>Application Developer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Prudential</t>
+          <t>Munich Re</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>Amelia, OH, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Spark, Scala, MySQL, NoSQL, Jenkins, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d75a6cef6409e12b</t>
+          <t>https://www.indeed.com/viewjob?jk=1c8f07e938168692</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Software Engineer (Hybrid)</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Nightwing</t>
+          <t>Weyerhaeuser</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Clarksville, TN, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, MLOps, MLflow, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=887221a715d1ff03</t>
+          <t>https://www.indeed.com/viewjob?jk=7d9f82346c5ff2d3</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Software Engineer (Hybrid)</t>
+          <t>Senior Software Engineer - MDM / RDM &amp; API Development</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Nightwing</t>
+          <t>Prudential</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Sterling, VA, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, Kinesis, SQS, RDS, Spark, Scala, MySQL, NoSQL, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3322d87953168bdc</t>
+          <t>https://www.indeed.com/viewjob?jk=d75a6cef6409e12b</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Advanced Metering Infrastructure (AMI) Engineer</t>
+          <t>Software Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>WSSC Water</t>
+          <t>Nightwing</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Laurel, MD, US USA</t>
+          <t>Clarksville, TN, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Oracle, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps</t>
+          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5b2aa36ee050b9b</t>
+          <t>https://www.indeed.com/viewjob?jk=887221a715d1ff03</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Software Systems Engineer, Release Reliability &amp; Automation (Autonomous Vehicles)</t>
+          <t>Software Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Nightwing</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, Power BI, CI/CD, Jenkins</t>
+          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=864266ab5f8e3aac</t>
+          <t>https://www.indeed.com/viewjob?jk=3322d87953168bdc</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Advanced Metering Infrastructure (AMI) Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Amplify</t>
+          <t>WSSC Water</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Laurel, MD, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Snowflake, DynamoDB, Data Modeling, Kimball, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Scala, Kafka, Oracle, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4d16d721d2057f3</t>
+          <t>https://www.indeed.com/viewjob?jk=c5b2aa36ee050b9b</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Software Engineer III - Java/Spark/AWS</t>
+          <t>Software Systems Engineer, Release Reliability &amp; Automation (Autonomous Vehicles)</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, ECS, RDS, Databricks, Spark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, Power BI, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c95674c932d41fb6</t>
+          <t>https://www.indeed.com/viewjob?jk=864266ab5f8e3aac</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Tableau Developer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Michael Kors</t>
+          <t>Amplify</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>East Rutherford, NJ, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Star Schema</t>
+          <t>AWS, S3, RDS, Snowflake, DynamoDB, Data Modeling, Kimball, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=904e084e965a45c4</t>
+          <t>https://www.indeed.com/viewjob?jk=b4d16d721d2057f3</t>
         </is>
       </c>
     </row>
@@ -3583,17 +3583,17 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Database Administrator</t>
+          <t>Software Engineer III - Java/Spark/AWS</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Rogue Community College</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,104 +3601,104 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, Power BI</t>
+          <t>AWS, EMR, Lambda, S3, ECS, RDS, Databricks, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f9335cc41b5edf2</t>
+          <t>https://www.indeed.com/viewjob?jk=c95674c932d41fb6</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>AWS Data Engineer</t>
+          <t>Tableau Developer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Appex Innovation</t>
+          <t>Michael Kors</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>East Rutherford, NJ, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD</t>
+          <t>AWS, Glue, Redshift, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f3534222ab81e17</t>
+          <t>https://www.indeed.com/viewjob?jk=904e084e965a45c4</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>AWS Data Engineer</t>
+          <t>Database Administrator</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Appex Innovation</t>
+          <t>Rogue Community College</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, Power BI</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3886cb86a753634c</t>
+          <t>https://www.indeed.com/viewjob?jk=7f9335cc41b5edf2</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Data Engineer 2</t>
+          <t>Senior Software Engineer, Back End (Python)</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>BLOC Resources, LLC</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Data Modeling, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c51290628ce41b82</t>
+          <t>https://www.indeed.com/viewjob?jk=3864c05dc9b353f8</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
+          <t>Data Engineer 2</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>BLOC Resources, LLC</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9637232a826c3ad</t>
+          <t>https://www.indeed.com/viewjob?jk=c51290628ce41b82</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Software Engineer I, Applied AI</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>CNH Industrial</t>
+          <t>Axon</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5b3837921976566</t>
+          <t>https://www.indeed.com/viewjob?jk=e858c83fc09cd77d</t>
         </is>
       </c>
     </row>
@@ -3863,17 +3863,17 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Microsoft Fabric</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>EoS Fitness</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ELT, Power BI</t>
+          <t>AWS, RDS, Spark, PySpark, Scala, MySQL, MongoDB, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bd7f3590528db3c</t>
+          <t>https://www.indeed.com/viewjob?jk=dd1518c4c02c12ef</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AWS Data Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>PGA TOUR Superstore</t>
+          <t>Appex Innovation</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Roswell, GA, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,34 +3916,34 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, Glue, Lambda, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73bdb2d180484ce2</t>
+          <t>https://www.indeed.com/viewjob?jk=7f3534222ab81e17</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>AWS Data Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Appex Innovation</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Gilbert, AZ, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,34 +3951,34 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=110f275787ec7bdb</t>
+          <t>https://www.indeed.com/viewjob?jk=3886cb86a753634c</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Data, Autonomy</t>
+          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Rivian</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,34 +3986,34 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, Databricks, Unity Catalog, Spark, Scala, DynamoDB, CI/CD</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-01-31</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a3560765ed8e488</t>
+          <t>https://www.indeed.com/viewjob?jk=f9637232a826c3ad</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End (Python)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>CNH Industrial</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3864c05dc9b353f8</t>
+          <t>https://www.indeed.com/viewjob?jk=e5b3837921976566</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer I, Applied AI</t>
+          <t>Senior Data Engineer - Microsoft Fabric</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Axon</t>
+          <t>EoS Fitness</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ELT, Power BI</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e858c83fc09cd77d</t>
+          <t>https://www.indeed.com/viewjob?jk=7bd7f3590528db3c</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>AI Applications Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Stanford University</t>
+          <t>PGA TOUR Superstore</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Roswell, GA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Vertex AI, Scala, Oracle, NoSQL, Data Modeling, MLOps, MLflow</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0dc1867fdcc5324</t>
+          <t>https://www.indeed.com/viewjob?jk=73bdb2d180484ce2</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Customer Reliability Engineer, Airflow</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Astronomer</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Gilbert, AZ, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,34 +4126,34 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, Snowflake, PostgreSQL, dbt, DataOps, Docker</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ac244565083c1d9</t>
+          <t>https://www.indeed.com/viewjob?jk=110f275787ec7bdb</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Sr. Software Engineer, Data, Autonomy</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>RapidFire Safety &amp; Security</t>
+          <t>Rivian</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,34 +4161,34 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, Data Modeling, Star Schema, Fact Tables, Dimension Tables, ETL, Power BI</t>
+          <t>AWS, Lambda, S3, IAM, Databricks, Unity Catalog, Spark, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8afc73df8ef8f40e</t>
+          <t>https://www.indeed.com/viewjob?jk=6a3560765ed8e488</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Salesforce Architect - Senior</t>
+          <t>AI Applications Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>CommunityForce Inc.</t>
+          <t>Stanford University</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>ECS, RDS, Azure, Scala, Kafka, Data Modeling, ETL, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Vertex AI, Scala, Oracle, NoSQL, Data Modeling, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d236cba8a6e8ae3</t>
+          <t>https://www.indeed.com/viewjob?jk=d0dc1867fdcc5324</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>AI Data Engineer-LLMs / Agentic Systems</t>
+          <t>Customer Reliability Engineer, Airflow</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Astronomer</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, PostgreSQL, MongoDB, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, Snowflake, PostgreSQL, dbt, DataOps, Docker</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,32 +4241,32 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92b5658394aee4e3</t>
+          <t>https://www.indeed.com/viewjob?jk=6ac244565083c1d9</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Callaway Golf</t>
+          <t>RapidFire Safety &amp; Security</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Spark, Snowflake, ETL, ELT, Terraform, Kubernetes, Git</t>
+          <t>RDS, Azure, Scala, SQL Server, Data Modeling, Star Schema, Fact Tables, Dimension Tables, ETL, Power BI</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,32 +4276,32 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab2d181891cc2eee</t>
+          <t>https://www.indeed.com/viewjob?jk=8afc73df8ef8f40e</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Salesforce Architect - Senior</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Emed</t>
+          <t>CommunityForce Inc.</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions</t>
+          <t>ECS, RDS, Azure, Scala, Kafka, Data Modeling, ETL, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,32 +4311,32 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e29e1c3d36f0e7c</t>
+          <t>https://www.indeed.com/viewjob?jk=7d236cba8a6e8ae3</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer, Engineering &amp; Ops</t>
+          <t>AI Data Engineer-LLMs / Agentic Systems</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>NBCUniversal</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Snowflake, ELT, dbt, MLOps, Airflow</t>
+          <t>AWS, S3, RDS, Scala, PostgreSQL, MongoDB, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,24 +4346,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df536a2594fa5881</t>
+          <t>https://www.indeed.com/viewjob?jk=92b5658394aee4e3</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Software Engineer - Master</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>TRM Labs</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, ETL, dbt, Power BI, Tableau, CI/CD</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dcb7ea8003fbc5dc</t>
+          <t>https://www.indeed.com/viewjob?jk=3fb1207979169793</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Microsoft Entra</t>
+          <t>Data Engineer - GRC Technology</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,34 +4406,34 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Oracle, Data Modeling, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f61688604ed96074</t>
+          <t>https://www.indeed.com/viewjob?jk=8842e67bf37c518a</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Westchester Medical Center Health Network</t>
+          <t>Callaway Golf</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Valhalla, NY, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,34 +4441,34 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Snowflake, SQL Server, Data Modeling, ELT, Power BI, Tableau, CI/CD</t>
+          <t>AWS, Azure, Databricks, Spark, Snowflake, ETL, ELT, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d807a7856ebe08db</t>
+          <t>https://www.indeed.com/viewjob?jk=ab2d181891cc2eee</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Data Engineer - GRC Technology</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Emed</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,34 +4476,34 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8842e67bf37c518a</t>
+          <t>https://www.indeed.com/viewjob?jk=1e29e1c3d36f0e7c</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer, Enterprise Data &amp; Analytics</t>
+          <t>Sr. Data Engineer, Engineering &amp; Ops</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Rivian</t>
+          <t>NBCUniversal</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,34 +4511,34 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, ECS, Databricks, Data Modeling, ELT, dbt</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Snowflake, ELT, dbt, MLOps, Airflow</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b74ac1e46b3dfa89</t>
+          <t>https://www.indeed.com/viewjob?jk=df536a2594fa5881</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Software Engineer - Master</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>TRM Labs</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, ETL, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fb1207979169793</t>
+          <t>https://www.indeed.com/viewjob?jk=dcb7ea8003fbc5dc</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>.NET Developer</t>
+          <t>Microsoft Entra</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Scala, Snowflake, SQL Server, Power BI, CI/CD, Azure DevOps, Git</t>
+          <t>RDS, Azure, Data Factory, Oracle, Data Modeling, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4afc3e61f8ae8b7b</t>
+          <t>https://www.indeed.com/viewjob?jk=f61688604ed96074</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Westchester Medical Center Health Network</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Valhalla, NY, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,34 +4616,34 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Snowflake, SQL Server, Data Modeling, ELT, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1315e6e62a7714e8</t>
+          <t>https://www.indeed.com/viewjob?jk=d807a7856ebe08db</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Data Platform Engineer - Alteryx Platform Management</t>
+          <t>Sr. Data Engineer, Enterprise Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Truist</t>
+          <t>Rivian</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,34 +4651,34 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, MongoDB, Jenkins, Maven, Jenkins</t>
+          <t>AWS, Glue, EMR, Lambda, S3, ECS, Databricks, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a738d45466c580a9</t>
+          <t>https://www.indeed.com/viewjob?jk=b74ac1e46b3dfa89</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>.NET Developer</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Guidewire Software, Inc.</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>S3, RDS, Azure, Scala, Snowflake, SQL Server, Power BI, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,24 +4696,24 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b5e082bd1857b0f</t>
+          <t>https://www.indeed.com/viewjob?jk=4afc3e61f8ae8b7b</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Data Platform Engineer - Alteryx Platform Management</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Truist</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,34 +4721,34 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, MongoDB, Jenkins, Maven, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bde05d459024e776</t>
+          <t>https://www.indeed.com/viewjob?jk=1315e6e62a7714e8</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Sr. Informatica IDMC MDM Software Engineer</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>RBC</t>
+          <t>Guidewire Software, Inc.</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,24 +4766,24 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5346f4c5e2b5352a</t>
+          <t>https://www.indeed.com/viewjob?jk=3b5e082bd1857b0f</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Informatica IDMC MDM Software Engineer</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>RBC</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,24 +4801,24 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af8d363b230dfbc2</t>
+          <t>https://www.indeed.com/viewjob?jk=5346f4c5e2b5352a</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Attribution Expansion</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>TRM Labs</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Spark, Snowflake, Data Modeling, dbt, MLflow, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Scala, Oracle, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,19 +4836,19 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=539a18aebac4ef5f</t>
+          <t>https://www.indeed.com/viewjob?jk=af8d363b230dfbc2</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Attribution Expansion</t>
+          <t>Data Platform Engineer - Alteryx Platform Management</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>TRM Labs</t>
+          <t>Truist</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -4861,15 +4861,85 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, MongoDB, Jenkins, Maven, Jenkins</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a738d45466c580a9</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer, Attribution Expansion</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>TRM Labs</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
           <t>RDS, BigQuery, Spark, Snowflake, Data Modeling, dbt, MLflow, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=539a18aebac4ef5f</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer, Attribution Expansion</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>TRM Labs</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>RDS, BigQuery, Spark, Snowflake, Data Modeling, dbt, MLflow, CI/CD, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=26436308d22e947d</t>
         </is>

--- a/results/job_matches_2026-03-05.xlsx
+++ b/results/job_matches_2026-03-05.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G129"/>
+  <dimension ref="A1:G97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,17 +643,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer - Consultant</t>
+          <t>Sr. Data Platform Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Real Time Medical Systems</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,34 +661,34 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, IAM, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7167050c109be2d4</t>
+          <t>https://www.indeed.com/viewjob?jk=415686b53cfda723</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer - Consultant</t>
+          <t>Sr. Data Platform Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Real Time Medical Systems</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Columbia, MD, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,34 +696,34 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, IAM, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=862a4a8989448fa0</t>
+          <t>https://www.indeed.com/viewjob?jk=41a92f9802d4f918</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer - Consultant</t>
+          <t>Senior Software Engineer, Cloud Infrastructure</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>ALTRUIST</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,34 +731,34 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark</t>
+          <t>AWS, S3, API Gateway, IAM, RDS, Scala, Kafka, PostgreSQL, DynamoDB, MLOps</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07e542bb4713fad0</t>
+          <t>https://www.indeed.com/viewjob?jk=b2b2e3b90367f3b4</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer - Consultant</t>
+          <t>Senior Software Engineer, Cloud Infrastructure</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>ALTRUIST</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,34 +766,34 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark</t>
+          <t>AWS, S3, API Gateway, IAM, RDS, Scala, Kafka, PostgreSQL, DynamoDB, MLOps</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c88dff775194e30</t>
+          <t>https://www.indeed.com/viewjob?jk=15721c69bc524693</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer - Consultant</t>
+          <t>Sr. Database Administrator - Computing Services</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Carnegie Mellon University</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,182 +801,182 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark</t>
+          <t>AWS, Redshift, S3, IAM, RDS, Azure, GCP, BigQuery, Cloud Storage, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8ced45fe117deb8</t>
+          <t>https://www.indeed.com/viewjob?jk=506f6b3eeea1e8bf</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer - Consultant</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Valvoline Global Operations</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>17.4</v>
+        <v>16</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP, Cloud Storage, Spark, PySpark</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dc8e0c810b3e7cd</t>
+          <t>https://www.indeed.com/viewjob?jk=ab16510fd1c2841d</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer - Consultant</t>
+          <t>Enterprise Data Platform Engineer – Washington, DC</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Creative Information Technology India</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Falls Church, VA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>17.4</v>
+        <v>16</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Delta Live Tables, Photon, Scala, ETL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7791942c877daada</t>
+          <t>https://www.indeed.com/viewjob?jk=0a74e373b48da5fc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer - Consultant</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>17.4</v>
+        <v>15.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6b39b9b56abc0bd</t>
+          <t>https://www.indeed.com/viewjob?jk=9e8500146d476812</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer - Consultant</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>17.4</v>
+        <v>15.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=648774ee33ca3b76</t>
+          <t>https://www.indeed.com/viewjob?jk=2ad2838bd8f61427</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer - Consultant</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>17.4</v>
+        <v>15.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,487 +986,487 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a93ca1ad887e17f0</t>
+          <t>https://www.indeed.com/viewjob?jk=9188fd233f524c42</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer - Consultant</t>
+          <t>Google Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>NMI</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Schaumburg, IL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>17.4</v>
+        <v>15.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Kafka, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d963e90dfb3fa4d6</t>
+          <t>https://www.indeed.com/viewjob?jk=e7cac4b03aa7cfe7</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer - Consultant</t>
+          <t>Google Cloud Data Architect</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Cloudious</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>17.4</v>
+        <v>15.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, HDFS, Hive</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=783ac47e6d62e414</t>
+          <t>https://www.indeed.com/viewjob?jk=73dc517b82db140b</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer - Consultant</t>
+          <t>Senior Specialist - System Management</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Glen Allen, VA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>17.4</v>
+        <v>15.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Unity Catalog, Delta Live Tables, Spark, Databricks Lakehouse, SQL Server</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e511c7108cd6e82d</t>
+          <t>https://www.indeed.com/viewjob?jk=293f842904007fda</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer - Consultant</t>
+          <t>Senior Engineer - DevOps/ DataOps</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>FICO</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>17.4</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, DataOps, MLOps, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a6a2ad30fc1236d</t>
+          <t>https://www.indeed.com/viewjob?jk=e1ed15cfc823b0b7</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer - Consultant</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Alight Solutions</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>17.4</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, GCP, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2d42f6d55a07b48</t>
+          <t>https://www.indeed.com/viewjob?jk=398f35933211332f</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer - Consultant</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>SRS Distribution</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>McKinney, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>17.4</v>
+        <v>13.9</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark</t>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Hadoop, Hive, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c423f392a018bf22</t>
+          <t>https://www.indeed.com/viewjob?jk=4cde050af8749e53</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer - Consultant</t>
+          <t>SQL Developer - Enterprise Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Pantherx Specialty Llc</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>17.4</v>
+        <v>13.9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb49af32ea451f63</t>
+          <t>https://www.indeed.com/viewjob?jk=41d495363374161e</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer - Consultant</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>The Cheesecake Factory</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Calabasas Hills, CA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>17.4</v>
+        <v>13.9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, BigQuery, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e7468c4fe6bdb23</t>
+          <t>https://www.indeed.com/viewjob?jk=bf6f08ab2860bc5c</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer - Consultant</t>
+          <t>Cloud Data Platform Administrator - 26-02191</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>17.4</v>
+        <v>13.9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark</t>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a3485c3c6153843</t>
+          <t>https://www.indeed.com/viewjob?jk=3695a4ce423ac8e5</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer - Consultant</t>
+          <t>Cloud Data Platform Administrator - 26-02191</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Alexandria, VA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>17.4</v>
+        <v>13.9</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark</t>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef4166ba4aa9b5a3</t>
+          <t>https://www.indeed.com/viewjob?jk=67be12c15c92c4c5</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer - Consultant</t>
+          <t>Cloud Data Platform Administrator - 26-02191</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>17.4</v>
+        <v>13.9</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark</t>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91d6e4beb774dd25</t>
+          <t>https://www.indeed.com/viewjob?jk=861fabb5acea2ca4</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer - Consultant</t>
+          <t>Cloud Data Platform Administrator - 26-02191</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>17.4</v>
+        <v>13.9</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark</t>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adcf2824745a050e</t>
+          <t>https://www.indeed.com/viewjob?jk=6235a9d4364b9757</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer - Consultant</t>
+          <t>Specialist Programmer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Infosys</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>17.4</v>
+        <v>13.9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark</t>
+          <t>AWS, Azure, GCP, Hadoop, Hive, Spark, PySpark, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64b296145590b995</t>
+          <t>https://www.indeed.com/viewjob?jk=9772b3b8d4167ecc</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer - Consultant</t>
+          <t>Incremental CRM - Data Developer 1</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Barclays</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Whippany, NJ, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>17.4</v>
+        <v>13.9</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark</t>
+          <t>AWS, Glue, Redshift, Athena, S3, RDS, Databricks, Scala, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,369 +1476,369 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c4169879098b22b</t>
+          <t>https://www.indeed.com/viewjob?jk=3c7931e975a12585</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer - Consultant</t>
+          <t>Software Engineer - Authentication</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Pindrop</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>17.4</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark</t>
+          <t>AWS, Kinesis, S3, RDS, Scala, MySQL, DynamoDB, MLOps, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44e1222f0eb14744</t>
+          <t>https://www.indeed.com/viewjob?jk=6513fcf97bbfd044</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer - Consultant</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>17.4</v>
+        <v>13.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark</t>
+          <t>AWS, Kinesis, IAM, Databricks, Spark, Scala, Kafka, Snowflake, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37bd1a8719f0aafc</t>
+          <t>https://www.indeed.com/viewjob?jk=a021dbda97cc3405</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer - Consultant</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Disney Experiences</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>17.4</v>
+        <v>13.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark</t>
+          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Scala, DynamoDB, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e151b2c0a32e2723</t>
+          <t>https://www.indeed.com/viewjob?jk=0a7ddc3760328a54</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer - Consultant</t>
+          <t>SSO Administrator</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>17.4</v>
+        <v>13.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, PostgreSQL, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c07dcca1b609463e</t>
+          <t>https://www.indeed.com/viewjob?jk=a9064a81c91aa262</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer - Consultant</t>
+          <t>Senior Software Engineer - Commercial Software</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>17.4</v>
+        <v>12.5</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, Oracle, MySQL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c721bd4ca7bdffe1</t>
+          <t>https://www.indeed.com/viewjob?jk=5f3de39cf73c3663</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer - Consultant</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>SRR Consultants</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Piscataway, NJ, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>17.4</v>
+        <v>12.5</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark</t>
+          <t>AWS, Glue, S3, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8e182c6058fd2a4</t>
+          <t>https://www.indeed.com/viewjob?jk=88619a1e983eef30</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer - Consultant</t>
+          <t>Senior Data Engineer, Data Lakehouse Infrastructure</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>TRM Labs</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>17.4</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4997f8f92f05b9d2</t>
+          <t>https://www.indeed.com/viewjob?jk=e899ea40640da235</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer - Consultant</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Halo Creative &amp; Media LLP</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>17.4</v>
+        <v>12.5</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a56481df82d7aa6</t>
+          <t>https://www.indeed.com/viewjob?jk=371d6385735b0f59</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer - Consultant</t>
+          <t>AWS DevOps Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Seqster PDM, Inc</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>17.4</v>
+        <v>12.5</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark</t>
+          <t>AWS, Lambda, S3, IAM, RDS, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb00c80fb9cb9b65</t>
+          <t>https://www.indeed.com/viewjob?jk=191c0857581cffe3</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer - Consultant</t>
+          <t>Java Software Engineer II (US)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>TD Bank</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Mount Laurel, NJ, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>17.4</v>
+        <v>12.5</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark</t>
+          <t>RDS, Azure, Scala, NoSQL, Splunk, Jenkins, Maven, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fd1863254c88e5d</t>
+          <t>https://www.indeed.com/viewjob?jk=8ee89e940b02cc06</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Sr. Data Platform Engineer</t>
+          <t>Senior Software Engineer II - AI/ML</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Real Time Medical Systems</t>
+          <t>Seismic</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1847,151 +1847,151 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>17.4</v>
+        <v>12.5</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, IAM, RDS, Spark, PySpark</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=415686b53cfda723</t>
+          <t>https://www.indeed.com/viewjob?jk=5d0bc9a390582054</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Sr. Data Platform Engineer</t>
+          <t>Senior Software Engineer, Back End (Java, Go, AWS)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Real Time Medical Systems</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Columbia, MD, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>17.4</v>
+        <v>11.8</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, IAM, RDS, Spark, PySpark</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41a92f9802d4f918</t>
+          <t>https://www.indeed.com/viewjob?jk=e716b4195b2da30b</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Cloud Infrastructure</t>
+          <t>Senior Software Engineer, Back End (Java, Go, AWS)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>ALTRUIST</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>17.4</v>
+        <v>11.8</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, IAM, RDS, Scala, Kafka, PostgreSQL, DynamoDB, MLOps</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2b2e3b90367f3b4</t>
+          <t>https://www.indeed.com/viewjob?jk=e1b9bbef981d9232</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Cloud Infrastructure</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>ALTRUIST</t>
+          <t>Daniels Health</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>17.4</v>
+        <v>11.8</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, IAM, RDS, Scala, Kafka, PostgreSQL, DynamoDB, MLOps</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15721c69bc524693</t>
+          <t>https://www.indeed.com/viewjob?jk=3486f1249174e37a</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Sr. Database Administrator - Computing Services</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Carnegie Mellon University</t>
+          <t>Daniels Health</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>17.4</v>
+        <v>11.8</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, IAM, RDS, Azure, GCP, BigQuery, Cloud Storage, Scala</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,67 +2001,67 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=506f6b3eeea1e8bf</t>
+          <t>https://www.indeed.com/viewjob?jk=1df7caac86af2291</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>ATC - AI &amp; Data Analyst - NAELFY26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Valvoline Global Operations</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Saint Petersburg, FL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>16</v>
+        <v>11.8</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP, Cloud Storage, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab16510fd1c2841d</t>
+          <t>https://www.indeed.com/viewjob?jk=1ce7a50a4bbe9ef2</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Enterprise Data Platform Engineer – Washington, DC</t>
+          <t>Senior Data Engineer, Data Product</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Creative Information Technology India</t>
+          <t>TRM Labs</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Falls Church, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>16</v>
+        <v>11.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Delta Live Tables, Photon, Scala, ETL</t>
+          <t>RDS, BigQuery, Dataflow, Spark, Scala, Kafka, dbt, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a74e373b48da5fc</t>
+          <t>https://www.indeed.com/viewjob?jk=351b720407fa6f6d</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Analytics, Full-Stack Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>SCAN Health Plan</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>15.3</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,102 +2106,102 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e8500146d476812</t>
+          <t>https://www.indeed.com/viewjob?jk=c24274a4aa989f95</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Waters</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Milford, MA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>15.3</v>
+        <v>11.8</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ad2838bd8f61427</t>
+          <t>https://www.indeed.com/viewjob?jk=1975adb5bfc7de33</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Application Developer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Munich Re</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Amelia, OH, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>15.3</v>
+        <v>11.8</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9188fd233f524c42</t>
+          <t>https://www.indeed.com/viewjob?jk=1c8f07e938168692</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Google Cloud Data Engineer</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>NMI</t>
+          <t>Weyerhaeuser</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Schaumburg, IL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>15.3</v>
+        <v>11.8</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Kafka, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, MLOps, MLflow, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7cac4b03aa7cfe7</t>
+          <t>https://www.indeed.com/viewjob?jk=7d9f82346c5ff2d3</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Google Cloud Data Architect</t>
+          <t>Senior Software Engineer - MDM / RDM &amp; API Development</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Cloudious</t>
+          <t>Prudential</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>15.3</v>
+        <v>11.8</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, HDFS, Hive</t>
+          <t>AWS, Kinesis, SQS, RDS, Spark, Scala, MySQL, NoSQL, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73dc517b82db140b</t>
+          <t>https://www.indeed.com/viewjob?jk=d75a6cef6409e12b</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Specialist - System Management</t>
+          <t>Software Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Nightwing</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Glen Allen, VA, US USA</t>
+          <t>Clarksville, TN, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>15.3</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Unity Catalog, Delta Live Tables, Spark, Databricks Lakehouse, SQL Server</t>
+          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=293f842904007fda</t>
+          <t>https://www.indeed.com/viewjob?jk=887221a715d1ff03</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Engineer - DevOps/ DataOps</t>
+          <t>Software Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>FICO</t>
+          <t>Nightwing</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>14.6</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, DataOps, MLOps, CI/CD, Jenkins</t>
+          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1ed15cfc823b0b7</t>
+          <t>https://www.indeed.com/viewjob?jk=3322d87953168bdc</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>Advanced Metering Infrastructure (AMI) Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Alight Solutions</t>
+          <t>WSSC Water</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Laurel, MD, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>14.6</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, GCP, Scala, CI/CD</t>
+          <t>RDS, Azure, Scala, Kafka, Oracle, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=398f35933211332f</t>
+          <t>https://www.indeed.com/viewjob?jk=c5b2aa36ee050b9b</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Software Systems Engineer, Release Reliability &amp; Automation (Autonomous Vehicles)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>SRS Distribution</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>McKinney, TX, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>13.9</v>
+        <v>11.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Hadoop, Hive, Spark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, Power BI, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cde050af8749e53</t>
+          <t>https://www.indeed.com/viewjob?jk=864266ab5f8e3aac</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>SQL Developer - Enterprise Data &amp; Analytics</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Pantherx Specialty Llc</t>
+          <t>Amplify</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>13.9</v>
+        <v>11.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, S3, RDS, Snowflake, DynamoDB, Data Modeling, Kimball, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41d495363374161e</t>
+          <t>https://www.indeed.com/viewjob?jk=b4d16d721d2057f3</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer III - Java/Spark/AWS</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>The Cheesecake Factory</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Calabasas Hills, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>13.9</v>
+        <v>11.8</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, BigQuery, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, EMR, Lambda, S3, ECS, RDS, Databricks, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf6f08ab2860bc5c</t>
+          <t>https://www.indeed.com/viewjob?jk=c95674c932d41fb6</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Cloud Data Platform Administrator - 26-02191</t>
+          <t>Software Engineer (Junior)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>TORCH.AI</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Leawood, KS, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>13.9</v>
+        <v>11.8</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
+          <t>AWS, IAM, Azure, GCP, Kafka, PostgreSQL, MongoDB, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3695a4ce423ac8e5</t>
+          <t>https://www.indeed.com/viewjob?jk=28e432d03da8db08</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Cloud Data Platform Administrator - 26-02191</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Alexandria, VA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>13.9</v>
+        <v>11.8</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67be12c15c92c4c5</t>
+          <t>https://www.indeed.com/viewjob?jk=a8b55e090bbab627</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Cloud Data Platform Administrator - 26-02191</t>
+          <t>Tableau Developer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Michael Kors</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>East Rutherford, NJ, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>13.9</v>
+        <v>11.8</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
+          <t>AWS, Glue, Redshift, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,67 +2561,67 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=861fabb5acea2ca4</t>
+          <t>https://www.indeed.com/viewjob?jk=904e084e965a45c4</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Cloud Data Platform Administrator - 26-02191</t>
+          <t>Database Administrator</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Rogue Community College</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>13.9</v>
+        <v>11.8</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, Power BI</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6235a9d4364b9757</t>
+          <t>https://www.indeed.com/viewjob?jk=7f9335cc41b5edf2</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Specialist Programmer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Infosys</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>13.9</v>
+        <v>11.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, Hive, Spark, PySpark, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, RDS, Spark, PySpark, Scala, MySQL, MongoDB, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,67 +2631,67 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9772b3b8d4167ecc</t>
+          <t>https://www.indeed.com/viewjob?jk=dd1518c4c02c12ef</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Incremental CRM - Data Developer 1</t>
+          <t>Senior Software Engineer, Back End (Python)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Barclays</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Whippany, NJ, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>13.9</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, RDS, Databricks, Scala, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c7931e975a12585</t>
+          <t>https://www.indeed.com/viewjob?jk=3864c05dc9b353f8</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Data Engineer 2</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>BLOC Resources, LLC</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>13.2</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, IAM, Databricks, Spark, Scala, Kafka, Snowflake, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a021dbda97cc3405</t>
+          <t>https://www.indeed.com/viewjob?jk=c51290628ce41b82</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Sr. Software Engineer I, Applied AI</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Disney Experiences</t>
+          <t>Axon</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>13.2</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Scala, DynamoDB, NoSQL, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a7ddc3760328a54</t>
+          <t>https://www.indeed.com/viewjob?jk=e858c83fc09cd77d</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>SSO Administrator</t>
+          <t>Senior Software Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>TRM Labs</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>13.2</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, PostgreSQL, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>RDS, BigQuery, Spark, Scala, Kafka, ETL, dbt, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9064a81c91aa262</t>
+          <t>https://www.indeed.com/viewjob?jk=8a517be0e10b2a44</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Commercial Software</t>
+          <t>Senior Data Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>TRM Labs</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, Oracle, MySQL</t>
+          <t>RDS, BigQuery, Spark, Scala, Kafka, ETL, dbt, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,67 +2806,67 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f3de39cf73c3663</t>
+          <t>https://www.indeed.com/viewjob?jk=60f6c2aecd2d1bdf</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AWS Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>SRR Consultants</t>
+          <t>Appex Innovation</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Piscataway, NJ, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, Glue, Lambda, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88619a1e983eef30</t>
+          <t>https://www.indeed.com/viewjob?jk=7f3534222ab81e17</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Data Lakehouse Infrastructure</t>
+          <t>AWS Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>TRM Labs</t>
+          <t>Appex Innovation</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,32 +2876,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e899ea40640da235</t>
+          <t>https://www.indeed.com/viewjob?jk=3886cb86a753634c</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>AWS DevOps Engineer</t>
+          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Seqster PDM, Inc</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,32 +2911,32 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=191c0857581cffe3</t>
+          <t>https://www.indeed.com/viewjob?jk=f9637232a826c3ad</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Java Software Engineer II (US)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>TD Bank</t>
+          <t>CNH Industrial</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Mount Laurel, NJ, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, NoSQL, Splunk, Jenkins, Maven, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,137 +2946,137 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ee89e940b02cc06</t>
+          <t>https://www.indeed.com/viewjob?jk=e5b3837921976566</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II - AI/ML</t>
+          <t>Senior Data Engineer - Microsoft Fabric</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Seismic</t>
+          <t>EoS Fitness</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ELT, Power BI</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d0bc9a390582054</t>
+          <t>https://www.indeed.com/viewjob?jk=7bd7f3590528db3c</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End (Java, Go, AWS)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>PGA TOUR Superstore</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Roswell, GA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Docker</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e716b4195b2da30b</t>
+          <t>https://www.indeed.com/viewjob?jk=73bdb2d180484ce2</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End (Java, Go, AWS)</t>
+          <t>Sr. Software Engineer, Data, Autonomy</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Rivian</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Docker</t>
+          <t>AWS, Lambda, S3, IAM, Databricks, Unity Catalog, Spark, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1b9bbef981d9232</t>
+          <t>https://www.indeed.com/viewjob?jk=6a3560765ed8e488</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>AI Applications Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Daniels Health</t>
+          <t>Stanford University</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Vertex AI, Scala, Oracle, NoSQL, Data Modeling, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1df7caac86af2291</t>
+          <t>https://www.indeed.com/viewjob?jk=d0dc1867fdcc5324</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>ATC - AI &amp; Data Analyst - NAELFY26</t>
+          <t>Customer Reliability Engineer, Airflow</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>Astronomer</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Saint Petersburg, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, Snowflake, PostgreSQL, dbt, DataOps, Docker</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,32 +3121,32 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ce7a50a4bbe9ef2</t>
+          <t>https://www.indeed.com/viewjob?jk=6ac244565083c1d9</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Data Product</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>TRM Labs</t>
+          <t>RapidFire Safety &amp; Security</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Dataflow, Spark, Scala, Kafka, dbt, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, SQL Server, Data Modeling, Star Schema, Fact Tables, Dimension Tables, ETL, Power BI</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,32 +3156,32 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=351b720407fa6f6d</t>
+          <t>https://www.indeed.com/viewjob?jk=8afc73df8ef8f40e</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Analytics, Full-Stack Engineer</t>
+          <t>Salesforce Architect - Senior</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>SCAN Health Plan</t>
+          <t>CommunityForce Inc.</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Snowflake, ETL, ELT, dbt</t>
+          <t>ECS, RDS, Azure, Scala, Kafka, Data Modeling, ETL, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,67 +3191,67 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c24274a4aa989f95</t>
+          <t>https://www.indeed.com/viewjob?jk=7d236cba8a6e8ae3</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>AI Data Engineer-LLMs / Agentic Systems</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Waters</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Milford, MA, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, S3, RDS, Scala, PostgreSQL, MongoDB, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1975adb5bfc7de33</t>
+          <t>https://www.indeed.com/viewjob?jk=92b5658394aee4e3</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Application Developer</t>
+          <t>Software Engineer - Master</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Munich Re</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Amelia, OH, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,67 +3261,67 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c8f07e938168692</t>
+          <t>https://www.indeed.com/viewjob?jk=3fb1207979169793</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Data Engineer - GRC Technology</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Weyerhaeuser</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, MLOps, MLflow, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d9f82346c5ff2d3</t>
+          <t>https://www.indeed.com/viewjob?jk=8842e67bf37c518a</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - MDM / RDM &amp; API Development</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Prudential</t>
+          <t>Callaway Golf</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Spark, Scala, MySQL, NoSQL, Jenkins, Jenkins</t>
+          <t>AWS, Azure, Databricks, Spark, Snowflake, ETL, ELT, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,32 +3331,32 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d75a6cef6409e12b</t>
+          <t>https://www.indeed.com/viewjob?jk=ab2d181891cc2eee</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Software Engineer (Hybrid)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Nightwing</t>
+          <t>Emed</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Clarksville, TN, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,32 +3366,32 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=887221a715d1ff03</t>
+          <t>https://www.indeed.com/viewjob?jk=1e29e1c3d36f0e7c</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Software Engineer (Hybrid)</t>
+          <t>Sr. Data Engineer, Engineering &amp; Ops</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Nightwing</t>
+          <t>NBCUniversal</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Sterling, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Snowflake, ELT, dbt, MLOps, Airflow</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,32 +3401,32 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3322d87953168bdc</t>
+          <t>https://www.indeed.com/viewjob?jk=df536a2594fa5881</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Advanced Metering Infrastructure (AMI) Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>WSSC Water</t>
+          <t>TRM Labs</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Laurel, MD, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Oracle, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, ETL, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,32 +3436,32 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5b2aa36ee050b9b</t>
+          <t>https://www.indeed.com/viewjob?jk=dcb7ea8003fbc5dc</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Software Systems Engineer, Release Reliability &amp; Automation (Autonomous Vehicles)</t>
+          <t>Microsoft Entra</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, Power BI, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Oracle, Data Modeling, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=864266ab5f8e3aac</t>
+          <t>https://www.indeed.com/viewjob?jk=f61688604ed96074</t>
         </is>
       </c>
     </row>
@@ -3483,90 +3483,90 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Amplify</t>
+          <t>Westchester Medical Center Health Network</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Valhalla, NY, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Snowflake, DynamoDB, Data Modeling, Kimball, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Snowflake, SQL Server, Data Modeling, ELT, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4d16d721d2057f3</t>
+          <t>https://www.indeed.com/viewjob?jk=d807a7856ebe08db</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Software Engineer (Junior)</t>
+          <t>Sr. Data Engineer, Enterprise Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>TORCH.AI</t>
+          <t>Rivian</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Leawood, KS, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Kafka, PostgreSQL, MongoDB, NoSQL, ETL, CI/CD</t>
+          <t>AWS, Glue, EMR, Lambda, S3, ECS, Databricks, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28e432d03da8db08</t>
+          <t>https://www.indeed.com/viewjob?jk=b74ac1e46b3dfa89</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>.NET Developer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>S3, RDS, Azure, Scala, Snowflake, SQL Server, Power BI, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,67 +3576,67 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8b55e090bbab627</t>
+          <t>https://www.indeed.com/viewjob?jk=4afc3e61f8ae8b7b</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Software Engineer III - Java/Spark/AWS</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, ECS, RDS, Databricks, Spark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c95674c932d41fb6</t>
+          <t>https://www.indeed.com/viewjob?jk=1315e6e62a7714e8</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Tableau Developer</t>
+          <t>Data Platform Engineer - Alteryx Platform Management</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Michael Kors</t>
+          <t>Truist</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>East Rutherford, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, MongoDB, Jenkins, Maven, Jenkins</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,67 +3646,67 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=904e084e965a45c4</t>
+          <t>https://www.indeed.com/viewjob?jk=a738d45466c580a9</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Database Administrator</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Rogue Community College</t>
+          <t>Guidewire Software, Inc.</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f9335cc41b5edf2</t>
+          <t>https://www.indeed.com/viewjob?jk=3b5e082bd1857b0f</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End (Python)</t>
+          <t>Sr. Informatica IDMC MDM Software Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>RBC</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,32 +3716,32 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3864c05dc9b353f8</t>
+          <t>https://www.indeed.com/viewjob?jk=5346f4c5e2b5352a</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Data Engineer 2</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>BLOC Resources, LLC</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Data Modeling, CI/CD</t>
+          <t>AWS, RDS, Scala, Oracle, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,32 +3751,32 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c51290628ce41b82</t>
+          <t>https://www.indeed.com/viewjob?jk=af8d363b230dfbc2</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer I, Applied AI</t>
+          <t>Senior Data Engineer, Attribution Expansion</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Axon</t>
+          <t>TRM Labs</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>RDS, BigQuery, Spark, Snowflake, Data Modeling, dbt, MLflow, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,14 +3786,14 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e858c83fc09cd77d</t>
+          <t>https://www.indeed.com/viewjob?jk=539a18aebac4ef5f</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Platform</t>
+          <t>Senior Data Engineer, Attribution Expansion</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -3807,11 +3807,11 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Spark, Scala, Kafka, ETL, dbt, Terraform, Docker, Kubernetes</t>
+          <t>RDS, BigQuery, Spark, Snowflake, Data Modeling, dbt, MLflow, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3820,1126 +3820,6 @@
         </is>
       </c>
       <c r="G97" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8a517be0e10b2a44</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer, Data Platform</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>TRM Labs</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D98" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>RDS, BigQuery, Spark, Scala, Kafka, ETL, dbt, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=60f6c2aecd2d1bdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Sr. Data Engineer</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>Adobe</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D99" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Spark, PySpark, Scala, MySQL, MongoDB, Docker, Kubernetes, Airflow</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dd1518c4c02c12ef</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>AWS Data Engineer</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>Appex Innovation</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Fort Mill, SC, US USA</t>
-        </is>
-      </c>
-      <c r="D100" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Lambda, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7f3534222ab81e17</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>AWS Data Engineer</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>Appex Innovation</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Fort Mill, SC, US USA</t>
-        </is>
-      </c>
-      <c r="D101" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Lambda, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3886cb86a753634c</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>NTT DATA</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D102" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f9637232a826c3ad</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>CNH Industrial</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>Oak Brook, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D103" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e5b3837921976566</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer - Microsoft Fabric</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>EoS Fitness</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D104" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ELT, Power BI</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7bd7f3590528db3c</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>PGA TOUR Superstore</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>Roswell, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D105" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=73bdb2d180484ce2</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>Azure Data Engineer</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>Gilbert, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D106" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Data Modeling, Dimensional Modeling, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=110f275787ec7bdb</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>Sr. Software Engineer, Data, Autonomy</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>Rivian</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D107" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, IAM, Databricks, Unity Catalog, Spark, Scala, DynamoDB, CI/CD</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>2026-01-31</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6a3560765ed8e488</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>AI Applications Engineer</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>Stanford University</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>Redwood City, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D108" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Vertex AI, Scala, Oracle, NoSQL, Data Modeling, MLOps, MLflow</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d0dc1867fdcc5324</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>Customer Reliability Engineer, Airflow</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>Astronomer</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D109" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, Snowflake, PostgreSQL, dbt, DataOps, Docker</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6ac244565083c1d9</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>Power BI Developer</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>RapidFire Safety &amp; Security</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>St. Louis, MO, US USA</t>
-        </is>
-      </c>
-      <c r="D110" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, SQL Server, Data Modeling, Star Schema, Fact Tables, Dimension Tables, ETL, Power BI</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8afc73df8ef8f40e</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>Salesforce Architect - Senior</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>CommunityForce Inc.</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>Ashburn, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D111" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>ECS, RDS, Azure, Scala, Kafka, Data Modeling, ETL, CI/CD, Jenkins, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7d236cba8a6e8ae3</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>AI Data Engineer-LLMs / Agentic Systems</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>Pfizer</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>Cambridge, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D112" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Scala, PostgreSQL, MongoDB, CI/CD, Jenkins, GitHub Actions, Docker</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=92b5658394aee4e3</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>Software Engineer - Master</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>Equifax</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>Alpharetta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D113" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3fb1207979169793</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>Data Engineer - GRC Technology</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>American Express</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D114" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>AWS, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>2026-02-26</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8842e67bf37c518a</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>Sr Data Engineer</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>Callaway Golf</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>Carlsbad, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D115" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Databricks, Spark, Snowflake, ETL, ELT, Terraform, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ab2d181891cc2eee</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>Emed</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>Miami, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D116" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1e29e1c3d36f0e7c</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>Sr. Data Engineer, Engineering &amp; Ops</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>NBCUniversal</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D117" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Snowflake, ELT, dbt, MLOps, Airflow</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=df536a2594fa5881</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>Senior Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>TRM Labs</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D118" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, ETL, dbt, Power BI, Tableau, CI/CD</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dcb7ea8003fbc5dc</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>Microsoft Entra</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D119" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Oracle, Data Modeling, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f61688604ed96074</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>Westchester Medical Center Health Network</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>Valhalla, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D120" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Snowflake, SQL Server, Data Modeling, ELT, Power BI, Tableau, CI/CD</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d807a7856ebe08db</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>Sr. Data Engineer, Enterprise Data &amp; Analytics</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>Rivian</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D121" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>AWS, Glue, EMR, Lambda, S3, ECS, Databricks, Data Modeling, ELT, dbt</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>2025-11-21</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b74ac1e46b3dfa89</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>.NET Developer</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>Caterpillar</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>Cary, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D122" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>S3, RDS, Azure, Scala, Snowflake, SQL Server, Power BI, CI/CD, Azure DevOps, Git</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4afc3e61f8ae8b7b</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D123" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1315e6e62a7714e8</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>Senior Full Stack Engineer</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>Guidewire Software, Inc.</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>San Mateo, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D124" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, MySQL, MongoDB, NoSQL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3b5e082bd1857b0f</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>Sr. Informatica IDMC MDM Software Engineer</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>RBC</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>Minneapolis, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D125" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, ETL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5346f4c5e2b5352a</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>LTIMindtree</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>Tampa, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D126" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Oracle, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=af8d363b230dfbc2</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>Data Platform Engineer - Alteryx Platform Management</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>Truist</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D127" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, MongoDB, Jenkins, Maven, Jenkins</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a738d45466c580a9</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer, Attribution Expansion</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>TRM Labs</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D128" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>RDS, BigQuery, Spark, Snowflake, Data Modeling, dbt, MLflow, CI/CD, Terraform, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=539a18aebac4ef5f</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer, Attribution Expansion</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>TRM Labs</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D129" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>RDS, BigQuery, Spark, Snowflake, Data Modeling, dbt, MLflow, CI/CD, Terraform, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=26436308d22e947d</t>
         </is>

--- a/results/job_matches_2026-03-05.xlsx
+++ b/results/job_matches_2026-03-05.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G97"/>
+  <dimension ref="A1:G102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1413,17 +1413,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Specialist Programmer</t>
+          <t>Sr. Software Engineer (Remote)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Infosys</t>
+          <t>Inspira Financial</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, Hive, Spark, PySpark, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, Azure Cosmos DB, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9772b3b8d4167ecc</t>
+          <t>https://www.indeed.com/viewjob?jk=1733261c550fa238</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Incremental CRM - Data Developer 1</t>
+          <t>Sr. Software Engineer (Remote)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Barclays</t>
+          <t>Inspira Financial</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Whippany, NJ, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,77 +1466,77 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, RDS, Databricks, Scala, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, Azure Cosmos DB, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c7931e975a12585</t>
+          <t>https://www.indeed.com/viewjob?jk=5d0e899d198425eb</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Software Engineer - Authentication</t>
+          <t>Incremental CRM - Data Developer 1</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Pindrop</t>
+          <t>Barclays</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Whippany, NJ, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, RDS, Scala, MySQL, DynamoDB, MLOps, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Redshift, Athena, S3, RDS, Databricks, Scala, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6513fcf97bbfd044</t>
+          <t>https://www.indeed.com/viewjob?jk=3c7931e975a12585</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Specialist Programmer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Infosys</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, IAM, Databricks, Spark, Scala, Kafka, Snowflake, NoSQL, CI/CD</t>
+          <t>AWS, Azure, GCP, Hadoop, Hive, Spark, PySpark, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a021dbda97cc3405</t>
+          <t>https://www.indeed.com/viewjob?jk=9772b3b8d4167ecc</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Software Engineer - Authentication</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Disney Experiences</t>
+          <t>Pindrop</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Scala, DynamoDB, NoSQL, ETL</t>
+          <t>AWS, Kinesis, S3, RDS, Scala, MySQL, DynamoDB, MLOps, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a7ddc3760328a54</t>
+          <t>https://www.indeed.com/viewjob?jk=6513fcf97bbfd044</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SSO Administrator</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, PostgreSQL, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, Kinesis, IAM, Databricks, Spark, Scala, Kafka, Snowflake, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9064a81c91aa262</t>
+          <t>https://www.indeed.com/viewjob?jk=a021dbda97cc3405</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Commercial Software</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Disney Experiences</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, Oracle, MySQL</t>
+          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Scala, DynamoDB, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f3de39cf73c3663</t>
+          <t>https://www.indeed.com/viewjob?jk=0a7ddc3760328a54</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>SSO Administrator</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>SRR Consultants</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Piscataway, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, PostgreSQL, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88619a1e983eef30</t>
+          <t>https://www.indeed.com/viewjob?jk=a9064a81c91aa262</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Data Lakehouse Infrastructure</t>
+          <t>Senior Software Engineer - Commercial Software</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>TRM Labs</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, Oracle, MySQL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e899ea40640da235</t>
+          <t>https://www.indeed.com/viewjob?jk=5f3de39cf73c3663</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Halo Creative &amp; Media LLP</t>
+          <t>SRR Consultants</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Piscataway, NJ, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, Glue, S3, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=371d6385735b0f59</t>
+          <t>https://www.indeed.com/viewjob?jk=88619a1e983eef30</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>AWS DevOps Engineer</t>
+          <t>Senior Data Engineer, Data Lakehouse Infrastructure</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Seqster PDM, Inc</t>
+          <t>TRM Labs</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=191c0857581cffe3</t>
+          <t>https://www.indeed.com/viewjob?jk=e899ea40640da235</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Java Software Engineer II (US)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>TD Bank</t>
+          <t>Halo Creative &amp; Media LLP</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Mount Laurel, NJ, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, NoSQL, Splunk, Jenkins, Maven, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ee89e940b02cc06</t>
+          <t>https://www.indeed.com/viewjob?jk=371d6385735b0f59</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II - AI/ML</t>
+          <t>AWS DevOps Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Seismic</t>
+          <t>Seqster PDM, Inc</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,77 +1851,77 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, IAM, RDS, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d0bc9a390582054</t>
+          <t>https://www.indeed.com/viewjob?jk=191c0857581cffe3</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End (Java, Go, AWS)</t>
+          <t>Java Software Engineer II (US)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>TD Bank</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Mount Laurel, NJ, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Docker</t>
+          <t>RDS, Azure, Scala, NoSQL, Splunk, Jenkins, Maven, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e716b4195b2da30b</t>
+          <t>https://www.indeed.com/viewjob?jk=8ee89e940b02cc06</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End (Java, Go, AWS)</t>
+          <t>Senior Software Engineer II - AI/ML</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Seismic</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Docker</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1b9bbef981d9232</t>
+          <t>https://www.indeed.com/viewjob?jk=5d0bc9a390582054</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Software Engineer, Back End (Java, Go, AWS)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Daniels Health</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3486f1249174e37a</t>
+          <t>https://www.indeed.com/viewjob?jk=e716b4195b2da30b</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Software Engineer, Back End (Java, Go, AWS)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Daniels Health</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1df7caac86af2291</t>
+          <t>https://www.indeed.com/viewjob?jk=e1b9bbef981d9232</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ATC - AI &amp; Data Analyst - NAELFY26</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>Daniels Health</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Saint Petersburg, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ce7a50a4bbe9ef2</t>
+          <t>https://www.indeed.com/viewjob?jk=3486f1249174e37a</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Data Product</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>TRM Labs</t>
+          <t>Daniels Health</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Dataflow, Spark, Scala, Kafka, dbt, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=351b720407fa6f6d</t>
+          <t>https://www.indeed.com/viewjob?jk=1df7caac86af2291</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Analytics, Full-Stack Engineer</t>
+          <t>ATC - AI &amp; Data Analyst - NAELFY26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>SCAN Health Plan</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>Saint Petersburg, FL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Snowflake, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c24274a4aa989f95</t>
+          <t>https://www.indeed.com/viewjob?jk=1ce7a50a4bbe9ef2</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Data Engineer, Data Product</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Waters</t>
+          <t>TRM Labs</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Milford, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
+          <t>RDS, BigQuery, Dataflow, Spark, Scala, Kafka, dbt, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1975adb5bfc7de33</t>
+          <t>https://www.indeed.com/viewjob?jk=351b720407fa6f6d</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Application Developer</t>
+          <t>Analytics, Full-Stack Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Munich Re</t>
+          <t>SCAN Health Plan</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Amelia, OH, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c8f07e938168692</t>
+          <t>https://www.indeed.com/viewjob?jk=c24274a4aa989f95</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Weyerhaeuser</t>
+          <t>Waters</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Milford, MA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, MLOps, MLflow, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d9f82346c5ff2d3</t>
+          <t>https://www.indeed.com/viewjob?jk=1975adb5bfc7de33</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - MDM / RDM &amp; API Development</t>
+          <t>Application Developer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Prudential</t>
+          <t>Munich Re</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>Amelia, OH, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Spark, Scala, MySQL, NoSQL, Jenkins, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d75a6cef6409e12b</t>
+          <t>https://www.indeed.com/viewjob?jk=1c8f07e938168692</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Software Engineer (Hybrid)</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Nightwing</t>
+          <t>Weyerhaeuser</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Clarksville, TN, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, MLOps, MLflow, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=887221a715d1ff03</t>
+          <t>https://www.indeed.com/viewjob?jk=7d9f82346c5ff2d3</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Software Engineer (Hybrid)</t>
+          <t>Senior Software Engineer - MDM / RDM &amp; API Development</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Nightwing</t>
+          <t>Prudential</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Sterling, VA, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, Kinesis, SQS, RDS, Spark, Scala, MySQL, NoSQL, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3322d87953168bdc</t>
+          <t>https://www.indeed.com/viewjob?jk=d75a6cef6409e12b</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Advanced Metering Infrastructure (AMI) Engineer</t>
+          <t>Software Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>WSSC Water</t>
+          <t>Nightwing</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Laurel, MD, US USA</t>
+          <t>Clarksville, TN, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Oracle, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps</t>
+          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5b2aa36ee050b9b</t>
+          <t>https://www.indeed.com/viewjob?jk=887221a715d1ff03</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Software Systems Engineer, Release Reliability &amp; Automation (Autonomous Vehicles)</t>
+          <t>Software Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Nightwing</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, Power BI, CI/CD, Jenkins</t>
+          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=864266ab5f8e3aac</t>
+          <t>https://www.indeed.com/viewjob?jk=3322d87953168bdc</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Advanced Metering Infrastructure (AMI) Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Amplify</t>
+          <t>WSSC Water</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Laurel, MD, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Snowflake, DynamoDB, Data Modeling, Kimball, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Scala, Kafka, Oracle, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4d16d721d2057f3</t>
+          <t>https://www.indeed.com/viewjob?jk=c5b2aa36ee050b9b</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Software Engineer III - Java/Spark/AWS</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Amplify</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, ECS, RDS, Databricks, Spark, Scala, Snowflake</t>
+          <t>AWS, S3, RDS, Snowflake, DynamoDB, Data Modeling, Kimball, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c95674c932d41fb6</t>
+          <t>https://www.indeed.com/viewjob?jk=b4d16d721d2057f3</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Software Engineer (Junior)</t>
+          <t>Software Engineer III - Java/Spark/AWS</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>TORCH.AI</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Leawood, KS, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Kafka, PostgreSQL, MongoDB, NoSQL, ETL, CI/CD</t>
+          <t>AWS, EMR, Lambda, S3, ECS, RDS, Databricks, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28e432d03da8db08</t>
+          <t>https://www.indeed.com/viewjob?jk=c95674c932d41fb6</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Software Systems Engineer, Release Reliability &amp; Automation (Autonomous Vehicles)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, Power BI, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8b55e090bbab627</t>
+          <t>https://www.indeed.com/viewjob?jk=864266ab5f8e3aac</t>
         </is>
       </c>
     </row>
@@ -2603,25 +2603,25 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Software Engineer (Junior)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>TORCH.AI</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Leawood, KS, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, PySpark, Scala, MySQL, MongoDB, Docker, Kubernetes, Airflow</t>
+          <t>AWS, IAM, Azure, GCP, Kafka, PostgreSQL, MongoDB, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd1518c4c02c12ef</t>
+          <t>https://www.indeed.com/viewjob?jk=28e432d03da8db08</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End (Python)</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3864c05dc9b353f8</t>
+          <t>https://www.indeed.com/viewjob?jk=a8b55e090bbab627</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Engineer 2</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>BLOC Resources, LLC</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Data Modeling, CI/CD</t>
+          <t>AWS, RDS, Spark, PySpark, Scala, MySQL, MongoDB, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c51290628ce41b82</t>
+          <t>https://www.indeed.com/viewjob?jk=dd1518c4c02c12ef</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer I, Applied AI</t>
+          <t>Senior Software Engineer, Back End (Python)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Axon</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e858c83fc09cd77d</t>
+          <t>https://www.indeed.com/viewjob?jk=3864c05dc9b353f8</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Platform</t>
+          <t>Data Engineer 2</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>TRM Labs</t>
+          <t>BLOC Resources, LLC</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Spark, Scala, Kafka, ETL, dbt, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a517be0e10b2a44</t>
+          <t>https://www.indeed.com/viewjob?jk=c51290628ce41b82</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Data Platform</t>
+          <t>Sr. Software Engineer I, Applied AI</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>TRM Labs</t>
+          <t>Axon</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Spark, Scala, Kafka, ETL, dbt, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60f6c2aecd2d1bdf</t>
+          <t>https://www.indeed.com/viewjob?jk=e858c83fc09cd77d</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>AWS Data Engineer</t>
+          <t>Senior Software Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Appex Innovation</t>
+          <t>TRM Labs</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD</t>
+          <t>RDS, BigQuery, Spark, Scala, Kafka, ETL, dbt, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f3534222ab81e17</t>
+          <t>https://www.indeed.com/viewjob?jk=8a517be0e10b2a44</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>AWS Data Engineer</t>
+          <t>Senior Data Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Appex Innovation</t>
+          <t>TRM Labs</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD</t>
+          <t>RDS, BigQuery, Spark, Scala, Kafka, ETL, dbt, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3886cb86a753634c</t>
+          <t>https://www.indeed.com/viewjob?jk=60f6c2aecd2d1bdf</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2906,29 +2906,29 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9637232a826c3ad</t>
+          <t>https://www.indeed.com/viewjob?jk=f85f1e8c0778adba</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>CNH Industrial</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5b3837921976566</t>
+          <t>https://www.indeed.com/viewjob?jk=3e2da1f14c27a331</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Microsoft Fabric</t>
+          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>EoS Fitness</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ELT, Power BI</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bd7f3590528db3c</t>
+          <t>https://www.indeed.com/viewjob?jk=140d02e1f58501f6</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>PGA TOUR Superstore</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Roswell, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73bdb2d180484ce2</t>
+          <t>https://www.indeed.com/viewjob?jk=eff547fec829449a</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Data, Autonomy</t>
+          <t>AWS Data Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Rivian</t>
+          <t>Appex Innovation</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, Databricks, Unity Catalog, Spark, Scala, DynamoDB, CI/CD</t>
+          <t>AWS, Glue, Lambda, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-01-31</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a3560765ed8e488</t>
+          <t>https://www.indeed.com/viewjob?jk=7f3534222ab81e17</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>AI Applications Engineer</t>
+          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Stanford University</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Vertex AI, Scala, Oracle, NoSQL, Data Modeling, MLOps, MLflow</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0dc1867fdcc5324</t>
+          <t>https://www.indeed.com/viewjob?jk=29d22d712d7958f0</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Customer Reliability Engineer, Airflow</t>
+          <t>AWS Data Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Astronomer</t>
+          <t>Appex Innovation</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, Snowflake, PostgreSQL, dbt, DataOps, Docker</t>
+          <t>AWS, Glue, Lambda, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ac244565083c1d9</t>
+          <t>https://www.indeed.com/viewjob?jk=3886cb86a753634c</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>RapidFire Safety &amp; Security</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, Data Modeling, Star Schema, Fact Tables, Dimension Tables, ETL, Power BI</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8afc73df8ef8f40e</t>
+          <t>https://www.indeed.com/viewjob?jk=f9637232a826c3ad</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Salesforce Architect - Senior</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>CommunityForce Inc.</t>
+          <t>CNH Industrial</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>ECS, RDS, Azure, Scala, Kafka, Data Modeling, ETL, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d236cba8a6e8ae3</t>
+          <t>https://www.indeed.com/viewjob?jk=e5b3837921976566</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>AI Data Engineer-LLMs / Agentic Systems</t>
+          <t>Senior Data Engineer - Microsoft Fabric</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>EoS Fitness</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, PostgreSQL, MongoDB, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ELT, Power BI</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,32 +3226,32 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92b5658394aee4e3</t>
+          <t>https://www.indeed.com/viewjob?jk=7bd7f3590528db3c</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Software Engineer - Master</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>PGA TOUR Superstore</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Roswell, GA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,67 +3261,67 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fb1207979169793</t>
+          <t>https://www.indeed.com/viewjob?jk=73bdb2d180484ce2</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Data Engineer - GRC Technology</t>
+          <t>Sr. Software Engineer, Data, Autonomy</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Rivian</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, S3, IAM, Databricks, Unity Catalog, Spark, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8842e67bf37c518a</t>
+          <t>https://www.indeed.com/viewjob?jk=6a3560765ed8e488</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>AI Applications Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Callaway Golf</t>
+          <t>Stanford University</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Spark, Snowflake, ETL, ELT, Terraform, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Vertex AI, Scala, Oracle, NoSQL, Data Modeling, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,32 +3331,32 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab2d181891cc2eee</t>
+          <t>https://www.indeed.com/viewjob?jk=d0dc1867fdcc5324</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Customer Reliability Engineer, Airflow</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Emed</t>
+          <t>Astronomer</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, Snowflake, PostgreSQL, dbt, DataOps, Docker</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,32 +3366,32 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e29e1c3d36f0e7c</t>
+          <t>https://www.indeed.com/viewjob?jk=6ac244565083c1d9</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer, Engineering &amp; Ops</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>NBCUniversal</t>
+          <t>RapidFire Safety &amp; Security</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Snowflake, ELT, dbt, MLOps, Airflow</t>
+          <t>RDS, Azure, Scala, SQL Server, Data Modeling, Star Schema, Fact Tables, Dimension Tables, ETL, Power BI</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,32 +3401,32 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df536a2594fa5881</t>
+          <t>https://www.indeed.com/viewjob?jk=8afc73df8ef8f40e</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Salesforce Architect - Senior</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>TRM Labs</t>
+          <t>CommunityForce Inc.</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, ETL, dbt, Power BI, Tableau, CI/CD</t>
+          <t>ECS, RDS, Azure, Scala, Kafka, Data Modeling, ETL, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dcb7ea8003fbc5dc</t>
+          <t>https://www.indeed.com/viewjob?jk=7d236cba8a6e8ae3</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Microsoft Entra</t>
+          <t>Software Engineer - Master</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Oracle, Data Modeling, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f61688604ed96074</t>
+          <t>https://www.indeed.com/viewjob?jk=3fb1207979169793</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Data Engineer - GRC Technology</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Westchester Medical Center Health Network</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Valhalla, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Snowflake, SQL Server, Data Modeling, ELT, Power BI, Tableau, CI/CD</t>
+          <t>AWS, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d807a7856ebe08db</t>
+          <t>https://www.indeed.com/viewjob?jk=8842e67bf37c518a</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer, Enterprise Data &amp; Analytics</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Rivian</t>
+          <t>Callaway Golf</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, ECS, Databricks, Data Modeling, ELT, dbt</t>
+          <t>AWS, Azure, Databricks, Spark, Snowflake, ETL, ELT, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b74ac1e46b3dfa89</t>
+          <t>https://www.indeed.com/viewjob?jk=ab2d181891cc2eee</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>.NET Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Emed</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Scala, Snowflake, SQL Server, Power BI, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4afc3e61f8ae8b7b</t>
+          <t>https://www.indeed.com/viewjob?jk=1e29e1c3d36f0e7c</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Data Engineer, Engineering &amp; Ops</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>NBCUniversal</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,29 +3601,29 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Snowflake, ELT, dbt, MLOps, Airflow</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1315e6e62a7714e8</t>
+          <t>https://www.indeed.com/viewjob?jk=df536a2594fa5881</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Data Platform Engineer - Alteryx Platform Management</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Truist</t>
+          <t>TRM Labs</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, MongoDB, Jenkins, Maven, Jenkins</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, ETL, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a738d45466c580a9</t>
+          <t>https://www.indeed.com/viewjob?jk=dcb7ea8003fbc5dc</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Microsoft Entra</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Guidewire Software, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Oracle, Data Modeling, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b5e082bd1857b0f</t>
+          <t>https://www.indeed.com/viewjob?jk=f61688604ed96074</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Sr. Informatica IDMC MDM Software Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>RBC</t>
+          <t>Westchester Medical Center Health Network</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Valhalla, NY, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,34 +3706,34 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Snowflake, SQL Server, Data Modeling, ELT, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5346f4c5e2b5352a</t>
+          <t>https://www.indeed.com/viewjob?jk=d807a7856ebe08db</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Data Engineer, Enterprise Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Rivian</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,34 +3741,34 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
+          <t>AWS, Glue, EMR, Lambda, S3, ECS, Databricks, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af8d363b230dfbc2</t>
+          <t>https://www.indeed.com/viewjob?jk=b74ac1e46b3dfa89</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Attribution Expansion</t>
+          <t>.NET Developer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>TRM Labs</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Spark, Snowflake, Data Modeling, dbt, MLflow, CI/CD, Terraform, Kubernetes</t>
+          <t>S3, RDS, Azure, Scala, Snowflake, SQL Server, Power BI, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,19 +3786,19 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=539a18aebac4ef5f</t>
+          <t>https://www.indeed.com/viewjob?jk=4afc3e61f8ae8b7b</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Attribution Expansion</t>
+          <t>Data Platform Engineer - Alteryx Platform Management</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>TRM Labs</t>
+          <t>Truist</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3811,15 +3811,190 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, MongoDB, Jenkins, Maven, Jenkins</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a738d45466c580a9</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Engineer</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Guidewire Software, Inc.</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>San Mateo, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, MySQL, MongoDB, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3b5e082bd1857b0f</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1315e6e62a7714e8</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Sr. Informatica IDMC MDM Software Engineer</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>RBC</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Minneapolis, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, ETL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5346f4c5e2b5352a</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer, Attribution Expansion</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>TRM Labs</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
           <t>RDS, BigQuery, Spark, Snowflake, Data Modeling, dbt, MLflow, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=539a18aebac4ef5f</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer, Attribution Expansion</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>TRM Labs</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>RDS, BigQuery, Spark, Snowflake, Data Modeling, dbt, MLflow, CI/CD, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=26436308d22e947d</t>
         </is>

--- a/results/job_matches_2026-03-05.xlsx
+++ b/results/job_matches_2026-03-05.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G102"/>
+  <dimension ref="A1:G86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,17 +503,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Engineer III: DevOps</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Jersey Mikes Corporate</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Tinton Falls, NJ, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, API Gateway, ECS, RDS, Azure, GCP, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc952e4224a3aa24</t>
+          <t>https://www.indeed.com/viewjob?jk=31cf41e0387f0b72</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer, Client Authentication</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Jersey Mikes Corporate</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Tinton Falls, NJ, US USA</t>
+          <t>Southlake, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling</t>
+          <t>IAM, RDS, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31cf41e0387f0b72</t>
+          <t>https://www.indeed.com/viewjob?jk=a908b362cb914674</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Client Authentication</t>
+          <t>Senior Data Engineer, ACVMax</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>ACV Auctions</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Southlake, TX, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>IAM, RDS, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a908b362cb914674</t>
+          <t>https://www.indeed.com/viewjob?jk=6c28dd5d00192a5b</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, ACVMax</t>
+          <t>Sr. Data Platform Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ACV Auctions</t>
+          <t>Real Time Medical Systems</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, IAM, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c28dd5d00192a5b</t>
+          <t>https://www.indeed.com/viewjob?jk=415686b53cfda723</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Columbia, MD, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -671,67 +671,67 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=415686b53cfda723</t>
+          <t>https://www.indeed.com/viewjob?jk=41a92f9802d4f918</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sr. Data Platform Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Real Time Medical Systems</t>
+          <t>Valvoline Global Operations</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Columbia, MD, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>17.4</v>
+        <v>16</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, IAM, RDS, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP, Cloud Storage, Spark, PySpark</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41a92f9802d4f918</t>
+          <t>https://www.indeed.com/viewjob?jk=ab16510fd1c2841d</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Cloud Infrastructure</t>
+          <t>Enterprise Data Platform Engineer – Washington, DC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ALTRUIST</t>
+          <t>Creative Information Technology India</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Falls Church, VA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>17.4</v>
+        <v>16</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, IAM, RDS, Scala, Kafka, PostgreSQL, DynamoDB, MLOps</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Delta Live Tables, Photon, Scala, ETL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2b2e3b90367f3b4</t>
+          <t>https://www.indeed.com/viewjob?jk=0a74e373b48da5fc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Cloud Infrastructure</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ALTRUIST</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>17.4</v>
+        <v>15.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, IAM, RDS, Scala, Kafka, PostgreSQL, DynamoDB, MLOps</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15721c69bc524693</t>
+          <t>https://www.indeed.com/viewjob?jk=9e8500146d476812</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sr. Database Administrator - Computing Services</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Carnegie Mellon University</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>17.4</v>
+        <v>15.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, IAM, RDS, Azure, GCP, BigQuery, Cloud Storage, Scala</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=506f6b3eeea1e8bf</t>
+          <t>https://www.indeed.com/viewjob?jk=2ad2838bd8f61427</t>
         </is>
       </c>
     </row>
@@ -823,55 +823,55 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Valvoline Global Operations</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP, Cloud Storage, Spark, PySpark</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab16510fd1c2841d</t>
+          <t>https://www.indeed.com/viewjob?jk=9188fd233f524c42</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Enterprise Data Platform Engineer – Washington, DC</t>
+          <t>Google Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Creative Information Technology India</t>
+          <t>NMI</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Falls Church, VA, US USA</t>
+          <t>Schaumburg, IL, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Delta Live Tables, Photon, Scala, ETL</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Kafka, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a74e373b48da5fc</t>
+          <t>https://www.indeed.com/viewjob?jk=e7cac4b03aa7cfe7</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Specialist - System Management</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Glen Allen, VA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Unity Catalog, Delta Live Tables, Spark, Databricks Lakehouse, SQL Server</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e8500146d476812</t>
+          <t>https://www.indeed.com/viewjob?jk=293f842904007fda</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Engineer - DevOps/ DataOps</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>FICO</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, DataOps, MLOps, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,67 +951,67 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ad2838bd8f61427</t>
+          <t>https://www.indeed.com/viewjob?jk=e1ed15cfc823b0b7</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Alight Solutions</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, GCP, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9188fd233f524c42</t>
+          <t>https://www.indeed.com/viewjob?jk=398f35933211332f</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Google Cloud Data Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>NMI</t>
+          <t>SRS Distribution</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Schaumburg, IL, US USA</t>
+          <t>McKinney, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Kafka, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Hadoop, Hive, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7cac4b03aa7cfe7</t>
+          <t>https://www.indeed.com/viewjob?jk=4cde050af8749e53</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Google Cloud Data Architect</t>
+          <t>SQL Developer - Enterprise Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Cloudious</t>
+          <t>Pantherx Specialty Llc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, HDFS, Hive</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73dc517b82db140b</t>
+          <t>https://www.indeed.com/viewjob?jk=41d495363374161e</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Specialist - System Management</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>The Cheesecake Factory</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Glen Allen, VA, US USA</t>
+          <t>Calabasas Hills, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Unity Catalog, Delta Live Tables, Spark, Databricks Lakehouse, SQL Server</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, BigQuery, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,94 +1091,94 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=293f842904007fda</t>
+          <t>https://www.indeed.com/viewjob?jk=bf6f08ab2860bc5c</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Engineer - DevOps/ DataOps</t>
+          <t>Sr. Software Engineer (Remote)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>FICO</t>
+          <t>Inspira Financial</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, DataOps, MLOps, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, Azure Cosmos DB, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1ed15cfc823b0b7</t>
+          <t>https://www.indeed.com/viewjob?jk=1733261c550fa238</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>Sr. Software Engineer (Remote)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Alight Solutions</t>
+          <t>Inspira Financial</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, GCP, Scala, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, Azure Cosmos DB, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=398f35933211332f</t>
+          <t>https://www.indeed.com/viewjob?jk=5d0e899d198425eb</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Specialist Programmer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SRS Distribution</t>
+          <t>Infosys</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>McKinney, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Hadoop, Hive, Spark, Scala, Snowflake</t>
+          <t>AWS, Azure, GCP, Hadoop, Hive, Spark, PySpark, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cde050af8749e53</t>
+          <t>https://www.indeed.com/viewjob?jk=9772b3b8d4167ecc</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SQL Developer - Enterprise Data &amp; Analytics</t>
+          <t>Incremental CRM - Data Developer 1</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Pantherx Specialty Llc</t>
+          <t>Barclays</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Whippany, NJ, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,77 +1221,77 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Glue, Redshift, Athena, S3, RDS, Databricks, Scala, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41d495363374161e</t>
+          <t>https://www.indeed.com/viewjob?jk=3c7931e975a12585</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer - Authentication</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>The Cheesecake Factory</t>
+          <t>Pindrop</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Calabasas Hills, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, BigQuery, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, Kinesis, S3, RDS, Scala, MySQL, DynamoDB, MLOps, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf6f08ab2860bc5c</t>
+          <t>https://www.indeed.com/viewjob?jk=6513fcf97bbfd044</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Cloud Data Platform Administrator - 26-02191</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
+          <t>AWS, Kinesis, IAM, Databricks, Spark, Scala, Kafka, Snowflake, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3695a4ce423ac8e5</t>
+          <t>https://www.indeed.com/viewjob?jk=a021dbda97cc3405</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Cloud Data Platform Administrator - 26-02191</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Disney Experiences</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Alexandria, VA, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
+          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Scala, DynamoDB, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67be12c15c92c4c5</t>
+          <t>https://www.indeed.com/viewjob?jk=0a7ddc3760328a54</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Cloud Data Platform Administrator - 26-02191</t>
+          <t>SSO Administrator</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, PostgreSQL, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=861fabb5acea2ca4</t>
+          <t>https://www.indeed.com/viewjob?jk=a9064a81c91aa262</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Cloud Data Platform Administrator - 26-02191</t>
+          <t>Senior Software Engineer - Commercial Software</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, Oracle, MySQL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,137 +1406,137 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6235a9d4364b9757</t>
+          <t>https://www.indeed.com/viewjob?jk=5f3de39cf73c3663</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer (Remote)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Inspira Financial</t>
+          <t>SRR Consultants</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Piscataway, NJ, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, Azure Cosmos DB, ETL, CI/CD, Jenkins</t>
+          <t>AWS, Glue, S3, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1733261c550fa238</t>
+          <t>https://www.indeed.com/viewjob?jk=88619a1e983eef30</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer (Remote)</t>
+          <t>Senior Data Engineer, Data Lakehouse Infrastructure</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Inspira Financial</t>
+          <t>TRM Labs</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, Azure Cosmos DB, ETL, CI/CD, Jenkins</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d0e899d198425eb</t>
+          <t>https://www.indeed.com/viewjob?jk=e899ea40640da235</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Incremental CRM - Data Developer 1</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Barclays</t>
+          <t>Halo Creative &amp; Media LLP</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Whippany, NJ, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, RDS, Databricks, Scala, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c7931e975a12585</t>
+          <t>https://www.indeed.com/viewjob?jk=371d6385735b0f59</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Specialist Programmer</t>
+          <t>IT Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Infosys</t>
+          <t>Novolex</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Lake Forest, IL, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, Hive, Spark, PySpark, Scala, Kafka, PostgreSQL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,19 +1546,19 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9772b3b8d4167ecc</t>
+          <t>https://www.indeed.com/viewjob?jk=024a63ca708c8a8f</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Software Engineer - Authentication</t>
+          <t>AWS DevOps Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Pindrop</t>
+          <t>Seqster PDM, Inc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1567,46 +1567,46 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, RDS, Scala, MySQL, DynamoDB, MLOps, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, IAM, RDS, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6513fcf97bbfd044</t>
+          <t>https://www.indeed.com/viewjob?jk=191c0857581cffe3</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Java Software Engineer II (US)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>TD Bank</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Mount Laurel, NJ, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, IAM, Databricks, Spark, Scala, Kafka, Snowflake, NoSQL, CI/CD</t>
+          <t>RDS, Azure, Scala, NoSQL, Splunk, Jenkins, Maven, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,137 +1616,137 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a021dbda97cc3405</t>
+          <t>https://www.indeed.com/viewjob?jk=8ee89e940b02cc06</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Software Engineer, Back End (Java, Go, AWS)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Disney Experiences</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Scala, DynamoDB, NoSQL, ETL</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a7ddc3760328a54</t>
+          <t>https://www.indeed.com/viewjob?jk=e716b4195b2da30b</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>SSO Administrator</t>
+          <t>Senior Software Engineer, Back End (Java, Go, AWS)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, PostgreSQL, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9064a81c91aa262</t>
+          <t>https://www.indeed.com/viewjob?jk=e1b9bbef981d9232</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Commercial Software</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Daniels Health</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, Oracle, MySQL</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f3de39cf73c3663</t>
+          <t>https://www.indeed.com/viewjob?jk=3486f1249174e37a</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>SRR Consultants</t>
+          <t>Daniels Health</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Piscataway, NJ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88619a1e983eef30</t>
+          <t>https://www.indeed.com/viewjob?jk=1df7caac86af2291</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Data Lakehouse Infrastructure</t>
+          <t>ATC - AI &amp; Data Analyst - NAELFY26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>TRM Labs</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Saint Petersburg, FL, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e899ea40640da235</t>
+          <t>https://www.indeed.com/viewjob?jk=1ce7a50a4bbe9ef2</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer, Data Product</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Halo Creative &amp; Media LLP</t>
+          <t>TRM Labs</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>RDS, BigQuery, Dataflow, Spark, Scala, Kafka, dbt, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=371d6385735b0f59</t>
+          <t>https://www.indeed.com/viewjob?jk=351b720407fa6f6d</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>AWS DevOps Engineer</t>
+          <t>Analytics, Full-Stack Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Seqster PDM, Inc</t>
+          <t>SCAN Health Plan</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=191c0857581cffe3</t>
+          <t>https://www.indeed.com/viewjob?jk=c24274a4aa989f95</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Java Software Engineer II (US)</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>TD Bank</t>
+          <t>Amplify</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Mount Laurel, NJ, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, NoSQL, Splunk, Jenkins, Maven, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, S3, RDS, Snowflake, DynamoDB, Data Modeling, Kimball, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,59 +1896,59 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ee89e940b02cc06</t>
+          <t>https://www.indeed.com/viewjob?jk=b4d16d721d2057f3</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II - AI/ML</t>
+          <t>Software Engineer III - Java/Spark/AWS</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Seismic</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Jenkins</t>
+          <t>AWS, EMR, Lambda, S3, ECS, RDS, Databricks, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d0bc9a390582054</t>
+          <t>https://www.indeed.com/viewjob?jk=c95674c932d41fb6</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End (Java, Go, AWS)</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Weyerhaeuser</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, MLOps, MLflow, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e716b4195b2da30b</t>
+          <t>https://www.indeed.com/viewjob?jk=7d9f82346c5ff2d3</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End (Java, Go, AWS)</t>
+          <t>Tableau Developer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Michael Kors</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>East Rutherford, NJ, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Docker</t>
+          <t>AWS, Glue, Redshift, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1b9bbef981d9232</t>
+          <t>https://www.indeed.com/viewjob?jk=904e084e965a45c4</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Software Systems Engineer, Release Reliability &amp; Automation (Autonomous Vehicles)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Daniels Health</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, Power BI, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3486f1249174e37a</t>
+          <t>https://www.indeed.com/viewjob?jk=864266ab5f8e3aac</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Software Engineer (Junior)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Daniels Health</t>
+          <t>TORCH.AI</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Leawood, KS, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
+          <t>AWS, IAM, Azure, GCP, Kafka, PostgreSQL, MongoDB, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1df7caac86af2291</t>
+          <t>https://www.indeed.com/viewjob?jk=28e432d03da8db08</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>ATC - AI &amp; Data Analyst - NAELFY26</t>
+          <t>Software Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>Nightwing</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Saint Petersburg, FL, US USA</t>
+          <t>Clarksville, TN, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ce7a50a4bbe9ef2</t>
+          <t>https://www.indeed.com/viewjob?jk=887221a715d1ff03</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Data Product</t>
+          <t>Software Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>TRM Labs</t>
+          <t>Nightwing</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Dataflow, Spark, Scala, Kafka, dbt, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=351b720407fa6f6d</t>
+          <t>https://www.indeed.com/viewjob?jk=3322d87953168bdc</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Analytics, Full-Stack Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>SCAN Health Plan</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Snowflake, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c24274a4aa989f95</t>
+          <t>https://www.indeed.com/viewjob?jk=a8b55e090bbab627</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Advanced Metering Infrastructure (AMI) Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Waters</t>
+          <t>WSSC Water</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Milford, MA, US USA</t>
+          <t>Laurel, MD, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
+          <t>RDS, Azure, Scala, Kafka, Oracle, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1975adb5bfc7de33</t>
+          <t>https://www.indeed.com/viewjob?jk=c5b2aa36ee050b9b</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Application Developer</t>
+          <t>Database Administrator</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Munich Re</t>
+          <t>Rogue Community College</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Amelia, OH, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,42 +2236,42 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, Power BI</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c8f07e938168692</t>
+          <t>https://www.indeed.com/viewjob?jk=7f9335cc41b5edf2</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Weyerhaeuser</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, MLOps, MLflow, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Spark, PySpark, Scala, MySQL, MongoDB, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d9f82346c5ff2d3</t>
+          <t>https://www.indeed.com/viewjob?jk=dd1518c4c02c12ef</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - MDM / RDM &amp; API Development</t>
+          <t>Senior Software Engineer, Back End (Python)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Prudential</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Spark, Scala, MySQL, NoSQL, Jenkins, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d75a6cef6409e12b</t>
+          <t>https://www.indeed.com/viewjob?jk=3864c05dc9b353f8</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Software Engineer (Hybrid)</t>
+          <t>Data Engineer 2</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Nightwing</t>
+          <t>BLOC Resources, LLC</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Clarksville, TN, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=887221a715d1ff03</t>
+          <t>https://www.indeed.com/viewjob?jk=c51290628ce41b82</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Software Engineer (Hybrid)</t>
+          <t>Sr. Software Engineer I, Applied AI</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Nightwing</t>
+          <t>Axon</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Sterling, VA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3322d87953168bdc</t>
+          <t>https://www.indeed.com/viewjob?jk=e858c83fc09cd77d</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Advanced Metering Infrastructure (AMI) Engineer</t>
+          <t>Senior Software Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>WSSC Water</t>
+          <t>TRM Labs</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Laurel, MD, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Oracle, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps</t>
+          <t>RDS, BigQuery, Spark, Scala, Kafka, ETL, dbt, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5b2aa36ee050b9b</t>
+          <t>https://www.indeed.com/viewjob?jk=8a517be0e10b2a44</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Data Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Amplify</t>
+          <t>TRM Labs</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Snowflake, DynamoDB, Data Modeling, Kimball, ETL, ELT, dbt</t>
+          <t>RDS, BigQuery, Spark, Scala, Kafka, ETL, dbt, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,207 +2456,207 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4d16d721d2057f3</t>
+          <t>https://www.indeed.com/viewjob?jk=60f6c2aecd2d1bdf</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Software Engineer III - Java/Spark/AWS</t>
+          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, ECS, RDS, Databricks, Spark, Scala, Snowflake</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c95674c932d41fb6</t>
+          <t>https://www.indeed.com/viewjob?jk=f85f1e8c0778adba</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Software Systems Engineer, Release Reliability &amp; Automation (Autonomous Vehicles)</t>
+          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, Power BI, CI/CD, Jenkins</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=864266ab5f8e3aac</t>
+          <t>https://www.indeed.com/viewjob?jk=3e2da1f14c27a331</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Tableau Developer</t>
+          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Michael Kors</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>East Rutherford, NJ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Star Schema</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=904e084e965a45c4</t>
+          <t>https://www.indeed.com/viewjob?jk=140d02e1f58501f6</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Database Administrator</t>
+          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Rogue Community College</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, Power BI</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f9335cc41b5edf2</t>
+          <t>https://www.indeed.com/viewjob?jk=eff547fec829449a</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Software Engineer (Junior)</t>
+          <t>AWS Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>TORCH.AI</t>
+          <t>Appex Innovation</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Leawood, KS, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Kafka, PostgreSQL, MongoDB, NoSQL, ETL, CI/CD</t>
+          <t>AWS, Glue, Lambda, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28e432d03da8db08</t>
+          <t>https://www.indeed.com/viewjob?jk=7f3534222ab81e17</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8b55e090bbab627</t>
+          <t>https://www.indeed.com/viewjob?jk=29d22d712d7958f0</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>AWS Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Appex Innovation</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, PySpark, Scala, MySQL, MongoDB, Docker, Kubernetes, Airflow</t>
+          <t>AWS, Glue, Lambda, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd1518c4c02c12ef</t>
+          <t>https://www.indeed.com/viewjob?jk=3886cb86a753634c</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End (Python)</t>
+          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3864c05dc9b353f8</t>
+          <t>https://www.indeed.com/viewjob?jk=f9637232a826c3ad</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Engineer 2</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>BLOC Resources, LLC</t>
+          <t>CNH Industrial</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Data Modeling, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c51290628ce41b82</t>
+          <t>https://www.indeed.com/viewjob?jk=e5b3837921976566</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer I, Applied AI</t>
+          <t>Senior Data Engineer - Microsoft Fabric</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Axon</t>
+          <t>EoS Fitness</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ELT, Power BI</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e858c83fc09cd77d</t>
+          <t>https://www.indeed.com/viewjob?jk=7bd7f3590528db3c</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Platform</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>TRM Labs</t>
+          <t>PGA TOUR Superstore</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Roswell, GA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Spark, Scala, Kafka, ETL, dbt, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a517be0e10b2a44</t>
+          <t>https://www.indeed.com/viewjob?jk=73bdb2d180484ce2</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Data Platform</t>
+          <t>Customer Reliability Engineer, Airflow</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>TRM Labs</t>
+          <t>Astronomer</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Spark, Scala, Kafka, ETL, dbt, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, Snowflake, PostgreSQL, dbt, DataOps, Docker</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60f6c2aecd2d1bdf</t>
+          <t>https://www.indeed.com/viewjob?jk=6ac244565083c1d9</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>RapidFire Safety &amp; Security</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, SQL Server, Data Modeling, Star Schema, Fact Tables, Dimension Tables, ETL, Power BI</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f85f1e8c0778adba</t>
+          <t>https://www.indeed.com/viewjob?jk=8afc73df8ef8f40e</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
+          <t>Salesforce Architect - Senior</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>CommunityForce Inc.</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,147 +2936,147 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>ECS, RDS, Azure, Scala, Kafka, Data Modeling, ETL, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e2da1f14c27a331</t>
+          <t>https://www.indeed.com/viewjob?jk=7d236cba8a6e8ae3</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
+          <t>Software Engineer - Master</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=140d02e1f58501f6</t>
+          <t>https://www.indeed.com/viewjob?jk=3fb1207979169793</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
+          <t>Data Engineer - GRC Technology</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eff547fec829449a</t>
+          <t>https://www.indeed.com/viewjob?jk=8842e67bf37c518a</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>AWS Data Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Appex Innovation</t>
+          <t>Callaway Golf</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD</t>
+          <t>AWS, Azure, Databricks, Spark, Snowflake, ETL, ELT, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f3534222ab81e17</t>
+          <t>https://www.indeed.com/viewjob?jk=ab2d181891cc2eee</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Emed</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29d22d712d7958f0</t>
+          <t>https://www.indeed.com/viewjob?jk=1e29e1c3d36f0e7c</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>AWS Data Engineer</t>
+          <t>Sr. Data Engineer, Engineering &amp; Ops</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Appex Innovation</t>
+          <t>NBCUniversal</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Snowflake, ELT, dbt, MLOps, Airflow</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,32 +3121,32 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3886cb86a753634c</t>
+          <t>https://www.indeed.com/viewjob?jk=df536a2594fa5881</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>TRM Labs</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, ETL, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,32 +3156,32 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9637232a826c3ad</t>
+          <t>https://www.indeed.com/viewjob?jk=dcb7ea8003fbc5dc</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Microsoft Entra</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>CNH Industrial</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
+          <t>RDS, Azure, Data Factory, Oracle, Data Modeling, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,67 +3191,67 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5b3837921976566</t>
+          <t>https://www.indeed.com/viewjob?jk=f61688604ed96074</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Microsoft Fabric</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>EoS Fitness</t>
+          <t>Westchester Medical Center Health Network</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Valhalla, NY, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Snowflake, SQL Server, Data Modeling, ELT, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bd7f3590528db3c</t>
+          <t>https://www.indeed.com/viewjob?jk=d807a7856ebe08db</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Informatica IDMC MDM Software Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>PGA TOUR Superstore</t>
+          <t>RBC</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Roswell, GA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,67 +3261,67 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73bdb2d180484ce2</t>
+          <t>https://www.indeed.com/viewjob?jk=5346f4c5e2b5352a</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Data, Autonomy</t>
+          <t>.NET Developer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Rivian</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, Databricks, Unity Catalog, Spark, Scala, DynamoDB, CI/CD</t>
+          <t>S3, RDS, Azure, Scala, Snowflake, SQL Server, Power BI, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-01-31</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a3560765ed8e488</t>
+          <t>https://www.indeed.com/viewjob?jk=4afc3e61f8ae8b7b</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>AI Applications Engineer</t>
+          <t>Senior Data Engineer, Attribution Expansion</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Stanford University</t>
+          <t>TRM Labs</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Vertex AI, Scala, Oracle, NoSQL, Data Modeling, MLOps, MLflow</t>
+          <t>RDS, BigQuery, Spark, Snowflake, Data Modeling, dbt, MLflow, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,32 +3331,32 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0dc1867fdcc5324</t>
+          <t>https://www.indeed.com/viewjob?jk=539a18aebac4ef5f</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Customer Reliability Engineer, Airflow</t>
+          <t>Senior Data Engineer, Attribution Expansion</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Astronomer</t>
+          <t>TRM Labs</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, Snowflake, PostgreSQL, dbt, DataOps, Docker</t>
+          <t>RDS, BigQuery, Spark, Snowflake, Data Modeling, dbt, MLflow, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,67 +3366,67 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ac244565083c1d9</t>
+          <t>https://www.indeed.com/viewjob?jk=26436308d22e947d</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>RapidFire Safety &amp; Security</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, Data Modeling, Star Schema, Fact Tables, Dimension Tables, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8afc73df8ef8f40e</t>
+          <t>https://www.indeed.com/viewjob?jk=1315e6e62a7714e8</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Salesforce Architect - Senior</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>CommunityForce Inc.</t>
+          <t>Guidewire Software, Inc.</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>ECS, RDS, Azure, Scala, Kafka, Data Modeling, ETL, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,567 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d236cba8a6e8ae3</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Software Engineer - Master</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Equifax</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Alpharetta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D87" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3fb1207979169793</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Data Engineer - GRC Technology</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>American Express</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>AWS, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>2026-02-26</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8842e67bf37c518a</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Sr Data Engineer</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>Callaway Golf</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Carlsbad, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D89" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Databricks, Spark, Snowflake, ETL, ELT, Terraform, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ab2d181891cc2eee</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>Emed</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Miami, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D90" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1e29e1c3d36f0e7c</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Sr. Data Engineer, Engineering &amp; Ops</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>NBCUniversal</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D91" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Snowflake, ELT, dbt, MLOps, Airflow</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=df536a2594fa5881</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Senior Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>TRM Labs</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, ETL, dbt, Power BI, Tableau, CI/CD</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dcb7ea8003fbc5dc</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Microsoft Entra</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Oracle, Data Modeling, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f61688604ed96074</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Westchester Medical Center Health Network</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Valhalla, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D94" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Snowflake, SQL Server, Data Modeling, ELT, Power BI, Tableau, CI/CD</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d807a7856ebe08db</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Sr. Data Engineer, Enterprise Data &amp; Analytics</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Rivian</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D95" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>AWS, Glue, EMR, Lambda, S3, ECS, Databricks, Data Modeling, ELT, dbt</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>2025-11-21</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b74ac1e46b3dfa89</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>.NET Developer</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>Caterpillar</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Cary, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D96" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>S3, RDS, Azure, Scala, Snowflake, SQL Server, Power BI, CI/CD, Azure DevOps, Git</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4afc3e61f8ae8b7b</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Data Platform Engineer - Alteryx Platform Management</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>Truist</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D97" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, MongoDB, Jenkins, Maven, Jenkins</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a738d45466c580a9</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>Senior Full Stack Engineer</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>Guidewire Software, Inc.</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>San Mateo, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D98" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, MySQL, MongoDB, NoSQL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=3b5e082bd1857b0f</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D99" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1315e6e62a7714e8</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>Sr. Informatica IDMC MDM Software Engineer</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>RBC</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Minneapolis, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D100" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, ETL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5346f4c5e2b5352a</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer, Attribution Expansion</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>TRM Labs</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D101" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>RDS, BigQuery, Spark, Snowflake, Data Modeling, dbt, MLflow, CI/CD, Terraform, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=539a18aebac4ef5f</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer, Attribution Expansion</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>TRM Labs</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D102" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>RDS, BigQuery, Spark, Snowflake, Data Modeling, dbt, MLflow, CI/CD, Terraform, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=26436308d22e947d</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-05.xlsx
+++ b/results/job_matches_2026-03-05.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G86"/>
+  <dimension ref="A1:G87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,17 +538,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Client Authentication</t>
+          <t>Senior Data Engineer, ACVMax</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>ACV Auctions</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Southlake, TX, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>IAM, RDS, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a908b362cb914674</t>
+          <t>https://www.indeed.com/viewjob?jk=6c28dd5d00192a5b</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, ACVMax</t>
+          <t>Senior Data Engineer, Client Authentication</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ACV Auctions</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>Southlake, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS</t>
+          <t>IAM, RDS, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c28dd5d00192a5b</t>
+          <t>https://www.indeed.com/viewjob?jk=a908b362cb914674</t>
         </is>
       </c>
     </row>
@@ -818,17 +818,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Google Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>NMI</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Schaumburg, IL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,34 +836,34 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Kafka, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9188fd233f524c42</t>
+          <t>https://www.indeed.com/viewjob?jk=e7cac4b03aa7cfe7</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Google Cloud Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>NMI</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Schaumburg, IL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,17 +871,17 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Kafka, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7cac4b03aa7cfe7</t>
+          <t>https://www.indeed.com/viewjob?jk=9188fd233f524c42</t>
         </is>
       </c>
     </row>
@@ -923,17 +923,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Engineer - DevOps/ DataOps</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>FICO</t>
+          <t>Alight Solutions</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, DataOps, MLOps, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, GCP, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1ed15cfc823b0b7</t>
+          <t>https://www.indeed.com/viewjob?jk=398f35933211332f</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>Senior Engineer - DevOps/ DataOps</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Alight Solutions</t>
+          <t>FICO</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, GCP, Scala, CI/CD</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, DataOps, MLOps, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=398f35933211332f</t>
+          <t>https://www.indeed.com/viewjob?jk=e1ed15cfc823b0b7</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>SQL Developer - Enterprise Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SRS Distribution</t>
+          <t>Pantherx Specialty Llc</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>McKinney, TX, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Hadoop, Hive, Spark, Scala, Snowflake</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cde050af8749e53</t>
+          <t>https://www.indeed.com/viewjob?jk=41d495363374161e</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SQL Developer - Enterprise Data &amp; Analytics</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Pantherx Specialty Llc</t>
+          <t>SRS Distribution</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>McKinney, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Hadoop, Hive, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41d495363374161e</t>
+          <t>https://www.indeed.com/viewjob?jk=4cde050af8749e53</t>
         </is>
       </c>
     </row>
@@ -1238,17 +1238,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Software Engineer - Authentication</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Pindrop</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, RDS, Scala, MySQL, DynamoDB, MLOps, CI/CD, Jenkins</t>
+          <t>AWS, Kinesis, IAM, Databricks, Spark, Scala, Kafka, Snowflake, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6513fcf97bbfd044</t>
+          <t>https://www.indeed.com/viewjob?jk=a021dbda97cc3405</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Disney Experiences</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, IAM, Databricks, Spark, Scala, Kafka, Snowflake, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Scala, DynamoDB, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a021dbda97cc3405</t>
+          <t>https://www.indeed.com/viewjob?jk=0a7ddc3760328a54</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Software Engineer - Authentication</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Disney Experiences</t>
+          <t>Pindrop</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,17 +1326,17 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Scala, DynamoDB, NoSQL, ETL</t>
+          <t>AWS, Kinesis, S3, RDS, Scala, MySQL, DynamoDB, MLOps, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a7ddc3760328a54</t>
+          <t>https://www.indeed.com/viewjob?jk=6513fcf97bbfd044</t>
         </is>
       </c>
     </row>
@@ -1378,17 +1378,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Commercial Software</t>
+          <t>IT Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Novolex</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Lake Forest, IL, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, Oracle, MySQL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f3de39cf73c3663</t>
+          <t>https://www.indeed.com/viewjob?jk=024a63ca708c8a8f</t>
         </is>
       </c>
     </row>
@@ -1483,17 +1483,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AWS DevOps Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Halo Creative &amp; Media LLP</t>
+          <t>Seqster PDM, Inc</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, Lambda, S3, IAM, RDS, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=371d6385735b0f59</t>
+          <t>https://www.indeed.com/viewjob?jk=191c0857581cffe3</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>IT Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Novolex</t>
+          <t>Halo Creative &amp; Media LLP</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Lake Forest, IL, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=024a63ca708c8a8f</t>
+          <t>https://www.indeed.com/viewjob?jk=371d6385735b0f59</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>AWS DevOps Engineer</t>
+          <t>Senior Software Engineer - Commercial Software</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Seqster PDM, Inc</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, Oracle, MySQL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=191c0857581cffe3</t>
+          <t>https://www.indeed.com/viewjob?jk=5f3de39cf73c3663</t>
         </is>
       </c>
     </row>
@@ -1623,17 +1623,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End (Java, Go, AWS)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Docker</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e716b4195b2da30b</t>
+          <t>https://www.indeed.com/viewjob?jk=38b673fd36dffa19</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End (Java, Go, AWS)</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Daniels Health</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,17 +1676,17 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Docker</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1b9bbef981d9232</t>
+          <t>https://www.indeed.com/viewjob?jk=3486f1249174e37a</t>
         </is>
       </c>
     </row>
@@ -1716,29 +1716,29 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3486f1249174e37a</t>
+          <t>https://www.indeed.com/viewjob?jk=1df7caac86af2291</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>ATC - AI &amp; Data Analyst - NAELFY26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Daniels Health</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Saint Petersburg, FL, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1df7caac86af2291</t>
+          <t>https://www.indeed.com/viewjob?jk=1ce7a50a4bbe9ef2</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ATC - AI &amp; Data Analyst - NAELFY26</t>
+          <t>Senior Data Engineer, Data Product</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>TRM Labs</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Saint Petersburg, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, BigQuery, Dataflow, Spark, Scala, Kafka, dbt, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ce7a50a4bbe9ef2</t>
+          <t>https://www.indeed.com/viewjob?jk=351b720407fa6f6d</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Data Product</t>
+          <t>Analytics, Full-Stack Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>TRM Labs</t>
+          <t>SCAN Health Plan</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Dataflow, Spark, Scala, Kafka, dbt, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=351b720407fa6f6d</t>
+          <t>https://www.indeed.com/viewjob?jk=c24274a4aa989f95</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Analytics, Full-Stack Engineer</t>
+          <t>Senior Software Engineer, Back End (Java, Go, AWS)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>SCAN Health Plan</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Snowflake, ETL, ELT, dbt</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c24274a4aa989f95</t>
+          <t>https://www.indeed.com/viewjob?jk=e716b4195b2da30b</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Software Engineer, Back End (Java, Go, AWS)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Amplify</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Snowflake, DynamoDB, Data Modeling, Kimball, ETL, ELT, dbt</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4d16d721d2057f3</t>
+          <t>https://www.indeed.com/viewjob?jk=e1b9bbef981d9232</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Software Engineer III - Java/Spark/AWS</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Amplify</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, ECS, RDS, Databricks, Spark, Scala, Snowflake</t>
+          <t>AWS, S3, RDS, Snowflake, DynamoDB, Data Modeling, Kimball, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c95674c932d41fb6</t>
+          <t>https://www.indeed.com/viewjob?jk=b4d16d721d2057f3</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Software Engineer III - Java/Spark/AWS</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Weyerhaeuser</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, MLOps, MLflow, CI/CD, Terraform, Docker</t>
+          <t>AWS, EMR, Lambda, S3, ECS, RDS, Databricks, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d9f82346c5ff2d3</t>
+          <t>https://www.indeed.com/viewjob?jk=c95674c932d41fb6</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Tableau Developer</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Michael Kors</t>
+          <t>Weyerhaeuser</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>East Rutherford, NJ, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, MLOps, MLflow, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=904e084e965a45c4</t>
+          <t>https://www.indeed.com/viewjob?jk=7d9f82346c5ff2d3</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Software Systems Engineer, Release Reliability &amp; Automation (Autonomous Vehicles)</t>
+          <t>Tableau Developer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Michael Kors</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>East Rutherford, NJ, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, Power BI, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Redshift, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=864266ab5f8e3aac</t>
+          <t>https://www.indeed.com/viewjob?jk=904e084e965a45c4</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Software Engineer (Junior)</t>
+          <t>Software Systems Engineer, Release Reliability &amp; Automation (Autonomous Vehicles)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>TORCH.AI</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Leawood, KS, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Kafka, PostgreSQL, MongoDB, NoSQL, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, Power BI, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28e432d03da8db08</t>
+          <t>https://www.indeed.com/viewjob?jk=864266ab5f8e3aac</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Software Engineer (Hybrid)</t>
+          <t>Software Engineer (Junior)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Nightwing</t>
+          <t>TORCH.AI</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Clarksville, TN, US USA</t>
+          <t>Leawood, KS, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, IAM, Azure, GCP, Kafka, PostgreSQL, MongoDB, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=887221a715d1ff03</t>
+          <t>https://www.indeed.com/viewjob?jk=28e432d03da8db08</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Sterling, VA, US USA</t>
+          <t>Clarksville, TN, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3322d87953168bdc</t>
+          <t>https://www.indeed.com/viewjob?jk=887221a715d1ff03</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Software Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Nightwing</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8b55e090bbab627</t>
+          <t>https://www.indeed.com/viewjob?jk=3322d87953168bdc</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Advanced Metering Infrastructure (AMI) Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>WSSC Water</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Laurel, MD, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Oracle, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5b2aa36ee050b9b</t>
+          <t>https://www.indeed.com/viewjob?jk=a8b55e090bbab627</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Database Administrator</t>
+          <t>Advanced Metering Infrastructure (AMI) Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Rogue Community College</t>
+          <t>WSSC Water</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>Laurel, MD, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,69 +2236,69 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, Power BI</t>
+          <t>RDS, Azure, Scala, Kafka, Oracle, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f9335cc41b5edf2</t>
+          <t>https://www.indeed.com/viewjob?jk=c5b2aa36ee050b9b</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Database Administrator</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Rogue Community College</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, PySpark, Scala, MySQL, MongoDB, Docker, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, Power BI</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd1518c4c02c12ef</t>
+          <t>https://www.indeed.com/viewjob?jk=7f9335cc41b5edf2</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End (Python)</t>
+          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3864c05dc9b353f8</t>
+          <t>https://www.indeed.com/viewjob?jk=f85f1e8c0778adba</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Engineer 2</t>
+          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>BLOC Resources, LLC</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Data Modeling, CI/CD</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c51290628ce41b82</t>
+          <t>https://www.indeed.com/viewjob?jk=3e2da1f14c27a331</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer I, Applied AI</t>
+          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Axon</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e858c83fc09cd77d</t>
+          <t>https://www.indeed.com/viewjob?jk=140d02e1f58501f6</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Platform</t>
+          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>TRM Labs</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Spark, Scala, Kafka, ETL, dbt, Terraform, Docker, Kubernetes</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a517be0e10b2a44</t>
+          <t>https://www.indeed.com/viewjob?jk=eff547fec829449a</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Data Platform</t>
+          <t>AWS Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>TRM Labs</t>
+          <t>Appex Innovation</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,17 +2446,17 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Spark, Scala, Kafka, ETL, dbt, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Glue, Lambda, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60f6c2aecd2d1bdf</t>
+          <t>https://www.indeed.com/viewjob?jk=7f3534222ab81e17</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2486,29 +2486,29 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f85f1e8c0778adba</t>
+          <t>https://www.indeed.com/viewjob?jk=29d22d712d7958f0</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Spark, PySpark, Scala, MySQL, MongoDB, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e2da1f14c27a331</t>
+          <t>https://www.indeed.com/viewjob?jk=dd1518c4c02c12ef</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
+          <t>AWS Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Appex Innovation</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Glue, Lambda, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=140d02e1f58501f6</t>
+          <t>https://www.indeed.com/viewjob?jk=3886cb86a753634c</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
+          <t>Data Engineer 2</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>BLOC Resources, LLC</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eff547fec829449a</t>
+          <t>https://www.indeed.com/viewjob?jk=c51290628ce41b82</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>AWS Data Engineer</t>
+          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Appex Innovation</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f3534222ab81e17</t>
+          <t>https://www.indeed.com/viewjob?jk=f9637232a826c3ad</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>CNH Industrial</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29d22d712d7958f0</t>
+          <t>https://www.indeed.com/viewjob?jk=e5b3837921976566</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>AWS Data Engineer</t>
+          <t>Senior Software Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Appex Innovation</t>
+          <t>TRM Labs</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD</t>
+          <t>RDS, BigQuery, Spark, Scala, Kafka, ETL, dbt, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3886cb86a753634c</t>
+          <t>https://www.indeed.com/viewjob?jk=8a517be0e10b2a44</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
+          <t>Senior Data Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>TRM Labs</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>RDS, BigQuery, Spark, Scala, Kafka, ETL, dbt, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9637232a826c3ad</t>
+          <t>https://www.indeed.com/viewjob?jk=60f6c2aecd2d1bdf</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer - Microsoft Fabric</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>CNH Industrial</t>
+          <t>EoS Fitness</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ELT, Power BI</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5b3837921976566</t>
+          <t>https://www.indeed.com/viewjob?jk=7bd7f3590528db3c</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Microsoft Fabric</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>EoS Fitness</t>
+          <t>PGA TOUR Superstore</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Roswell, GA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ELT, Power BI</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bd7f3590528db3c</t>
+          <t>https://www.indeed.com/viewjob?jk=73bdb2d180484ce2</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer, Back End (Python)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>PGA TOUR Superstore</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Roswell, GA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73bdb2d180484ce2</t>
+          <t>https://www.indeed.com/viewjob?jk=3864c05dc9b353f8</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Customer Reliability Engineer, Airflow</t>
+          <t>Sr. Software Engineer I, Applied AI</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Astronomer</t>
+          <t>Axon</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, Snowflake, PostgreSQL, dbt, DataOps, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ac244565083c1d9</t>
+          <t>https://www.indeed.com/viewjob?jk=e858c83fc09cd77d</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Customer Reliability Engineer, Airflow</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>RapidFire Safety &amp; Security</t>
+          <t>Astronomer</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, Data Modeling, Star Schema, Fact Tables, Dimension Tables, ETL, Power BI</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, Snowflake, PostgreSQL, dbt, DataOps, Docker</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8afc73df8ef8f40e</t>
+          <t>https://www.indeed.com/viewjob?jk=6ac244565083c1d9</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Salesforce Architect - Senior</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>CommunityForce Inc.</t>
+          <t>RapidFire Safety &amp; Security</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>ECS, RDS, Azure, Scala, Kafka, Data Modeling, ETL, CI/CD, Jenkins, Azure DevOps</t>
+          <t>RDS, Azure, Scala, SQL Server, Data Modeling, Star Schema, Fact Tables, Dimension Tables, ETL, Power BI</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d236cba8a6e8ae3</t>
+          <t>https://www.indeed.com/viewjob?jk=8afc73df8ef8f40e</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Software Engineer - Master</t>
+          <t>Salesforce Architect - Senior</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>CommunityForce Inc.</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>ECS, RDS, Azure, Scala, Kafka, Data Modeling, ETL, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fb1207979169793</t>
+          <t>https://www.indeed.com/viewjob?jk=7d236cba8a6e8ae3</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Engineer - GRC Technology</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Callaway Golf</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, Databricks, Spark, Snowflake, ETL, ELT, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8842e67bf37c518a</t>
+          <t>https://www.indeed.com/viewjob?jk=ab2d181891cc2eee</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Callaway Golf</t>
+          <t>Emed</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Spark, Snowflake, ETL, ELT, Terraform, Kubernetes, Git</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab2d181891cc2eee</t>
+          <t>https://www.indeed.com/viewjob?jk=1e29e1c3d36f0e7c</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Data Engineer, Engineering &amp; Ops</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Emed</t>
+          <t>NBCUniversal</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Snowflake, ELT, dbt, MLOps, Airflow</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e29e1c3d36f0e7c</t>
+          <t>https://www.indeed.com/viewjob?jk=df536a2594fa5881</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer, Engineering &amp; Ops</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>NBCUniversal</t>
+          <t>TRM Labs</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Snowflake, ELT, dbt, MLOps, Airflow</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, ETL, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df536a2594fa5881</t>
+          <t>https://www.indeed.com/viewjob?jk=dcb7ea8003fbc5dc</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Microsoft Entra</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>TRM Labs</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, ETL, dbt, Power BI, Tableau, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Oracle, Data Modeling, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dcb7ea8003fbc5dc</t>
+          <t>https://www.indeed.com/viewjob?jk=f61688604ed96074</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Microsoft Entra</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Westchester Medical Center Health Network</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Valhalla, NY, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Oracle, Data Modeling, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Snowflake, SQL Server, Data Modeling, ELT, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f61688604ed96074</t>
+          <t>https://www.indeed.com/viewjob?jk=d807a7856ebe08db</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Data Engineer - GRC Technology</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Westchester Medical Center Health Network</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Valhalla, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Snowflake, SQL Server, Data Modeling, ELT, Power BI, Tableau, CI/CD</t>
+          <t>AWS, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d807a7856ebe08db</t>
+          <t>https://www.indeed.com/viewjob?jk=8842e67bf37c518a</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Sr. Informatica IDMC MDM Software Engineer</t>
+          <t>Software Engineer - Master</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>RBC</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, ETL, CI/CD</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5346f4c5e2b5352a</t>
+          <t>https://www.indeed.com/viewjob?jk=3fb1207979169793</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>.NET Developer</t>
+          <t>Sr. Informatica IDMC MDM Software Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>RBC</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Scala, Snowflake, SQL Server, Power BI, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4afc3e61f8ae8b7b</t>
+          <t>https://www.indeed.com/viewjob?jk=5346f4c5e2b5352a</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Attribution Expansion</t>
+          <t>.NET Developer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>TRM Labs</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Spark, Snowflake, Data Modeling, dbt, MLflow, CI/CD, Terraform, Kubernetes</t>
+          <t>S3, RDS, Azure, Scala, Snowflake, SQL Server, Power BI, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=539a18aebac4ef5f</t>
+          <t>https://www.indeed.com/viewjob?jk=4afc3e61f8ae8b7b</t>
         </is>
       </c>
     </row>
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26436308d22e947d</t>
+          <t>https://www.indeed.com/viewjob?jk=539a18aebac4ef5f</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer, Attribution Expansion</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>TRM Labs</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, BigQuery, Spark, Snowflake, Data Modeling, dbt, MLflow, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1315e6e62a7714e8</t>
+          <t>https://www.indeed.com/viewjob?jk=26436308d22e947d</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Guidewire Software, Inc.</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,15 +3426,50 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1315e6e62a7714e8</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Engineer</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Guidewire Software, Inc.</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>San Mateo, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
           <t>AWS, RDS, Azure, GCP, Scala, Oracle, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=3b5e082bd1857b0f</t>
         </is>

--- a/results/job_matches_2026-03-05.xlsx
+++ b/results/job_matches_2026-03-05.xlsx
@@ -538,17 +538,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, ACVMax</t>
+          <t>Senior Data Engineer, Client Authentication</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ACV Auctions</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>Southlake, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS</t>
+          <t>IAM, RDS, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c28dd5d00192a5b</t>
+          <t>https://www.indeed.com/viewjob?jk=a908b362cb914674</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Client Authentication</t>
+          <t>Senior Data Engineer, ACVMax</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>ACV Auctions</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Southlake, TX, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>IAM, RDS, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a908b362cb914674</t>
+          <t>https://www.indeed.com/viewjob?jk=6c28dd5d00192a5b</t>
         </is>
       </c>
     </row>
@@ -818,17 +818,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Google Cloud Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>NMI</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Schaumburg, IL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,34 +836,34 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Kafka, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7cac4b03aa7cfe7</t>
+          <t>https://www.indeed.com/viewjob?jk=9188fd233f524c42</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Google Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>NMI</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Schaumburg, IL, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,17 +871,17 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Kafka, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9188fd233f524c42</t>
+          <t>https://www.indeed.com/viewjob?jk=e7cac4b03aa7cfe7</t>
         </is>
       </c>
     </row>
@@ -923,17 +923,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>Senior Engineer - DevOps/ DataOps</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Alight Solutions</t>
+          <t>FICO</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, GCP, Scala, CI/CD</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, DataOps, MLOps, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=398f35933211332f</t>
+          <t>https://www.indeed.com/viewjob?jk=e1ed15cfc823b0b7</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Engineer - DevOps/ DataOps</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>FICO</t>
+          <t>Alight Solutions</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, DataOps, MLOps, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, GCP, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1ed15cfc823b0b7</t>
+          <t>https://www.indeed.com/viewjob?jk=398f35933211332f</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SQL Developer - Enterprise Data &amp; Analytics</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Pantherx Specialty Llc</t>
+          <t>SRS Distribution</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>McKinney, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Hadoop, Hive, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41d495363374161e</t>
+          <t>https://www.indeed.com/viewjob?jk=4cde050af8749e53</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>SQL Developer - Enterprise Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SRS Distribution</t>
+          <t>Pantherx Specialty Llc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>McKinney, TX, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Hadoop, Hive, Spark, Scala, Snowflake</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cde050af8749e53</t>
+          <t>https://www.indeed.com/viewjob?jk=41d495363374161e</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Software Engineer (Remote)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>The Cheesecake Factory</t>
+          <t>Inspira Financial</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Calabasas Hills, CA, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,17 +1081,17 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, BigQuery, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, Azure Cosmos DB, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf6f08ab2860bc5c</t>
+          <t>https://www.indeed.com/viewjob?jk=1733261c550fa238</t>
         </is>
       </c>
     </row>
@@ -1121,29 +1121,29 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1733261c550fa238</t>
+          <t>https://www.indeed.com/viewjob?jk=5d0e899d198425eb</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer (Remote)</t>
+          <t>Specialist Programmer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Inspira Financial</t>
+          <t>Infosys</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, Azure Cosmos DB, ETL, CI/CD, Jenkins</t>
+          <t>AWS, Azure, GCP, Hadoop, Hive, Spark, PySpark, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d0e899d198425eb</t>
+          <t>https://www.indeed.com/viewjob?jk=9772b3b8d4167ecc</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Specialist Programmer</t>
+          <t>Incremental CRM - Data Developer 1</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Infosys</t>
+          <t>Barclays</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Whippany, NJ, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,52 +1186,52 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, Hive, Spark, PySpark, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, Glue, Redshift, Athena, S3, RDS, Databricks, Scala, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9772b3b8d4167ecc</t>
+          <t>https://www.indeed.com/viewjob?jk=3c7931e975a12585</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Incremental CRM - Data Developer 1</t>
+          <t>Software Engineer - Authentication</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Barclays</t>
+          <t>Pindrop</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Whippany, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, RDS, Databricks, Scala, SQL Server, ETL</t>
+          <t>AWS, Kinesis, S3, RDS, Scala, MySQL, DynamoDB, MLOps, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c7931e975a12585</t>
+          <t>https://www.indeed.com/viewjob?jk=6513fcf97bbfd044</t>
         </is>
       </c>
     </row>
@@ -1308,17 +1308,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Software Engineer - Authentication</t>
+          <t>SSO Administrator</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Pindrop</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,42 +1326,42 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, RDS, Scala, MySQL, DynamoDB, MLOps, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, PostgreSQL, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6513fcf97bbfd044</t>
+          <t>https://www.indeed.com/viewjob?jk=a9064a81c91aa262</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SSO Administrator</t>
+          <t>Senior Software Engineer - Commercial Software</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, PostgreSQL, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, Oracle, MySQL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9064a81c91aa262</t>
+          <t>https://www.indeed.com/viewjob?jk=5f3de39cf73c3663</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>IT Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Novolex</t>
+          <t>SRR Consultants</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Lake Forest, IL, US USA</t>
+          <t>Piscataway, NJ, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Glue, S3, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=024a63ca708c8a8f</t>
+          <t>https://www.indeed.com/viewjob?jk=88619a1e983eef30</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer, Data Lakehouse Infrastructure</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>SRR Consultants</t>
+          <t>TRM Labs</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Piscataway, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88619a1e983eef30</t>
+          <t>https://www.indeed.com/viewjob?jk=e899ea40640da235</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Data Lakehouse Infrastructure</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>TRM Labs</t>
+          <t>Halo Creative &amp; Media LLP</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e899ea40640da235</t>
+          <t>https://www.indeed.com/viewjob?jk=371d6385735b0f59</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>AWS DevOps Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Seqster PDM, Inc</t>
+          <t>Advance Auto Parts</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=191c0857581cffe3</t>
+          <t>https://www.indeed.com/viewjob?jk=3e2d8bc5a4c9174d</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>IT Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Halo Creative &amp; Media LLP</t>
+          <t>Novolex</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Lake Forest, IL, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=371d6385735b0f59</t>
+          <t>https://www.indeed.com/viewjob?jk=024a63ca708c8a8f</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Commercial Software</t>
+          <t>AWS DevOps Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Seqster PDM, Inc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, Oracle, MySQL</t>
+          <t>AWS, Lambda, S3, IAM, RDS, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f3de39cf73c3663</t>
+          <t>https://www.indeed.com/viewjob?jk=191c0857581cffe3</t>
         </is>
       </c>
     </row>
@@ -1658,17 +1658,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Software Engineer, Back End (Java, Go, AWS)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Daniels Health</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3486f1249174e37a</t>
+          <t>https://www.indeed.com/viewjob?jk=e716b4195b2da30b</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Software Engineer, Back End (Java, Go, AWS)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Daniels Health</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1df7caac86af2291</t>
+          <t>https://www.indeed.com/viewjob?jk=e1b9bbef981d9232</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ATC - AI &amp; Data Analyst - NAELFY26</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>Daniels Health</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Saint Petersburg, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ce7a50a4bbe9ef2</t>
+          <t>https://www.indeed.com/viewjob?jk=3486f1249174e37a</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Data Product</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>TRM Labs</t>
+          <t>Daniels Health</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Dataflow, Spark, Scala, Kafka, dbt, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=351b720407fa6f6d</t>
+          <t>https://www.indeed.com/viewjob?jk=1df7caac86af2291</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Analytics, Full-Stack Engineer</t>
+          <t>ATC - AI &amp; Data Analyst - NAELFY26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>SCAN Health Plan</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>Saint Petersburg, FL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Snowflake, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c24274a4aa989f95</t>
+          <t>https://www.indeed.com/viewjob?jk=1ce7a50a4bbe9ef2</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End (Java, Go, AWS)</t>
+          <t>Senior Data Engineer, Data Product</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>TRM Labs</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Docker</t>
+          <t>RDS, BigQuery, Dataflow, Spark, Scala, Kafka, dbt, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e716b4195b2da30b</t>
+          <t>https://www.indeed.com/viewjob?jk=351b720407fa6f6d</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End (Java, Go, AWS)</t>
+          <t>Analytics, Full-Stack Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>SCAN Health Plan</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,17 +1886,17 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Docker</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1b9bbef981d9232</t>
+          <t>https://www.indeed.com/viewjob?jk=c24274a4aa989f95</t>
         </is>
       </c>
     </row>
@@ -2008,17 +2008,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Tableau Developer</t>
+          <t>Software Systems Engineer, Release Reliability &amp; Automation (Autonomous Vehicles)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Michael Kors</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>East Rutherford, NJ, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, Power BI, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=904e084e965a45c4</t>
+          <t>https://www.indeed.com/viewjob?jk=864266ab5f8e3aac</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Software Systems Engineer, Release Reliability &amp; Automation (Autonomous Vehicles)</t>
+          <t>Software Engineer (Junior)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>TORCH.AI</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Leawood, KS, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, Power BI, CI/CD, Jenkins</t>
+          <t>AWS, IAM, Azure, GCP, Kafka, PostgreSQL, MongoDB, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=864266ab5f8e3aac</t>
+          <t>https://www.indeed.com/viewjob?jk=28e432d03da8db08</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Software Engineer (Junior)</t>
+          <t>Software Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>TORCH.AI</t>
+          <t>Nightwing</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Leawood, KS, US USA</t>
+          <t>Clarksville, TN, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Kafka, PostgreSQL, MongoDB, NoSQL, ETL, CI/CD</t>
+          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28e432d03da8db08</t>
+          <t>https://www.indeed.com/viewjob?jk=887221a715d1ff03</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Clarksville, TN, US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=887221a715d1ff03</t>
+          <t>https://www.indeed.com/viewjob?jk=3322d87953168bdc</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Software Engineer (Hybrid)</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Nightwing</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Sterling, VA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3322d87953168bdc</t>
+          <t>https://www.indeed.com/viewjob?jk=a8b55e090bbab627</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Tableau Developer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Michael Kors</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>East Rutherford, NJ, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Glue, Redshift, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8b55e090bbab627</t>
+          <t>https://www.indeed.com/viewjob?jk=904e084e965a45c4</t>
         </is>
       </c>
     </row>
@@ -2288,17 +2288,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Spark, PySpark, Scala, MySQL, MongoDB, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f85f1e8c0778adba</t>
+          <t>https://www.indeed.com/viewjob?jk=dd1518c4c02c12ef</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
+          <t>Senior Software Engineer, Back End (Python)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e2da1f14c27a331</t>
+          <t>https://www.indeed.com/viewjob?jk=3864c05dc9b353f8</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
+          <t>Data Engineer 2</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>BLOC Resources, LLC</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=140d02e1f58501f6</t>
+          <t>https://www.indeed.com/viewjob?jk=c51290628ce41b82</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
+          <t>Sr. Software Engineer I, Applied AI</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Axon</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eff547fec829449a</t>
+          <t>https://www.indeed.com/viewjob?jk=e858c83fc09cd77d</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>AWS Data Engineer</t>
+          <t>Senior Software Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Appex Innovation</t>
+          <t>TRM Labs</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD</t>
+          <t>RDS, BigQuery, Spark, Scala, Kafka, ETL, dbt, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f3534222ab81e17</t>
+          <t>https://www.indeed.com/viewjob?jk=8a517be0e10b2a44</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
+          <t>Senior Data Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>TRM Labs</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>RDS, BigQuery, Spark, Scala, Kafka, ETL, dbt, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29d22d712d7958f0</t>
+          <t>https://www.indeed.com/viewjob?jk=60f6c2aecd2d1bdf</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, PySpark, Scala, MySQL, MongoDB, Docker, Kubernetes, Airflow</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd1518c4c02c12ef</t>
+          <t>https://www.indeed.com/viewjob?jk=f85f1e8c0778adba</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>AWS Data Engineer</t>
+          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Appex Innovation</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3886cb86a753634c</t>
+          <t>https://www.indeed.com/viewjob?jk=3e2da1f14c27a331</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Engineer 2</t>
+          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>BLOC Resources, LLC</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,17 +2586,17 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Data Modeling, CI/CD</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c51290628ce41b82</t>
+          <t>https://www.indeed.com/viewjob?jk=140d02e1f58501f6</t>
         </is>
       </c>
     </row>
@@ -2626,29 +2626,29 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9637232a826c3ad</t>
+          <t>https://www.indeed.com/viewjob?jk=eff547fec829449a</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AWS Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>CNH Industrial</t>
+          <t>Appex Innovation</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, Glue, Lambda, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5b3837921976566</t>
+          <t>https://www.indeed.com/viewjob?jk=7f3534222ab81e17</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Platform</t>
+          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>TRM Labs</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Spark, Scala, Kafka, ETL, dbt, Terraform, Docker, Kubernetes</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a517be0e10b2a44</t>
+          <t>https://www.indeed.com/viewjob?jk=29d22d712d7958f0</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Data Platform</t>
+          <t>AWS Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>TRM Labs</t>
+          <t>Appex Innovation</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Spark, Scala, Kafka, ETL, dbt, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Glue, Lambda, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60f6c2aecd2d1bdf</t>
+          <t>https://www.indeed.com/viewjob?jk=3886cb86a753634c</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Microsoft Fabric</t>
+          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>EoS Fitness</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ELT, Power BI</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bd7f3590528db3c</t>
+          <t>https://www.indeed.com/viewjob?jk=f9637232a826c3ad</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>PGA TOUR Superstore</t>
+          <t>CNH Industrial</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Roswell, GA, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73bdb2d180484ce2</t>
+          <t>https://www.indeed.com/viewjob?jk=e5b3837921976566</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End (Python)</t>
+          <t>Senior Data Engineer - Microsoft Fabric</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>EoS Fitness</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ELT, Power BI</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3864c05dc9b353f8</t>
+          <t>https://www.indeed.com/viewjob?jk=7bd7f3590528db3c</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer I, Applied AI</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Axon</t>
+          <t>PGA TOUR Superstore</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Roswell, GA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e858c83fc09cd77d</t>
+          <t>https://www.indeed.com/viewjob?jk=73bdb2d180484ce2</t>
         </is>
       </c>
     </row>
@@ -2988,17 +2988,17 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Software Engineer - Master</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Callaway Golf</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Spark, Snowflake, ETL, ELT, Terraform, Kubernetes, Git</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab2d181891cc2eee</t>
+          <t>https://www.indeed.com/viewjob?jk=3fb1207979169793</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer - GRC Technology</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Emed</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e29e1c3d36f0e7c</t>
+          <t>https://www.indeed.com/viewjob?jk=8842e67bf37c518a</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer, Engineering &amp; Ops</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>NBCUniversal</t>
+          <t>Callaway Golf</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Snowflake, ELT, dbt, MLOps, Airflow</t>
+          <t>AWS, Azure, Databricks, Spark, Snowflake, ETL, ELT, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df536a2594fa5881</t>
+          <t>https://www.indeed.com/viewjob?jk=ab2d181891cc2eee</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>TRM Labs</t>
+          <t>Emed</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, ETL, dbt, Power BI, Tableau, CI/CD</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dcb7ea8003fbc5dc</t>
+          <t>https://www.indeed.com/viewjob?jk=1e29e1c3d36f0e7c</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Microsoft Entra</t>
+          <t>Sr. Data Engineer, Engineering &amp; Ops</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>NBCUniversal</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Oracle, Data Modeling, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Snowflake, ELT, dbt, MLOps, Airflow</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f61688604ed96074</t>
+          <t>https://www.indeed.com/viewjob?jk=df536a2594fa5881</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Westchester Medical Center Health Network</t>
+          <t>TRM Labs</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Valhalla, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Snowflake, SQL Server, Data Modeling, ELT, Power BI, Tableau, CI/CD</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, ETL, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d807a7856ebe08db</t>
+          <t>https://www.indeed.com/viewjob?jk=dcb7ea8003fbc5dc</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Data Engineer - GRC Technology</t>
+          <t>Microsoft Entra</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Oracle, Data Modeling, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8842e67bf37c518a</t>
+          <t>https://www.indeed.com/viewjob?jk=f61688604ed96074</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Software Engineer - Master</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Westchester Medical Center Health Network</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Valhalla, NY, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Snowflake, SQL Server, Data Modeling, ELT, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fb1207979169793</t>
+          <t>https://www.indeed.com/viewjob?jk=d807a7856ebe08db</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Sr. Informatica IDMC MDM Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>RBC</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5346f4c5e2b5352a</t>
+          <t>https://www.indeed.com/viewjob?jk=1315e6e62a7714e8</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>.NET Developer</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Guidewire Software, Inc.</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Scala, Snowflake, SQL Server, Power BI, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4afc3e61f8ae8b7b</t>
+          <t>https://www.indeed.com/viewjob?jk=3b5e082bd1857b0f</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Attribution Expansion</t>
+          <t>.NET Developer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>TRM Labs</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Spark, Snowflake, Data Modeling, dbt, MLflow, CI/CD, Terraform, Kubernetes</t>
+          <t>S3, RDS, Azure, Scala, Snowflake, SQL Server, Power BI, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=539a18aebac4ef5f</t>
+          <t>https://www.indeed.com/viewjob?jk=4afc3e61f8ae8b7b</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Attribution Expansion</t>
+          <t>Sr. Informatica IDMC MDM Software Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>TRM Labs</t>
+          <t>RBC</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Spark, Snowflake, Data Modeling, dbt, MLflow, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26436308d22e947d</t>
+          <t>https://www.indeed.com/viewjob?jk=5346f4c5e2b5352a</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer, Attribution Expansion</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>TRM Labs</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, BigQuery, Spark, Snowflake, Data Modeling, dbt, MLflow, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1315e6e62a7714e8</t>
+          <t>https://www.indeed.com/viewjob?jk=539a18aebac4ef5f</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Senior Data Engineer, Attribution Expansion</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Guidewire Software, Inc.</t>
+          <t>TRM Labs</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>RDS, BigQuery, Spark, Snowflake, Data Modeling, dbt, MLflow, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b5e082bd1857b0f</t>
+          <t>https://www.indeed.com/viewjob?jk=26436308d22e947d</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-05.xlsx
+++ b/results/job_matches_2026-03-05.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G87"/>
+  <dimension ref="A1:G86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,17 +538,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Client Authentication</t>
+          <t>Senior Data Engineer, ACVMax</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>ACV Auctions</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Southlake, TX, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>IAM, RDS, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a908b362cb914674</t>
+          <t>https://www.indeed.com/viewjob?jk=6c28dd5d00192a5b</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, ACVMax</t>
+          <t>Senior Data Engineer, Client Authentication</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ACV Auctions</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>Southlake, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS</t>
+          <t>IAM, RDS, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c28dd5d00192a5b</t>
+          <t>https://www.indeed.com/viewjob?jk=a908b362cb914674</t>
         </is>
       </c>
     </row>
@@ -818,17 +818,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Google Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>NMI</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Schaumburg, IL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,34 +836,34 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Kafka, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9188fd233f524c42</t>
+          <t>https://www.indeed.com/viewjob?jk=e7cac4b03aa7cfe7</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Google Cloud Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>NMI</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Schaumburg, IL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,17 +871,17 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Kafka, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7cac4b03aa7cfe7</t>
+          <t>https://www.indeed.com/viewjob?jk=9188fd233f524c42</t>
         </is>
       </c>
     </row>
@@ -923,17 +923,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Engineer - DevOps/ DataOps</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>FICO</t>
+          <t>Alight Solutions</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, DataOps, MLOps, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, GCP, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1ed15cfc823b0b7</t>
+          <t>https://www.indeed.com/viewjob?jk=398f35933211332f</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>Senior Engineer - DevOps/ DataOps</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Alight Solutions</t>
+          <t>FICO</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, GCP, Scala, CI/CD</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, DataOps, MLOps, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=398f35933211332f</t>
+          <t>https://www.indeed.com/viewjob?jk=e1ed15cfc823b0b7</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>SQL Developer - Enterprise Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SRS Distribution</t>
+          <t>Pantherx Specialty Llc</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>McKinney, TX, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Hadoop, Hive, Spark, Scala, Snowflake</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cde050af8749e53</t>
+          <t>https://www.indeed.com/viewjob?jk=41d495363374161e</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SQL Developer - Enterprise Data &amp; Analytics</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Pantherx Specialty Llc</t>
+          <t>SRS Distribution</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>McKinney, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Hadoop, Hive, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41d495363374161e</t>
+          <t>https://www.indeed.com/viewjob?jk=4cde050af8749e53</t>
         </is>
       </c>
     </row>
@@ -1168,52 +1168,52 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Incremental CRM - Data Developer 1</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Barclays</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Whippany, NJ, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, RDS, Databricks, Scala, SQL Server, ETL</t>
+          <t>AWS, Kinesis, IAM, Databricks, Spark, Scala, Kafka, Snowflake, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c7931e975a12585</t>
+          <t>https://www.indeed.com/viewjob?jk=a021dbda97cc3405</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Software Engineer - Authentication</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Pindrop</t>
+          <t>Disney Experiences</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, RDS, Scala, MySQL, DynamoDB, MLOps, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Scala, DynamoDB, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6513fcf97bbfd044</t>
+          <t>https://www.indeed.com/viewjob?jk=0a7ddc3760328a54</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Software Engineer - Authentication</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Pindrop</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, IAM, Databricks, Spark, Scala, Kafka, Snowflake, NoSQL, CI/CD</t>
+          <t>AWS, Kinesis, S3, RDS, Scala, MySQL, DynamoDB, MLOps, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a021dbda97cc3405</t>
+          <t>https://www.indeed.com/viewjob?jk=6513fcf97bbfd044</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>SSO Administrator</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Disney Experiences</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Scala, DynamoDB, NoSQL, ETL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, PostgreSQL, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,59 +1301,59 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a7ddc3760328a54</t>
+          <t>https://www.indeed.com/viewjob?jk=a9064a81c91aa262</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SSO Administrator</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Advance Auto Parts</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, PostgreSQL, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9064a81c91aa262</t>
+          <t>https://www.indeed.com/viewjob?jk=3e2d8bc5a4c9174d</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Commercial Software</t>
+          <t>IT Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Novolex</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Lake Forest, IL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, Oracle, MySQL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f3de39cf73c3663</t>
+          <t>https://www.indeed.com/viewjob?jk=024a63ca708c8a8f</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AWS DevOps Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Halo Creative &amp; Media LLP</t>
+          <t>Seqster PDM, Inc</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, Lambda, S3, IAM, RDS, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=371d6385735b0f59</t>
+          <t>https://www.indeed.com/viewjob?jk=191c0857581cffe3</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Advance Auto Parts</t>
+          <t>Halo Creative &amp; Media LLP</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e2d8bc5a4c9174d</t>
+          <t>https://www.indeed.com/viewjob?jk=371d6385735b0f59</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>IT Data Engineer</t>
+          <t>Senior Software Engineer - Commercial Software</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Novolex</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Lake Forest, IL, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, Oracle, MySQL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=024a63ca708c8a8f</t>
+          <t>https://www.indeed.com/viewjob?jk=5f3de39cf73c3663</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>AWS DevOps Engineer</t>
+          <t>Java Software Engineer II (US)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Seqster PDM, Inc</t>
+          <t>TD Bank</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Mount Laurel, NJ, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>RDS, Azure, Scala, NoSQL, Splunk, Jenkins, Maven, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,59 +1581,59 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=191c0857581cffe3</t>
+          <t>https://www.indeed.com/viewjob?jk=8ee89e940b02cc06</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Java Software Engineer II (US)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>TD Bank</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Mount Laurel, NJ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, NoSQL, Splunk, Jenkins, Maven, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ee89e940b02cc06</t>
+          <t>https://www.indeed.com/viewjob?jk=38b673fd36dffa19</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Daniels Health</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38b673fd36dffa19</t>
+          <t>https://www.indeed.com/viewjob?jk=3486f1249174e37a</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End (Java, Go, AWS)</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Daniels Health</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Docker</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e716b4195b2da30b</t>
+          <t>https://www.indeed.com/viewjob?jk=1df7caac86af2291</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End (Java, Go, AWS)</t>
+          <t>ATC - AI &amp; Data Analyst - NAELFY26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Saint Petersburg, FL, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1b9bbef981d9232</t>
+          <t>https://www.indeed.com/viewjob?jk=1ce7a50a4bbe9ef2</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Data Engineer, Data Product</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Daniels Health</t>
+          <t>TRM Labs</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
+          <t>RDS, BigQuery, Dataflow, Spark, Scala, Kafka, dbt, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3486f1249174e37a</t>
+          <t>https://www.indeed.com/viewjob?jk=351b720407fa6f6d</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Analytics, Full-Stack Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Daniels Health</t>
+          <t>SCAN Health Plan</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1df7caac86af2291</t>
+          <t>https://www.indeed.com/viewjob?jk=c24274a4aa989f95</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ATC - AI &amp; Data Analyst - NAELFY26</t>
+          <t>Senior Software Engineer, Back End (Java, Go, AWS)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Saint Petersburg, FL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ce7a50a4bbe9ef2</t>
+          <t>https://www.indeed.com/viewjob?jk=e716b4195b2da30b</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Data Product</t>
+          <t>Senior Software Engineer, Back End (Java, Go, AWS)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>TRM Labs</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Dataflow, Spark, Scala, Kafka, dbt, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=351b720407fa6f6d</t>
+          <t>https://www.indeed.com/viewjob?jk=e1b9bbef981d9232</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Analytics, Full-Stack Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>SCAN Health Plan</t>
+          <t>Amplify</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Snowflake, ETL, ELT, dbt</t>
+          <t>AWS, S3, RDS, Snowflake, DynamoDB, Data Modeling, Kimball, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c24274a4aa989f95</t>
+          <t>https://www.indeed.com/viewjob?jk=b4d16d721d2057f3</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Software Engineer III - Java/Spark/AWS</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Amplify</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Snowflake, DynamoDB, Data Modeling, Kimball, ETL, ELT, dbt</t>
+          <t>AWS, EMR, Lambda, S3, ECS, RDS, Databricks, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4d16d721d2057f3</t>
+          <t>https://www.indeed.com/viewjob?jk=c95674c932d41fb6</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Software Engineer III - Java/Spark/AWS</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Weyerhaeuser</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, ECS, RDS, Databricks, Spark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, MLOps, MLflow, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c95674c932d41fb6</t>
+          <t>https://www.indeed.com/viewjob?jk=7d9f82346c5ff2d3</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Software Systems Engineer, Release Reliability &amp; Automation (Autonomous Vehicles)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Weyerhaeuser</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, MLOps, MLflow, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, Power BI, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d9f82346c5ff2d3</t>
+          <t>https://www.indeed.com/viewjob?jk=864266ab5f8e3aac</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Software Systems Engineer, Release Reliability &amp; Automation (Autonomous Vehicles)</t>
+          <t>Software Engineer (Junior)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>TORCH.AI</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Leawood, KS, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, Power BI, CI/CD, Jenkins</t>
+          <t>AWS, IAM, Azure, GCP, Kafka, PostgreSQL, MongoDB, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=864266ab5f8e3aac</t>
+          <t>https://www.indeed.com/viewjob?jk=28e432d03da8db08</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Software Engineer (Junior)</t>
+          <t>Software Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>TORCH.AI</t>
+          <t>Nightwing</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Leawood, KS, US USA</t>
+          <t>Clarksville, TN, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Kafka, PostgreSQL, MongoDB, NoSQL, ETL, CI/CD</t>
+          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28e432d03da8db08</t>
+          <t>https://www.indeed.com/viewjob?jk=887221a715d1ff03</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Clarksville, TN, US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=887221a715d1ff03</t>
+          <t>https://www.indeed.com/viewjob?jk=3322d87953168bdc</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Software Engineer (Hybrid)</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Nightwing</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Sterling, VA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3322d87953168bdc</t>
+          <t>https://www.indeed.com/viewjob?jk=a8b55e090bbab627</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Tableau Developer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Michael Kors</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>East Rutherford, NJ, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Glue, Redshift, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8b55e090bbab627</t>
+          <t>https://www.indeed.com/viewjob?jk=904e084e965a45c4</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Tableau Developer</t>
+          <t>Advanced Metering Infrastructure (AMI) Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Michael Kors</t>
+          <t>WSSC Water</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>East Rutherford, NJ, US USA</t>
+          <t>Laurel, MD, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Star Schema</t>
+          <t>RDS, Azure, Scala, Kafka, Oracle, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=904e084e965a45c4</t>
+          <t>https://www.indeed.com/viewjob?jk=c5b2aa36ee050b9b</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Advanced Metering Infrastructure (AMI) Engineer</t>
+          <t>Database Administrator</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>WSSC Water</t>
+          <t>Rogue Community College</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Laurel, MD, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,69 +2236,69 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Oracle, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, Power BI</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5b2aa36ee050b9b</t>
+          <t>https://www.indeed.com/viewjob?jk=7f9335cc41b5edf2</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Database Administrator</t>
+          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Rogue Community College</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, Power BI</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f9335cc41b5edf2</t>
+          <t>https://www.indeed.com/viewjob?jk=f85f1e8c0778adba</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, PySpark, Scala, MySQL, MongoDB, Docker, Kubernetes, Airflow</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd1518c4c02c12ef</t>
+          <t>https://www.indeed.com/viewjob?jk=3e2da1f14c27a331</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End (Python)</t>
+          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3864c05dc9b353f8</t>
+          <t>https://www.indeed.com/viewjob?jk=140d02e1f58501f6</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Engineer 2</t>
+          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>BLOC Resources, LLC</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Data Modeling, CI/CD</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c51290628ce41b82</t>
+          <t>https://www.indeed.com/viewjob?jk=eff547fec829449a</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer I, Applied AI</t>
+          <t>AWS Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Axon</t>
+          <t>Appex Innovation</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Glue, Lambda, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e858c83fc09cd77d</t>
+          <t>https://www.indeed.com/viewjob?jk=7f3534222ab81e17</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Platform</t>
+          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>TRM Labs</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Spark, Scala, Kafka, ETL, dbt, Terraform, Docker, Kubernetes</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a517be0e10b2a44</t>
+          <t>https://www.indeed.com/viewjob?jk=29d22d712d7958f0</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Data Platform</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>TRM Labs</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Spark, Scala, Kafka, ETL, dbt, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Spark, PySpark, Scala, MySQL, MongoDB, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60f6c2aecd2d1bdf</t>
+          <t>https://www.indeed.com/viewjob?jk=dd1518c4c02c12ef</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
+          <t>AWS Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Appex Innovation</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Glue, Lambda, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f85f1e8c0778adba</t>
+          <t>https://www.indeed.com/viewjob?jk=3886cb86a753634c</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
+          <t>Data Engineer 2</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>BLOC Resources, LLC</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,17 +2551,17 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e2da1f14c27a331</t>
+          <t>https://www.indeed.com/viewjob?jk=c51290628ce41b82</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2591,29 +2591,29 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=140d02e1f58501f6</t>
+          <t>https://www.indeed.com/viewjob?jk=f9637232a826c3ad</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>CNH Industrial</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eff547fec829449a</t>
+          <t>https://www.indeed.com/viewjob?jk=e5b3837921976566</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>AWS Data Engineer</t>
+          <t>Senior Software Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Appex Innovation</t>
+          <t>TRM Labs</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD</t>
+          <t>RDS, BigQuery, Spark, Scala, Kafka, ETL, dbt, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f3534222ab81e17</t>
+          <t>https://www.indeed.com/viewjob?jk=8a517be0e10b2a44</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
+          <t>Senior Data Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>TRM Labs</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>RDS, BigQuery, Spark, Scala, Kafka, ETL, dbt, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29d22d712d7958f0</t>
+          <t>https://www.indeed.com/viewjob?jk=60f6c2aecd2d1bdf</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>AWS Data Engineer</t>
+          <t>Senior Data Engineer - Microsoft Fabric</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Appex Innovation</t>
+          <t>EoS Fitness</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ELT, Power BI</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3886cb86a753634c</t>
+          <t>https://www.indeed.com/viewjob?jk=7bd7f3590528db3c</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>PGA TOUR Superstore</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Roswell, GA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9637232a826c3ad</t>
+          <t>https://www.indeed.com/viewjob?jk=73bdb2d180484ce2</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Software Engineer, Back End (Python)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>CNH Industrial</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5b3837921976566</t>
+          <t>https://www.indeed.com/viewjob?jk=3864c05dc9b353f8</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Microsoft Fabric</t>
+          <t>Sr. Software Engineer I, Applied AI</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>EoS Fitness</t>
+          <t>Axon</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bd7f3590528db3c</t>
+          <t>https://www.indeed.com/viewjob?jk=e858c83fc09cd77d</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Customer Reliability Engineer, Airflow</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>PGA TOUR Superstore</t>
+          <t>Astronomer</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Roswell, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, Snowflake, PostgreSQL, dbt, DataOps, Docker</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73bdb2d180484ce2</t>
+          <t>https://www.indeed.com/viewjob?jk=6ac244565083c1d9</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Customer Reliability Engineer, Airflow</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Astronomer</t>
+          <t>RapidFire Safety &amp; Security</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, Snowflake, PostgreSQL, dbt, DataOps, Docker</t>
+          <t>RDS, Azure, Scala, SQL Server, Data Modeling, Star Schema, Fact Tables, Dimension Tables, ETL, Power BI</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ac244565083c1d9</t>
+          <t>https://www.indeed.com/viewjob?jk=8afc73df8ef8f40e</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Salesforce Architect - Senior</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>RapidFire Safety &amp; Security</t>
+          <t>CommunityForce Inc.</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, Data Modeling, Star Schema, Fact Tables, Dimension Tables, ETL, Power BI</t>
+          <t>ECS, RDS, Azure, Scala, Kafka, Data Modeling, ETL, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8afc73df8ef8f40e</t>
+          <t>https://www.indeed.com/viewjob?jk=7d236cba8a6e8ae3</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Salesforce Architect - Senior</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>CommunityForce Inc.</t>
+          <t>Callaway Golf</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>ECS, RDS, Azure, Scala, Kafka, Data Modeling, ETL, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, Azure, Databricks, Spark, Snowflake, ETL, ELT, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d236cba8a6e8ae3</t>
+          <t>https://www.indeed.com/viewjob?jk=ab2d181891cc2eee</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Software Engineer - Master</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Emed</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fb1207979169793</t>
+          <t>https://www.indeed.com/viewjob?jk=1e29e1c3d36f0e7c</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Data Engineer - GRC Technology</t>
+          <t>Sr. Data Engineer, Engineering &amp; Ops</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>NBCUniversal</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, ETL, ELT</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Snowflake, ELT, dbt, MLOps, Airflow</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8842e67bf37c518a</t>
+          <t>https://www.indeed.com/viewjob?jk=df536a2594fa5881</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Callaway Golf</t>
+          <t>TRM Labs</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Spark, Snowflake, ETL, ELT, Terraform, Kubernetes, Git</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, ETL, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab2d181891cc2eee</t>
+          <t>https://www.indeed.com/viewjob?jk=dcb7ea8003fbc5dc</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Microsoft Entra</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Emed</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Oracle, Data Modeling, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e29e1c3d36f0e7c</t>
+          <t>https://www.indeed.com/viewjob?jk=f61688604ed96074</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer, Engineering &amp; Ops</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>NBCUniversal</t>
+          <t>Westchester Medical Center Health Network</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Valhalla, NY, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Snowflake, ELT, dbt, MLOps, Airflow</t>
+          <t>AWS, RDS, Azure, Snowflake, SQL Server, Data Modeling, ELT, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df536a2594fa5881</t>
+          <t>https://www.indeed.com/viewjob?jk=d807a7856ebe08db</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Data Engineer - GRC Technology</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>TRM Labs</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, ETL, dbt, Power BI, Tableau, CI/CD</t>
+          <t>AWS, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dcb7ea8003fbc5dc</t>
+          <t>https://www.indeed.com/viewjob?jk=8842e67bf37c518a</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Microsoft Entra</t>
+          <t>Software Engineer - Master</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Oracle, Data Modeling, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f61688604ed96074</t>
+          <t>https://www.indeed.com/viewjob?jk=3fb1207979169793</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Westchester Medical Center Health Network</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Valhalla, NY, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Snowflake, SQL Server, Data Modeling, ELT, Power BI, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d807a7856ebe08db</t>
+          <t>https://www.indeed.com/viewjob?jk=1315e6e62a7714e8</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Guidewire Software, Inc.</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1315e6e62a7714e8</t>
+          <t>https://www.indeed.com/viewjob?jk=3b5e082bd1857b0f</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>.NET Developer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Guidewire Software, Inc.</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>S3, RDS, Azure, Scala, Snowflake, SQL Server, Power BI, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b5e082bd1857b0f</t>
+          <t>https://www.indeed.com/viewjob?jk=4afc3e61f8ae8b7b</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>.NET Developer</t>
+          <t>Sr. Informatica IDMC MDM Software Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>RBC</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Scala, Snowflake, SQL Server, Power BI, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4afc3e61f8ae8b7b</t>
+          <t>https://www.indeed.com/viewjob?jk=5346f4c5e2b5352a</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Sr. Informatica IDMC MDM Software Engineer</t>
+          <t>Senior Data Engineer, Attribution Expansion</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>RBC</t>
+          <t>TRM Labs</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, ETL, CI/CD</t>
+          <t>RDS, BigQuery, Spark, Snowflake, Data Modeling, dbt, MLflow, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5346f4c5e2b5352a</t>
+          <t>https://www.indeed.com/viewjob?jk=539a18aebac4ef5f</t>
         </is>
       </c>
     </row>
@@ -3435,41 +3435,6 @@
         </is>
       </c>
       <c r="G86" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=539a18aebac4ef5f</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer, Attribution Expansion</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>TRM Labs</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D87" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>RDS, BigQuery, Spark, Snowflake, Data Modeling, dbt, MLflow, CI/CD, Terraform, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=26436308d22e947d</t>
         </is>

--- a/results/job_matches_2026-03-05.xlsx
+++ b/results/job_matches_2026-03-05.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G86"/>
+  <dimension ref="A1:G89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,17 +538,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, ACVMax</t>
+          <t>Senior Data Engineer, Client Authentication</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ACV Auctions</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>Southlake, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS</t>
+          <t>IAM, RDS, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c28dd5d00192a5b</t>
+          <t>https://www.indeed.com/viewjob?jk=a908b362cb914674</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Client Authentication</t>
+          <t>Senior Data Engineer, ACVMax</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>ACV Auctions</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Southlake, TX, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>IAM, RDS, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a908b362cb914674</t>
+          <t>https://www.indeed.com/viewjob?jk=6c28dd5d00192a5b</t>
         </is>
       </c>
     </row>
@@ -818,17 +818,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Google Cloud Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>NMI</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Schaumburg, IL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,34 +836,34 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Kafka, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7cac4b03aa7cfe7</t>
+          <t>https://www.indeed.com/viewjob?jk=9188fd233f524c42</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Google Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>NMI</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Schaumburg, IL, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,17 +871,17 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Kafka, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9188fd233f524c42</t>
+          <t>https://www.indeed.com/viewjob?jk=e7cac4b03aa7cfe7</t>
         </is>
       </c>
     </row>
@@ -923,17 +923,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>Senior Engineer - DevOps/ DataOps</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Alight Solutions</t>
+          <t>FICO</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, GCP, Scala, CI/CD</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, DataOps, MLOps, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=398f35933211332f</t>
+          <t>https://www.indeed.com/viewjob?jk=e1ed15cfc823b0b7</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Engineer - DevOps/ DataOps</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>FICO</t>
+          <t>Alight Solutions</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, DataOps, MLOps, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, GCP, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1ed15cfc823b0b7</t>
+          <t>https://www.indeed.com/viewjob?jk=398f35933211332f</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SQL Developer - Enterprise Data &amp; Analytics</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Pantherx Specialty Llc</t>
+          <t>SRS Distribution</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>McKinney, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Hadoop, Hive, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41d495363374161e</t>
+          <t>https://www.indeed.com/viewjob?jk=4cde050af8749e53</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>SQL Developer - Enterprise Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SRS Distribution</t>
+          <t>Pantherx Specialty Llc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>McKinney, TX, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Hadoop, Hive, Spark, Scala, Snowflake</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cde050af8749e53</t>
+          <t>https://www.indeed.com/viewjob?jk=41d495363374161e</t>
         </is>
       </c>
     </row>
@@ -1168,17 +1168,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Software Engineer - Authentication</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Pindrop</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, IAM, Databricks, Spark, Scala, Kafka, Snowflake, NoSQL, CI/CD</t>
+          <t>AWS, Kinesis, S3, RDS, Scala, MySQL, DynamoDB, MLOps, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a021dbda97cc3405</t>
+          <t>https://www.indeed.com/viewjob?jk=6513fcf97bbfd044</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Disney Experiences</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Scala, DynamoDB, NoSQL, ETL</t>
+          <t>AWS, Kinesis, IAM, Databricks, Spark, Scala, Kafka, Snowflake, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a7ddc3760328a54</t>
+          <t>https://www.indeed.com/viewjob?jk=a021dbda97cc3405</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Software Engineer - Authentication</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Pindrop</t>
+          <t>Disney Experiences</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,17 +1256,17 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, RDS, Scala, MySQL, DynamoDB, MLOps, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Scala, DynamoDB, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6513fcf97bbfd044</t>
+          <t>https://www.indeed.com/viewjob?jk=0a7ddc3760328a54</t>
         </is>
       </c>
     </row>
@@ -1308,17 +1308,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Software Engineer - Commercial Software</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Advance Auto Parts</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, Oracle, MySQL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e2d8bc5a4c9174d</t>
+          <t>https://www.indeed.com/viewjob?jk=5f3de39cf73c3663</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>IT Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Novolex</t>
+          <t>SRR Consultants</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Lake Forest, IL, US USA</t>
+          <t>Piscataway, NJ, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Glue, S3, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=024a63ca708c8a8f</t>
+          <t>https://www.indeed.com/viewjob?jk=88619a1e983eef30</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer, Data Lakehouse Infrastructure</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>SRR Consultants</t>
+          <t>TRM Labs</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Piscataway, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88619a1e983eef30</t>
+          <t>https://www.indeed.com/viewjob?jk=e899ea40640da235</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Data Lakehouse Infrastructure</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>TRM Labs</t>
+          <t>Halo Creative &amp; Media LLP</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e899ea40640da235</t>
+          <t>https://www.indeed.com/viewjob?jk=371d6385735b0f59</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>AWS DevOps Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Seqster PDM, Inc</t>
+          <t>Advance Auto Parts</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=191c0857581cffe3</t>
+          <t>https://www.indeed.com/viewjob?jk=3e2d8bc5a4c9174d</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>IT Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Halo Creative &amp; Media LLP</t>
+          <t>Novolex</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Lake Forest, IL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=371d6385735b0f59</t>
+          <t>https://www.indeed.com/viewjob?jk=024a63ca708c8a8f</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Commercial Software</t>
+          <t>AWS DevOps Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Seqster PDM, Inc</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, Oracle, MySQL</t>
+          <t>AWS, Lambda, S3, IAM, RDS, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f3de39cf73c3663</t>
+          <t>https://www.indeed.com/viewjob?jk=191c0857581cffe3</t>
         </is>
       </c>
     </row>
@@ -1623,17 +1623,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Software Engineer, Back End (Java, Go, AWS)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Daniels Health</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3486f1249174e37a</t>
+          <t>https://www.indeed.com/viewjob?jk=e716b4195b2da30b</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Software Engineer, Back End (Java, Go, AWS)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Daniels Health</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1df7caac86af2291</t>
+          <t>https://www.indeed.com/viewjob?jk=e1b9bbef981d9232</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ATC - AI &amp; Data Analyst - NAELFY26</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>Daniels Health</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Saint Petersburg, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ce7a50a4bbe9ef2</t>
+          <t>https://www.indeed.com/viewjob?jk=3486f1249174e37a</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Data Product</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>TRM Labs</t>
+          <t>Daniels Health</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Dataflow, Spark, Scala, Kafka, dbt, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=351b720407fa6f6d</t>
+          <t>https://www.indeed.com/viewjob?jk=1df7caac86af2291</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Analytics, Full-Stack Engineer</t>
+          <t>ATC - AI &amp; Data Analyst - NAELFY26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>SCAN Health Plan</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>Saint Petersburg, FL, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Snowflake, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c24274a4aa989f95</t>
+          <t>https://www.indeed.com/viewjob?jk=1ce7a50a4bbe9ef2</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End (Java, Go, AWS)</t>
+          <t>Senior Data Engineer, Data Product</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>TRM Labs</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Docker</t>
+          <t>RDS, BigQuery, Dataflow, Spark, Scala, Kafka, dbt, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e716b4195b2da30b</t>
+          <t>https://www.indeed.com/viewjob?jk=351b720407fa6f6d</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End (Java, Go, AWS)</t>
+          <t>Analytics, Full-Stack Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>SCAN Health Plan</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Docker</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1b9bbef981d9232</t>
+          <t>https://www.indeed.com/viewjob?jk=c24274a4aa989f95</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>GD162 Senior Software Systems Engineer &amp; Architect</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Amplify</t>
+          <t>ADNET Systems, Inc</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Greenbelt, MD, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Snowflake, DynamoDB, Data Modeling, Kimball, ETL, ELT, dbt</t>
+          <t>AWS, Lambda, S3, Scala, Dask, DynamoDB, ELT, CI/CD, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4d16d721d2057f3</t>
+          <t>https://www.indeed.com/viewjob?jk=ef183b27f01923fb</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Software Engineer III - Java/Spark/AWS</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Amplify</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, ECS, RDS, Databricks, Spark, Scala, Snowflake</t>
+          <t>AWS, S3, RDS, Snowflake, DynamoDB, Data Modeling, Kimball, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c95674c932d41fb6</t>
+          <t>https://www.indeed.com/viewjob?jk=b4d16d721d2057f3</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Database Administrator</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Weyerhaeuser</t>
+          <t>Hard Rock International</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Hollywood, FL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, MLOps, MLflow, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, Snowflake, PostgreSQL, Cassandra, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d9f82346c5ff2d3</t>
+          <t>https://www.indeed.com/viewjob?jk=169d4a00d377fdae</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Software Systems Engineer, Release Reliability &amp; Automation (Autonomous Vehicles)</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Weyerhaeuser</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, Power BI, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, MLOps, MLflow, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=864266ab5f8e3aac</t>
+          <t>https://www.indeed.com/viewjob?jk=7d9f82346c5ff2d3</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Software Engineer (Junior)</t>
+          <t>Software Systems Engineer, Release Reliability &amp; Automation (Autonomous Vehicles)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>TORCH.AI</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Leawood, KS, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Kafka, PostgreSQL, MongoDB, NoSQL, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, Power BI, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28e432d03da8db08</t>
+          <t>https://www.indeed.com/viewjob?jk=864266ab5f8e3aac</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Software Engineer (Hybrid)</t>
+          <t>Software Engineer (Junior)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Nightwing</t>
+          <t>TORCH.AI</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Clarksville, TN, US USA</t>
+          <t>Leawood, KS, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, IAM, Azure, GCP, Kafka, PostgreSQL, MongoDB, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=887221a715d1ff03</t>
+          <t>https://www.indeed.com/viewjob?jk=28e432d03da8db08</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Sterling, VA, US USA</t>
+          <t>Clarksville, TN, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3322d87953168bdc</t>
+          <t>https://www.indeed.com/viewjob?jk=887221a715d1ff03</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Software Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Nightwing</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8b55e090bbab627</t>
+          <t>https://www.indeed.com/viewjob?jk=3322d87953168bdc</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Tableau Developer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Michael Kors</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>East Rutherford, NJ, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=904e084e965a45c4</t>
+          <t>https://www.indeed.com/viewjob?jk=a8b55e090bbab627</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Advanced Metering Infrastructure (AMI) Engineer</t>
+          <t>Software Engineer III - Java/Spark/AWS</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>WSSC Water</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Laurel, MD, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Oracle, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps</t>
+          <t>AWS, EMR, Lambda, S3, ECS, RDS, Databricks, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5b2aa36ee050b9b</t>
+          <t>https://www.indeed.com/viewjob?jk=c95674c932d41fb6</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Database Administrator</t>
+          <t>Tableau Developer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Rogue Community College</t>
+          <t>Michael Kors</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>East Rutherford, NJ, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,69 +2236,69 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, Power BI</t>
+          <t>AWS, Glue, Redshift, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f9335cc41b5edf2</t>
+          <t>https://www.indeed.com/viewjob?jk=904e084e965a45c4</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
+          <t>Advanced Metering Infrastructure (AMI) Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>WSSC Water</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Laurel, MD, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, Kafka, Oracle, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f85f1e8c0778adba</t>
+          <t>https://www.indeed.com/viewjob?jk=c5b2aa36ee050b9b</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Spark, PySpark, Scala, MySQL, MongoDB, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e2da1f14c27a331</t>
+          <t>https://www.indeed.com/viewjob?jk=dd1518c4c02c12ef</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
+          <t>Senior Software Engineer, Back End (Python)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=140d02e1f58501f6</t>
+          <t>https://www.indeed.com/viewjob?jk=3864c05dc9b353f8</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
+          <t>Data Engineer 2</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>BLOC Resources, LLC</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eff547fec829449a</t>
+          <t>https://www.indeed.com/viewjob?jk=c51290628ce41b82</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>AWS Data Engineer</t>
+          <t>Sr. Software Engineer I, Applied AI</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Appex Innovation</t>
+          <t>Axon</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f3534222ab81e17</t>
+          <t>https://www.indeed.com/viewjob?jk=e858c83fc09cd77d</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
+          <t>Senior Software Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>TRM Labs</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>RDS, BigQuery, Spark, Scala, Kafka, ETL, dbt, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29d22d712d7958f0</t>
+          <t>https://www.indeed.com/viewjob?jk=8a517be0e10b2a44</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Data Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>TRM Labs</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, PySpark, Scala, MySQL, MongoDB, Docker, Kubernetes, Airflow</t>
+          <t>RDS, BigQuery, Spark, Scala, Kafka, ETL, dbt, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd1518c4c02c12ef</t>
+          <t>https://www.indeed.com/viewjob?jk=60f6c2aecd2d1bdf</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>AWS Data Engineer</t>
+          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Appex Innovation</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3886cb86a753634c</t>
+          <t>https://www.indeed.com/viewjob?jk=f85f1e8c0778adba</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineer 2</t>
+          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>BLOC Resources, LLC</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,17 +2551,17 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Data Modeling, CI/CD</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c51290628ce41b82</t>
+          <t>https://www.indeed.com/viewjob?jk=3e2da1f14c27a331</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2591,29 +2591,29 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9637232a826c3ad</t>
+          <t>https://www.indeed.com/viewjob?jk=140d02e1f58501f6</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>CNH Industrial</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5b3837921976566</t>
+          <t>https://www.indeed.com/viewjob?jk=eff547fec829449a</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Platform</t>
+          <t>AWS Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>TRM Labs</t>
+          <t>Appex Innovation</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Spark, Scala, Kafka, ETL, dbt, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Glue, Lambda, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a517be0e10b2a44</t>
+          <t>https://www.indeed.com/viewjob?jk=7f3534222ab81e17</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Data Platform</t>
+          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>TRM Labs</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Spark, Scala, Kafka, ETL, dbt, Terraform, Docker, Kubernetes</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60f6c2aecd2d1bdf</t>
+          <t>https://www.indeed.com/viewjob?jk=29d22d712d7958f0</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Microsoft Fabric</t>
+          <t>AWS Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>EoS Fitness</t>
+          <t>Appex Innovation</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ELT, Power BI</t>
+          <t>AWS, Glue, Lambda, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bd7f3590528db3c</t>
+          <t>https://www.indeed.com/viewjob?jk=3886cb86a753634c</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>PGA TOUR Superstore</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Roswell, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73bdb2d180484ce2</t>
+          <t>https://www.indeed.com/viewjob?jk=f9637232a826c3ad</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End (Python)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>CNH Industrial</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3864c05dc9b353f8</t>
+          <t>https://www.indeed.com/viewjob?jk=e5b3837921976566</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer I, Applied AI</t>
+          <t>Senior Data Engineer - Microsoft Fabric</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Axon</t>
+          <t>EoS Fitness</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ELT, Power BI</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e858c83fc09cd77d</t>
+          <t>https://www.indeed.com/viewjob?jk=7bd7f3590528db3c</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Customer Reliability Engineer, Airflow</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Astronomer</t>
+          <t>PGA TOUR Superstore</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Roswell, GA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, Snowflake, PostgreSQL, dbt, DataOps, Docker</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ac244565083c1d9</t>
+          <t>https://www.indeed.com/viewjob?jk=73bdb2d180484ce2</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Customer Reliability Engineer, Airflow</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>RapidFire Safety &amp; Security</t>
+          <t>Astronomer</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, Data Modeling, Star Schema, Fact Tables, Dimension Tables, ETL, Power BI</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, Snowflake, PostgreSQL, dbt, DataOps, Docker</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8afc73df8ef8f40e</t>
+          <t>https://www.indeed.com/viewjob?jk=6ac244565083c1d9</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Salesforce Architect - Senior</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>CommunityForce Inc.</t>
+          <t>RapidFire Safety &amp; Security</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>ECS, RDS, Azure, Scala, Kafka, Data Modeling, ETL, CI/CD, Jenkins, Azure DevOps</t>
+          <t>RDS, Azure, Scala, SQL Server, Data Modeling, Star Schema, Fact Tables, Dimension Tables, ETL, Power BI</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d236cba8a6e8ae3</t>
+          <t>https://www.indeed.com/viewjob?jk=8afc73df8ef8f40e</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Salesforce Architect - Senior</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Callaway Golf</t>
+          <t>CommunityForce Inc.</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Spark, Snowflake, ETL, ELT, Terraform, Kubernetes, Git</t>
+          <t>ECS, RDS, Azure, Scala, Kafka, Data Modeling, ETL, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab2d181891cc2eee</t>
+          <t>https://www.indeed.com/viewjob?jk=7d236cba8a6e8ae3</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer - Master</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Emed</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e29e1c3d36f0e7c</t>
+          <t>https://www.indeed.com/viewjob?jk=3fb1207979169793</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer, Engineering &amp; Ops</t>
+          <t>Data Engineer - GRC Technology</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>NBCUniversal</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Snowflake, ELT, dbt, MLOps, Airflow</t>
+          <t>AWS, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df536a2594fa5881</t>
+          <t>https://www.indeed.com/viewjob?jk=8842e67bf37c518a</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Informatica MDM and Databricks Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>TRM Labs</t>
+          <t>Xpedient Technologies</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, ETL, dbt, Power BI, Tableau, CI/CD</t>
+          <t>RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dcb7ea8003fbc5dc</t>
+          <t>https://www.indeed.com/viewjob?jk=4cb9515aa944d7a5</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Microsoft Entra</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Callaway Golf</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Oracle, Data Modeling, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, Azure, Databricks, Spark, Snowflake, ETL, ELT, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f61688604ed96074</t>
+          <t>https://www.indeed.com/viewjob?jk=ab2d181891cc2eee</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Westchester Medical Center Health Network</t>
+          <t>Emed</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Valhalla, NY, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Snowflake, SQL Server, Data Modeling, ELT, Power BI, Tableau, CI/CD</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d807a7856ebe08db</t>
+          <t>https://www.indeed.com/viewjob?jk=1e29e1c3d36f0e7c</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Data Engineer - GRC Technology</t>
+          <t>Sr. Data Engineer, Engineering &amp; Ops</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>NBCUniversal</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, ETL, ELT</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Snowflake, ELT, dbt, MLOps, Airflow</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8842e67bf37c518a</t>
+          <t>https://www.indeed.com/viewjob?jk=df536a2594fa5881</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Software Engineer - Master</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>TRM Labs</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, ETL, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fb1207979169793</t>
+          <t>https://www.indeed.com/viewjob?jk=dcb7ea8003fbc5dc</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Microsoft Entra</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Oracle, Data Modeling, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1315e6e62a7714e8</t>
+          <t>https://www.indeed.com/viewjob?jk=f61688604ed96074</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Guidewire Software, Inc.</t>
+          <t>Westchester Medical Center Health Network</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Valhalla, NY, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Snowflake, SQL Server, Data Modeling, ELT, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b5e082bd1857b0f</t>
+          <t>https://www.indeed.com/viewjob?jk=d807a7856ebe08db</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>.NET Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Daniels Health</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Scala, Snowflake, SQL Server, Power BI, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, ETL, ELT, Git</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4afc3e61f8ae8b7b</t>
+          <t>https://www.indeed.com/viewjob?jk=447d4d5607b3f3c6</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Sr. Informatica IDMC MDM Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>RBC</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5346f4c5e2b5352a</t>
+          <t>https://www.indeed.com/viewjob?jk=1315e6e62a7714e8</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Attribution Expansion</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>TRM Labs</t>
+          <t>Guidewire Software, Inc.</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Spark, Snowflake, Data Modeling, dbt, MLflow, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=539a18aebac4ef5f</t>
+          <t>https://www.indeed.com/viewjob?jk=3b5e082bd1857b0f</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Attribution Expansion</t>
+          <t>.NET Developer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>TRM Labs</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,15 +3426,120 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
+          <t>S3, RDS, Azure, Scala, Snowflake, SQL Server, Power BI, CI/CD, Azure DevOps, Git</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4afc3e61f8ae8b7b</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Sr. Informatica IDMC MDM Software Engineer</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>RBC</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Minneapolis, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, ETL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5346f4c5e2b5352a</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer, Attribution Expansion</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>TRM Labs</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
           <t>RDS, BigQuery, Spark, Snowflake, Data Modeling, dbt, MLflow, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=539a18aebac4ef5f</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer, Attribution Expansion</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>TRM Labs</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>RDS, BigQuery, Spark, Snowflake, Data Modeling, dbt, MLflow, CI/CD, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=26436308d22e947d</t>
         </is>

--- a/results/job_matches_2026-03-05.xlsx
+++ b/results/job_matches_2026-03-05.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G89"/>
+  <dimension ref="A1:G85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,17 +538,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Client Authentication</t>
+          <t>Senior Data Engineer, ACVMax</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>ACV Auctions</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Southlake, TX, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>IAM, RDS, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a908b362cb914674</t>
+          <t>https://www.indeed.com/viewjob?jk=6c28dd5d00192a5b</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, ACVMax</t>
+          <t>Sr. Data Platform Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ACV Auctions</t>
+          <t>Real Time Medical Systems</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, IAM, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c28dd5d00192a5b</t>
+          <t>https://www.indeed.com/viewjob?jk=415686b53cfda723</t>
         </is>
       </c>
     </row>
@@ -618,7 +618,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Columbia, MD, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -636,59 +636,59 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=415686b53cfda723</t>
+          <t>https://www.indeed.com/viewjob?jk=41a92f9802d4f918</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sr. Data Platform Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Real Time Medical Systems</t>
+          <t>Valvoline Global Operations</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Columbia, MD, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>17.4</v>
+        <v>16</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, IAM, RDS, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP, Cloud Storage, Spark, PySpark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41a92f9802d4f918</t>
+          <t>https://www.indeed.com/viewjob?jk=ab16510fd1c2841d</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Enterprise Data Platform Engineer – Washington, DC</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Valvoline Global Operations</t>
+          <t>Creative Information Technology India</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Falls Church, VA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,42 +696,42 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP, Cloud Storage, Spark, PySpark</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Delta Live Tables, Photon, Scala, ETL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab16510fd1c2841d</t>
+          <t>https://www.indeed.com/viewjob?jk=0a74e373b48da5fc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Enterprise Data Platform Engineer – Washington, DC</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Creative Information Technology India</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Falls Church, VA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Delta Live Tables, Photon, Scala, ETL</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a74e373b48da5fc</t>
+          <t>https://www.indeed.com/viewjob?jk=9e8500146d476812</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e8500146d476812</t>
+          <t>https://www.indeed.com/viewjob?jk=2ad2838bd8f61427</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Google Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>NMI</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Schaumburg, IL, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Kafka, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ad2838bd8f61427</t>
+          <t>https://www.indeed.com/viewjob?jk=e7cac4b03aa7cfe7</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Specialist - System Management</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Glen Allen, VA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,42 +836,42 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Unity Catalog, Delta Live Tables, Spark, Databricks Lakehouse, SQL Server</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9188fd233f524c42</t>
+          <t>https://www.indeed.com/viewjob?jk=293f842904007fda</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Google Cloud Data Engineer</t>
+          <t>Senior Engineer - DevOps/ DataOps</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>NMI</t>
+          <t>FICO</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Schaumburg, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Kafka, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, DataOps, MLOps, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7cac4b03aa7cfe7</t>
+          <t>https://www.indeed.com/viewjob?jk=e1ed15cfc823b0b7</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Specialist - System Management</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Alight Solutions</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Glen Allen, VA, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Unity Catalog, Delta Live Tables, Spark, Databricks Lakehouse, SQL Server</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, GCP, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=293f842904007fda</t>
+          <t>https://www.indeed.com/viewjob?jk=398f35933211332f</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Engineer - DevOps/ DataOps</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>FICO</t>
+          <t>SRS Distribution</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>McKinney, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, DataOps, MLOps, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Hadoop, Hive, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1ed15cfc823b0b7</t>
+          <t>https://www.indeed.com/viewjob?jk=4cde050af8749e53</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>SQL Developer - Enterprise Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Alight Solutions</t>
+          <t>Pantherx Specialty Llc</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, GCP, Scala, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=398f35933211332f</t>
+          <t>https://www.indeed.com/viewjob?jk=41d495363374161e</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Sr. Software Engineer (Remote)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SRS Distribution</t>
+          <t>Inspira Financial</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>McKinney, TX, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,34 +1011,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Hadoop, Hive, Spark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, Azure Cosmos DB, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cde050af8749e53</t>
+          <t>https://www.indeed.com/viewjob?jk=1733261c550fa238</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SQL Developer - Enterprise Data &amp; Analytics</t>
+          <t>Sr. Software Engineer (Remote)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Pantherx Specialty Llc</t>
+          <t>Inspira Financial</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,34 +1046,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, Azure Cosmos DB, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41d495363374161e</t>
+          <t>https://www.indeed.com/viewjob?jk=5d0e899d198425eb</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer (Remote)</t>
+          <t>Specialist Programmer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Inspira Financial</t>
+          <t>Infosys</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,77 +1081,77 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, Azure Cosmos DB, ETL, CI/CD, Jenkins</t>
+          <t>AWS, Azure, GCP, Hadoop, Hive, Spark, PySpark, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1733261c550fa238</t>
+          <t>https://www.indeed.com/viewjob?jk=9772b3b8d4167ecc</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer (Remote)</t>
+          <t>Software Engineer - Authentication</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Inspira Financial</t>
+          <t>Pindrop</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, Azure Cosmos DB, ETL, CI/CD, Jenkins</t>
+          <t>AWS, Kinesis, S3, RDS, Scala, MySQL, DynamoDB, MLOps, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d0e899d198425eb</t>
+          <t>https://www.indeed.com/viewjob?jk=6513fcf97bbfd044</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Specialist Programmer</t>
+          <t>SSO Administrator</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Infosys</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, Hive, Spark, PySpark, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, PostgreSQL, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,67 +1161,67 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9772b3b8d4167ecc</t>
+          <t>https://www.indeed.com/viewjob?jk=a9064a81c91aa262</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Software Engineer - Authentication</t>
+          <t>Senior Software Engineer - Commercial Software</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Pindrop</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, RDS, Scala, MySQL, DynamoDB, MLOps, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, Oracle, MySQL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6513fcf97bbfd044</t>
+          <t>https://www.indeed.com/viewjob?jk=5f3de39cf73c3663</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>SRR Consultants</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Piscataway, NJ, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, IAM, Databricks, Spark, Scala, Kafka, Snowflake, NoSQL, CI/CD</t>
+          <t>AWS, Glue, S3, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a021dbda97cc3405</t>
+          <t>https://www.indeed.com/viewjob?jk=88619a1e983eef30</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Data Engineer, Data Lakehouse Infrastructure</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Disney Experiences</t>
+          <t>TRM Labs</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Scala, DynamoDB, NoSQL, ETL</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a7ddc3760328a54</t>
+          <t>https://www.indeed.com/viewjob?jk=e899ea40640da235</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>SSO Administrator</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Halo Creative &amp; Media LLP</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, PostgreSQL, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9064a81c91aa262</t>
+          <t>https://www.indeed.com/viewjob?jk=371d6385735b0f59</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Commercial Software</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Advance Auto Parts</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, Oracle, MySQL</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f3de39cf73c3663</t>
+          <t>https://www.indeed.com/viewjob?jk=3e2d8bc5a4c9174d</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>IT Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>SRR Consultants</t>
+          <t>Novolex</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Piscataway, NJ, US USA</t>
+          <t>Lake Forest, IL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88619a1e983eef30</t>
+          <t>https://www.indeed.com/viewjob?jk=024a63ca708c8a8f</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Data Lakehouse Infrastructure</t>
+          <t>AWS DevOps Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>TRM Labs</t>
+          <t>Seqster PDM, Inc</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, IAM, RDS, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e899ea40640da235</t>
+          <t>https://www.indeed.com/viewjob?jk=191c0857581cffe3</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Java Software Engineer II (US)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Halo Creative &amp; Media LLP</t>
+          <t>TD Bank</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Mount Laurel, NJ, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>RDS, Azure, Scala, NoSQL, Splunk, Jenkins, Maven, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=371d6385735b0f59</t>
+          <t>https://www.indeed.com/viewjob?jk=8ee89e940b02cc06</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Advance Auto Parts</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,102 +1476,102 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e2d8bc5a4c9174d</t>
+          <t>https://www.indeed.com/viewjob?jk=38b673fd36dffa19</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>IT Data Engineer</t>
+          <t>Senior Software Engineer, Back End (Java, Go, AWS)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Novolex</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Lake Forest, IL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=024a63ca708c8a8f</t>
+          <t>https://www.indeed.com/viewjob?jk=e716b4195b2da30b</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>AWS DevOps Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Seqster PDM, Inc</t>
+          <t>Daniels Health</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=191c0857581cffe3</t>
+          <t>https://www.indeed.com/viewjob?jk=3486f1249174e37a</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Java Software Engineer II (US)</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>TD Bank</t>
+          <t>Daniels Health</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Mount Laurel, NJ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, NoSQL, Splunk, Jenkins, Maven, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ee89e940b02cc06</t>
+          <t>https://www.indeed.com/viewjob?jk=1df7caac86af2291</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>ATC - AI &amp; Data Analyst - NAELFY26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Saint Petersburg, FL, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38b673fd36dffa19</t>
+          <t>https://www.indeed.com/viewjob?jk=1ce7a50a4bbe9ef2</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End (Java, Go, AWS)</t>
+          <t>Senior Data Engineer, Data Product</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>TRM Labs</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Docker</t>
+          <t>RDS, BigQuery, Dataflow, Spark, Scala, Kafka, dbt, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e716b4195b2da30b</t>
+          <t>https://www.indeed.com/viewjob?jk=351b720407fa6f6d</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End (Java, Go, AWS)</t>
+          <t>Analytics, Full-Stack Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>SCAN Health Plan</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Docker</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1b9bbef981d9232</t>
+          <t>https://www.indeed.com/viewjob?jk=c24274a4aa989f95</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>GD162 Senior Software Systems Engineer &amp; Architect</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Daniels Health</t>
+          <t>ADNET Systems, Inc</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Greenbelt, MD, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, Scala, Dask, DynamoDB, ELT, CI/CD, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3486f1249174e37a</t>
+          <t>https://www.indeed.com/viewjob?jk=ef183b27f01923fb</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Software Engineer, Intern - Summer 2026, Austin</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Daniels Health</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
+          <t>RDS, Kafka, MySQL, Cassandra, NoSQL, Splunk, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1df7caac86af2291</t>
+          <t>https://www.indeed.com/viewjob?jk=dd858b6050894467</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ATC - AI &amp; Data Analyst - NAELFY26</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>Amplify</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Saint Petersburg, FL, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, S3, RDS, Snowflake, DynamoDB, Data Modeling, Kimball, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ce7a50a4bbe9ef2</t>
+          <t>https://www.indeed.com/viewjob?jk=b4d16d721d2057f3</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Data Product</t>
+          <t>Database Administrator</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>TRM Labs</t>
+          <t>Hard Rock International</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Hollywood, FL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Dataflow, Spark, Scala, Kafka, dbt, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, Snowflake, PostgreSQL, Cassandra, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=351b720407fa6f6d</t>
+          <t>https://www.indeed.com/viewjob?jk=169d4a00d377fdae</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Analytics, Full-Stack Engineer</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>SCAN Health Plan</t>
+          <t>Weyerhaeuser</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Snowflake, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, MLOps, MLflow, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c24274a4aa989f95</t>
+          <t>https://www.indeed.com/viewjob?jk=7d9f82346c5ff2d3</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>GD162 Senior Software Systems Engineer &amp; Architect</t>
+          <t>Software Systems Engineer, Release Reliability &amp; Automation (Autonomous Vehicles)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>ADNET Systems, Inc</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Greenbelt, MD, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Scala, Dask, DynamoDB, ELT, CI/CD, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, Power BI, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef183b27f01923fb</t>
+          <t>https://www.indeed.com/viewjob?jk=864266ab5f8e3aac</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Software Engineer (Junior)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Amplify</t>
+          <t>TORCH.AI</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Leawood, KS, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Snowflake, DynamoDB, Data Modeling, Kimball, ETL, ELT, dbt</t>
+          <t>AWS, IAM, Azure, GCP, Kafka, PostgreSQL, MongoDB, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4d16d721d2057f3</t>
+          <t>https://www.indeed.com/viewjob?jk=28e432d03da8db08</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Database Administrator</t>
+          <t>Software Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Hard Rock International</t>
+          <t>Nightwing</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Hollywood, FL, US USA</t>
+          <t>Clarksville, TN, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, Snowflake, PostgreSQL, Cassandra, CI/CD, Terraform</t>
+          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=169d4a00d377fdae</t>
+          <t>https://www.indeed.com/viewjob?jk=887221a715d1ff03</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Software Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Weyerhaeuser</t>
+          <t>Nightwing</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, MLOps, MLflow, CI/CD, Terraform, Docker</t>
+          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d9f82346c5ff2d3</t>
+          <t>https://www.indeed.com/viewjob?jk=3322d87953168bdc</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Software Systems Engineer, Release Reliability &amp; Automation (Autonomous Vehicles)</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, Power BI, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=864266ab5f8e3aac</t>
+          <t>https://www.indeed.com/viewjob?jk=a8b55e090bbab627</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Software Engineer (Junior)</t>
+          <t>Software Engineer III - Java/Spark/AWS</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>TORCH.AI</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Leawood, KS, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Kafka, PostgreSQL, MongoDB, NoSQL, ETL, CI/CD</t>
+          <t>AWS, EMR, Lambda, S3, ECS, RDS, Databricks, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28e432d03da8db08</t>
+          <t>https://www.indeed.com/viewjob?jk=c95674c932d41fb6</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Software Engineer (Hybrid)</t>
+          <t>Tableau Developer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Nightwing</t>
+          <t>Michael Kors</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Clarksville, TN, US USA</t>
+          <t>East Rutherford, NJ, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, Glue, Redshift, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=887221a715d1ff03</t>
+          <t>https://www.indeed.com/viewjob?jk=904e084e965a45c4</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Software Engineer (Hybrid)</t>
+          <t>Advanced Metering Infrastructure (AMI) Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Nightwing</t>
+          <t>WSSC Water</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Sterling, VA, US USA</t>
+          <t>Laurel, MD, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, Kafka, Oracle, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3322d87953168bdc</t>
+          <t>https://www.indeed.com/viewjob?jk=c5b2aa36ee050b9b</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Spark, PySpark, Scala, MySQL, MongoDB, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8b55e090bbab627</t>
+          <t>https://www.indeed.com/viewjob?jk=dd1518c4c02c12ef</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Software Engineer III - Java/Spark/AWS</t>
+          <t>Senior Software Engineer, Back End (Python)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, ECS, RDS, Databricks, Spark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c95674c932d41fb6</t>
+          <t>https://www.indeed.com/viewjob?jk=3864c05dc9b353f8</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Tableau Developer</t>
+          <t>Data Engineer 2</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Michael Kors</t>
+          <t>BLOC Resources, LLC</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>East Rutherford, NJ, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=904e084e965a45c4</t>
+          <t>https://www.indeed.com/viewjob?jk=c51290628ce41b82</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Advanced Metering Infrastructure (AMI) Engineer</t>
+          <t>Sr. Software Engineer I, Applied AI</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>WSSC Water</t>
+          <t>Axon</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Laurel, MD, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Oracle, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5b2aa36ee050b9b</t>
+          <t>https://www.indeed.com/viewjob?jk=e858c83fc09cd77d</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Software Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>TRM Labs</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, PySpark, Scala, MySQL, MongoDB, Docker, Kubernetes, Airflow</t>
+          <t>RDS, BigQuery, Spark, Scala, Kafka, ETL, dbt, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd1518c4c02c12ef</t>
+          <t>https://www.indeed.com/viewjob?jk=8a517be0e10b2a44</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End (Python)</t>
+          <t>Senior Data Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>TRM Labs</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Docker, Kubernetes</t>
+          <t>RDS, BigQuery, Spark, Scala, Kafka, ETL, dbt, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3864c05dc9b353f8</t>
+          <t>https://www.indeed.com/viewjob?jk=60f6c2aecd2d1bdf</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Engineer 2</t>
+          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>BLOC Resources, LLC</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Data Modeling, CI/CD</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c51290628ce41b82</t>
+          <t>https://www.indeed.com/viewjob?jk=f85f1e8c0778adba</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer I, Applied AI</t>
+          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Axon</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e858c83fc09cd77d</t>
+          <t>https://www.indeed.com/viewjob?jk=3e2da1f14c27a331</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Platform</t>
+          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>TRM Labs</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Spark, Scala, Kafka, ETL, dbt, Terraform, Docker, Kubernetes</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a517be0e10b2a44</t>
+          <t>https://www.indeed.com/viewjob?jk=140d02e1f58501f6</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Data Platform</t>
+          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>TRM Labs</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Spark, Scala, Kafka, ETL, dbt, Terraform, Docker, Kubernetes</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60f6c2aecd2d1bdf</t>
+          <t>https://www.indeed.com/viewjob?jk=eff547fec829449a</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
+          <t>AWS Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Appex Innovation</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Glue, Lambda, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f85f1e8c0778adba</t>
+          <t>https://www.indeed.com/viewjob?jk=7f3534222ab81e17</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2556,29 +2556,29 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e2da1f14c27a331</t>
+          <t>https://www.indeed.com/viewjob?jk=29d22d712d7958f0</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
+          <t>AWS Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Appex Innovation</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,17 +2586,17 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Glue, Lambda, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=140d02e1f58501f6</t>
+          <t>https://www.indeed.com/viewjob?jk=3886cb86a753634c</t>
         </is>
       </c>
     </row>
@@ -2626,29 +2626,29 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eff547fec829449a</t>
+          <t>https://www.indeed.com/viewjob?jk=f9637232a826c3ad</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>AWS Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Appex Innovation</t>
+          <t>CNH Industrial</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f3534222ab81e17</t>
+          <t>https://www.indeed.com/viewjob?jk=e5b3837921976566</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
+          <t>Senior Data Engineer - Microsoft Fabric</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>EoS Fitness</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ELT, Power BI</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29d22d712d7958f0</t>
+          <t>https://www.indeed.com/viewjob?jk=7bd7f3590528db3c</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>AWS Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Appex Innovation</t>
+          <t>PGA TOUR Superstore</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Roswell, GA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3886cb86a753634c</t>
+          <t>https://www.indeed.com/viewjob?jk=73bdb2d180484ce2</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
+          <t>Customer Reliability Engineer, Airflow</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Astronomer</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, Snowflake, PostgreSQL, dbt, DataOps, Docker</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9637232a826c3ad</t>
+          <t>https://www.indeed.com/viewjob?jk=6ac244565083c1d9</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>CNH Industrial</t>
+          <t>RapidFire Safety &amp; Security</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
+          <t>RDS, Azure, Scala, SQL Server, Data Modeling, Star Schema, Fact Tables, Dimension Tables, ETL, Power BI</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5b3837921976566</t>
+          <t>https://www.indeed.com/viewjob?jk=8afc73df8ef8f40e</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Microsoft Fabric</t>
+          <t>Salesforce Architect - Senior</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>EoS Fitness</t>
+          <t>CommunityForce Inc.</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ELT, Power BI</t>
+          <t>ECS, RDS, Azure, Scala, Kafka, Data Modeling, ETL, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bd7f3590528db3c</t>
+          <t>https://www.indeed.com/viewjob?jk=7d236cba8a6e8ae3</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer - Master</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>PGA TOUR Superstore</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Roswell, GA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,102 +2876,102 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73bdb2d180484ce2</t>
+          <t>https://www.indeed.com/viewjob?jk=3fb1207979169793</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Customer Reliability Engineer, Airflow</t>
+          <t>Data Engineer - GRC Technology</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Astronomer</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, Snowflake, PostgreSQL, dbt, DataOps, Docker</t>
+          <t>AWS, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ac244565083c1d9</t>
+          <t>https://www.indeed.com/viewjob?jk=8842e67bf37c518a</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Informatica MDM and Databricks Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>RapidFire Safety &amp; Security</t>
+          <t>Xpedient Technologies</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, Data Modeling, Star Schema, Fact Tables, Dimension Tables, ETL, Power BI</t>
+          <t>RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8afc73df8ef8f40e</t>
+          <t>https://www.indeed.com/viewjob?jk=4cb9515aa944d7a5</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Salesforce Architect - Senior</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>CommunityForce Inc.</t>
+          <t>Callaway Golf</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>ECS, RDS, Azure, Scala, Kafka, Data Modeling, ETL, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, Azure, Databricks, Spark, Snowflake, ETL, ELT, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d236cba8a6e8ae3</t>
+          <t>https://www.indeed.com/viewjob?jk=ab2d181891cc2eee</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Software Engineer - Master</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Emed</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fb1207979169793</t>
+          <t>https://www.indeed.com/viewjob?jk=1e29e1c3d36f0e7c</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Data Engineer - GRC Technology</t>
+          <t>Sr. Data Engineer, Engineering &amp; Ops</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>NBCUniversal</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, ETL, ELT</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Snowflake, ELT, dbt, MLOps, Airflow</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8842e67bf37c518a</t>
+          <t>https://www.indeed.com/viewjob?jk=df536a2594fa5881</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Informatica MDM and Databricks Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Xpedient Technologies</t>
+          <t>TRM Labs</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ELT</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, ETL, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cb9515aa944d7a5</t>
+          <t>https://www.indeed.com/viewjob?jk=dcb7ea8003fbc5dc</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Microsoft Entra</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Callaway Golf</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Spark, Snowflake, ETL, ELT, Terraform, Kubernetes, Git</t>
+          <t>RDS, Azure, Data Factory, Oracle, Data Modeling, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab2d181891cc2eee</t>
+          <t>https://www.indeed.com/viewjob?jk=f61688604ed96074</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Emed</t>
+          <t>Westchester Medical Center Health Network</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Valhalla, NY, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Snowflake, SQL Server, Data Modeling, ELT, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e29e1c3d36f0e7c</t>
+          <t>https://www.indeed.com/viewjob?jk=d807a7856ebe08db</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer, Engineering &amp; Ops</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>NBCUniversal</t>
+          <t>Daniels Health</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Snowflake, ELT, dbt, MLOps, Airflow</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, ETL, ELT, Git</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df536a2594fa5881</t>
+          <t>https://www.indeed.com/viewjob?jk=447d4d5607b3f3c6</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>TRM Labs</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, ETL, dbt, Power BI, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dcb7ea8003fbc5dc</t>
+          <t>https://www.indeed.com/viewjob?jk=1315e6e62a7714e8</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Microsoft Entra</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Guidewire Software, Inc.</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Oracle, Data Modeling, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f61688604ed96074</t>
+          <t>https://www.indeed.com/viewjob?jk=3b5e082bd1857b0f</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>.NET Developer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Westchester Medical Center Health Network</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Valhalla, NY, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Snowflake, SQL Server, Data Modeling, ELT, Power BI, Tableau, CI/CD</t>
+          <t>S3, RDS, Azure, Scala, Snowflake, SQL Server, Power BI, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d807a7856ebe08db</t>
+          <t>https://www.indeed.com/viewjob?jk=4afc3e61f8ae8b7b</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Informatica IDMC MDM Software Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Daniels Health</t>
+          <t>RBC</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, ETL, ELT, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=447d4d5607b3f3c6</t>
+          <t>https://www.indeed.com/viewjob?jk=5346f4c5e2b5352a</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer, Attribution Expansion</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>TRM Labs</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, BigQuery, Spark, Snowflake, Data Modeling, dbt, MLflow, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1315e6e62a7714e8</t>
+          <t>https://www.indeed.com/viewjob?jk=539a18aebac4ef5f</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Senior Data Engineer, Attribution Expansion</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Guidewire Software, Inc.</t>
+          <t>TRM Labs</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>RDS, BigQuery, Spark, Snowflake, Data Modeling, dbt, MLflow, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3400,146 +3400,6 @@
         </is>
       </c>
       <c r="G85" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3b5e082bd1857b0f</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>.NET Developer</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>Caterpillar</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Cary, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D86" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>S3, RDS, Azure, Scala, Snowflake, SQL Server, Power BI, CI/CD, Azure DevOps, Git</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4afc3e61f8ae8b7b</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Sr. Informatica IDMC MDM Software Engineer</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>RBC</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Minneapolis, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D87" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, ETL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5346f4c5e2b5352a</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer, Attribution Expansion</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>TRM Labs</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>RDS, BigQuery, Spark, Snowflake, Data Modeling, dbt, MLflow, CI/CD, Terraform, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=539a18aebac4ef5f</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer, Attribution Expansion</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>TRM Labs</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D89" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>RDS, BigQuery, Spark, Snowflake, Data Modeling, dbt, MLflow, CI/CD, Terraform, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=26436308d22e947d</t>
         </is>

--- a/results/job_matches_2026-03-05.xlsx
+++ b/results/job_matches_2026-03-05.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G85"/>
+  <dimension ref="A1:G87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -718,12 +718,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -736,12 +736,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e8500146d476812</t>
+          <t>https://www.indeed.com/viewjob?jk=32d044bc27a4af8a</t>
         </is>
       </c>
     </row>
@@ -753,7 +753,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ad2838bd8f61427</t>
+          <t>https://www.indeed.com/viewjob?jk=aed60e56cae31294</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Google Cloud Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>NMI</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Schaumburg, IL, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Kafka, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7cac4b03aa7cfe7</t>
+          <t>https://www.indeed.com/viewjob?jk=44f958ba0cbc0f43</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Specialist - System Management</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Glen Allen, VA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Unity Catalog, Delta Live Tables, Spark, Databricks Lakehouse, SQL Server</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=293f842904007fda</t>
+          <t>https://www.indeed.com/viewjob?jk=9e8500146d476812</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Engineer - DevOps/ DataOps</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>FICO</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, DataOps, MLOps, CI/CD, Jenkins</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1ed15cfc823b0b7</t>
+          <t>https://www.indeed.com/viewjob?jk=2ad2838bd8f61427</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>Google Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Alight Solutions</t>
+          <t>NMI</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Schaumburg, IL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, GCP, Scala, CI/CD</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Kafka, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=398f35933211332f</t>
+          <t>https://www.indeed.com/viewjob?jk=e7cac4b03aa7cfe7</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Specialist - System Management</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SRS Distribution</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>McKinney, TX, US USA</t>
+          <t>Glen Allen, VA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Hadoop, Hive, Spark, Scala, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Unity Catalog, Delta Live Tables, Spark, Databricks Lakehouse, SQL Server</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cde050af8749e53</t>
+          <t>https://www.indeed.com/viewjob?jk=293f842904007fda</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SQL Developer - Enterprise Data &amp; Analytics</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Pantherx Specialty Llc</t>
+          <t>Alight Solutions</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, GCP, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,172 +986,172 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41d495363374161e</t>
+          <t>https://www.indeed.com/viewjob?jk=398f35933211332f</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer (Remote)</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Inspira Financial</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, Azure Cosmos DB, ETL, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, GCP, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1733261c550fa238</t>
+          <t>https://www.indeed.com/viewjob?jk=e83bd0fd320bb829</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer (Remote)</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Inspira Financial</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, Azure Cosmos DB, ETL, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, GCP, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d0e899d198425eb</t>
+          <t>https://www.indeed.com/viewjob?jk=105f562c4b87c831</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Specialist Programmer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Infosys</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Wichita, KS, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, Hive, Spark, PySpark, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, GCP, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9772b3b8d4167ecc</t>
+          <t>https://www.indeed.com/viewjob?jk=56a2fccd9b09c654</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Engineer - Authentication</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Pindrop</t>
+          <t>SRS Distribution</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>McKinney, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, RDS, Scala, MySQL, DynamoDB, MLOps, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Hadoop, Hive, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6513fcf97bbfd044</t>
+          <t>https://www.indeed.com/viewjob?jk=4cde050af8749e53</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SSO Administrator</t>
+          <t>SQL Developer - Enterprise Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Pantherx Specialty Llc</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, PostgreSQL, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,137 +1161,137 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9064a81c91aa262</t>
+          <t>https://www.indeed.com/viewjob?jk=41d495363374161e</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Commercial Software</t>
+          <t>Sr. Software Engineer (Remote)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Inspira Financial</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, Oracle, MySQL</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, Azure Cosmos DB, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f3de39cf73c3663</t>
+          <t>https://www.indeed.com/viewjob?jk=1733261c550fa238</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Software Engineer (Remote)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SRR Consultants</t>
+          <t>Inspira Financial</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Piscataway, NJ, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, Azure Cosmos DB, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88619a1e983eef30</t>
+          <t>https://www.indeed.com/viewjob?jk=5d0e899d198425eb</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Data Lakehouse Infrastructure</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>TRM Labs</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MongoDB, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e899ea40640da235</t>
+          <t>https://www.indeed.com/viewjob?jk=022d9e279d3ddb80</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Specialist Programmer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Halo Creative &amp; Media LLP</t>
+          <t>Infosys</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, Azure, GCP, Hadoop, Hive, Spark, PySpark, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=371d6385735b0f59</t>
+          <t>https://www.indeed.com/viewjob?jk=9772b3b8d4167ecc</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Software Engineer - Authentication</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Advance Auto Parts</t>
+          <t>Pindrop</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, Kinesis, S3, RDS, Scala, MySQL, DynamoDB, MLOps, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e2d8bc5a4c9174d</t>
+          <t>https://www.indeed.com/viewjob?jk=6513fcf97bbfd044</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>IT Data Engineer</t>
+          <t>SSO Administrator</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Novolex</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Lake Forest, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, PostgreSQL, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=024a63ca708c8a8f</t>
+          <t>https://www.indeed.com/viewjob?jk=a9064a81c91aa262</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>AWS DevOps Engineer</t>
+          <t>Senior Software Engineer - Commercial Software</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Seqster PDM, Inc</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, Oracle, MySQL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=191c0857581cffe3</t>
+          <t>https://www.indeed.com/viewjob?jk=5f3de39cf73c3663</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Java Software Engineer II (US)</t>
+          <t>Senior Data Engineer, Data Lakehouse Infrastructure</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>TD Bank</t>
+          <t>TRM Labs</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Mount Laurel, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, NoSQL, Splunk, Jenkins, Maven, Docker, Kubernetes, Jenkins</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ee89e940b02cc06</t>
+          <t>https://www.indeed.com/viewjob?jk=e899ea40640da235</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Advance Auto Parts</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,102 +1476,102 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38b673fd36dffa19</t>
+          <t>https://www.indeed.com/viewjob?jk=3e2d8bc5a4c9174d</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End (Java, Go, AWS)</t>
+          <t>IT Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Novolex</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Lake Forest, IL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Docker</t>
+          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e716b4195b2da30b</t>
+          <t>https://www.indeed.com/viewjob?jk=024a63ca708c8a8f</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>AWS DevOps Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Daniels Health</t>
+          <t>Seqster PDM, Inc</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, IAM, RDS, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3486f1249174e37a</t>
+          <t>https://www.indeed.com/viewjob?jk=191c0857581cffe3</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Java Software Engineer II (US)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Daniels Health</t>
+          <t>TD Bank</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Mount Laurel, NJ, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
+          <t>RDS, Azure, Scala, NoSQL, Splunk, Jenkins, Maven, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1df7caac86af2291</t>
+          <t>https://www.indeed.com/viewjob?jk=8ee89e940b02cc06</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ATC - AI &amp; Data Analyst - NAELFY26</t>
+          <t>Senior Software Engineer, Back End (Java, Go, AWS)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Saint Petersburg, FL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ce7a50a4bbe9ef2</t>
+          <t>https://www.indeed.com/viewjob?jk=e716b4195b2da30b</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Data Product</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>TRM Labs</t>
+          <t>Daniels Health</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Dataflow, Spark, Scala, Kafka, dbt, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=351b720407fa6f6d</t>
+          <t>https://www.indeed.com/viewjob?jk=3486f1249174e37a</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Analytics, Full-Stack Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>SCAN Health Plan</t>
+          <t>Daniels Health</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Snowflake, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c24274a4aa989f95</t>
+          <t>https://www.indeed.com/viewjob?jk=1df7caac86af2291</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>GD162 Senior Software Systems Engineer &amp; Architect</t>
+          <t>ATC - AI &amp; Data Analyst - NAELFY26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>ADNET Systems, Inc</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Greenbelt, MD, US USA</t>
+          <t>Saint Petersburg, FL, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Scala, Dask, DynamoDB, ELT, CI/CD, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef183b27f01923fb</t>
+          <t>https://www.indeed.com/viewjob?jk=1ce7a50a4bbe9ef2</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Software Engineer, Intern - Summer 2026, Austin</t>
+          <t>Senior Data Engineer, Data Product</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>TRM Labs</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Kafka, MySQL, Cassandra, NoSQL, Splunk, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>RDS, BigQuery, Dataflow, Spark, Scala, Kafka, dbt, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd858b6050894467</t>
+          <t>https://www.indeed.com/viewjob?jk=351b720407fa6f6d</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Analytics, Full-Stack Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Amplify</t>
+          <t>SCAN Health Plan</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Snowflake, DynamoDB, Data Modeling, Kimball, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4d16d721d2057f3</t>
+          <t>https://www.indeed.com/viewjob?jk=c24274a4aa989f95</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Database Administrator</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Hard Rock International</t>
+          <t>Amplify</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Hollywood, FL, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, Snowflake, PostgreSQL, Cassandra, CI/CD, Terraform</t>
+          <t>AWS, S3, RDS, Snowflake, DynamoDB, Data Modeling, Kimball, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=169d4a00d377fdae</t>
+          <t>https://www.indeed.com/viewjob?jk=b4d16d721d2057f3</t>
         </is>
       </c>
     </row>
@@ -2078,17 +2078,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Tableau Developer</t>
+          <t>Database Administrator</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Michael Kors</t>
+          <t>Hard Rock International</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>East Rutherford, NJ, US USA</t>
+          <t>Hollywood, FL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, Snowflake, PostgreSQL, Cassandra, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=904e084e965a45c4</t>
+          <t>https://www.indeed.com/viewjob?jk=169d4a00d377fdae</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Advanced Metering Infrastructure (AMI) Engineer</t>
+          <t>Tableau Developer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>WSSC Water</t>
+          <t>Michael Kors</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Laurel, MD, US USA</t>
+          <t>East Rutherford, NJ, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Oracle, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps</t>
+          <t>AWS, Glue, Redshift, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5b2aa36ee050b9b</t>
+          <t>https://www.indeed.com/viewjob?jk=904e084e965a45c4</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Advanced Metering Infrastructure (AMI) Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>WSSC Water</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Laurel, MD, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, PySpark, Scala, MySQL, MongoDB, Docker, Kubernetes, Airflow</t>
+          <t>RDS, Azure, Scala, Kafka, Oracle, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd1518c4c02c12ef</t>
+          <t>https://www.indeed.com/viewjob?jk=c5b2aa36ee050b9b</t>
         </is>
       </c>
     </row>
@@ -2188,7 +2188,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3864c05dc9b353f8</t>
+          <t>https://www.indeed.com/viewjob?jk=f65ac6c3f1cf1646</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Engineer 2</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>BLOC Resources, LLC</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Data Modeling, CI/CD</t>
+          <t>AWS, RDS, Spark, PySpark, Scala, MySQL, MongoDB, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c51290628ce41b82</t>
+          <t>https://www.indeed.com/viewjob?jk=dd1518c4c02c12ef</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer I, Applied AI</t>
+          <t>Senior Software Engineer, Back End (Python)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Axon</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e858c83fc09cd77d</t>
+          <t>https://www.indeed.com/viewjob?jk=3864c05dc9b353f8</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Platform</t>
+          <t>Data Engineer 2</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>TRM Labs</t>
+          <t>BLOC Resources, LLC</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Spark, Scala, Kafka, ETL, dbt, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a517be0e10b2a44</t>
+          <t>https://www.indeed.com/viewjob?jk=c51290628ce41b82</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Data Platform</t>
+          <t>Sr. Software Engineer I, Applied AI</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>TRM Labs</t>
+          <t>Axon</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Spark, Scala, Kafka, ETL, dbt, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60f6c2aecd2d1bdf</t>
+          <t>https://www.indeed.com/viewjob?jk=e858c83fc09cd77d</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
+          <t>Senior Software Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>TRM Labs</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>RDS, BigQuery, Spark, Scala, Kafka, ETL, dbt, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f85f1e8c0778adba</t>
+          <t>https://www.indeed.com/viewjob?jk=8a517be0e10b2a44</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
+          <t>Senior Data Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>TRM Labs</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,17 +2411,17 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>RDS, BigQuery, Spark, Scala, Kafka, ETL, dbt, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e2da1f14c27a331</t>
+          <t>https://www.indeed.com/viewjob?jk=60f6c2aecd2d1bdf</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=140d02e1f58501f6</t>
+          <t>https://www.indeed.com/viewjob?jk=f85f1e8c0778adba</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eff547fec829449a</t>
+          <t>https://www.indeed.com/viewjob?jk=3e2da1f14c27a331</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>AWS Data Engineer</t>
+          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Appex Innovation</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f3534222ab81e17</t>
+          <t>https://www.indeed.com/viewjob?jk=140d02e1f58501f6</t>
         </is>
       </c>
     </row>
@@ -2556,12 +2556,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29d22d712d7958f0</t>
+          <t>https://www.indeed.com/viewjob?jk=eff547fec829449a</t>
         </is>
       </c>
     </row>
@@ -2591,12 +2591,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3886cb86a753634c</t>
+          <t>https://www.indeed.com/viewjob?jk=7f3534222ab81e17</t>
         </is>
       </c>
     </row>
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9637232a826c3ad</t>
+          <t>https://www.indeed.com/viewjob?jk=29d22d712d7958f0</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AWS Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>CNH Industrial</t>
+          <t>Appex Innovation</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, Glue, Lambda, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5b3837921976566</t>
+          <t>https://www.indeed.com/viewjob?jk=3886cb86a753634c</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Microsoft Fabric</t>
+          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>EoS Fitness</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ELT, Power BI</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bd7f3590528db3c</t>
+          <t>https://www.indeed.com/viewjob?jk=f9637232a826c3ad</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>PGA TOUR Superstore</t>
+          <t>CNH Industrial</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Roswell, GA, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,19 +2736,19 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73bdb2d180484ce2</t>
+          <t>https://www.indeed.com/viewjob?jk=e5b3837921976566</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Customer Reliability Engineer, Airflow</t>
+          <t>Senior Data Engineer - Microsoft Fabric</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Astronomer</t>
+          <t>EoS Fitness</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, Snowflake, PostgreSQL, dbt, DataOps, Docker</t>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ELT, Power BI</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ac244565083c1d9</t>
+          <t>https://www.indeed.com/viewjob?jk=7bd7f3590528db3c</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>RapidFire Safety &amp; Security</t>
+          <t>PGA TOUR Superstore</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Roswell, GA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, Data Modeling, Star Schema, Fact Tables, Dimension Tables, ETL, Power BI</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8afc73df8ef8f40e</t>
+          <t>https://www.indeed.com/viewjob?jk=73bdb2d180484ce2</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Salesforce Architect - Senior</t>
+          <t>Customer Reliability Engineer, Airflow</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>CommunityForce Inc.</t>
+          <t>Astronomer</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>ECS, RDS, Azure, Scala, Kafka, Data Modeling, ETL, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, Snowflake, PostgreSQL, dbt, DataOps, Docker</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d236cba8a6e8ae3</t>
+          <t>https://www.indeed.com/viewjob?jk=6ac244565083c1d9</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Software Engineer - Master</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>RapidFire Safety &amp; Security</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>RDS, Azure, Scala, SQL Server, Data Modeling, Star Schema, Fact Tables, Dimension Tables, ETL, Power BI</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,59 +2876,59 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fb1207979169793</t>
+          <t>https://www.indeed.com/viewjob?jk=8afc73df8ef8f40e</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Engineer - GRC Technology</t>
+          <t>Salesforce Architect - Senior</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>CommunityForce Inc.</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, ETL, ELT</t>
+          <t>ECS, RDS, Azure, Scala, Kafka, Data Modeling, ETL, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8842e67bf37c518a</t>
+          <t>https://www.indeed.com/viewjob?jk=7d236cba8a6e8ae3</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Informatica MDM and Databricks Engineer</t>
+          <t>Software Engineer - Master</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Xpedient Technologies</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ELT</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cb9515aa944d7a5</t>
+          <t>https://www.indeed.com/viewjob?jk=3fb1207979169793</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Data Engineer - GRC Technology</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Callaway Golf</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Spark, Snowflake, ETL, ELT, Terraform, Kubernetes, Git</t>
+          <t>AWS, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab2d181891cc2eee</t>
+          <t>https://www.indeed.com/viewjob?jk=8842e67bf37c518a</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Emed</t>
+          <t>Callaway Golf</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions</t>
+          <t>AWS, Azure, Databricks, Spark, Snowflake, ETL, ELT, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e29e1c3d36f0e7c</t>
+          <t>https://www.indeed.com/viewjob?jk=ab2d181891cc2eee</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer, Engineering &amp; Ops</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>NBCUniversal</t>
+          <t>Emed</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Snowflake, ELT, dbt, MLOps, Airflow</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df536a2594fa5881</t>
+          <t>https://www.indeed.com/viewjob?jk=1e29e1c3d36f0e7c</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Sr. Data Engineer, Engineering &amp; Ops</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>TRM Labs</t>
+          <t>NBCUniversal</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, ETL, dbt, Power BI, Tableau, CI/CD</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Snowflake, ELT, dbt, MLOps, Airflow</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dcb7ea8003fbc5dc</t>
+          <t>https://www.indeed.com/viewjob?jk=df536a2594fa5881</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Microsoft Entra</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>TRM Labs</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Oracle, Data Modeling, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, ETL, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f61688604ed96074</t>
+          <t>https://www.indeed.com/viewjob?jk=dcb7ea8003fbc5dc</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Microsoft Entra</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Westchester Medical Center Health Network</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Valhalla, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Snowflake, SQL Server, Data Modeling, ELT, Power BI, Tableau, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Oracle, Data Modeling, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d807a7856ebe08db</t>
+          <t>https://www.indeed.com/viewjob?jk=f61688604ed96074</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Daniels Health</t>
+          <t>Westchester Medical Center Health Network</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Valhalla, NY, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, ETL, ELT, Git</t>
+          <t>AWS, RDS, Azure, Snowflake, SQL Server, Data Modeling, ELT, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=447d4d5607b3f3c6</t>
+          <t>https://www.indeed.com/viewjob?jk=d807a7856ebe08db</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Daniels Health</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, ETL, ELT, Git</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1315e6e62a7714e8</t>
+          <t>https://www.indeed.com/viewjob?jk=aedcadc853d15f82</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Guidewire Software, Inc.</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b5e082bd1857b0f</t>
+          <t>https://www.indeed.com/viewjob?jk=1315e6e62a7714e8</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>.NET Developer</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Guidewire Software, Inc.</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Scala, Snowflake, SQL Server, Power BI, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4afc3e61f8ae8b7b</t>
+          <t>https://www.indeed.com/viewjob?jk=3b5e082bd1857b0f</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Sr. Informatica IDMC MDM Software Engineer</t>
+          <t>.NET Developer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>RBC</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, ETL, CI/CD</t>
+          <t>S3, RDS, Azure, Scala, Snowflake, SQL Server, Power BI, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5346f4c5e2b5352a</t>
+          <t>https://www.indeed.com/viewjob?jk=4afc3e61f8ae8b7b</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Attribution Expansion</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>TRM Labs</t>
+          <t>Daniels Health</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Spark, Snowflake, Data Modeling, dbt, MLflow, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, ETL, ELT, Git</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=539a18aebac4ef5f</t>
+          <t>https://www.indeed.com/viewjob?jk=447d4d5607b3f3c6</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Attribution Expansion</t>
+          <t>Sr. Informatica IDMC MDM Software Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>TRM Labs</t>
+          <t>RBC</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,15 +3391,85 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, ETL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5346f4c5e2b5352a</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer, Attribution Expansion</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>TRM Labs</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
           <t>RDS, BigQuery, Spark, Snowflake, Data Modeling, dbt, MLflow, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=539a18aebac4ef5f</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer, Attribution Expansion</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>TRM Labs</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>RDS, BigQuery, Spark, Snowflake, Data Modeling, dbt, MLflow, CI/CD, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=26436308d22e947d</t>
         </is>

--- a/results/job_matches_2026-03-05.xlsx
+++ b/results/job_matches_2026-03-05.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G87"/>
+  <dimension ref="A1:G90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,17 +468,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Junior Oracle Apps Developer</t>
+          <t>Full Stack Engineer (React + Node.js)-5</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -486,17 +486,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, ECS, RDS, Azure, Blob Storage</t>
+          <t>AWS, SQS, SNS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0adde35786282b2b</t>
+          <t>https://www.indeed.com/viewjob?jk=01d5f2b9fa96100b</t>
         </is>
       </c>
     </row>
@@ -508,55 +508,55 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Jersey Mikes Corporate</t>
+          <t>AmeriLife</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Tinton Falls, NJ, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.8</v>
+        <v>19.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31cf41e0387f0b72</t>
+          <t>https://www.indeed.com/viewjob?jk=857bb2d652273e9a</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, ACVMax</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ACV Auctions</t>
+          <t>Jersey Mikes Corporate</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>Tinton Falls, NJ, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,7 +566,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c28dd5d00192a5b</t>
+          <t>https://www.indeed.com/viewjob?jk=31cf41e0387f0b72</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Enterprise Data Platform Engineer – Washington, DC</t>
+          <t>Cloud Data Platform Administrator – Washington, DC</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -958,17 +958,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>CLOUD ENGINEER (AWS) (REMOTE/USA) - GDM (GRAY MEDIA GROUP)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Alight Solutions</t>
+          <t>GRAY MEDIA</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, GCP, Scala, CI/CD</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Google Cloud Platform, GCP, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=398f35933211332f</t>
+          <t>https://www.indeed.com/viewjob?jk=0beb94e2f1648144</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>Alight Solutions</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,17 +1011,17 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, GCP, Scala, Snowflake</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, GCP, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e83bd0fd320bb829</t>
+          <t>https://www.indeed.com/viewjob?jk=398f35933211332f</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=105f562c4b87c831</t>
+          <t>https://www.indeed.com/viewjob?jk=e83bd0fd320bb829</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Wichita, KS, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,59 +1091,59 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56a2fccd9b09c654</t>
+          <t>https://www.indeed.com/viewjob?jk=105f562c4b87c831</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SRS Distribution</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>McKinney, TX, US USA</t>
+          <t>Wichita, KS, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Hadoop, Hive, Spark, Scala, Snowflake</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, GCP, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cde050af8749e53</t>
+          <t>https://www.indeed.com/viewjob?jk=56a2fccd9b09c654</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SQL Developer - Enterprise Data &amp; Analytics</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Pantherx Specialty Llc</t>
+          <t>Upstart</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41d495363374161e</t>
+          <t>https://www.indeed.com/viewjob?jk=3dab96c17b78fc32</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer (Remote)</t>
+          <t>SQL Developer - Enterprise Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Inspira Financial</t>
+          <t>Pantherx Specialty Llc</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,17 +1186,17 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, Azure Cosmos DB, ETL, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1733261c550fa238</t>
+          <t>https://www.indeed.com/viewjob?jk=41d495363374161e</t>
         </is>
       </c>
     </row>
@@ -1226,29 +1226,29 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d0e899d198425eb</t>
+          <t>https://www.indeed.com/viewjob?jk=1733261c550fa238</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Sr. Software Engineer (Remote)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Inspira Financial</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,29 +1256,29 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MongoDB, NoSQL, Splunk</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, Azure Cosmos DB, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=022d9e279d3ddb80</t>
+          <t>https://www.indeed.com/viewjob?jk=5d0e899d198425eb</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Specialist Programmer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Infosys</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1291,69 +1291,69 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, Hive, Spark, PySpark, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MongoDB, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9772b3b8d4167ecc</t>
+          <t>https://www.indeed.com/viewjob?jk=022d9e279d3ddb80</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Software Engineer - Authentication</t>
+          <t>Specialist Programmer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Pindrop</t>
+          <t>Infosys</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, RDS, Scala, MySQL, DynamoDB, MLOps, CI/CD, Jenkins</t>
+          <t>AWS, Azure, GCP, Hadoop, Hive, Spark, PySpark, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6513fcf97bbfd044</t>
+          <t>https://www.indeed.com/viewjob?jk=9772b3b8d4167ecc</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SSO Administrator</t>
+          <t>SENIOR DATA ENGINEER</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,77 +1361,77 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, PostgreSQL, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9064a81c91aa262</t>
+          <t>https://www.indeed.com/viewjob?jk=bee5a340a7f65e61</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Commercial Software</t>
+          <t>Software Engineer - Authentication</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Pindrop</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, Oracle, MySQL</t>
+          <t>AWS, Kinesis, S3, RDS, Scala, MySQL, DynamoDB, MLOps, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f3de39cf73c3663</t>
+          <t>https://www.indeed.com/viewjob?jk=6513fcf97bbfd044</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Data Lakehouse Infrastructure</t>
+          <t>SSO Administrator</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>TRM Labs</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, PostgreSQL, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e899ea40640da235</t>
+          <t>https://www.indeed.com/viewjob?jk=a9064a81c91aa262</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Software Engineer - Commercial Software</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Advance Auto Parts</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, Oracle, MySQL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e2d8bc5a4c9174d</t>
+          <t>https://www.indeed.com/viewjob?jk=5f3de39cf73c3663</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>IT Data Engineer</t>
+          <t>Senior Data Engineer, Data Lakehouse Infrastructure</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Novolex</t>
+          <t>TRM Labs</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Lake Forest, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=024a63ca708c8a8f</t>
+          <t>https://www.indeed.com/viewjob?jk=e899ea40640da235</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>AWS DevOps Engineer</t>
+          <t>Data Platform Engineer-3</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Seqster PDM, Inc</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=191c0857581cffe3</t>
+          <t>https://www.indeed.com/viewjob?jk=f753e538739bd670</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Java Software Engineer II (US)</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>TD Bank</t>
+          <t>Advance Auto Parts</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Mount Laurel, NJ, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,112 +1571,112 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, NoSQL, Splunk, Jenkins, Maven, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ee89e940b02cc06</t>
+          <t>https://www.indeed.com/viewjob?jk=3e2d8bc5a4c9174d</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End (Java, Go, AWS)</t>
+          <t>IT Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Novolex</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Lake Forest, IL, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Docker</t>
+          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e716b4195b2da30b</t>
+          <t>https://www.indeed.com/viewjob?jk=024a63ca708c8a8f</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>AWS DevOps Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Daniels Health</t>
+          <t>Seqster PDM, Inc</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, IAM, RDS, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3486f1249174e37a</t>
+          <t>https://www.indeed.com/viewjob?jk=191c0857581cffe3</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Java Software Engineer II (US)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Daniels Health</t>
+          <t>TD Bank</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Mount Laurel, NJ, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
+          <t>RDS, Azure, Scala, NoSQL, Splunk, Jenkins, Maven, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1df7caac86af2291</t>
+          <t>https://www.indeed.com/viewjob?jk=8ee89e940b02cc06</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ATC - AI &amp; Data Analyst - NAELFY26</t>
+          <t>Senior Software Engineer, Back End (Java, Go, AWS)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Saint Petersburg, FL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ce7a50a4bbe9ef2</t>
+          <t>https://www.indeed.com/viewjob?jk=e716b4195b2da30b</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Data Product</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>TRM Labs</t>
+          <t>Daniels Health</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Dataflow, Spark, Scala, Kafka, dbt, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=351b720407fa6f6d</t>
+          <t>https://www.indeed.com/viewjob?jk=3486f1249174e37a</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Analytics, Full-Stack Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>SCAN Health Plan</t>
+          <t>Daniels Health</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Snowflake, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c24274a4aa989f95</t>
+          <t>https://www.indeed.com/viewjob?jk=1df7caac86af2291</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>ATC - AI &amp; Data Analyst - NAELFY26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Amplify</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Saint Petersburg, FL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Snowflake, DynamoDB, Data Modeling, Kimball, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4d16d721d2057f3</t>
+          <t>https://www.indeed.com/viewjob?jk=1ce7a50a4bbe9ef2</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Senior Data Engineer, Data Product</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Weyerhaeuser</t>
+          <t>TRM Labs</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, MLOps, MLflow, CI/CD, Terraform, Docker</t>
+          <t>RDS, BigQuery, Dataflow, Spark, Scala, Kafka, dbt, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d9f82346c5ff2d3</t>
+          <t>https://www.indeed.com/viewjob?jk=351b720407fa6f6d</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Software Systems Engineer, Release Reliability &amp; Automation (Autonomous Vehicles)</t>
+          <t>Analytics, Full-Stack Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>SCAN Health Plan</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, Power BI, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=864266ab5f8e3aac</t>
+          <t>https://www.indeed.com/viewjob?jk=c24274a4aa989f95</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Software Engineer (Junior)</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>TORCH.AI</t>
+          <t>Amplify</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Leawood, KS, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Kafka, PostgreSQL, MongoDB, NoSQL, ETL, CI/CD</t>
+          <t>AWS, S3, RDS, Snowflake, DynamoDB, Data Modeling, Kimball, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28e432d03da8db08</t>
+          <t>https://www.indeed.com/viewjob?jk=b4d16d721d2057f3</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Software Engineer (Hybrid)</t>
+          <t>Software Engineer III - Java/Spark/AWS</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Nightwing</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Clarksville, TN, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, EMR, Lambda, S3, ECS, RDS, Databricks, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=887221a715d1ff03</t>
+          <t>https://www.indeed.com/viewjob?jk=c95674c932d41fb6</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Software Engineer (Hybrid)</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Nightwing</t>
+          <t>Weyerhaeuser</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Sterling, VA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, MLOps, MLflow, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3322d87953168bdc</t>
+          <t>https://www.indeed.com/viewjob?jk=7d9f82346c5ff2d3</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Software Systems Engineer, Release Reliability &amp; Automation (Autonomous Vehicles)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, Power BI, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8b55e090bbab627</t>
+          <t>https://www.indeed.com/viewjob?jk=864266ab5f8e3aac</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Software Engineer III - Java/Spark/AWS</t>
+          <t>Software Engineer (Junior)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>TORCH.AI</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Leawood, KS, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, ECS, RDS, Databricks, Spark, Scala, Snowflake</t>
+          <t>AWS, IAM, Azure, GCP, Kafka, PostgreSQL, MongoDB, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c95674c932d41fb6</t>
+          <t>https://www.indeed.com/viewjob?jk=28e432d03da8db08</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Database Administrator</t>
+          <t>Software Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Hard Rock International</t>
+          <t>Nightwing</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Hollywood, FL, US USA</t>
+          <t>Clarksville, TN, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, Snowflake, PostgreSQL, Cassandra, CI/CD, Terraform</t>
+          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=169d4a00d377fdae</t>
+          <t>https://www.indeed.com/viewjob?jk=887221a715d1ff03</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Tableau Developer</t>
+          <t>Software Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Michael Kors</t>
+          <t>Nightwing</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>East Rutherford, NJ, US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Star Schema</t>
+          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=904e084e965a45c4</t>
+          <t>https://www.indeed.com/viewjob?jk=3322d87953168bdc</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Advanced Metering Infrastructure (AMI) Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>WSSC Water</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Laurel, MD, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Oracle, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,67 +2176,67 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5b2aa36ee050b9b</t>
+          <t>https://www.indeed.com/viewjob?jk=a8b55e090bbab627</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End (Python)</t>
+          <t>Database Administrator</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Hard Rock International</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Hollywood, FL, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, Snowflake, PostgreSQL, Cassandra, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f65ac6c3f1cf1646</t>
+          <t>https://www.indeed.com/viewjob?jk=169d4a00d377fdae</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Tableau Developer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Michael Kors</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>East Rutherford, NJ, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, PySpark, Scala, MySQL, MongoDB, Docker, Kubernetes, Airflow</t>
+          <t>AWS, Glue, Redshift, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd1518c4c02c12ef</t>
+          <t>https://www.indeed.com/viewjob?jk=904e084e965a45c4</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End (Python)</t>
+          <t>Advanced Metering Infrastructure (AMI) Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>WSSC Water</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Laurel, MD, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, Kafka, Oracle, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3864c05dc9b353f8</t>
+          <t>https://www.indeed.com/viewjob?jk=c5b2aa36ee050b9b</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Engineer 2</t>
+          <t>Senior Software Engineer, Back End (Python)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>BLOC Resources, LLC</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Data Modeling, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c51290628ce41b82</t>
+          <t>https://www.indeed.com/viewjob?jk=f65ac6c3f1cf1646</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer I, Applied AI</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Axon</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Spark, PySpark, Scala, MySQL, MongoDB, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e858c83fc09cd77d</t>
+          <t>https://www.indeed.com/viewjob?jk=dd1518c4c02c12ef</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Platform</t>
+          <t>Senior Software Engineer, Back End (Python)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>TRM Labs</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Spark, Scala, Kafka, ETL, dbt, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a517be0e10b2a44</t>
+          <t>https://www.indeed.com/viewjob?jk=3864c05dc9b353f8</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Data Platform</t>
+          <t>Data Engineer 2</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>TRM Labs</t>
+          <t>BLOC Resources, LLC</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Spark, Scala, Kafka, ETL, dbt, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60f6c2aecd2d1bdf</t>
+          <t>https://www.indeed.com/viewjob?jk=c51290628ce41b82</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
+          <t>Sr. Software Engineer I, Applied AI</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Axon</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f85f1e8c0778adba</t>
+          <t>https://www.indeed.com/viewjob?jk=e858c83fc09cd77d</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
+          <t>Senior Software Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>TRM Labs</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>RDS, BigQuery, Spark, Scala, Kafka, ETL, dbt, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e2da1f14c27a331</t>
+          <t>https://www.indeed.com/viewjob?jk=8a517be0e10b2a44</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
+          <t>Senior Data Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>TRM Labs</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>RDS, BigQuery, Spark, Scala, Kafka, ETL, dbt, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=140d02e1f58501f6</t>
+          <t>https://www.indeed.com/viewjob?jk=60f6c2aecd2d1bdf</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Space Telescope Science Institute</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, ECS, IAM, Hive, Scala, PostgreSQL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eff547fec829449a</t>
+          <t>https://www.indeed.com/viewjob?jk=6055970eb603df79</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>AWS Data Engineer</t>
+          <t>AI Engineer III</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Appex Innovation</t>
+          <t>CareSource</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD</t>
+          <t>API Gateway, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f3534222ab81e17</t>
+          <t>https://www.indeed.com/viewjob?jk=640c68fe3716b1e6</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2626,29 +2626,29 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29d22d712d7958f0</t>
+          <t>https://www.indeed.com/viewjob?jk=f85f1e8c0778adba</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>AWS Data Engineer</t>
+          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Appex Innovation</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,17 +2656,17 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3886cb86a753634c</t>
+          <t>https://www.indeed.com/viewjob?jk=3e2da1f14c27a331</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2696,29 +2696,29 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9637232a826c3ad</t>
+          <t>https://www.indeed.com/viewjob?jk=140d02e1f58501f6</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>CNH Industrial</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5b3837921976566</t>
+          <t>https://www.indeed.com/viewjob?jk=eff547fec829449a</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Microsoft Fabric</t>
+          <t>AWS Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>EoS Fitness</t>
+          <t>Appex Innovation</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ELT, Power BI</t>
+          <t>AWS, Glue, Lambda, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bd7f3590528db3c</t>
+          <t>https://www.indeed.com/viewjob?jk=7f3534222ab81e17</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>PGA TOUR Superstore</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Roswell, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73bdb2d180484ce2</t>
+          <t>https://www.indeed.com/viewjob?jk=29d22d712d7958f0</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Customer Reliability Engineer, Airflow</t>
+          <t>AWS Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Astronomer</t>
+          <t>Appex Innovation</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, Snowflake, PostgreSQL, dbt, DataOps, Docker</t>
+          <t>AWS, Glue, Lambda, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ac244565083c1d9</t>
+          <t>https://www.indeed.com/viewjob?jk=3886cb86a753634c</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>RapidFire Safety &amp; Security</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, Data Modeling, Star Schema, Fact Tables, Dimension Tables, ETL, Power BI</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8afc73df8ef8f40e</t>
+          <t>https://www.indeed.com/viewjob?jk=f9637232a826c3ad</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Salesforce Architect - Senior</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>CommunityForce Inc.</t>
+          <t>CNH Industrial</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>ECS, RDS, Azure, Scala, Kafka, Data Modeling, ETL, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,32 +2911,32 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d236cba8a6e8ae3</t>
+          <t>https://www.indeed.com/viewjob?jk=e5b3837921976566</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Software Engineer - Master</t>
+          <t>Senior Data Engineer - Microsoft Fabric</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>EoS Fitness</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ELT, Power BI</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,67 +2946,67 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fb1207979169793</t>
+          <t>https://www.indeed.com/viewjob?jk=7bd7f3590528db3c</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Engineer - GRC Technology</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Centene</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, MySQL, MongoDB, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8842e67bf37c518a</t>
+          <t>https://www.indeed.com/viewjob?jk=11d92da9c37770a7</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Customer Reliability Engineer, Airflow</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Callaway Golf</t>
+          <t>Astronomer</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Spark, Snowflake, ETL, ELT, Terraform, Kubernetes, Git</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, Snowflake, PostgreSQL, dbt, DataOps, Docker</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,67 +3016,67 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab2d181891cc2eee</t>
+          <t>https://www.indeed.com/viewjob?jk=6ac244565083c1d9</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Developer - Database Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Emed</t>
+          <t>RAMSOFT</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, HBase, Scala, Snowflake, MySQL, NoSQL, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e29e1c3d36f0e7c</t>
+          <t>https://www.indeed.com/viewjob?jk=4ce0ac7d0a937f32</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer, Engineering &amp; Ops</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>NBCUniversal</t>
+          <t>RapidFire Safety &amp; Security</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Snowflake, ELT, dbt, MLOps, Airflow</t>
+          <t>RDS, Azure, Scala, SQL Server, Data Modeling, Star Schema, Fact Tables, Dimension Tables, ETL, Power BI</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df536a2594fa5881</t>
+          <t>https://www.indeed.com/viewjob?jk=8afc73df8ef8f40e</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Software Engineer - Master</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>TRM Labs</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, ETL, dbt, Power BI, Tableau, CI/CD</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dcb7ea8003fbc5dc</t>
+          <t>https://www.indeed.com/viewjob?jk=3fb1207979169793</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Microsoft Entra</t>
+          <t>Data Engineer - GRC Technology</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Oracle, Data Modeling, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f61688604ed96074</t>
+          <t>https://www.indeed.com/viewjob?jk=8842e67bf37c518a</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Westchester Medical Center Health Network</t>
+          <t>Emed</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Valhalla, NY, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Snowflake, SQL Server, Data Modeling, ELT, Power BI, Tableau, CI/CD</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d807a7856ebe08db</t>
+          <t>https://www.indeed.com/viewjob?jk=1e29e1c3d36f0e7c</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Data Engineer, Engineering &amp; Ops</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Daniels Health</t>
+          <t>NBCUniversal</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, ETL, ELT, Git</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Snowflake, ELT, dbt, MLOps, Airflow</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aedcadc853d15f82</t>
+          <t>https://www.indeed.com/viewjob?jk=df536a2594fa5881</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>TRM Labs</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, ETL, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1315e6e62a7714e8</t>
+          <t>https://www.indeed.com/viewjob?jk=dcb7ea8003fbc5dc</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Guidewire Software, Inc.</t>
+          <t>Westchester Medical Center Health Network</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Valhalla, NY, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Snowflake, SQL Server, Data Modeling, ELT, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b5e082bd1857b0f</t>
+          <t>https://www.indeed.com/viewjob?jk=d807a7856ebe08db</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>.NET Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Daniels Health</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,17 +3321,17 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Scala, Snowflake, SQL Server, Power BI, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, ETL, ELT, Git</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4afc3e61f8ae8b7b</t>
+          <t>https://www.indeed.com/viewjob?jk=aedcadc853d15f82</t>
         </is>
       </c>
     </row>
@@ -3373,17 +3373,17 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Sr. Informatica IDMC MDM Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>RBC</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5346f4c5e2b5352a</t>
+          <t>https://www.indeed.com/viewjob?jk=1315e6e62a7714e8</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Attribution Expansion</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>TRM Labs</t>
+          <t>Guidewire Software, Inc.</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Spark, Snowflake, Data Modeling, dbt, MLflow, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=539a18aebac4ef5f</t>
+          <t>https://www.indeed.com/viewjob?jk=3b5e082bd1857b0f</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Attribution Expansion</t>
+          <t>.NET Developer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>TRM Labs</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,15 +3461,120 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
+          <t>S3, RDS, Azure, Scala, Snowflake, SQL Server, Power BI, CI/CD, Azure DevOps, Git</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4afc3e61f8ae8b7b</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Sr. Informatica IDMC MDM Software Engineer</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>RBC</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Minneapolis, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, ETL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5346f4c5e2b5352a</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer, Attribution Expansion</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>TRM Labs</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
           <t>RDS, BigQuery, Spark, Snowflake, Data Modeling, dbt, MLflow, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=539a18aebac4ef5f</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer, Attribution Expansion</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>TRM Labs</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>RDS, BigQuery, Spark, Snowflake, Data Modeling, dbt, MLflow, CI/CD, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=26436308d22e947d</t>
         </is>

--- a/results/job_matches_2026-03-05.xlsx
+++ b/results/job_matches_2026-03-05.xlsx
@@ -923,17 +923,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Specialist - System Management</t>
+          <t>System Architect</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Systems Engineering Solutions Corporation</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Glen Allen, VA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,69 +941,69 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Unity Catalog, Delta Live Tables, Spark, Databricks Lakehouse, SQL Server</t>
+          <t>AWS, Glue, EMR, Kinesis, Redshift, S3, IAM, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=293f842904007fda</t>
+          <t>https://www.indeed.com/viewjob?jk=634fcd15ef04d7bf</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CLOUD ENGINEER (AWS) (REMOTE/USA) - GDM (GRAY MEDIA GROUP)</t>
+          <t>Senior Specialist - System Management</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>GRAY MEDIA</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Glen Allen, VA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Google Cloud Platform, GCP, Scala, DynamoDB</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Unity Catalog, Delta Live Tables, Spark, Databricks Lakehouse, SQL Server</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0beb94e2f1648144</t>
+          <t>https://www.indeed.com/viewjob?jk=293f842904007fda</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>CLOUD ENGINEER (AWS) (REMOTE/USA) - GDM (GRAY MEDIA GROUP)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Alight Solutions</t>
+          <t>GRAY MEDIA</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,34 +1011,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, GCP, Scala, CI/CD</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Google Cloud Platform, GCP, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=398f35933211332f</t>
+          <t>https://www.indeed.com/viewjob?jk=0beb94e2f1648144</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>Alight Solutions</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,17 +1046,17 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, GCP, Scala, Snowflake</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, GCP, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e83bd0fd320bb829</t>
+          <t>https://www.indeed.com/viewjob?jk=398f35933211332f</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=105f562c4b87c831</t>
+          <t>https://www.indeed.com/viewjob?jk=e83bd0fd320bb829</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Wichita, KS, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56a2fccd9b09c654</t>
+          <t>https://www.indeed.com/viewjob?jk=105f562c4b87c831</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Upstart</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Wichita, KS, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, GCP, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dab96c17b78fc32</t>
+          <t>https://www.indeed.com/viewjob?jk=56a2fccd9b09c654</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SQL Developer - Enterprise Data &amp; Analytics</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Pantherx Specialty Llc</t>
+          <t>Upstart</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41d495363374161e</t>
+          <t>https://www.indeed.com/viewjob?jk=3dab96c17b78fc32</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer (Remote)</t>
+          <t>SQL Developer - Enterprise Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Inspira Financial</t>
+          <t>Pantherx Specialty Llc</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,17 +1221,17 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, Azure Cosmos DB, ETL, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1733261c550fa238</t>
+          <t>https://www.indeed.com/viewjob?jk=41d495363374161e</t>
         </is>
       </c>
     </row>
@@ -1261,29 +1261,29 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d0e899d198425eb</t>
+          <t>https://www.indeed.com/viewjob?jk=1733261c550fa238</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Sr. Software Engineer (Remote)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Inspira Financial</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,29 +1291,29 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MongoDB, NoSQL, Splunk</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, Azure Cosmos DB, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=022d9e279d3ddb80</t>
+          <t>https://www.indeed.com/viewjob?jk=5d0e899d198425eb</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Specialist Programmer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Infosys</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1326,69 +1326,69 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, Hive, Spark, PySpark, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MongoDB, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9772b3b8d4167ecc</t>
+          <t>https://www.indeed.com/viewjob?jk=022d9e279d3ddb80</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SENIOR DATA ENGINEER</t>
+          <t>Specialist Programmer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Infosys</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, Azure, GCP, Hadoop, Hive, Spark, PySpark, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bee5a340a7f65e61</t>
+          <t>https://www.indeed.com/viewjob?jk=9772b3b8d4167ecc</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Software Engineer - Authentication</t>
+          <t>SENIOR DATA ENGINEER</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Pindrop</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, RDS, Scala, MySQL, DynamoDB, MLOps, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6513fcf97bbfd044</t>
+          <t>https://www.indeed.com/viewjob?jk=bee5a340a7f65e61</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SSO Administrator</t>
+          <t>Software Engineer - Authentication</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Pindrop</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,42 +1431,42 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, PostgreSQL, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, Kinesis, S3, RDS, Scala, MySQL, DynamoDB, MLOps, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9064a81c91aa262</t>
+          <t>https://www.indeed.com/viewjob?jk=6513fcf97bbfd044</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Commercial Software</t>
+          <t>SSO Administrator</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, Oracle, MySQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, PostgreSQL, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f3de39cf73c3663</t>
+          <t>https://www.indeed.com/viewjob?jk=a9064a81c91aa262</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Data Lakehouse Infrastructure</t>
+          <t>Senior Software Engineer - Commercial Software</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>TRM Labs</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, Oracle, MySQL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e899ea40640da235</t>
+          <t>https://www.indeed.com/viewjob?jk=5f3de39cf73c3663</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Platform Engineer-3</t>
+          <t>Senior Data Engineer, Data Lakehouse Infrastructure</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>TRM Labs</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f753e538739bd670</t>
+          <t>https://www.indeed.com/viewjob?jk=e899ea40640da235</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Data Platform Engineer-3</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Advance Auto Parts</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e2d8bc5a4c9174d</t>
+          <t>https://www.indeed.com/viewjob?jk=f753e538739bd670</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>IT Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Novolex</t>
+          <t>Advance Auto Parts</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Lake Forest, IL, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=024a63ca708c8a8f</t>
+          <t>https://www.indeed.com/viewjob?jk=3e2d8bc5a4c9174d</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>AWS DevOps Engineer</t>
+          <t>IT Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Seqster PDM, Inc</t>
+          <t>Novolex</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Lake Forest, IL, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=191c0857581cffe3</t>
+          <t>https://www.indeed.com/viewjob?jk=024a63ca708c8a8f</t>
         </is>
       </c>
     </row>
@@ -1868,17 +1868,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Analytics, Full-Stack Engineer</t>
+          <t>Senior Application Platform Architect - 6163848</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>SCAN Health Plan</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>Saint Petersburg, FL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Snowflake, ETL, ELT, dbt</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Hadoop, Scala, PostgreSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c24274a4aa989f95</t>
+          <t>https://www.indeed.com/viewjob?jk=7ea7fc0fae83610a</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Full Stack Engineer (NYC)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Amplify</t>
+          <t>KNIT</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Snowflake, DynamoDB, Data Modeling, Kimball, ETL, ELT, dbt</t>
+          <t>AWS, S3, SQS, ECS, RDS, Scala, MongoDB, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4d16d721d2057f3</t>
+          <t>https://www.indeed.com/viewjob?jk=f0457dc96d28b81f</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Software Engineer III - Java/Spark/AWS</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Amplify</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, ECS, RDS, Databricks, Spark, Scala, Snowflake</t>
+          <t>AWS, S3, RDS, Snowflake, DynamoDB, Data Modeling, Kimball, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c95674c932d41fb6</t>
+          <t>https://www.indeed.com/viewjob?jk=b4d16d721d2057f3</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Software Engineer III - Java/Spark/AWS</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Weyerhaeuser</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, MLOps, MLflow, CI/CD, Terraform, Docker</t>
+          <t>AWS, EMR, Lambda, S3, ECS, RDS, Databricks, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d9f82346c5ff2d3</t>
+          <t>https://www.indeed.com/viewjob?jk=c95674c932d41fb6</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Software Systems Engineer, Release Reliability &amp; Automation (Autonomous Vehicles)</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Weyerhaeuser</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, Power BI, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, MLOps, MLflow, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=864266ab5f8e3aac</t>
+          <t>https://www.indeed.com/viewjob?jk=7d9f82346c5ff2d3</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Software Engineer (Junior)</t>
+          <t>Software Systems Engineer, Release Reliability &amp; Automation (Autonomous Vehicles)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>TORCH.AI</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Leawood, KS, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Kafka, PostgreSQL, MongoDB, NoSQL, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, Power BI, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28e432d03da8db08</t>
+          <t>https://www.indeed.com/viewjob?jk=864266ab5f8e3aac</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Software Engineer (Hybrid)</t>
+          <t>Software Engineer (Junior)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Nightwing</t>
+          <t>TORCH.AI</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Clarksville, TN, US USA</t>
+          <t>Leawood, KS, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, IAM, Azure, GCP, Kafka, PostgreSQL, MongoDB, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=887221a715d1ff03</t>
+          <t>https://www.indeed.com/viewjob?jk=28e432d03da8db08</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Sterling, VA, US USA</t>
+          <t>Clarksville, TN, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3322d87953168bdc</t>
+          <t>https://www.indeed.com/viewjob?jk=887221a715d1ff03</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Software Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Nightwing</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8b55e090bbab627</t>
+          <t>https://www.indeed.com/viewjob?jk=3322d87953168bdc</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Database Administrator</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Hard Rock International</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Hollywood, FL, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, Snowflake, PostgreSQL, Cassandra, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=169d4a00d377fdae</t>
+          <t>https://www.indeed.com/viewjob?jk=a8b55e090bbab627</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Tableau Developer</t>
+          <t>Advanced Metering Infrastructure (AMI) Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Michael Kors</t>
+          <t>WSSC Water</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>East Rutherford, NJ, US USA</t>
+          <t>Laurel, MD, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Star Schema</t>
+          <t>RDS, Azure, Scala, Kafka, Oracle, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=904e084e965a45c4</t>
+          <t>https://www.indeed.com/viewjob?jk=c5b2aa36ee050b9b</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Advanced Metering Infrastructure (AMI) Engineer</t>
+          <t>Tableau Developer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>WSSC Water</t>
+          <t>Michael Kors</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Laurel, MD, US USA</t>
+          <t>East Rutherford, NJ, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Oracle, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps</t>
+          <t>AWS, Glue, Redshift, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,59 +2281,59 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5b2aa36ee050b9b</t>
+          <t>https://www.indeed.com/viewjob?jk=904e084e965a45c4</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End (Python)</t>
+          <t>Database Administrator</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Hard Rock International</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Hollywood, FL, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, Snowflake, PostgreSQL, Cassandra, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f65ac6c3f1cf1646</t>
+          <t>https://www.indeed.com/viewjob?jk=169d4a00d377fdae</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Software Engineer, Back End (Python)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, PySpark, Scala, MySQL, MongoDB, Docker, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd1518c4c02c12ef</t>
+          <t>https://www.indeed.com/viewjob?jk=f65ac6c3f1cf1646</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End (Python)</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, RDS, Spark, PySpark, Scala, MySQL, MongoDB, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3864c05dc9b353f8</t>
+          <t>https://www.indeed.com/viewjob?jk=dd1518c4c02c12ef</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Engineer 2</t>
+          <t>Senior Software Engineer, Back End (Python)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>BLOC Resources, LLC</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Data Modeling, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c51290628ce41b82</t>
+          <t>https://www.indeed.com/viewjob?jk=3864c05dc9b353f8</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer I, Applied AI</t>
+          <t>Data Engineer 2</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Axon</t>
+          <t>BLOC Resources, LLC</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e858c83fc09cd77d</t>
+          <t>https://www.indeed.com/viewjob?jk=c51290628ce41b82</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Platform</t>
+          <t>Sr. Software Engineer I, Applied AI</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>TRM Labs</t>
+          <t>Axon</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Spark, Scala, Kafka, ETL, dbt, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,14 +2491,14 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a517be0e10b2a44</t>
+          <t>https://www.indeed.com/viewjob?jk=e858c83fc09cd77d</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Data Platform</t>
+          <t>Senior Software Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60f6c2aecd2d1bdf</t>
+          <t>https://www.indeed.com/viewjob?jk=8a517be0e10b2a44</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>Senior Data Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Space Telescope Science Institute</t>
+          <t>TRM Labs</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, Hive, Scala, PostgreSQL, CI/CD, Terraform, Kubernetes</t>
+          <t>RDS, BigQuery, Spark, Scala, Kafka, ETL, dbt, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6055970eb603df79</t>
+          <t>https://www.indeed.com/viewjob?jk=60f6c2aecd2d1bdf</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>AI Engineer III</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>CareSource</t>
+          <t>Space Telescope Science Institute</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, S3, ECS, IAM, Hive, Scala, PostgreSQL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=640c68fe3716b1e6</t>
+          <t>https://www.indeed.com/viewjob?jk=6055970eb603df79</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
+          <t>AI Engineer III</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>CareSource</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>API Gateway, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f85f1e8c0778adba</t>
+          <t>https://www.indeed.com/viewjob?jk=640c68fe3716b1e6</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e2da1f14c27a331</t>
+          <t>https://www.indeed.com/viewjob?jk=f85f1e8c0778adba</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=140d02e1f58501f6</t>
+          <t>https://www.indeed.com/viewjob?jk=3e2da1f14c27a331</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eff547fec829449a</t>
+          <t>https://www.indeed.com/viewjob?jk=140d02e1f58501f6</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>AWS Data Engineer</t>
+          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Appex Innovation</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f3534222ab81e17</t>
+          <t>https://www.indeed.com/viewjob?jk=eff547fec829449a</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
+          <t>AWS Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Appex Innovation</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Glue, Lambda, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29d22d712d7958f0</t>
+          <t>https://www.indeed.com/viewjob?jk=7f3534222ab81e17</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>AWS Data Engineer</t>
+          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Appex Innovation</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3886cb86a753634c</t>
+          <t>https://www.indeed.com/viewjob?jk=29d22d712d7958f0</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
+          <t>AWS Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Appex Innovation</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Glue, Lambda, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9637232a826c3ad</t>
+          <t>https://www.indeed.com/viewjob?jk=3886cb86a753634c</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>CNH Industrial</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5b3837921976566</t>
+          <t>https://www.indeed.com/viewjob?jk=f9637232a826c3ad</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Microsoft Fabric</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>EoS Fitness</t>
+          <t>CNH Industrial</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bd7f3590528db3c</t>
+          <t>https://www.indeed.com/viewjob?jk=e5b3837921976566</t>
         </is>
       </c>
     </row>
@@ -3023,17 +3023,17 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Software Developer - Database Engineer</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>RAMSOFT</t>
+          <t>RapidFire Safety &amp; Security</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, HBase, Scala, Snowflake, MySQL, NoSQL, Data Modeling, Power BI</t>
+          <t>RDS, Azure, Scala, SQL Server, Data Modeling, Star Schema, Fact Tables, Dimension Tables, ETL, Power BI</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ce0ac7d0a937f32</t>
+          <t>https://www.indeed.com/viewjob?jk=8afc73df8ef8f40e</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Software Developer - Database Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>RapidFire Safety &amp; Security</t>
+          <t>RAMSOFT</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,17 +3076,17 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, Data Modeling, Star Schema, Fact Tables, Dimension Tables, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, HBase, Scala, Snowflake, MySQL, NoSQL, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8afc73df8ef8f40e</t>
+          <t>https://www.indeed.com/viewjob?jk=4ce0ac7d0a937f32</t>
         </is>
       </c>
     </row>
@@ -3268,17 +3268,17 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Sr. Software Engineer - Risk Platform (Hybrid)</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Westchester Medical Center Health Network</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Valhalla, NY, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,17 +3286,17 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Snowflake, SQL Server, Data Modeling, ELT, Power BI, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Cassandra, ETL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d807a7856ebe08db</t>
+          <t>https://www.indeed.com/viewjob?jk=a1593d7242ad3914</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-05.xlsx
+++ b/results/job_matches_2026-03-05.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G90"/>
+  <dimension ref="A1:G87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,122 +538,122 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer – DE20260503002</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Jersey Mikes Corporate</t>
+          <t>eGrove Systems Corporation</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Tinton Falls, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.8</v>
+        <v>17.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, HDFS, Hive, Spark, Scala, Oracle</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31cf41e0387f0b72</t>
+          <t>https://www.indeed.com/viewjob?jk=6093ead5fe385f5d</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sr. Data Platform Engineer</t>
+          <t>Senior Data Engineer - INDIA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Real Time Medical Systems</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Prosper, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.4</v>
+        <v>16</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, IAM, RDS, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=415686b53cfda723</t>
+          <t>https://www.indeed.com/viewjob?jk=f8eebff65cda31d0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sr. Data Platform Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Real Time Medical Systems</t>
+          <t>Valvoline Global Operations</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Columbia, MD, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17.4</v>
+        <v>16</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, IAM, RDS, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP, Cloud Storage, Spark, PySpark</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41a92f9802d4f918</t>
+          <t>https://www.indeed.com/viewjob?jk=ab16510fd1c2841d</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cloud Data Platform Administrator – Washington, DC</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Valvoline Global Operations</t>
+          <t>Creative Information Technology India</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Falls Church, VA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,52 +661,52 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP, Cloud Storage, Spark, PySpark</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Delta Live Tables, Photon, Scala, ETL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab16510fd1c2841d</t>
+          <t>https://www.indeed.com/viewjob?jk=0a74e373b48da5fc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Cloud Data Platform Administrator – Washington, DC</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Creative Information Technology India</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Falls Church, VA, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Delta Live Tables, Photon, Scala, ETL</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a74e373b48da5fc</t>
+          <t>https://www.indeed.com/viewjob?jk=32d044bc27a4af8a</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -736,12 +736,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32d044bc27a4af8a</t>
+          <t>https://www.indeed.com/viewjob?jk=aed60e56cae31294</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aed60e56cae31294</t>
+          <t>https://www.indeed.com/viewjob?jk=44f958ba0cbc0f43</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44f958ba0cbc0f43</t>
+          <t>https://www.indeed.com/viewjob?jk=9e8500146d476812</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e8500146d476812</t>
+          <t>https://www.indeed.com/viewjob?jk=2ad2838bd8f61427</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Google Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>NMI</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Schaumburg, IL, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Kafka, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ad2838bd8f61427</t>
+          <t>https://www.indeed.com/viewjob?jk=e7cac4b03aa7cfe7</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Google Cloud Data Engineer</t>
+          <t>Senior Systems Administrator, Cloud (GTA)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>NMI</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Schaumburg, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,17 +906,17 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Kafka, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, S3, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, AWS CodePipeline</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7cac4b03aa7cfe7</t>
+          <t>https://www.indeed.com/viewjob?jk=094fcc384185954f</t>
         </is>
       </c>
     </row>
@@ -1378,17 +1378,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>SENIOR DATA ENGINEER</t>
+          <t>Cloud Platform Engineer - Virtual</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Alight Solutions</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bee5a340a7f65e61</t>
+          <t>https://www.indeed.com/viewjob?jk=a286c7ca862c4e1a</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Software Engineer - Authentication</t>
+          <t>SENIOR DATA ENGINEER</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Pindrop</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, RDS, Scala, MySQL, DynamoDB, MLOps, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6513fcf97bbfd044</t>
+          <t>https://www.indeed.com/viewjob?jk=bee5a340a7f65e61</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SSO Administrator</t>
+          <t>Software Engineer - Authentication</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Pindrop</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,77 +1466,77 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, PostgreSQL, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, Kinesis, S3, RDS, Scala, MySQL, DynamoDB, MLOps, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9064a81c91aa262</t>
+          <t>https://www.indeed.com/viewjob?jk=6513fcf97bbfd044</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Commercial Software</t>
+          <t>Advisor Application Designer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>HJ Staffing</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, Oracle, MySQL</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f3de39cf73c3663</t>
+          <t>https://www.indeed.com/viewjob?jk=a988f0c0aeaa0fa5</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Data Lakehouse Infrastructure</t>
+          <t>SSO Administrator</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>TRM Labs</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, PostgreSQL, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e899ea40640da235</t>
+          <t>https://www.indeed.com/viewjob?jk=a9064a81c91aa262</t>
         </is>
       </c>
     </row>
@@ -1658,17 +1658,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Java Software Engineer II (US)</t>
+          <t>Senior Software Engineer - Commercial Software</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>TD Bank</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Mount Laurel, NJ, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, NoSQL, Splunk, Jenkins, Maven, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, Oracle, MySQL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,42 +1686,42 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ee89e940b02cc06</t>
+          <t>https://www.indeed.com/viewjob?jk=5f3de39cf73c3663</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End (Java, Go, AWS)</t>
+          <t>Java Software Engineer II (US)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>TD Bank</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Mount Laurel, NJ, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Docker</t>
+          <t>RDS, Azure, Scala, NoSQL, Splunk, Jenkins, Maven, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e716b4195b2da30b</t>
+          <t>https://www.indeed.com/viewjob?jk=8ee89e940b02cc06</t>
         </is>
       </c>
     </row>
@@ -1833,17 +1833,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Data Product</t>
+          <t>Senior Software Engineer, Back End (Java, Go, AWS)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>TRM Labs</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Dataflow, Spark, Scala, Kafka, dbt, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=351b720407fa6f6d</t>
+          <t>https://www.indeed.com/viewjob?jk=e716b4195b2da30b</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Application Platform Architect - 6163848</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>LERETA, LLC</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Saint Petersburg, FL, US USA</t>
+          <t>Pomona, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Hadoop, Scala, PostgreSQL, CI/CD, Docker</t>
+          <t>Azure, Data Factory, Data Lake Storage, Scala, Snowflake, SQL Server, Data Modeling, Fact Tables, ELT, Power BI</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ea7fc0fae83610a</t>
+          <t>https://www.indeed.com/viewjob?jk=ad5d067156fc62f1</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer (NYC)</t>
+          <t>Applied Machine Learning Engineer (All Levels)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>KNIT</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, ECS, RDS, Scala, MongoDB, CI/CD, GitHub Actions, Docker</t>
+          <t>AWS, Azure, GCP, Spark, ELT, MLflow, CI/CD, Terraform, Docker, Git</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0457dc96d28b81f</t>
+          <t>https://www.indeed.com/viewjob?jk=c1910fa4b9572adb</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Application Platform Architect - 6163848</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Amplify</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Saint Petersburg, FL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Snowflake, DynamoDB, Data Modeling, Kimball, ETL, ELT, dbt</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Hadoop, Scala, PostgreSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4d16d721d2057f3</t>
+          <t>https://www.indeed.com/viewjob?jk=7ea7fc0fae83610a</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Software Engineer III - Java/Spark/AWS</t>
+          <t>Senior Full Stack Engineer (NYC)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>KNIT</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, ECS, RDS, Databricks, Spark, Scala, Snowflake</t>
+          <t>AWS, S3, SQS, ECS, RDS, Scala, MongoDB, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c95674c932d41fb6</t>
+          <t>https://www.indeed.com/viewjob?jk=f0457dc96d28b81f</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Weyerhaeuser</t>
+          <t>Amplify</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, MLOps, MLflow, CI/CD, Terraform, Docker</t>
+          <t>AWS, S3, RDS, Snowflake, DynamoDB, Data Modeling, Kimball, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d9f82346c5ff2d3</t>
+          <t>https://www.indeed.com/viewjob?jk=b4d16d721d2057f3</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Software Systems Engineer, Release Reliability &amp; Automation (Autonomous Vehicles)</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Weyerhaeuser</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, Power BI, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, MLOps, MLflow, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=864266ab5f8e3aac</t>
+          <t>https://www.indeed.com/viewjob?jk=7d9f82346c5ff2d3</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Software Engineer (Junior)</t>
+          <t>Software Systems Engineer, Release Reliability &amp; Automation (Autonomous Vehicles)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>TORCH.AI</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Leawood, KS, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Kafka, PostgreSQL, MongoDB, NoSQL, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, Power BI, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28e432d03da8db08</t>
+          <t>https://www.indeed.com/viewjob?jk=864266ab5f8e3aac</t>
         </is>
       </c>
     </row>
@@ -2183,17 +2183,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Software Engineer III - Java/Spark/AWS</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, EMR, Lambda, S3, ECS, RDS, Databricks, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8b55e090bbab627</t>
+          <t>https://www.indeed.com/viewjob?jk=c95674c932d41fb6</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Advanced Metering Infrastructure (AMI) Engineer</t>
+          <t>Database Administrator</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>WSSC Water</t>
+          <t>Hard Rock International</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Laurel, MD, US USA</t>
+          <t>Hollywood, FL, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,17 +2236,17 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Oracle, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, Snowflake, PostgreSQL, Cassandra, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5b2aa36ee050b9b</t>
+          <t>https://www.indeed.com/viewjob?jk=169d4a00d377fdae</t>
         </is>
       </c>
     </row>
@@ -2288,17 +2288,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Database Administrator</t>
+          <t>Advanced Metering Infrastructure (AMI) Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Hard Rock International</t>
+          <t>WSSC Water</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Hollywood, FL, US USA</t>
+          <t>Laurel, MD, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,29 +2306,29 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, Snowflake, PostgreSQL, Cassandra, CI/CD, Terraform</t>
+          <t>RDS, Azure, Scala, Kafka, Oracle, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=169d4a00d377fdae</t>
+          <t>https://www.indeed.com/viewjob?jk=c5b2aa36ee050b9b</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End (Python)</t>
+          <t>Sr. ETL/SQL Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Capgemini Government Solutions</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, ETL, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f65ac6c3f1cf1646</t>
+          <t>https://www.indeed.com/viewjob?jk=724ffe7f1d3da135</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Space Telescope Science Institute</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, PySpark, Scala, MySQL, MongoDB, Docker, Kubernetes, Airflow</t>
+          <t>AWS, S3, ECS, IAM, Hive, Scala, PostgreSQL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd1518c4c02c12ef</t>
+          <t>https://www.indeed.com/viewjob?jk=6055970eb603df79</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End (Python)</t>
+          <t>AI Engineer III</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>CareSource</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Docker, Kubernetes</t>
+          <t>API Gateway, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3864c05dc9b353f8</t>
+          <t>https://www.indeed.com/viewjob?jk=640c68fe3716b1e6</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Engineer 2</t>
+          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>BLOC Resources, LLC</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Data Modeling, CI/CD</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c51290628ce41b82</t>
+          <t>https://www.indeed.com/viewjob?jk=f85f1e8c0778adba</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer I, Applied AI</t>
+          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Axon</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e858c83fc09cd77d</t>
+          <t>https://www.indeed.com/viewjob?jk=3e2da1f14c27a331</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Platform</t>
+          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>TRM Labs</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Spark, Scala, Kafka, ETL, dbt, Terraform, Docker, Kubernetes</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a517be0e10b2a44</t>
+          <t>https://www.indeed.com/viewjob?jk=140d02e1f58501f6</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Data Platform</t>
+          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>TRM Labs</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Spark, Scala, Kafka, ETL, dbt, Terraform, Docker, Kubernetes</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60f6c2aecd2d1bdf</t>
+          <t>https://www.indeed.com/viewjob?jk=eff547fec829449a</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Space Telescope Science Institute</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, Hive, Scala, PostgreSQL, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6055970eb603df79</t>
+          <t>https://www.indeed.com/viewjob?jk=29d22d712d7958f0</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>AI Engineer III</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>CareSource</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Spark, PySpark, Scala, MySQL, MongoDB, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=640c68fe3716b1e6</t>
+          <t>https://www.indeed.com/viewjob?jk=dd1518c4c02c12ef</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
+          <t>AWS Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Appex Innovation</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Glue, Lambda, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f85f1e8c0778adba</t>
+          <t>https://www.indeed.com/viewjob?jk=3886cb86a753634c</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
+          <t>Data Engineer 2</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>BLOC Resources, LLC</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,17 +2691,17 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e2da1f14c27a331</t>
+          <t>https://www.indeed.com/viewjob?jk=c51290628ce41b82</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2731,29 +2731,29 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=140d02e1f58501f6</t>
+          <t>https://www.indeed.com/viewjob?jk=f9637232a826c3ad</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>CNH Industrial</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eff547fec829449a</t>
+          <t>https://www.indeed.com/viewjob?jk=e5b3837921976566</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>AWS Data Engineer</t>
+          <t>Senior Software Engineer, Back End (Python)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Appex Innovation</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f3534222ab81e17</t>
+          <t>https://www.indeed.com/viewjob?jk=f65ac6c3f1cf1646</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
+          <t>Senior Software Engineer, Back End (Python)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29d22d712d7958f0</t>
+          <t>https://www.indeed.com/viewjob?jk=3864c05dc9b353f8</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>AWS Data Engineer</t>
+          <t>Sr. Software Engineer I, Applied AI</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Appex Innovation</t>
+          <t>Axon</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3886cb86a753634c</t>
+          <t>https://www.indeed.com/viewjob?jk=e858c83fc09cd77d</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
+          <t>Senior Data Engineer - Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>WesBanco Bank, Inc.</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Bowie, MD, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9637232a826c3ad</t>
+          <t>https://www.indeed.com/viewjob?jk=a3a02cdb2b181be3</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer - Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>CNH Industrial</t>
+          <t>WesBanco Bank, Inc.</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Wheeling, WV, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,17 +2936,17 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5b3837921976566</t>
+          <t>https://www.indeed.com/viewjob?jk=fb6ee55d393e301c</t>
         </is>
       </c>
     </row>
@@ -3023,17 +3023,17 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Software Developer - Database Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>RapidFire Safety &amp; Security</t>
+          <t>RAMSOFT</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, Data Modeling, Star Schema, Fact Tables, Dimension Tables, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, HBase, Scala, Snowflake, MySQL, NoSQL, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8afc73df8ef8f40e</t>
+          <t>https://www.indeed.com/viewjob?jk=4ce0ac7d0a937f32</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Software Developer - Database Engineer</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>RAMSOFT</t>
+          <t>RapidFire Safety &amp; Security</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, HBase, Scala, Snowflake, MySQL, NoSQL, Data Modeling, Power BI</t>
+          <t>RDS, Azure, Scala, SQL Server, Data Modeling, Star Schema, Fact Tables, Dimension Tables, ETL, Power BI</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ce0ac7d0a937f32</t>
+          <t>https://www.indeed.com/viewjob?jk=8afc73df8ef8f40e</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Software Engineer - Master</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Emed</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fb1207979169793</t>
+          <t>https://www.indeed.com/viewjob?jk=1e29e1c3d36f0e7c</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Data Engineer - GRC Technology</t>
+          <t>Sr. Data Engineer, Engineering &amp; Ops</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>NBCUniversal</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, ETL, ELT</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Snowflake, ELT, dbt, MLOps, Airflow</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8842e67bf37c518a</t>
+          <t>https://www.indeed.com/viewjob?jk=df536a2594fa5881</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer - GRC Technology</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Emed</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e29e1c3d36f0e7c</t>
+          <t>https://www.indeed.com/viewjob?jk=8842e67bf37c518a</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer, Engineering &amp; Ops</t>
+          <t>Sr. Software Engineer - Risk Platform (Hybrid)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>NBCUniversal</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Snowflake, ELT, dbt, MLOps, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Cassandra, ETL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df536a2594fa5881</t>
+          <t>https://www.indeed.com/viewjob?jk=a1593d7242ad3914</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>TRM Labs</t>
+          <t>Daniels Health</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, ETL, dbt, Power BI, Tableau, CI/CD</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, ETL, ELT, Git</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dcb7ea8003fbc5dc</t>
+          <t>https://www.indeed.com/viewjob?jk=aedcadc853d15f82</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - Risk Platform (Hybrid)</t>
+          <t>Advisor Solution Architect</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>HJ Staffing</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Cassandra, ETL, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1593d7242ad3914</t>
+          <t>https://www.indeed.com/viewjob?jk=20d4ea50920ad807</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Daniels Health</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, ETL, ELT, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aedcadc853d15f82</t>
+          <t>https://www.indeed.com/viewjob?jk=1315e6e62a7714e8</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Daniels Health</t>
+          <t>Guidewire Software, Inc.</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, ETL, ELT, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=447d4d5607b3f3c6</t>
+          <t>https://www.indeed.com/viewjob?jk=3b5e082bd1857b0f</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>.NET Developer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>S3, RDS, Azure, Scala, Snowflake, SQL Server, Power BI, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1315e6e62a7714e8</t>
+          <t>https://www.indeed.com/viewjob?jk=4afc3e61f8ae8b7b</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Guidewire Software, Inc.</t>
+          <t>Daniels Health</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, ETL, ELT, Git</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b5e082bd1857b0f</t>
+          <t>https://www.indeed.com/viewjob?jk=447d4d5607b3f3c6</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>.NET Developer</t>
+          <t>Sr. Informatica IDMC MDM Software Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>RBC</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Scala, Snowflake, SQL Server, Power BI, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,112 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4afc3e61f8ae8b7b</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Sr. Informatica IDMC MDM Software Engineer</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>RBC</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Minneapolis, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, ETL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=5346f4c5e2b5352a</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer, Attribution Expansion</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>TRM Labs</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D89" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>RDS, BigQuery, Spark, Snowflake, Data Modeling, dbt, MLflow, CI/CD, Terraform, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=539a18aebac4ef5f</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer, Attribution Expansion</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>TRM Labs</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D90" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>RDS, BigQuery, Spark, Snowflake, Data Modeling, dbt, MLflow, CI/CD, Terraform, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=26436308d22e947d</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-05.xlsx
+++ b/results/job_matches_2026-03-05.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G87"/>
+  <dimension ref="A1:G90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,12 +683,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>JBS Dev</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, Lambda, S3, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32d044bc27a4af8a</t>
+          <t>https://www.indeed.com/viewjob?jk=49f6c2df00dd6e11</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer (Costa Rica)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>JBS Dev</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,17 +731,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, Lambda, S3, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aed60e56cae31294</t>
+          <t>https://www.indeed.com/viewjob?jk=05c819aa2a88511d</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -771,12 +771,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44f958ba0cbc0f43</t>
+          <t>https://www.indeed.com/viewjob?jk=32d044bc27a4af8a</t>
         </is>
       </c>
     </row>
@@ -788,12 +788,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e8500146d476812</t>
+          <t>https://www.indeed.com/viewjob?jk=aed60e56cae31294</t>
         </is>
       </c>
     </row>
@@ -823,12 +823,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ad2838bd8f61427</t>
+          <t>https://www.indeed.com/viewjob?jk=44f958ba0cbc0f43</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Google Cloud Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>NMI</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Schaumburg, IL, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Kafka, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7cac4b03aa7cfe7</t>
+          <t>https://www.indeed.com/viewjob?jk=9e8500146d476812</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Systems Administrator, Cloud (GTA)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,34 +906,34 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, AWS CodePipeline</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=094fcc384185954f</t>
+          <t>https://www.indeed.com/viewjob?jk=2ad2838bd8f61427</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>System Architect</t>
+          <t>Senior Systems Administrator, Cloud (GTA)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Systems Engineering Solutions Corporation</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Kinesis, Redshift, S3, IAM, RDS, Spark, PySpark</t>
+          <t>AWS, S3, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, AWS CodePipeline</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=634fcd15ef04d7bf</t>
+          <t>https://www.indeed.com/viewjob?jk=094fcc384185954f</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Specialist - System Management</t>
+          <t>System Architect</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Systems Engineering Solutions Corporation</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Glen Allen, VA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,69 +976,69 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Unity Catalog, Delta Live Tables, Spark, Databricks Lakehouse, SQL Server</t>
+          <t>AWS, Glue, EMR, Kinesis, Redshift, S3, IAM, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=293f842904007fda</t>
+          <t>https://www.indeed.com/viewjob?jk=634fcd15ef04d7bf</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CLOUD ENGINEER (AWS) (REMOTE/USA) - GDM (GRAY MEDIA GROUP)</t>
+          <t>Senior Specialist - System Management</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>GRAY MEDIA</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Glen Allen, VA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Google Cloud Platform, GCP, Scala, DynamoDB</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Unity Catalog, Delta Live Tables, Spark, Databricks Lakehouse, SQL Server</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0beb94e2f1648144</t>
+          <t>https://www.indeed.com/viewjob?jk=293f842904007fda</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>CLOUD ENGINEER (AWS) (REMOTE/USA) - GDM (GRAY MEDIA GROUP)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Alight Solutions</t>
+          <t>GRAY MEDIA</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,34 +1046,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, GCP, Scala, CI/CD</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Google Cloud Platform, GCP, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=398f35933211332f</t>
+          <t>https://www.indeed.com/viewjob?jk=0beb94e2f1648144</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>Alight Solutions</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,17 +1081,17 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, GCP, Scala, Snowflake</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, GCP, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e83bd0fd320bb829</t>
+          <t>https://www.indeed.com/viewjob?jk=398f35933211332f</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=105f562c4b87c831</t>
+          <t>https://www.indeed.com/viewjob?jk=e83bd0fd320bb829</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Wichita, KS, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56a2fccd9b09c654</t>
+          <t>https://www.indeed.com/viewjob?jk=105f562c4b87c831</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Upstart</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Wichita, KS, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, GCP, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dab96c17b78fc32</t>
+          <t>https://www.indeed.com/viewjob?jk=56a2fccd9b09c654</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SQL Developer - Enterprise Data &amp; Analytics</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Pantherx Specialty Llc</t>
+          <t>Upstart</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,17 +1221,17 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41d495363374161e</t>
+          <t>https://www.indeed.com/viewjob?jk=3dab96c17b78fc32</t>
         </is>
       </c>
     </row>
@@ -1378,17 +1378,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer - Virtual</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Alight Solutions</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Royal Oak, MI, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a286c7ca862c4e1a</t>
+          <t>https://www.indeed.com/viewjob?jk=6bb3681c5da818f2</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SENIOR DATA ENGINEER</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bee5a340a7f65e61</t>
+          <t>https://www.indeed.com/viewjob?jk=343b07159d1b6928</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Software Engineer - Authentication</t>
+          <t>Cloud Platform Engineer - Virtual</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Pindrop</t>
+          <t>Alight Solutions</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, RDS, Scala, MySQL, DynamoDB, MLOps, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6513fcf97bbfd044</t>
+          <t>https://www.indeed.com/viewjob?jk=a286c7ca862c4e1a</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Advisor Application Designer</t>
+          <t>SENIOR DATA ENGINEER</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>HJ Staffing</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a988f0c0aeaa0fa5</t>
+          <t>https://www.indeed.com/viewjob?jk=bee5a340a7f65e61</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SSO Administrator</t>
+          <t>Software Engineer - Authentication</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Pindrop</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,104 +1536,104 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, PostgreSQL, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, Kinesis, S3, RDS, Scala, MySQL, DynamoDB, MLOps, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9064a81c91aa262</t>
+          <t>https://www.indeed.com/viewjob?jk=6513fcf97bbfd044</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Platform Engineer-3</t>
+          <t>Advisor Application Designer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>HJ Staffing</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f753e538739bd670</t>
+          <t>https://www.indeed.com/viewjob?jk=a988f0c0aeaa0fa5</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>SSO Administrator</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Advance Auto Parts</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, PostgreSQL, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e2d8bc5a4c9174d</t>
+          <t>https://www.indeed.com/viewjob?jk=a9064a81c91aa262</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>IT Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Novolex</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Lake Forest, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Step Functions, Medallion Architecture, Spark, Scala, ETL, ELT, CI/CD, GitHub Actions, AWS CodePipeline</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=024a63ca708c8a8f</t>
+          <t>https://www.indeed.com/viewjob?jk=83c604950fd47a32</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Commercial Software</t>
+          <t>Data Platform Engineer-3</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, Oracle, MySQL</t>
+          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f3de39cf73c3663</t>
+          <t>https://www.indeed.com/viewjob?jk=f753e538739bd670</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Java Software Engineer II (US)</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>TD Bank</t>
+          <t>Advance Auto Parts</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Mount Laurel, NJ, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,77 +1711,77 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, NoSQL, Splunk, Jenkins, Maven, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ee89e940b02cc06</t>
+          <t>https://www.indeed.com/viewjob?jk=3e2d8bc5a4c9174d</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>IT Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Daniels Health</t>
+          <t>Novolex</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Lake Forest, IL, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3486f1249174e37a</t>
+          <t>https://www.indeed.com/viewjob?jk=024a63ca708c8a8f</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Software Engineer - Commercial Software</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Daniels Health</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, Oracle, MySQL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1df7caac86af2291</t>
+          <t>https://www.indeed.com/viewjob?jk=5f3de39cf73c3663</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ATC - AI &amp; Data Analyst - NAELFY26</t>
+          <t>Java Software Engineer II (US)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>TD Bank</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Saint Petersburg, FL, US USA</t>
+          <t>Mount Laurel, NJ, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Scala, NoSQL, Splunk, Jenkins, Maven, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ce7a50a4bbe9ef2</t>
+          <t>https://www.indeed.com/viewjob?jk=8ee89e940b02cc06</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End (Java, Go, AWS)</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Daniels Health</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Docker</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e716b4195b2da30b</t>
+          <t>https://www.indeed.com/viewjob?jk=3486f1249174e37a</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>LERETA, LLC</t>
+          <t>Daniels Health</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Pomona, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Data Lake Storage, Scala, Snowflake, SQL Server, Data Modeling, Fact Tables, ELT, Power BI</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad5d067156fc62f1</t>
+          <t>https://www.indeed.com/viewjob?jk=1df7caac86af2291</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Applied Machine Learning Engineer (All Levels)</t>
+          <t>ATC - AI &amp; Data Analyst - NAELFY26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Saint Petersburg, FL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, ELT, MLflow, CI/CD, Terraform, Docker, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1910fa4b9572adb</t>
+          <t>https://www.indeed.com/viewjob?jk=1ce7a50a4bbe9ef2</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Application Platform Architect - 6163848</t>
+          <t>Senior Software Engineer, Back End (Java, Go, AWS)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Saint Petersburg, FL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Hadoop, Scala, PostgreSQL, CI/CD, Docker</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ea7fc0fae83610a</t>
+          <t>https://www.indeed.com/viewjob?jk=e716b4195b2da30b</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer (NYC)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>KNIT</t>
+          <t>LERETA, LLC</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Pomona, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, ECS, RDS, Scala, MongoDB, CI/CD, GitHub Actions, Docker</t>
+          <t>Azure, Data Factory, Data Lake Storage, Scala, Snowflake, SQL Server, Data Modeling, Fact Tables, ELT, Power BI</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0457dc96d28b81f</t>
+          <t>https://www.indeed.com/viewjob?jk=ad5d067156fc62f1</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Applied Machine Learning Engineer (All Levels)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Amplify</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Snowflake, DynamoDB, Data Modeling, Kimball, ETL, ELT, dbt</t>
+          <t>AWS, Azure, GCP, Spark, ELT, MLflow, CI/CD, Terraform, Docker, Git</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4d16d721d2057f3</t>
+          <t>https://www.indeed.com/viewjob?jk=c1910fa4b9572adb</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Senior Application Platform Architect - 6163848</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Weyerhaeuser</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Saint Petersburg, FL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, MLOps, MLflow, CI/CD, Terraform, Docker</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Hadoop, Scala, PostgreSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d9f82346c5ff2d3</t>
+          <t>https://www.indeed.com/viewjob?jk=7ea7fc0fae83610a</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Software Systems Engineer, Release Reliability &amp; Automation (Autonomous Vehicles)</t>
+          <t>Senior Full Stack Engineer (NYC)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>KNIT</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, Power BI, CI/CD, Jenkins</t>
+          <t>AWS, S3, SQS, ECS, RDS, Scala, MongoDB, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=864266ab5f8e3aac</t>
+          <t>https://www.indeed.com/viewjob?jk=f0457dc96d28b81f</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Software Engineer (Hybrid)</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Nightwing</t>
+          <t>Amplify</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Clarksville, TN, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Snowflake, DynamoDB, Data Modeling, Kimball, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=887221a715d1ff03</t>
+          <t>https://www.indeed.com/viewjob?jk=b4d16d721d2057f3</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Software Engineer (Hybrid)</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Nightwing</t>
+          <t>Weyerhaeuser</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Sterling, VA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, MLOps, MLflow, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3322d87953168bdc</t>
+          <t>https://www.indeed.com/viewjob?jk=7d9f82346c5ff2d3</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Software Engineer III - Java/Spark/AWS</t>
+          <t>Software Systems Engineer, Release Reliability &amp; Automation (Autonomous Vehicles)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, ECS, RDS, Databricks, Spark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, Power BI, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c95674c932d41fb6</t>
+          <t>https://www.indeed.com/viewjob?jk=864266ab5f8e3aac</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Database Administrator</t>
+          <t>Software Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Hard Rock International</t>
+          <t>Nightwing</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Hollywood, FL, US USA</t>
+          <t>Clarksville, TN, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, Snowflake, PostgreSQL, Cassandra, CI/CD, Terraform</t>
+          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=169d4a00d377fdae</t>
+          <t>https://www.indeed.com/viewjob?jk=887221a715d1ff03</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Tableau Developer</t>
+          <t>Software Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Michael Kors</t>
+          <t>Nightwing</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>East Rutherford, NJ, US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Star Schema</t>
+          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=904e084e965a45c4</t>
+          <t>https://www.indeed.com/viewjob?jk=3322d87953168bdc</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Advanced Metering Infrastructure (AMI) Engineer</t>
+          <t>Software Engineer III - Java/Spark/AWS</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>WSSC Water</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Laurel, MD, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Oracle, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps</t>
+          <t>AWS, EMR, Lambda, S3, ECS, RDS, Databricks, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5b2aa36ee050b9b</t>
+          <t>https://www.indeed.com/viewjob?jk=c95674c932d41fb6</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Sr. ETL/SQL Engineer</t>
+          <t>Database Administrator</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Capgemini Government Solutions</t>
+          <t>Hard Rock International</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Hollywood, FL, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, ETL, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, Snowflake, PostgreSQL, Cassandra, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,94 +2351,94 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=724ffe7f1d3da135</t>
+          <t>https://www.indeed.com/viewjob?jk=169d4a00d377fdae</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>Tableau Developer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Space Telescope Science Institute</t>
+          <t>Michael Kors</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>East Rutherford, NJ, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, Hive, Scala, PostgreSQL, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, Glue, Redshift, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6055970eb603df79</t>
+          <t>https://www.indeed.com/viewjob?jk=904e084e965a45c4</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>AI Engineer III</t>
+          <t>Advanced Metering Infrastructure (AMI) Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>CareSource</t>
+          <t>WSSC Water</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Laurel, MD, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
+          <t>RDS, Azure, Scala, Kafka, Oracle, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=640c68fe3716b1e6</t>
+          <t>https://www.indeed.com/viewjob?jk=c5b2aa36ee050b9b</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
+          <t>Sr. ETL/SQL Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Capgemini Government Solutions</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, ETL, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f85f1e8c0778adba</t>
+          <t>https://www.indeed.com/viewjob?jk=724ffe7f1d3da135</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Space Telescope Science Institute</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, ECS, IAM, Hive, Scala, PostgreSQL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e2da1f14c27a331</t>
+          <t>https://www.indeed.com/viewjob?jk=6055970eb603df79</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
+          <t>AI Engineer III</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>CareSource</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>API Gateway, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=140d02e1f58501f6</t>
+          <t>https://www.indeed.com/viewjob?jk=640c68fe3716b1e6</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eff547fec829449a</t>
+          <t>https://www.indeed.com/viewjob?jk=f85f1e8c0778adba</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2591,29 +2591,29 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29d22d712d7958f0</t>
+          <t>https://www.indeed.com/viewjob?jk=3e2da1f14c27a331</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, PySpark, Scala, MySQL, MongoDB, Docker, Kubernetes, Airflow</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd1518c4c02c12ef</t>
+          <t>https://www.indeed.com/viewjob?jk=140d02e1f58501f6</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>AWS Data Engineer</t>
+          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Appex Innovation</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3886cb86a753634c</t>
+          <t>https://www.indeed.com/viewjob?jk=eff547fec829449a</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Engineer 2</t>
+          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>BLOC Resources, LLC</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Data Modeling, CI/CD</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c51290628ce41b82</t>
+          <t>https://www.indeed.com/viewjob?jk=29d22d712d7958f0</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Spark, PySpark, Scala, MySQL, MongoDB, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9637232a826c3ad</t>
+          <t>https://www.indeed.com/viewjob?jk=dd1518c4c02c12ef</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AWS Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>CNH Industrial</t>
+          <t>Appex Innovation</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, Glue, Lambda, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5b3837921976566</t>
+          <t>https://www.indeed.com/viewjob?jk=3886cb86a753634c</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End (Python)</t>
+          <t>Data Engineer 2</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>BLOC Resources, LLC</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f65ac6c3f1cf1646</t>
+          <t>https://www.indeed.com/viewjob?jk=c51290628ce41b82</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End (Python)</t>
+          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3864c05dc9b353f8</t>
+          <t>https://www.indeed.com/viewjob?jk=f9637232a826c3ad</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer I, Applied AI</t>
+          <t>Senior Software Engineer, Back End (Python)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Axon</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e858c83fc09cd77d</t>
+          <t>https://www.indeed.com/viewjob?jk=f65ac6c3f1cf1646</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Data &amp; Analytics</t>
+          <t>Senior Software Engineer, Back End (Python)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>WesBanco Bank, Inc.</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Bowie, MD, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3a02cdb2b181be3</t>
+          <t>https://www.indeed.com/viewjob?jk=3864c05dc9b353f8</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Data &amp; Analytics</t>
+          <t>Sr. Software Engineer I, Applied AI</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>WesBanco Bank, Inc.</t>
+          <t>Axon</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Wheeling, WV, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb6ee55d393e301c</t>
+          <t>https://www.indeed.com/viewjob?jk=e858c83fc09cd77d</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Senior Data Engineer - Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Centene</t>
+          <t>WesBanco Bank, Inc.</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>Bowie, MD, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, MySQL, MongoDB, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11d92da9c37770a7</t>
+          <t>https://www.indeed.com/viewjob?jk=a3a02cdb2b181be3</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Customer Reliability Engineer, Airflow</t>
+          <t>Senior Data Engineer - Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Astronomer</t>
+          <t>WesBanco Bank, Inc.</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Wheeling, WV, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, Snowflake, PostgreSQL, dbt, DataOps, Docker</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ac244565083c1d9</t>
+          <t>https://www.indeed.com/viewjob?jk=fb6ee55d393e301c</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Software Developer - Database Engineer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>RAMSOFT</t>
+          <t>Centene</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, HBase, Scala, Snowflake, MySQL, NoSQL, Data Modeling, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, MySQL, MongoDB, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ce0ac7d0a937f32</t>
+          <t>https://www.indeed.com/viewjob?jk=11d92da9c37770a7</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Customer Reliability Engineer, Airflow</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>RapidFire Safety &amp; Security</t>
+          <t>Astronomer</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, Data Modeling, Star Schema, Fact Tables, Dimension Tables, ETL, Power BI</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, Snowflake, PostgreSQL, dbt, DataOps, Docker</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,67 +3086,67 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8afc73df8ef8f40e</t>
+          <t>https://www.indeed.com/viewjob?jk=6ac244565083c1d9</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Developer - Database Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Emed</t>
+          <t>RAMSOFT</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, HBase, Scala, Snowflake, MySQL, NoSQL, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e29e1c3d36f0e7c</t>
+          <t>https://www.indeed.com/viewjob?jk=4ce0ac7d0a937f32</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer, Engineering &amp; Ops</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>NBCUniversal</t>
+          <t>RapidFire Safety &amp; Security</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Snowflake, ELT, dbt, MLOps, Airflow</t>
+          <t>RDS, Azure, Scala, SQL Server, Data Modeling, Star Schema, Fact Tables, Dimension Tables, ETL, Power BI</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df536a2594fa5881</t>
+          <t>https://www.indeed.com/viewjob?jk=8afc73df8ef8f40e</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Data Engineer - GRC Technology</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Emed</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8842e67bf37c518a</t>
+          <t>https://www.indeed.com/viewjob?jk=1e29e1c3d36f0e7c</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - Risk Platform (Hybrid)</t>
+          <t>Sr. Data Engineer, Engineering &amp; Ops</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>NBCUniversal</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Cassandra, ETL, Docker, Kubernetes</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Snowflake, ELT, dbt, MLOps, Airflow</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1593d7242ad3914</t>
+          <t>https://www.indeed.com/viewjob?jk=df536a2594fa5881</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer - GRC Technology</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Daniels Health</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, ETL, ELT, Git</t>
+          <t>AWS, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aedcadc853d15f82</t>
+          <t>https://www.indeed.com/viewjob?jk=8842e67bf37c518a</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Advisor Solution Architect</t>
+          <t>Senior Backend Engineer - Startup</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>HJ Staffing</t>
+          <t>TALENThire</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, Kinesis, GCP, Scala, Kafka, PostgreSQL, ELT, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20d4ea50920ad807</t>
+          <t>https://www.indeed.com/viewjob?jk=5f9f397d4f8fa7f1</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Software Engineer - Risk Platform (Hybrid)</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Cassandra, ETL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1315e6e62a7714e8</t>
+          <t>https://www.indeed.com/viewjob?jk=a1593d7242ad3914</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Guidewire Software, Inc.</t>
+          <t>Daniels Health</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, ETL, ELT, Git</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b5e082bd1857b0f</t>
+          <t>https://www.indeed.com/viewjob?jk=aedcadc853d15f82</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>.NET Developer</t>
+          <t>Advisor Solution Architect</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>HJ Staffing</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Scala, Snowflake, SQL Server, Power BI, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4afc3e61f8ae8b7b</t>
+          <t>https://www.indeed.com/viewjob?jk=20d4ea50920ad807</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Daniels Health</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, ETL, ELT, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=447d4d5607b3f3c6</t>
+          <t>https://www.indeed.com/viewjob?jk=1315e6e62a7714e8</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Sr. Informatica IDMC MDM Software Engineer</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>RBC</t>
+          <t>Guidewire Software, Inc.</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,15 +3461,120 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, MySQL, MongoDB, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3b5e082bd1857b0f</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>.NET Developer</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Caterpillar</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Cary, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>S3, RDS, Azure, Scala, Snowflake, SQL Server, Power BI, CI/CD, Azure DevOps, Git</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4afc3e61f8ae8b7b</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Daniels Health</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, ETL, ELT, Git</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=447d4d5607b3f3c6</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Sr. Informatica IDMC MDM Software Engineer</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>RBC</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Minneapolis, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
           <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, ETL, CI/CD</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=5346f4c5e2b5352a</t>
         </is>

--- a/results/job_matches_2026-03-05.xlsx
+++ b/results/job_matches_2026-03-05.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G90"/>
+  <dimension ref="A1:G100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,35 +573,35 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - INDIA</t>
+          <t>Sr. Database Administrator - Computing Services</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Carnegie Mellon University</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Prosper, TX, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16</v>
+        <v>17.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Redshift, S3, IAM, RDS, Azure, GCP, BigQuery, Cloud Storage, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8eebff65cda31d0</t>
+          <t>https://www.indeed.com/viewjob?jk=506f6b3eeea1e8bf</t>
         </is>
       </c>
     </row>
@@ -643,17 +643,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Cloud Data Platform Administrator – Washington, DC</t>
+          <t>Senior Data Engineer - INDIA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Creative Information Technology India</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Falls Church, VA, US USA</t>
+          <t>Prosper, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,17 +661,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Delta Live Tables, Photon, Scala, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a74e373b48da5fc</t>
+          <t>https://www.indeed.com/viewjob?jk=f8eebff65cda31d0</t>
         </is>
       </c>
     </row>
@@ -683,12 +683,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>JBS Dev</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49f6c2df00dd6e11</t>
+          <t>https://www.indeed.com/viewjob?jk=32d044bc27a4af8a</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Costa Rica)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>JBS Dev</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,17 +731,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05c819aa2a88511d</t>
+          <t>https://www.indeed.com/viewjob?jk=aed60e56cae31294</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -771,12 +771,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32d044bc27a4af8a</t>
+          <t>https://www.indeed.com/viewjob?jk=44f958ba0cbc0f43</t>
         </is>
       </c>
     </row>
@@ -788,12 +788,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aed60e56cae31294</t>
+          <t>https://www.indeed.com/viewjob?jk=9e8500146d476812</t>
         </is>
       </c>
     </row>
@@ -823,12 +823,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44f958ba0cbc0f43</t>
+          <t>https://www.indeed.com/viewjob?jk=2ad2838bd8f61427</t>
         </is>
       </c>
     </row>
@@ -858,12 +858,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>JBS Dev</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,34 +871,34 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, Lambda, S3, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e8500146d476812</t>
+          <t>https://www.indeed.com/viewjob?jk=49f6c2df00dd6e11</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer (Costa Rica)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>JBS Dev</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,17 +906,17 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, Lambda, S3, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ad2838bd8f61427</t>
+          <t>https://www.indeed.com/viewjob?jk=05c819aa2a88511d</t>
         </is>
       </c>
     </row>
@@ -1203,25 +1203,25 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Upstart</t>
+          <t>Tenable</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbia, MD, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, SQS, SNS, Scala, Kafka, PostgreSQL, DynamoDB, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dab96c17b78fc32</t>
+          <t>https://www.indeed.com/viewjob?jk=b05ba9e572547c57</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer (Remote)</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Inspira Financial</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, Azure Cosmos DB, ETL, CI/CD, Jenkins</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1733261c550fa238</t>
+          <t>https://www.indeed.com/viewjob?jk=afa51ac883fa48a6</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer (Remote)</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Inspira Financial</t>
+          <t>Upstart</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, Azure Cosmos DB, ETL, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d0e899d198425eb</t>
+          <t>https://www.indeed.com/viewjob?jk=3dab96c17b78fc32</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Sr. Software Engineer (Remote)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Inspira Financial</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MongoDB, NoSQL, Splunk</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, Azure Cosmos DB, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=022d9e279d3ddb80</t>
+          <t>https://www.indeed.com/viewjob?jk=1733261c550fa238</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Specialist Programmer</t>
+          <t>Sr. Software Engineer (Remote)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Infosys</t>
+          <t>Inspira Financial</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,42 +1361,42 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, Hive, Spark, PySpark, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, Azure Cosmos DB, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9772b3b8d4167ecc</t>
+          <t>https://www.indeed.com/viewjob?jk=5d0e899d198425eb</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Azure CI/CD Developer (FTE / Hybrid)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Royal Oak, MI, US USA</t>
+          <t>Oaks, PA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bb3681c5da818f2</t>
+          <t>https://www.indeed.com/viewjob?jk=ffe5d7e4f5833213</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MongoDB, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,59 +1441,59 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=343b07159d1b6928</t>
+          <t>https://www.indeed.com/viewjob?jk=022d9e279d3ddb80</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer - Virtual</t>
+          <t>Specialist Programmer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Alight Solutions</t>
+          <t>Infosys</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Azure, GCP, Hadoop, Hive, Spark, PySpark, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a286c7ca862c4e1a</t>
+          <t>https://www.indeed.com/viewjob?jk=9772b3b8d4167ecc</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SENIOR DATA ENGINEER</t>
+          <t>Sr Software Development Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Clearwater Analytics (CWAN)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, SQS, SNS, Azure, GCP, Hadoop, Hive, HBase, Spark, Scala</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bee5a340a7f65e61</t>
+          <t>https://www.indeed.com/viewjob?jk=6efe960a7ab141ac</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Software Engineer - Authentication</t>
+          <t>SENIOR DATA ENGINEER</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Pindrop</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, RDS, Scala, MySQL, DynamoDB, MLOps, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6513fcf97bbfd044</t>
+          <t>https://www.indeed.com/viewjob?jk=bee5a340a7f65e61</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Advisor Application Designer</t>
+          <t>Software Engineer - Authentication</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>HJ Staffing</t>
+          <t>Pindrop</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Jenkins</t>
+          <t>AWS, Kinesis, S3, RDS, Scala, MySQL, DynamoDB, MLOps, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a988f0c0aeaa0fa5</t>
+          <t>https://www.indeed.com/viewjob?jk=6513fcf97bbfd044</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SSO Administrator</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Yusen Logistics</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,17 +1606,17 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, PostgreSQL, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kimball, ELT, dbt</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9064a81c91aa262</t>
+          <t>https://www.indeed.com/viewjob?jk=7f92de33105c0bad</t>
         </is>
       </c>
     </row>
@@ -1628,20 +1628,20 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Yusen Logistics</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, Medallion Architecture, Spark, Scala, ETL, ELT, CI/CD, GitHub Actions, AWS CodePipeline</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kimball, ELT, dbt</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83c604950fd47a32</t>
+          <t>https://www.indeed.com/viewjob?jk=772460af87c5b60c</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Platform Engineer-3</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>Royal Oak, MI, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f753e538739bd670</t>
+          <t>https://www.indeed.com/viewjob?jk=6bb3681c5da818f2</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Advance Auto Parts</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,102 +1721,102 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e2d8bc5a4c9174d</t>
+          <t>https://www.indeed.com/viewjob?jk=343b07159d1b6928</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>IT Data Engineer</t>
+          <t>Cloud Platform Engineer - Virtual</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Novolex</t>
+          <t>Alight Solutions</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Lake Forest, IL, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=024a63ca708c8a8f</t>
+          <t>https://www.indeed.com/viewjob?jk=a286c7ca862c4e1a</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Commercial Software</t>
+          <t>Advisor Application Designer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>HJ Staffing</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, Oracle, MySQL</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f3de39cf73c3663</t>
+          <t>https://www.indeed.com/viewjob?jk=a988f0c0aeaa0fa5</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Java Software Engineer II (US)</t>
+          <t>SSO Administrator</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>TD Bank</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Mount Laurel, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, NoSQL, Splunk, Jenkins, Maven, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, PostgreSQL, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ee89e940b02cc06</t>
+          <t>https://www.indeed.com/viewjob?jk=a9064a81c91aa262</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Daniels Health</t>
+          <t>AllCloud</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
+          <t>AWS, EMR, Kinesis, Redshift, RDS, Hadoop, Spark, Scala, Kafka, MySQL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3486f1249174e37a</t>
+          <t>https://www.indeed.com/viewjob?jk=49fcd1d4ac195cdf</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Software Engineer - Commercial Software</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Daniels Health</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, Oracle, MySQL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,102 +1896,102 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1df7caac86af2291</t>
+          <t>https://www.indeed.com/viewjob?jk=5f3de39cf73c3663</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ATC - AI &amp; Data Analyst - NAELFY26</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Saint Petersburg, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Step Functions, Medallion Architecture, Spark, Scala, ETL, ELT, CI/CD, GitHub Actions, AWS CodePipeline</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ce7a50a4bbe9ef2</t>
+          <t>https://www.indeed.com/viewjob?jk=83c604950fd47a32</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End (Java, Go, AWS)</t>
+          <t>Data Platform Engineer-3</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Docker</t>
+          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e716b4195b2da30b</t>
+          <t>https://www.indeed.com/viewjob?jk=f753e538739bd670</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>LERETA, LLC</t>
+          <t>Advance Auto Parts</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Pomona, CA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Data Lake Storage, Scala, Snowflake, SQL Server, Data Modeling, Fact Tables, ELT, Power BI</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,94 +2001,94 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad5d067156fc62f1</t>
+          <t>https://www.indeed.com/viewjob?jk=3e2d8bc5a4c9174d</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Applied Machine Learning Engineer (All Levels)</t>
+          <t>IT Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>Novolex</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Lake Forest, IL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, ELT, MLflow, CI/CD, Terraform, Docker, Git</t>
+          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1910fa4b9572adb</t>
+          <t>https://www.indeed.com/viewjob?jk=024a63ca708c8a8f</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Application Platform Architect - 6163848</t>
+          <t>Java Software Engineer II (US)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>TD Bank</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Saint Petersburg, FL, US USA</t>
+          <t>Mount Laurel, NJ, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Hadoop, Scala, PostgreSQL, CI/CD, Docker</t>
+          <t>RDS, Azure, Scala, NoSQL, Splunk, Jenkins, Maven, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ea7fc0fae83610a</t>
+          <t>https://www.indeed.com/viewjob?jk=8ee89e940b02cc06</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer (NYC)</t>
+          <t>Senior Software Engineer, Back End (Java, Go, AWS)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>KNIT</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,17 +2096,17 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, ECS, RDS, Scala, MongoDB, CI/CD, GitHub Actions, Docker</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0457dc96d28b81f</t>
+          <t>https://www.indeed.com/viewjob?jk=e716b4195b2da30b</t>
         </is>
       </c>
     </row>
@@ -2118,12 +2118,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Amplify</t>
+          <t>Daniels Health</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Snowflake, DynamoDB, Data Modeling, Kimball, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4d16d721d2057f3</t>
+          <t>https://www.indeed.com/viewjob?jk=3486f1249174e37a</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Weyerhaeuser</t>
+          <t>Daniels Health</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, MLOps, MLflow, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d9f82346c5ff2d3</t>
+          <t>https://www.indeed.com/viewjob?jk=1df7caac86af2291</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Software Systems Engineer, Release Reliability &amp; Automation (Autonomous Vehicles)</t>
+          <t>ATC - AI &amp; Data Analyst - NAELFY26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Saint Petersburg, FL, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, Power BI, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=864266ab5f8e3aac</t>
+          <t>https://www.indeed.com/viewjob?jk=1ce7a50a4bbe9ef2</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Software Engineer (Hybrid)</t>
+          <t>Senior Application Platform Architect - 6163848</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Nightwing</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Clarksville, TN, US USA</t>
+          <t>Saint Petersburg, FL, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Hadoop, Scala, PostgreSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=887221a715d1ff03</t>
+          <t>https://www.indeed.com/viewjob?jk=7ea7fc0fae83610a</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Software Engineer (Hybrid)</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Nightwing</t>
+          <t>Amplify</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Sterling, VA, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Snowflake, DynamoDB, Data Modeling, Kimball, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3322d87953168bdc</t>
+          <t>https://www.indeed.com/viewjob?jk=b4d16d721d2057f3</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Software Engineer III - Java/Spark/AWS</t>
+          <t>Selenium Automation tester</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, ECS, RDS, Databricks, Spark, Scala, Snowflake</t>
+          <t>Azure, Scala, Kafka, Oracle, SQL Server, ETL, CI/CD, Jenkins, Azure DevOps, Maven</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c95674c932d41fb6</t>
+          <t>https://www.indeed.com/viewjob?jk=bc0fe4c47cda2838</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Database Administrator</t>
+          <t>Applied Machine Learning Engineer (All Levels)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Hard Rock International</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Hollywood, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, Snowflake, PostgreSQL, Cassandra, CI/CD, Terraform</t>
+          <t>AWS, Azure, GCP, Spark, ELT, MLflow, CI/CD, Terraform, Docker, Git</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=169d4a00d377fdae</t>
+          <t>https://www.indeed.com/viewjob?jk=c1910fa4b9572adb</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Tableau Developer</t>
+          <t>Senior Full Stack Engineer (NYC)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Michael Kors</t>
+          <t>KNIT</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>East Rutherford, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Star Schema</t>
+          <t>AWS, S3, SQS, ECS, RDS, Scala, MongoDB, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=904e084e965a45c4</t>
+          <t>https://www.indeed.com/viewjob?jk=f0457dc96d28b81f</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Advanced Metering Infrastructure (AMI) Engineer</t>
+          <t>GD162 Senior Software Systems Engineer &amp; Architect</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>WSSC Water</t>
+          <t>ADNET Systems, Inc</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Laurel, MD, US USA</t>
+          <t>Greenbelt, MD, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,42 +2411,42 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Oracle, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps</t>
+          <t>AWS, Lambda, S3, Scala, Dask, DynamoDB, ELT, CI/CD, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5b2aa36ee050b9b</t>
+          <t>https://www.indeed.com/viewjob?jk=ef183b27f01923fb</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Sr. ETL/SQL Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Capgemini Government Solutions</t>
+          <t>LERETA, LLC</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Pomona, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, ETL, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>Azure, Data Factory, Data Lake Storage, Scala, Snowflake, SQL Server, Data Modeling, Fact Tables, ELT, Power BI</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,67 +2456,67 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=724ffe7f1d3da135</t>
+          <t>https://www.indeed.com/viewjob?jk=ad5d067156fc62f1</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>Software Engineer III - Java/Spark/AWS</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Space Telescope Science Institute</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, Hive, Scala, PostgreSQL, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, EMR, Lambda, S3, ECS, RDS, Databricks, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6055970eb603df79</t>
+          <t>https://www.indeed.com/viewjob?jk=c95674c932d41fb6</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>AI Engineer III</t>
+          <t>Database Administrator</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>CareSource</t>
+          <t>Hard Rock International</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Hollywood, FL, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, Snowflake, PostgreSQL, Cassandra, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,172 +2526,172 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=640c68fe3716b1e6</t>
+          <t>https://www.indeed.com/viewjob?jk=169d4a00d377fdae</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
+          <t>Software Systems Engineer, Release Reliability &amp; Automation (Autonomous Vehicles)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, Power BI, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f85f1e8c0778adba</t>
+          <t>https://www.indeed.com/viewjob?jk=864266ab5f8e3aac</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
+          <t>Advanced Metering Infrastructure (AMI) Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>WSSC Water</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Laurel, MD, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, Kafka, Oracle, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e2da1f14c27a331</t>
+          <t>https://www.indeed.com/viewjob?jk=c5b2aa36ee050b9b</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
+          <t>Tableau Developer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Michael Kors</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>East Rutherford, NJ, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Glue, Redshift, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=140d02e1f58501f6</t>
+          <t>https://www.indeed.com/viewjob?jk=904e084e965a45c4</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Weyerhaeuser</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, MLOps, MLflow, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eff547fec829449a</t>
+          <t>https://www.indeed.com/viewjob?jk=7d9f82346c5ff2d3</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
+          <t>Software Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Nightwing</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Clarksville, TN, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29d22d712d7958f0</t>
+          <t>https://www.indeed.com/viewjob?jk=887221a715d1ff03</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Software Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Nightwing</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, PySpark, Scala, MySQL, MongoDB, Docker, Kubernetes, Airflow</t>
+          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd1518c4c02c12ef</t>
+          <t>https://www.indeed.com/viewjob?jk=3322d87953168bdc</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>AWS Data Engineer</t>
+          <t>Senior Software Engineer, Back End (Python)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Appex Innovation</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3886cb86a753634c</t>
+          <t>https://www.indeed.com/viewjob?jk=f65ac6c3f1cf1646</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineer 2</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>BLOC Resources, LLC</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Data Modeling, CI/CD</t>
+          <t>AWS, RDS, Spark, PySpark, Scala, MySQL, MongoDB, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c51290628ce41b82</t>
+          <t>https://www.indeed.com/viewjob?jk=dd1518c4c02c12ef</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
+          <t>Senior Software Engineer, Back End (Python)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9637232a826c3ad</t>
+          <t>https://www.indeed.com/viewjob?jk=3864c05dc9b353f8</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End (Python)</t>
+          <t>Data Engineer 2</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>BLOC Resources, LLC</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f65ac6c3f1cf1646</t>
+          <t>https://www.indeed.com/viewjob?jk=c51290628ce41b82</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End (Python)</t>
+          <t>Sr. Software Engineer I, Applied AI</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Axon</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3864c05dc9b353f8</t>
+          <t>https://www.indeed.com/viewjob?jk=e858c83fc09cd77d</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer I, Applied AI</t>
+          <t>Sr. ETL/SQL Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Axon</t>
+          <t>Capgemini Government Solutions</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, ETL, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e858c83fc09cd77d</t>
+          <t>https://www.indeed.com/viewjob?jk=724ffe7f1d3da135</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Data &amp; Analytics</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>WesBanco Bank, Inc.</t>
+          <t>Space Telescope Science Institute</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Bowie, MD, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT, dbt</t>
+          <t>AWS, S3, ECS, IAM, Hive, Scala, PostgreSQL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3a02cdb2b181be3</t>
+          <t>https://www.indeed.com/viewjob?jk=6055970eb603df79</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Data &amp; Analytics</t>
+          <t>AI Engineer III</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>WesBanco Bank, Inc.</t>
+          <t>CareSource</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Wheeling, WV, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT, dbt</t>
+          <t>API Gateway, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb6ee55d393e301c</t>
+          <t>https://www.indeed.com/viewjob?jk=640c68fe3716b1e6</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Centene</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, MySQL, MongoDB, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11d92da9c37770a7</t>
+          <t>https://www.indeed.com/viewjob?jk=f85f1e8c0778adba</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Customer Reliability Engineer, Airflow</t>
+          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Astronomer</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, Snowflake, PostgreSQL, dbt, DataOps, Docker</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ac244565083c1d9</t>
+          <t>https://www.indeed.com/viewjob?jk=3e2da1f14c27a331</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Software Developer - Database Engineer</t>
+          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>RAMSOFT</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, HBase, Scala, Snowflake, MySQL, NoSQL, Data Modeling, Power BI</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ce0ac7d0a937f32</t>
+          <t>https://www.indeed.com/viewjob?jk=140d02e1f58501f6</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>RapidFire Safety &amp; Security</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,42 +3146,42 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, Data Modeling, Star Schema, Fact Tables, Dimension Tables, ETL, Power BI</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8afc73df8ef8f40e</t>
+          <t>https://www.indeed.com/viewjob?jk=eff547fec829449a</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Emed</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,32 +3191,32 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e29e1c3d36f0e7c</t>
+          <t>https://www.indeed.com/viewjob?jk=29d22d712d7958f0</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer, Engineering &amp; Ops</t>
+          <t>AWS Data Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>NBCUniversal</t>
+          <t>Appex Innovation</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Snowflake, ELT, dbt, MLOps, Airflow</t>
+          <t>AWS, Glue, Lambda, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,67 +3226,67 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df536a2594fa5881</t>
+          <t>https://www.indeed.com/viewjob?jk=3886cb86a753634c</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Data Engineer - GRC Technology</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Zoom Communications</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8842e67bf37c518a</t>
+          <t>https://www.indeed.com/viewjob?jk=d44e3274520e56d6</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer - Startup</t>
+          <t>Senior Data Engineer - Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>TALENThire</t>
+          <t>WesBanco Bank, Inc.</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Bowie, MD, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, GCP, Scala, Kafka, PostgreSQL, ELT, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,32 +3296,32 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f9f397d4f8fa7f1</t>
+          <t>https://www.indeed.com/viewjob?jk=a3a02cdb2b181be3</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - Risk Platform (Hybrid)</t>
+          <t>Senior Data Engineer - Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>WesBanco Bank, Inc.</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Wheeling, WV, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Cassandra, ETL, Docker, Kubernetes</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,102 +3331,102 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1593d7242ad3914</t>
+          <t>https://www.indeed.com/viewjob?jk=fb6ee55d393e301c</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Applications Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Daniels Health</t>
+          <t>Stanford University</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, ETL, ELT, Git</t>
+          <t>AWS, RDS, Azure, Vertex AI, Scala, Oracle, NoSQL, Data Modeling, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aedcadc853d15f82</t>
+          <t>https://www.indeed.com/viewjob?jk=d0dc1867fdcc5324</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Advisor Solution Architect</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>HJ Staffing</t>
+          <t>RapidFire Safety &amp; Security</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, CI/CD, Jenkins, Terraform</t>
+          <t>RDS, Azure, Scala, SQL Server, Data Modeling, Star Schema, Fact Tables, Dimension Tables, ETL, Power BI</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20d4ea50920ad807</t>
+          <t>https://www.indeed.com/viewjob?jk=8afc73df8ef8f40e</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Developer - Database Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>RAMSOFT</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, HBase, Scala, Snowflake, MySQL, NoSQL, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,32 +3436,32 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1315e6e62a7714e8</t>
+          <t>https://www.indeed.com/viewjob?jk=4ce0ac7d0a937f32</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Guidewire Software, Inc.</t>
+          <t>Centene</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, MySQL, MongoDB, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b5e082bd1857b0f</t>
+          <t>https://www.indeed.com/viewjob?jk=11d92da9c37770a7</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>.NET Developer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Vizient, Inc.</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Scala, Snowflake, SQL Server, Power BI, CI/CD, Azure DevOps, Git</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, SQL Server, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4afc3e61f8ae8b7b</t>
+          <t>https://www.indeed.com/viewjob?jk=2e60ff8bc1e60898</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Daniels Health</t>
+          <t>Emed</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, ETL, ELT, Git</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=447d4d5607b3f3c6</t>
+          <t>https://www.indeed.com/viewjob?jk=1e29e1c3d36f0e7c</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Sr. Informatica IDMC MDM Software Engineer</t>
+          <t>Senior Java Integration Consultant</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>RBC</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Springfield, IL, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,17 +3566,367 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
+          <t>AWS, API Gateway, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7439985744d87583</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Senior Backend Engineer - Startup</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>TALENThire</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>AWS, Kinesis, GCP, Scala, Kafka, PostgreSQL, ELT, CI/CD, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5f9f397d4f8fa7f1</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Sr. Software Engineer - Risk Platform (Hybrid)</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>CrowdStrike</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Sunnyvale, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Cassandra, ETL, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a1593d7242ad3914</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Daniels Health</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, ETL, ELT, Git</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=aedcadc853d15f82</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Daniels Health</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, ETL, ELT, Git</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=447d4d5607b3f3c6</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Advisor Solution Architect</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>HJ Staffing</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, CI/CD, Jenkins, Terraform</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=20d4ea50920ad807</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1315e6e62a7714e8</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Sr. Informatica IDMC MDM Software Engineer</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>RBC</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Minneapolis, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
           <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, ETL, CI/CD</t>
         </is>
       </c>
-      <c r="F90" t="inlineStr">
+      <c r="F97" t="inlineStr">
         <is>
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr">
+      <c r="G97" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=5346f4c5e2b5352a</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>.NET Developer</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Caterpillar</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Cary, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>S3, RDS, Azure, Scala, Snowflake, SQL Server, Power BI, CI/CD, Azure DevOps, Git</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4afc3e61f8ae8b7b</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Engineer</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Guidewire Software, Inc.</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>San Mateo, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, MySQL, MongoDB, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3b5e082bd1857b0f</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>DevOps Engineer (Must have Kubernetes)</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Cornerstone Defense</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Chantilly, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Hadoop, Spark, PostgreSQL, CI/CD, Maven, Terraform, Docker, Kubernetes, AKS, Git</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7329904e6957c2e7</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-05.xlsx
+++ b/results/job_matches_2026-03-05.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G100"/>
+  <dimension ref="A1:G119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,25 +503,25 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>ML Infrastructure Architect</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>AmeriLife</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>19.4</v>
+        <v>18.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL</t>
+          <t>AWS, Redshift, S3, Azure, Google Cloud Platform, BigQuery, Scala, Snowflake, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=857bb2d652273e9a</t>
+          <t>https://www.indeed.com/viewjob?jk=60711b668acbd0b3</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer – DE20260503002</t>
+          <t>ML Infrastructure Architect</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>eGrove Systems Corporation</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, HDFS, Hive, Spark, Scala, Oracle</t>
+          <t>AWS, Redshift, S3, Azure, Google Cloud Platform, BigQuery, Scala, Snowflake, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6093ead5fe385f5d</t>
+          <t>https://www.indeed.com/viewjob?jk=db8a35e2b334dacc</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sr. Database Administrator - Computing Services</t>
+          <t>Data Engineer – DE20260503002</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Carnegie Mellon University</t>
+          <t>eGrove Systems Corporation</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,77 +591,77 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, IAM, RDS, Azure, GCP, BigQuery, Cloud Storage, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, HDFS, Hive, Spark, Scala, Oracle</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=506f6b3eeea1e8bf</t>
+          <t>https://www.indeed.com/viewjob?jk=6093ead5fe385f5d</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>ML Infrastructure Architect</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Valvoline Global Operations</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP, Cloud Storage, Spark, PySpark</t>
+          <t>AWS, Glue, S3, IAM, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab16510fd1c2841d</t>
+          <t>https://www.indeed.com/viewjob?jk=fd9f71c3bc119fac</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - INDIA</t>
+          <t>ML Infrastructure Architect</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Prosper, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Glue, S3, IAM, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8eebff65cda31d0</t>
+          <t>https://www.indeed.com/viewjob?jk=7bc520629d7c84b2</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer - INDIA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Prosper, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32d044bc27a4af8a</t>
+          <t>https://www.indeed.com/viewjob?jk=f8eebff65cda31d0</t>
         </is>
       </c>
     </row>
@@ -718,65 +718,65 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Valvoline Global Operations</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP, Cloud Storage, Spark, PySpark</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aed60e56cae31294</t>
+          <t>https://www.indeed.com/viewjob?jk=ab16510fd1c2841d</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Quant Analytics Associate Senior - Management Information System</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Snowflake, ETL, ELT, dbt, Tableau</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44f958ba0cbc0f43</t>
+          <t>https://www.indeed.com/viewjob?jk=3c4dd2cc48a2f29b</t>
         </is>
       </c>
     </row>
@@ -788,12 +788,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>JBS Dev</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,34 +801,34 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, Lambda, S3, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e8500146d476812</t>
+          <t>https://www.indeed.com/viewjob?jk=49f6c2df00dd6e11</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer (Costa Rica)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>JBS Dev</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,17 +836,17 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, Lambda, S3, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ad2838bd8f61427</t>
+          <t>https://www.indeed.com/viewjob?jk=05c819aa2a88511d</t>
         </is>
       </c>
     </row>
@@ -858,12 +858,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>JBS Dev</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49f6c2df00dd6e11</t>
+          <t>https://www.indeed.com/viewjob?jk=32d044bc27a4af8a</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Costa Rica)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>JBS Dev</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,34 +906,34 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05c819aa2a88511d</t>
+          <t>https://www.indeed.com/viewjob?jk=aed60e56cae31294</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Systems Administrator, Cloud (GTA)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,34 +941,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, AWS CodePipeline</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=094fcc384185954f</t>
+          <t>https://www.indeed.com/viewjob?jk=44f958ba0cbc0f43</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>System Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Systems Engineering Solutions Corporation</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Kinesis, Redshift, S3, IAM, RDS, Spark, PySpark</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=634fcd15ef04d7bf</t>
+          <t>https://www.indeed.com/viewjob?jk=9e8500146d476812</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Specialist - System Management</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Glen Allen, VA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Unity Catalog, Delta Live Tables, Spark, Databricks Lakehouse, SQL Server</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=293f842904007fda</t>
+          <t>https://www.indeed.com/viewjob?jk=2ad2838bd8f61427</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CLOUD ENGINEER (AWS) (REMOTE/USA) - GDM (GRAY MEDIA GROUP)</t>
+          <t>Senior Software Engineer - Typescript and AWS services</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>GRAY MEDIA</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Schaumburg, IL, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Google Cloud Platform, GCP, Scala, DynamoDB</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, DynamoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,59 +1056,59 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0beb94e2f1648144</t>
+          <t>https://www.indeed.com/viewjob?jk=021dcffcbccd49c9</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>System Architect</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Alight Solutions</t>
+          <t>Systems Engineering Solutions Corporation</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, GCP, Scala, CI/CD</t>
+          <t>AWS, Glue, EMR, Kinesis, Redshift, S3, IAM, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=398f35933211332f</t>
+          <t>https://www.indeed.com/viewjob?jk=634fcd15ef04d7bf</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Software Engineer, Data</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>Acrisure LLC</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, GCP, Scala, Snowflake</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Polars, Data Modeling</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e83bd0fd320bb829</t>
+          <t>https://www.indeed.com/viewjob?jk=c7869ee373ec84ed</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>CLOUD ENGINEER (AWS) (REMOTE/USA) - GDM (GRAY MEDIA GROUP)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>GRAY MEDIA</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, GCP, Scala, Snowflake</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Google Cloud Platform, GCP, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=105f562c4b87c831</t>
+          <t>https://www.indeed.com/viewjob?jk=0beb94e2f1648144</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>Alight Solutions</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Wichita, KS, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, GCP, Scala, Snowflake</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, GCP, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56a2fccd9b09c654</t>
+          <t>https://www.indeed.com/viewjob?jk=398f35933211332f</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Tenable</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Columbia, MD, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, Scala, Kafka, PostgreSQL, DynamoDB, NoSQL, Splunk, CI/CD</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, GCP, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b05ba9e572547c57</t>
+          <t>https://www.indeed.com/viewjob?jk=e83bd0fd320bb829</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala, Dimensional Modeling</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, GCP, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afa51ac883fa48a6</t>
+          <t>https://www.indeed.com/viewjob?jk=105f562c4b87c831</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Upstart</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Wichita, KS, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, GCP, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dab96c17b78fc32</t>
+          <t>https://www.indeed.com/viewjob?jk=56a2fccd9b09c654</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer (Remote)</t>
+          <t>Software Engineer, Data</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Inspira Financial</t>
+          <t>Acrisure LLC</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, Azure Cosmos DB, ETL, CI/CD, Jenkins</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1733261c550fa238</t>
+          <t>https://www.indeed.com/viewjob?jk=459162c660bc8082</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer (Remote)</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Inspira Financial</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, Azure Cosmos DB, ETL, CI/CD, Jenkins</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d0e899d198425eb</t>
+          <t>https://www.indeed.com/viewjob?jk=afa51ac883fa48a6</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Azure CI/CD Developer (FTE / Hybrid)</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Upstart</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Oaks, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffe5d7e4f5833213</t>
+          <t>https://www.indeed.com/viewjob?jk=3dab96c17b78fc32</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Sr. Software Engineer (Remote)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Inspira Financial</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MongoDB, NoSQL, Splunk</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, Azure Cosmos DB, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=022d9e279d3ddb80</t>
+          <t>https://www.indeed.com/viewjob?jk=1733261c550fa238</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Specialist Programmer</t>
+          <t>Sr. Software Engineer (Remote)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Infosys</t>
+          <t>Inspira Financial</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,42 +1466,42 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, Hive, Spark, PySpark, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, Azure Cosmos DB, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9772b3b8d4167ecc</t>
+          <t>https://www.indeed.com/viewjob?jk=5d0e899d198425eb</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Sr Software Development Engineer</t>
+          <t>Azure CI/CD Developer (FTE / Hybrid)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Clearwater Analytics (CWAN)</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Oaks, PA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, Azure, GCP, Hadoop, Hive, HBase, Spark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6efe960a7ab141ac</t>
+          <t>https://www.indeed.com/viewjob?jk=ffe5d7e4f5833213</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SENIOR DATA ENGINEER</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MongoDB, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,59 +1546,59 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bee5a340a7f65e61</t>
+          <t>https://www.indeed.com/viewjob?jk=022d9e279d3ddb80</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Software Engineer - Authentication</t>
+          <t>Specialist Programmer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Pindrop</t>
+          <t>Infosys</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, RDS, Scala, MySQL, DynamoDB, MLOps, CI/CD, Jenkins</t>
+          <t>AWS, Azure, GCP, Hadoop, Hive, Spark, PySpark, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6513fcf97bbfd044</t>
+          <t>https://www.indeed.com/viewjob?jk=9772b3b8d4167ecc</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer III- Python/PySpark</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Yusen Logistics</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kimball, ELT, dbt</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Databricks, Spark, PySpark, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f92de33105c0bad</t>
+          <t>https://www.indeed.com/viewjob?jk=82b1dd2ce5d3671a</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Support Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Yusen Logistics</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kimball, ELT, dbt</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Hadoop, HDFS, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=772460af87c5b60c</t>
+          <t>https://www.indeed.com/viewjob?jk=625bf5ef0b332ad3</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Support Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Royal Oak, MI, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Hadoop, HDFS, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bb3681c5da818f2</t>
+          <t>https://www.indeed.com/viewjob?jk=dd39a203b7587e31</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>Yusen Logistics</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kimball, ELT, dbt</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=343b07159d1b6928</t>
+          <t>https://www.indeed.com/viewjob?jk=7f92de33105c0bad</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer - Virtual</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Alight Solutions</t>
+          <t>Yusen Logistics</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kimball, ELT, dbt</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a286c7ca862c4e1a</t>
+          <t>https://www.indeed.com/viewjob?jk=772460af87c5b60c</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Advisor Application Designer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>HJ Staffing</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Royal Oak, MI, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Jenkins</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a988f0c0aeaa0fa5</t>
+          <t>https://www.indeed.com/viewjob?jk=6bb3681c5da818f2</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>SSO Administrator</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,42 +1816,42 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, PostgreSQL, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9064a81c91aa262</t>
+          <t>https://www.indeed.com/viewjob?jk=343b07159d1b6928</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Cloud Platform Engineer - Virtual</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>AllCloud</t>
+          <t>Alight Solutions</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, Redshift, RDS, Hadoop, Spark, Scala, Kafka, MySQL</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,67 +1861,67 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49fcd1d4ac195cdf</t>
+          <t>https://www.indeed.com/viewjob?jk=a286c7ca862c4e1a</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Commercial Software</t>
+          <t>SENIOR DATA ENGINEER</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, Oracle, MySQL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f3de39cf73c3663</t>
+          <t>https://www.indeed.com/viewjob?jk=bee5a340a7f65e61</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Software Development Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Clearwater Analytics (CWAN)</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, Medallion Architecture, Spark, Scala, ETL, ELT, CI/CD, GitHub Actions, AWS CodePipeline</t>
+          <t>AWS, SQS, SNS, Azure, GCP, Hadoop, Hive, HBase, Spark, Scala</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83c604950fd47a32</t>
+          <t>https://www.indeed.com/viewjob?jk=6efe960a7ab141ac</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Platform Engineer-3</t>
+          <t>Software Engineer - Authentication</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Pindrop</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
+          <t>AWS, Kinesis, S3, RDS, Scala, MySQL, DynamoDB, MLOps, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f753e538739bd670</t>
+          <t>https://www.indeed.com/viewjob?jk=6513fcf97bbfd044</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>AI Intern</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Advance Auto Parts</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,59 +2001,59 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e2d8bc5a4c9174d</t>
+          <t>https://www.indeed.com/viewjob?jk=0c4618ffec69d30a</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>IT Data Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Novolex</t>
+          <t>TWG Global AI</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Lake Forest, IL, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=024a63ca708c8a8f</t>
+          <t>https://www.indeed.com/viewjob?jk=edb6a72ac37333e2</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Java Software Engineer II (US)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>TD Bank</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Mount Laurel, NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,77 +2061,77 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, NoSQL, Splunk, Jenkins, Maven, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Step Functions, Medallion Architecture, Spark, Scala, ETL, ELT, CI/CD, GitHub Actions, AWS CodePipeline</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ee89e940b02cc06</t>
+          <t>https://www.indeed.com/viewjob?jk=83c604950fd47a32</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End (Java, Go, AWS)</t>
+          <t>Data Platform Engineer-3</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Docker</t>
+          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e716b4195b2da30b</t>
+          <t>https://www.indeed.com/viewjob?jk=f753e538739bd670</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Daniels Health</t>
+          <t>Advance Auto Parts</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3486f1249174e37a</t>
+          <t>https://www.indeed.com/viewjob?jk=3e2d8bc5a4c9174d</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>IT Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Daniels Health</t>
+          <t>Novolex</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Lake Forest, IL, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,137 +2176,137 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1df7caac86af2291</t>
+          <t>https://www.indeed.com/viewjob?jk=024a63ca708c8a8f</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>ATC - AI &amp; Data Analyst - NAELFY26</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>AllCloud</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Saint Petersburg, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, EMR, Kinesis, Redshift, RDS, Hadoop, Spark, Scala, Kafka, MySQL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ce7a50a4bbe9ef2</t>
+          <t>https://www.indeed.com/viewjob?jk=49fcd1d4ac195cdf</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Application Platform Architect - 6163848</t>
+          <t>Senior Software Engineer - Commercial Software</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Saint Petersburg, FL, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Hadoop, Scala, PostgreSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, Oracle, MySQL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ea7fc0fae83610a</t>
+          <t>https://www.indeed.com/viewjob?jk=5f3de39cf73c3663</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>ML Infrastructure Architect</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Amplify</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Snowflake, DynamoDB, Data Modeling, Kimball, ETL, ELT, dbt</t>
+          <t>IAM, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala, Kafka, Power BI</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4d16d721d2057f3</t>
+          <t>https://www.indeed.com/viewjob?jk=76cb3bc7e109c2ac</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Selenium Automation tester</t>
+          <t>ML Infrastructure Architect</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Azure, Scala, Kafka, Oracle, SQL Server, ETL, CI/CD, Jenkins, Azure DevOps, Maven</t>
+          <t>IAM, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala, Kafka, Power BI</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,59 +2316,59 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc0fe4c47cda2838</t>
+          <t>https://www.indeed.com/viewjob?jk=c8547c2271ca5aef</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Applied Machine Learning Engineer (All Levels)</t>
+          <t>Java Software Engineer II (US)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>TD Bank</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Mount Laurel, NJ, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, ELT, MLflow, CI/CD, Terraform, Docker, Git</t>
+          <t>RDS, Azure, Scala, NoSQL, Splunk, Jenkins, Maven, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1910fa4b9572adb</t>
+          <t>https://www.indeed.com/viewjob?jk=8ee89e940b02cc06</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer (NYC)</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>KNIT</t>
+          <t>Daniels Health</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, ECS, RDS, Scala, MongoDB, CI/CD, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0457dc96d28b81f</t>
+          <t>https://www.indeed.com/viewjob?jk=3486f1249174e37a</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>GD162 Senior Software Systems Engineer &amp; Architect</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ADNET Systems, Inc</t>
+          <t>Daniels Health</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Greenbelt, MD, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Scala, Dask, DynamoDB, ELT, CI/CD, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef183b27f01923fb</t>
+          <t>https://www.indeed.com/viewjob?jk=1df7caac86af2291</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>ATC - AI &amp; Data Analyst - NAELFY26</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>LERETA, LLC</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Pomona, CA, US USA</t>
+          <t>Saint Petersburg, FL, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Data Lake Storage, Scala, Snowflake, SQL Server, Data Modeling, Fact Tables, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad5d067156fc62f1</t>
+          <t>https://www.indeed.com/viewjob?jk=1ce7a50a4bbe9ef2</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Software Engineer III - Java/Spark/AWS</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Genentech</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, ECS, RDS, Databricks, Spark, Scala, Snowflake</t>
+          <t>AWS, Step Functions, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c95674c932d41fb6</t>
+          <t>https://www.indeed.com/viewjob?jk=d20f4b9e6a3cbb70</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Database Administrator</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Hard Rock International</t>
+          <t>Genentech</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Hollywood, FL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, Snowflake, PostgreSQL, Cassandra, CI/CD, Terraform</t>
+          <t>AWS, Step Functions, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=169d4a00d377fdae</t>
+          <t>https://www.indeed.com/viewjob?jk=c89d6a7d2041de38</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Software Systems Engineer, Release Reliability &amp; Automation (Autonomous Vehicles)</t>
+          <t>Senior Software Engineer, Back End (Java, Go, AWS)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, Power BI, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=864266ab5f8e3aac</t>
+          <t>https://www.indeed.com/viewjob?jk=e716b4195b2da30b</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Advanced Metering Infrastructure (AMI) Engineer</t>
+          <t>ML Infrastructure Architect</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>WSSC Water</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Laurel, MD, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Oracle, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps</t>
+          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5b2aa36ee050b9b</t>
+          <t>https://www.indeed.com/viewjob?jk=5c6fa42304d7e851</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Tableau Developer</t>
+          <t>Senior LLM Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Michael Kors</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>East Rutherford, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Star Schema</t>
+          <t>AWS, Azure, Vertex AI, Scala, Oracle, PostgreSQL, MySQL, MongoDB, NoSQL, MLOps</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=904e084e965a45c4</t>
+          <t>https://www.indeed.com/viewjob?jk=109c9c4a6595ba95</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>ML Infrastructure Architect</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Weyerhaeuser</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, MLOps, MLflow, CI/CD, Terraform, Docker</t>
+          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d9f82346c5ff2d3</t>
+          <t>https://www.indeed.com/viewjob?jk=dfd0ac225b61c5b4</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Software Engineer (Hybrid)</t>
+          <t>Senior LLM Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Nightwing</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Clarksville, TN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, Azure, Vertex AI, Scala, Oracle, PostgreSQL, MySQL, MongoDB, NoSQL, MLOps</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=887221a715d1ff03</t>
+          <t>https://www.indeed.com/viewjob?jk=8723fa94634ae387</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Software Engineer (Hybrid)</t>
+          <t>ML Infrastructure Architect</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Nightwing</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Sterling, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,112 +2726,112 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3322d87953168bdc</t>
+          <t>https://www.indeed.com/viewjob?jk=22b3d9d74319cb4d</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End (Python)</t>
+          <t>ML Infrastructure Architect</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f65ac6c3f1cf1646</t>
+          <t>https://www.indeed.com/viewjob?jk=cdf51adf8a1f9c98</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Stanley Martin Homes</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, PySpark, Scala, MySQL, MongoDB, Docker, Kubernetes, Airflow</t>
+          <t>RDS, BigQuery, Hadoop, Spark, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, MLOps</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd1518c4c02c12ef</t>
+          <t>https://www.indeed.com/viewjob?jk=f934b2c21443f198</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End (Python)</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Amplify</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Snowflake, DynamoDB, Data Modeling, Kimball, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,242 +2841,242 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3864c05dc9b353f8</t>
+          <t>https://www.indeed.com/viewjob?jk=b4d16d721d2057f3</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Engineer 2</t>
+          <t>Senior Application Platform Architect - 6163848</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>BLOC Resources, LLC</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Saint Petersburg, FL, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Data Modeling, CI/CD</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Hadoop, Scala, PostgreSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c51290628ce41b82</t>
+          <t>https://www.indeed.com/viewjob?jk=7ea7fc0fae83610a</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer I, Applied AI</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Axon</t>
+          <t>LERETA, LLC</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Pomona, CA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>Azure, Data Factory, Data Lake Storage, Scala, Snowflake, SQL Server, Data Modeling, Fact Tables, ELT, Power BI</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e858c83fc09cd77d</t>
+          <t>https://www.indeed.com/viewjob?jk=ad5d067156fc62f1</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Sr. ETL/SQL Engineer</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Capgemini Government Solutions</t>
+          <t>Weyerhaeuser</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, ETL, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, MLOps, MLflow, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=724ffe7f1d3da135</t>
+          <t>https://www.indeed.com/viewjob?jk=7d9f82346c5ff2d3</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>Software Systems Engineer, Release Reliability &amp; Automation (Autonomous Vehicles)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Space Telescope Science Institute</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, Hive, Scala, PostgreSQL, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, Power BI, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6055970eb603df79</t>
+          <t>https://www.indeed.com/viewjob?jk=864266ab5f8e3aac</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>AI Engineer III</t>
+          <t>Software Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>CareSource</t>
+          <t>Nightwing</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Clarksville, TN, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=640c68fe3716b1e6</t>
+          <t>https://www.indeed.com/viewjob?jk=887221a715d1ff03</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
+          <t>Software Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Nightwing</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f85f1e8c0778adba</t>
+          <t>https://www.indeed.com/viewjob?jk=3322d87953168bdc</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
+          <t>Database Administrator</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Hard Rock International</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Hollywood, FL, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, Snowflake, PostgreSQL, Cassandra, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,59 +3086,59 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e2da1f14c27a331</t>
+          <t>https://www.indeed.com/viewjob?jk=169d4a00d377fdae</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
+          <t>Advanced Metering Infrastructure (AMI) Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>WSSC Water</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Laurel, MD, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, Kafka, Oracle, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=140d02e1f58501f6</t>
+          <t>https://www.indeed.com/viewjob?jk=c5b2aa36ee050b9b</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
+          <t>Sr. ETL/SQL Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Capgemini Government Solutions</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, ETL, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eff547fec829449a</t>
+          <t>https://www.indeed.com/viewjob?jk=724ffe7f1d3da135</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Space Telescope Science Institute</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, ECS, IAM, Hive, Scala, PostgreSQL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29d22d712d7958f0</t>
+          <t>https://www.indeed.com/viewjob?jk=6055970eb603df79</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>AWS Data Engineer</t>
+          <t>AI Engineer III</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Appex Innovation</t>
+          <t>CareSource</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD</t>
+          <t>API Gateway, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3886cb86a753634c</t>
+          <t>https://www.indeed.com/viewjob?jk=640c68fe3716b1e6</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Zoom Communications</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d44e3274520e56d6</t>
+          <t>https://www.indeed.com/viewjob?jk=f85f1e8c0778adba</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Data &amp; Analytics</t>
+          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>WesBanco Bank, Inc.</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Bowie, MD, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT, dbt</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3a02cdb2b181be3</t>
+          <t>https://www.indeed.com/viewjob?jk=3e2da1f14c27a331</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Data &amp; Analytics</t>
+          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>WesBanco Bank, Inc.</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Wheeling, WV, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT, dbt</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb6ee55d393e301c</t>
+          <t>https://www.indeed.com/viewjob?jk=140d02e1f58501f6</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>AI Applications Engineer</t>
+          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Stanford University</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Vertex AI, Scala, Oracle, NoSQL, Data Modeling, MLOps, MLflow</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0dc1867fdcc5324</t>
+          <t>https://www.indeed.com/viewjob?jk=eff547fec829449a</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>RapidFire Safety &amp; Security</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, Data Modeling, Star Schema, Fact Tables, Dimension Tables, ETL, Power BI</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8afc73df8ef8f40e</t>
+          <t>https://www.indeed.com/viewjob?jk=29d22d712d7958f0</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Software Developer - Database Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>RAMSOFT</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, HBase, Scala, Snowflake, MySQL, NoSQL, Data Modeling, Power BI</t>
+          <t>AWS, RDS, Spark, PySpark, Scala, MySQL, MongoDB, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ce0ac7d0a937f32</t>
+          <t>https://www.indeed.com/viewjob?jk=dd1518c4c02c12ef</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>AWS Data Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Centene</t>
+          <t>Appex Innovation</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, MySQL, MongoDB, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Lambda, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,102 +3471,102 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11d92da9c37770a7</t>
+          <t>https://www.indeed.com/viewjob?jk=3886cb86a753634c</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer 2</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Vizient, Inc.</t>
+          <t>BLOC Resources, LLC</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, SQL Server, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e60ff8bc1e60898</t>
+          <t>https://www.indeed.com/viewjob?jk=c51290628ce41b82</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Emed</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Spark, Power BI, Tableau, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e29e1c3d36f0e7c</t>
+          <t>https://www.indeed.com/viewjob?jk=aaf9596bf4159924</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Java Integration Consultant</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Springfield, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Spark, Power BI, Tableau, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,137 +3576,137 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7439985744d87583</t>
+          <t>https://www.indeed.com/viewjob?jk=ab90611f6b141379</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer - Startup</t>
+          <t>Senior Software Engineer, Back End (Python)</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>TALENThire</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, GCP, Scala, Kafka, PostgreSQL, ELT, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f9f397d4f8fa7f1</t>
+          <t>https://www.indeed.com/viewjob?jk=f65ac6c3f1cf1646</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - Risk Platform (Hybrid)</t>
+          <t>Senior Software Engineer, Back End (Python)</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Cassandra, ETL, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1593d7242ad3914</t>
+          <t>https://www.indeed.com/viewjob?jk=3864c05dc9b353f8</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Software Engineer I, Applied AI</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Daniels Health</t>
+          <t>Axon</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, ETL, ELT, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aedcadc853d15f82</t>
+          <t>https://www.indeed.com/viewjob?jk=e858c83fc09cd77d</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Specialist - Software Engineering</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Daniels Health</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, ETL, ELT, Git</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, NoSQL, Splunk, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,67 +3716,67 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=447d4d5607b3f3c6</t>
+          <t>https://www.indeed.com/viewjob?jk=a3c595f778e26600</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Advisor Solution Architect</t>
+          <t>Specialist - Software Engineering</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>HJ Staffing</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, NoSQL, Splunk, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20d4ea50920ad807</t>
+          <t>https://www.indeed.com/viewjob?jk=678f6a09a0ac0c26</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Specialist - Software Engineering</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, NoSQL, Splunk, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,67 +3786,67 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1315e6e62a7714e8</t>
+          <t>https://www.indeed.com/viewjob?jk=c6e8b8be5cf1c082</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Sr. Informatica IDMC MDM Software Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>RBC</t>
+          <t>Zoom Communications</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5346f4c5e2b5352a</t>
+          <t>https://www.indeed.com/viewjob?jk=d44e3274520e56d6</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>.NET Developer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Centene</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Scala, Snowflake, SQL Server, Power BI, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, MySQL, MongoDB, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,77 +3856,742 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4afc3e61f8ae8b7b</t>
+          <t>https://www.indeed.com/viewjob?jk=11d92da9c37770a7</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Senior Data Engineer - Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Guidewire Software, Inc.</t>
+          <t>WesBanco Bank, Inc.</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Bowie, MD, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b5e082bd1857b0f</t>
+          <t>https://www.indeed.com/viewjob?jk=a3a02cdb2b181be3</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>DevOps Engineer (Must have Kubernetes)</t>
+          <t>Senior Data Engineer - Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Cornerstone Defense</t>
+          <t>WesBanco Bank, Inc.</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Chantilly, VA, US USA</t>
+          <t>Wheeling, WV, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT, dbt</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fb6ee55d393e301c</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Software Developer - Database Engineer</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>RAMSOFT</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>CO, US USA</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, HBase, Scala, Snowflake, MySQL, NoSQL, Data Modeling, Power BI</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4ce0ac7d0a937f32</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Power BI Developer</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>RapidFire Safety &amp; Security</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>St. Louis, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, SQL Server, Data Modeling, Star Schema, Fact Tables, Dimension Tables, ETL, Power BI</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8afc73df8ef8f40e</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Vizient, Inc.</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
         <v>10.4</v>
       </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>Hadoop, Spark, PostgreSQL, CI/CD, Maven, Terraform, Docker, Kubernetes, AKS, Git</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7329904e6957c2e7</t>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, SQL Server, Dimensional Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2e60ff8bc1e60898</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Product Architect Big Data Google Cloud Platform</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Reston Hospital Center - Reston</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Reston, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Lambda, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Scala, Kafka, Docker</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cc86aeda9d2a8bcb</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Product Architect Big Data Google Cloud Platform</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>St. David's HealthCare</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Lambda, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Scala, Kafka, Docker</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=613cb57ccf3485d6</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Product Architect Big Data Google Cloud Platform</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>HCA Florida West Tampa Hospital</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Lambda, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Scala, Kafka, Docker</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1ee6462dda08d180</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Product Architect Big Data Google Cloud Platform</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Medical City Healthcare</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Lambda, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Scala, Kafka, Docker</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ae11beaa0be9d78e</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>LLM Application Engineer</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, RDS, Databricks, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, MLOps</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5633278896c16c3b</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>LLM Application Engineer</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, RDS, Databricks, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, MLOps</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4e56614bfb72e3b3</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Senior Advanced Analytics</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>AT&amp;T</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Oracle, MySQL, ELT, Power BI</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=92f0640d212f7db6</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Engineer II- Java</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c70cf8723aeaf7eb</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Engineer II- Java</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6f106012aaf32c49</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Daniels Health</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, ETL, ELT, Git</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=aedcadc853d15f82</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Daniels Health</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, ETL, ELT, Git</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=447d4d5607b3f3c6</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Sr. Software Engineer - Risk Platform (Hybrid)</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>CrowdStrike</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Sunnyvale, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Cassandra, ETL, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a1593d7242ad3914</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1315e6e62a7714e8</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Engineer</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Guidewire Software, Inc.</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>San Mateo, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, MySQL, MongoDB, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3b5e082bd1857b0f</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>.NET Developer</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Caterpillar</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Cary, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>S3, RDS, Azure, Scala, Snowflake, SQL Server, Power BI, CI/CD, Azure DevOps, Git</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4afc3e61f8ae8b7b</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Sr. Informatica IDMC MDM Software Engineer</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>RBC</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Minneapolis, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, ETL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5346f4c5e2b5352a</t>
         </is>
       </c>
     </row>
